--- a/input.xlsx
+++ b/input.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\backup01\Desktop\병아리\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C9F9D29-AB23-4C7A-84EC-983712DCEEA1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B42681A8-CF1E-4C8C-94D6-4ACC9C829703}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -174,7 +174,7 @@
     <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
     <numFmt numFmtId="180" formatCode="\+#,##0;\-#,##0;0"/>
   </numFmts>
-  <fonts count="19" x14ac:knownFonts="1">
+  <fonts count="18" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color theme="1"/>
@@ -304,13 +304,6 @@
     </font>
     <font>
       <sz val="10"/>
-      <color rgb="FF64748B"/>
-      <name val="Noto Sans KR"/>
-      <family val="3"/>
-      <charset val="129"/>
-    </font>
-    <font>
-      <sz val="10"/>
       <color rgb="FF1E293B"/>
       <name val="Noto Sans KR"/>
       <family val="3"/>
@@ -325,7 +318,7 @@
       <charset val="129"/>
     </font>
   </fonts>
-  <fills count="13">
+  <fills count="12">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -373,11 +366,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFEEF2FF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
       </patternFill>
     </fill>
     <fill>
@@ -613,7 +601,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="58">
+  <cellXfs count="57">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -729,13 +717,10 @@
     <xf numFmtId="4" fontId="15" fillId="9" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="180" fontId="16" fillId="10" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="16" fillId="10" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="3" fontId="17" fillId="11" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="18" fillId="12" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -745,22 +730,15 @@
     <xf numFmtId="0" fontId="10" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="41" fontId="4" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="9" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="41" fontId="4" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -770,6 +748,13 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="9" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="백분율" xfId="2" builtinId="5"/>
@@ -1063,38 +1048,38 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="32" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A1" s="44" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="43"/>
-      <c r="C1" s="43"/>
-      <c r="D1" s="43"/>
-      <c r="E1" s="43"/>
-      <c r="F1" s="43"/>
-      <c r="G1" s="43"/>
-      <c r="H1" s="43"/>
-      <c r="I1" s="43"/>
-      <c r="J1" s="43"/>
-      <c r="K1" s="43"/>
-      <c r="L1" s="43"/>
-      <c r="M1" s="43"/>
+      <c r="A1" s="43" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="42"/>
+      <c r="C1" s="42"/>
+      <c r="D1" s="42"/>
+      <c r="E1" s="42"/>
+      <c r="F1" s="42"/>
+      <c r="G1" s="42"/>
+      <c r="H1" s="42"/>
+      <c r="I1" s="42"/>
+      <c r="J1" s="42"/>
+      <c r="K1" s="42"/>
+      <c r="L1" s="42"/>
+      <c r="M1" s="42"/>
     </row>
     <row r="2" spans="1:13" ht="20" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A2" s="42" t="s">
+      <c r="A2" s="41" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="43"/>
-      <c r="C2" s="43"/>
-      <c r="D2" s="43"/>
-      <c r="E2" s="43"/>
-      <c r="F2" s="43"/>
-      <c r="G2" s="43"/>
-      <c r="H2" s="43"/>
-      <c r="I2" s="43"/>
-      <c r="J2" s="43"/>
-      <c r="K2" s="43"/>
-      <c r="L2" s="43"/>
-      <c r="M2" s="43"/>
+      <c r="B2" s="42"/>
+      <c r="C2" s="42"/>
+      <c r="D2" s="42"/>
+      <c r="E2" s="42"/>
+      <c r="F2" s="42"/>
+      <c r="G2" s="42"/>
+      <c r="H2" s="42"/>
+      <c r="I2" s="42"/>
+      <c r="J2" s="42"/>
+      <c r="K2" s="42"/>
+      <c r="L2" s="42"/>
+      <c r="M2" s="42"/>
     </row>
     <row r="3" spans="1:13" ht="36" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A3" s="32" t="s">
@@ -1150,17 +1135,17 @@
       <c r="D4" s="38">
         <v>4214.17</v>
       </c>
-      <c r="E4" s="39">
-        <v>0</v>
-      </c>
-      <c r="F4" s="40"/>
-      <c r="G4" s="40"/>
-      <c r="H4" s="40"/>
-      <c r="I4" s="40"/>
-      <c r="J4" s="40"/>
-      <c r="K4" s="40"/>
-      <c r="L4" s="40"/>
-      <c r="M4" s="40"/>
+      <c r="E4" s="37">
+        <v>0</v>
+      </c>
+      <c r="F4" s="39"/>
+      <c r="G4" s="39"/>
+      <c r="H4" s="39"/>
+      <c r="I4" s="39"/>
+      <c r="J4" s="39"/>
+      <c r="K4" s="39"/>
+      <c r="L4" s="39"/>
+      <c r="M4" s="39"/>
     </row>
     <row r="5" spans="1:13" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A5" s="35">
@@ -1175,17 +1160,17 @@
       <c r="D5" s="38">
         <v>4309.63</v>
       </c>
-      <c r="E5" s="39">
-        <v>0</v>
-      </c>
-      <c r="F5" s="40"/>
-      <c r="G5" s="40"/>
-      <c r="H5" s="40"/>
-      <c r="I5" s="40"/>
-      <c r="J5" s="40"/>
-      <c r="K5" s="40"/>
-      <c r="L5" s="40"/>
-      <c r="M5" s="40"/>
+      <c r="E5" s="37">
+        <v>637905</v>
+      </c>
+      <c r="F5" s="39"/>
+      <c r="G5" s="39"/>
+      <c r="H5" s="39"/>
+      <c r="I5" s="39"/>
+      <c r="J5" s="39"/>
+      <c r="K5" s="39"/>
+      <c r="L5" s="39"/>
+      <c r="M5" s="39"/>
     </row>
     <row r="6" spans="1:13" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A6" s="35">
@@ -1200,17 +1185,17 @@
       <c r="D6" s="38">
         <v>4309.63</v>
       </c>
-      <c r="E6" s="39">
-        <v>0</v>
-      </c>
-      <c r="F6" s="40"/>
-      <c r="G6" s="40"/>
-      <c r="H6" s="40"/>
-      <c r="I6" s="40"/>
-      <c r="J6" s="40"/>
-      <c r="K6" s="40"/>
-      <c r="L6" s="40"/>
-      <c r="M6" s="40"/>
+      <c r="E6" s="37">
+        <v>0</v>
+      </c>
+      <c r="F6" s="39"/>
+      <c r="G6" s="39"/>
+      <c r="H6" s="39"/>
+      <c r="I6" s="39"/>
+      <c r="J6" s="39"/>
+      <c r="K6" s="39"/>
+      <c r="L6" s="39"/>
+      <c r="M6" s="39"/>
     </row>
     <row r="7" spans="1:13" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A7" s="35">
@@ -1225,17 +1210,17 @@
       <c r="D7" s="38">
         <v>4309.63</v>
       </c>
-      <c r="E7" s="39">
-        <v>0</v>
-      </c>
-      <c r="F7" s="40"/>
-      <c r="G7" s="40"/>
-      <c r="H7" s="40"/>
-      <c r="I7" s="40"/>
-      <c r="J7" s="40"/>
-      <c r="K7" s="40"/>
-      <c r="L7" s="40"/>
-      <c r="M7" s="40"/>
+      <c r="E7" s="37">
+        <v>0</v>
+      </c>
+      <c r="F7" s="39"/>
+      <c r="G7" s="39"/>
+      <c r="H7" s="39"/>
+      <c r="I7" s="39"/>
+      <c r="J7" s="39"/>
+      <c r="K7" s="39"/>
+      <c r="L7" s="39"/>
+      <c r="M7" s="39"/>
     </row>
     <row r="8" spans="1:13" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A8" s="35">
@@ -1250,17 +1235,17 @@
       <c r="D8" s="38">
         <v>4457.5200000000004</v>
       </c>
-      <c r="E8" s="39">
-        <v>0</v>
-      </c>
-      <c r="F8" s="40"/>
-      <c r="G8" s="40"/>
-      <c r="H8" s="40"/>
-      <c r="I8" s="40"/>
-      <c r="J8" s="40"/>
-      <c r="K8" s="40"/>
-      <c r="L8" s="40"/>
-      <c r="M8" s="40"/>
+      <c r="E8" s="37">
+        <v>567748</v>
+      </c>
+      <c r="F8" s="39"/>
+      <c r="G8" s="39"/>
+      <c r="H8" s="39"/>
+      <c r="I8" s="39"/>
+      <c r="J8" s="39"/>
+      <c r="K8" s="39"/>
+      <c r="L8" s="39"/>
+      <c r="M8" s="39"/>
     </row>
     <row r="9" spans="1:13" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A9" s="35">
@@ -1275,17 +1260,17 @@
       <c r="D9" s="38">
         <v>4525.4799999999996</v>
       </c>
-      <c r="E9" s="39">
-        <v>0</v>
-      </c>
-      <c r="F9" s="40"/>
-      <c r="G9" s="40"/>
-      <c r="H9" s="40"/>
-      <c r="I9" s="40"/>
-      <c r="J9" s="40"/>
-      <c r="K9" s="40"/>
-      <c r="L9" s="40"/>
-      <c r="M9" s="40"/>
+      <c r="E9" s="37">
+        <v>219464</v>
+      </c>
+      <c r="F9" s="39"/>
+      <c r="G9" s="39"/>
+      <c r="H9" s="39"/>
+      <c r="I9" s="39"/>
+      <c r="J9" s="39"/>
+      <c r="K9" s="39"/>
+      <c r="L9" s="39"/>
+      <c r="M9" s="39"/>
     </row>
     <row r="10" spans="1:13" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A10" s="35">
@@ -1300,17 +1285,17 @@
       <c r="D10" s="38">
         <v>4551.0600000000004</v>
       </c>
-      <c r="E10" s="39">
-        <v>0</v>
-      </c>
-      <c r="F10" s="40"/>
-      <c r="G10" s="40"/>
-      <c r="H10" s="40"/>
-      <c r="I10" s="40"/>
-      <c r="J10" s="40"/>
-      <c r="K10" s="40"/>
-      <c r="L10" s="40"/>
-      <c r="M10" s="40"/>
+      <c r="E10" s="37">
+        <v>0</v>
+      </c>
+      <c r="F10" s="39"/>
+      <c r="G10" s="39"/>
+      <c r="H10" s="39"/>
+      <c r="I10" s="39"/>
+      <c r="J10" s="39"/>
+      <c r="K10" s="39"/>
+      <c r="L10" s="39"/>
+      <c r="M10" s="39"/>
     </row>
     <row r="11" spans="1:13" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A11" s="35">
@@ -1325,17 +1310,17 @@
       <c r="D11" s="38">
         <v>4552.37</v>
       </c>
-      <c r="E11" s="39">
-        <v>0</v>
-      </c>
-      <c r="F11" s="40"/>
-      <c r="G11" s="40"/>
-      <c r="H11" s="40"/>
-      <c r="I11" s="40"/>
-      <c r="J11" s="40"/>
-      <c r="K11" s="40"/>
-      <c r="L11" s="40"/>
-      <c r="M11" s="40"/>
+      <c r="E11" s="37">
+        <v>0</v>
+      </c>
+      <c r="F11" s="39"/>
+      <c r="G11" s="39"/>
+      <c r="H11" s="39"/>
+      <c r="I11" s="39"/>
+      <c r="J11" s="39"/>
+      <c r="K11" s="39"/>
+      <c r="L11" s="39"/>
+      <c r="M11" s="39"/>
     </row>
     <row r="12" spans="1:13" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A12" s="35">
@@ -1350,17 +1335,17 @@
       <c r="D12" s="38">
         <v>4586.32</v>
       </c>
-      <c r="E12" s="39">
-        <v>0</v>
-      </c>
-      <c r="F12" s="40"/>
-      <c r="G12" s="40"/>
-      <c r="H12" s="40"/>
-      <c r="I12" s="40"/>
-      <c r="J12" s="40"/>
-      <c r="K12" s="40"/>
-      <c r="L12" s="40"/>
-      <c r="M12" s="40"/>
+      <c r="E12" s="37">
+        <v>50895</v>
+      </c>
+      <c r="F12" s="39"/>
+      <c r="G12" s="39"/>
+      <c r="H12" s="39"/>
+      <c r="I12" s="39"/>
+      <c r="J12" s="39"/>
+      <c r="K12" s="39"/>
+      <c r="L12" s="39"/>
+      <c r="M12" s="39"/>
     </row>
     <row r="13" spans="1:13" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A13" s="35">
@@ -1375,17 +1360,17 @@
       <c r="D13" s="38">
         <v>4586.32</v>
       </c>
-      <c r="E13" s="39">
-        <v>0</v>
-      </c>
-      <c r="F13" s="40"/>
-      <c r="G13" s="40"/>
-      <c r="H13" s="40"/>
-      <c r="I13" s="40"/>
-      <c r="J13" s="40"/>
-      <c r="K13" s="40"/>
-      <c r="L13" s="40"/>
-      <c r="M13" s="40"/>
+      <c r="E13" s="37">
+        <v>0</v>
+      </c>
+      <c r="F13" s="39"/>
+      <c r="G13" s="39"/>
+      <c r="H13" s="39"/>
+      <c r="I13" s="39"/>
+      <c r="J13" s="39"/>
+      <c r="K13" s="39"/>
+      <c r="L13" s="39"/>
+      <c r="M13" s="39"/>
     </row>
     <row r="14" spans="1:13" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A14" s="35">
@@ -1400,17 +1385,17 @@
       <c r="D14" s="38">
         <v>4586.32</v>
       </c>
-      <c r="E14" s="39">
-        <v>0</v>
-      </c>
-      <c r="F14" s="40"/>
-      <c r="G14" s="40"/>
-      <c r="H14" s="40"/>
-      <c r="I14" s="40"/>
-      <c r="J14" s="40"/>
-      <c r="K14" s="40"/>
-      <c r="L14" s="40"/>
-      <c r="M14" s="40"/>
+      <c r="E14" s="37">
+        <v>0</v>
+      </c>
+      <c r="F14" s="39"/>
+      <c r="G14" s="39"/>
+      <c r="H14" s="39"/>
+      <c r="I14" s="39"/>
+      <c r="J14" s="39"/>
+      <c r="K14" s="39"/>
+      <c r="L14" s="39"/>
+      <c r="M14" s="39"/>
     </row>
     <row r="15" spans="1:13" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A15" s="35">
@@ -1425,17 +1410,17 @@
       <c r="D15" s="38">
         <v>4624.79</v>
       </c>
-      <c r="E15" s="39">
-        <v>0</v>
-      </c>
-      <c r="F15" s="40"/>
-      <c r="G15" s="40"/>
-      <c r="H15" s="40"/>
-      <c r="I15" s="40"/>
-      <c r="J15" s="40"/>
-      <c r="K15" s="40"/>
-      <c r="L15" s="40"/>
-      <c r="M15" s="40"/>
+      <c r="E15" s="37">
+        <v>0</v>
+      </c>
+      <c r="F15" s="39"/>
+      <c r="G15" s="39"/>
+      <c r="H15" s="39"/>
+      <c r="I15" s="39"/>
+      <c r="J15" s="39"/>
+      <c r="K15" s="39"/>
+      <c r="L15" s="39"/>
+      <c r="M15" s="39"/>
     </row>
     <row r="16" spans="1:13" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A16" s="35">
@@ -1450,17 +1435,17 @@
       <c r="D16" s="38">
         <v>4692.6400000000003</v>
       </c>
-      <c r="E16" s="39">
-        <v>0</v>
-      </c>
-      <c r="F16" s="40"/>
-      <c r="G16" s="40"/>
-      <c r="H16" s="40"/>
-      <c r="I16" s="40"/>
-      <c r="J16" s="40"/>
-      <c r="K16" s="40"/>
-      <c r="L16" s="40"/>
-      <c r="M16" s="40"/>
+      <c r="E16" s="37">
+        <v>0</v>
+      </c>
+      <c r="F16" s="39"/>
+      <c r="G16" s="39"/>
+      <c r="H16" s="39"/>
+      <c r="I16" s="39"/>
+      <c r="J16" s="39"/>
+      <c r="K16" s="39"/>
+      <c r="L16" s="39"/>
+      <c r="M16" s="39"/>
     </row>
     <row r="17" spans="1:13" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A17" s="35">
@@ -1475,17 +1460,17 @@
       <c r="D17" s="38">
         <v>4723.1000000000004</v>
       </c>
-      <c r="E17" s="39">
-        <v>0</v>
-      </c>
-      <c r="F17" s="40"/>
-      <c r="G17" s="40"/>
-      <c r="H17" s="40"/>
-      <c r="I17" s="40"/>
-      <c r="J17" s="40"/>
-      <c r="K17" s="40"/>
-      <c r="L17" s="40"/>
-      <c r="M17" s="40"/>
+      <c r="E17" s="37">
+        <v>0</v>
+      </c>
+      <c r="F17" s="39"/>
+      <c r="G17" s="39"/>
+      <c r="H17" s="39"/>
+      <c r="I17" s="39"/>
+      <c r="J17" s="39"/>
+      <c r="K17" s="39"/>
+      <c r="L17" s="39"/>
+      <c r="M17" s="39"/>
     </row>
     <row r="18" spans="1:13" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A18" s="35">
@@ -1500,17 +1485,17 @@
       <c r="D18" s="38">
         <v>4797.55</v>
       </c>
-      <c r="E18" s="39">
-        <v>0</v>
-      </c>
-      <c r="F18" s="40"/>
-      <c r="G18" s="40"/>
-      <c r="H18" s="40"/>
-      <c r="I18" s="40"/>
-      <c r="J18" s="40"/>
-      <c r="K18" s="40"/>
-      <c r="L18" s="40"/>
-      <c r="M18" s="40"/>
+      <c r="E18" s="37">
+        <v>137220</v>
+      </c>
+      <c r="F18" s="39"/>
+      <c r="G18" s="39"/>
+      <c r="H18" s="39"/>
+      <c r="I18" s="39"/>
+      <c r="J18" s="39"/>
+      <c r="K18" s="39"/>
+      <c r="L18" s="39"/>
+      <c r="M18" s="39"/>
     </row>
     <row r="19" spans="1:13" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A19" s="35">
@@ -1525,17 +1510,17 @@
       <c r="D19" s="38">
         <v>4840.74</v>
       </c>
-      <c r="E19" s="39">
-        <v>0</v>
-      </c>
-      <c r="F19" s="40"/>
-      <c r="G19" s="40"/>
-      <c r="H19" s="40"/>
-      <c r="I19" s="40"/>
-      <c r="J19" s="40"/>
-      <c r="K19" s="40"/>
-      <c r="L19" s="40"/>
-      <c r="M19" s="40"/>
+      <c r="E19" s="37">
+        <v>359198</v>
+      </c>
+      <c r="F19" s="39"/>
+      <c r="G19" s="39"/>
+      <c r="H19" s="39"/>
+      <c r="I19" s="39"/>
+      <c r="J19" s="39"/>
+      <c r="K19" s="39"/>
+      <c r="L19" s="39"/>
+      <c r="M19" s="39"/>
     </row>
     <row r="20" spans="1:13" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A20" s="35">
@@ -1550,17 +1535,17 @@
       <c r="D20" s="38">
         <v>4840.74</v>
       </c>
-      <c r="E20" s="39">
-        <v>0</v>
-      </c>
-      <c r="F20" s="40"/>
-      <c r="G20" s="40"/>
-      <c r="H20" s="40"/>
-      <c r="I20" s="40"/>
-      <c r="J20" s="40"/>
-      <c r="K20" s="40"/>
-      <c r="L20" s="40"/>
-      <c r="M20" s="40"/>
+      <c r="E20" s="37">
+        <v>0</v>
+      </c>
+      <c r="F20" s="39"/>
+      <c r="G20" s="39"/>
+      <c r="H20" s="39"/>
+      <c r="I20" s="39"/>
+      <c r="J20" s="39"/>
+      <c r="K20" s="39"/>
+      <c r="L20" s="39"/>
+      <c r="M20" s="39"/>
     </row>
     <row r="21" spans="1:13" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A21" s="35">
@@ -1575,17 +1560,17 @@
       <c r="D21" s="38">
         <v>4840.74</v>
       </c>
-      <c r="E21" s="39">
-        <v>0</v>
-      </c>
-      <c r="F21" s="40"/>
-      <c r="G21" s="40"/>
-      <c r="H21" s="40"/>
-      <c r="I21" s="40"/>
-      <c r="J21" s="40"/>
-      <c r="K21" s="40"/>
-      <c r="L21" s="40"/>
-      <c r="M21" s="40"/>
+      <c r="E21" s="37">
+        <v>0</v>
+      </c>
+      <c r="F21" s="39"/>
+      <c r="G21" s="39"/>
+      <c r="H21" s="39"/>
+      <c r="I21" s="39"/>
+      <c r="J21" s="39"/>
+      <c r="K21" s="39"/>
+      <c r="L21" s="39"/>
+      <c r="M21" s="39"/>
     </row>
     <row r="22" spans="1:13" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A22" s="35">
@@ -1600,17 +1585,17 @@
       <c r="D22" s="38">
         <v>4904.66</v>
       </c>
-      <c r="E22" s="39">
-        <v>0</v>
-      </c>
-      <c r="F22" s="40"/>
-      <c r="G22" s="40"/>
-      <c r="H22" s="40"/>
-      <c r="I22" s="40"/>
-      <c r="J22" s="40"/>
-      <c r="K22" s="40"/>
-      <c r="L22" s="40"/>
-      <c r="M22" s="40"/>
+      <c r="E22" s="37">
+        <v>1355409</v>
+      </c>
+      <c r="F22" s="39"/>
+      <c r="G22" s="39"/>
+      <c r="H22" s="39"/>
+      <c r="I22" s="39"/>
+      <c r="J22" s="39"/>
+      <c r="K22" s="39"/>
+      <c r="L22" s="39"/>
+      <c r="M22" s="39"/>
     </row>
     <row r="23" spans="1:13" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A23" s="35">
@@ -1625,17 +1610,17 @@
       <c r="D23" s="38">
         <v>4904.66</v>
       </c>
-      <c r="E23" s="39">
-        <v>0</v>
-      </c>
-      <c r="F23" s="40"/>
-      <c r="G23" s="40"/>
-      <c r="H23" s="40"/>
-      <c r="I23" s="40"/>
-      <c r="J23" s="40"/>
-      <c r="K23" s="40"/>
-      <c r="L23" s="40"/>
-      <c r="M23" s="40"/>
+      <c r="E23" s="37">
+        <v>716854</v>
+      </c>
+      <c r="F23" s="39"/>
+      <c r="G23" s="39"/>
+      <c r="H23" s="39"/>
+      <c r="I23" s="39"/>
+      <c r="J23" s="39"/>
+      <c r="K23" s="39"/>
+      <c r="L23" s="39"/>
+      <c r="M23" s="39"/>
     </row>
     <row r="24" spans="1:13" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A24" s="35">
@@ -1650,17 +1635,17 @@
       <c r="D24" s="38">
         <v>4909.93</v>
       </c>
-      <c r="E24" s="39">
-        <v>0</v>
-      </c>
-      <c r="F24" s="40"/>
-      <c r="G24" s="40"/>
-      <c r="H24" s="40"/>
-      <c r="I24" s="40"/>
-      <c r="J24" s="40"/>
-      <c r="K24" s="40"/>
-      <c r="L24" s="40"/>
-      <c r="M24" s="40"/>
+      <c r="E24" s="37">
+        <v>50520</v>
+      </c>
+      <c r="F24" s="39"/>
+      <c r="G24" s="39"/>
+      <c r="H24" s="39"/>
+      <c r="I24" s="39"/>
+      <c r="J24" s="39"/>
+      <c r="K24" s="39"/>
+      <c r="L24" s="39"/>
+      <c r="M24" s="39"/>
     </row>
     <row r="25" spans="1:13" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A25" s="35">
@@ -1675,17 +1660,17 @@
       <c r="D25" s="38">
         <v>4952.53</v>
       </c>
-      <c r="E25" s="39">
-        <v>0</v>
-      </c>
-      <c r="F25" s="40"/>
-      <c r="G25" s="40"/>
-      <c r="H25" s="40"/>
-      <c r="I25" s="40"/>
-      <c r="J25" s="40"/>
-      <c r="K25" s="40"/>
-      <c r="L25" s="40"/>
-      <c r="M25" s="40"/>
+      <c r="E25" s="37">
+        <v>401877</v>
+      </c>
+      <c r="F25" s="39"/>
+      <c r="G25" s="39"/>
+      <c r="H25" s="39"/>
+      <c r="I25" s="39"/>
+      <c r="J25" s="39"/>
+      <c r="K25" s="39"/>
+      <c r="L25" s="39"/>
+      <c r="M25" s="39"/>
     </row>
     <row r="26" spans="1:13" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A26" s="35">
@@ -1700,17 +1685,17 @@
       <c r="D26" s="38">
         <v>4990.07</v>
       </c>
-      <c r="E26" s="39">
-        <v>0</v>
-      </c>
-      <c r="F26" s="40"/>
-      <c r="G26" s="40"/>
-      <c r="H26" s="40"/>
-      <c r="I26" s="40"/>
-      <c r="J26" s="40"/>
-      <c r="K26" s="40"/>
-      <c r="L26" s="40"/>
-      <c r="M26" s="40"/>
+      <c r="E26" s="37">
+        <v>871409</v>
+      </c>
+      <c r="F26" s="39"/>
+      <c r="G26" s="39"/>
+      <c r="H26" s="39"/>
+      <c r="I26" s="39"/>
+      <c r="J26" s="39"/>
+      <c r="K26" s="39"/>
+      <c r="L26" s="39"/>
+      <c r="M26" s="39"/>
     </row>
     <row r="27" spans="1:13" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A27" s="35">
@@ -1725,17 +1710,17 @@
       <c r="D27" s="38">
         <v>4990.07</v>
       </c>
-      <c r="E27" s="39">
-        <v>0</v>
-      </c>
-      <c r="F27" s="40"/>
-      <c r="G27" s="40"/>
-      <c r="H27" s="40"/>
-      <c r="I27" s="40"/>
-      <c r="J27" s="40"/>
-      <c r="K27" s="40"/>
-      <c r="L27" s="40"/>
-      <c r="M27" s="40"/>
+      <c r="E27" s="37">
+        <v>0</v>
+      </c>
+      <c r="F27" s="39"/>
+      <c r="G27" s="39"/>
+      <c r="H27" s="39"/>
+      <c r="I27" s="39"/>
+      <c r="J27" s="39"/>
+      <c r="K27" s="39"/>
+      <c r="L27" s="39"/>
+      <c r="M27" s="39"/>
     </row>
     <row r="28" spans="1:13" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A28" s="35">
@@ -1750,17 +1735,17 @@
       <c r="D28" s="38">
         <v>4990.07</v>
       </c>
-      <c r="E28" s="39">
-        <v>0</v>
-      </c>
-      <c r="F28" s="40"/>
-      <c r="G28" s="40"/>
-      <c r="H28" s="40"/>
-      <c r="I28" s="40"/>
-      <c r="J28" s="40"/>
-      <c r="K28" s="40"/>
-      <c r="L28" s="40"/>
-      <c r="M28" s="40"/>
+      <c r="E28" s="37">
+        <v>0</v>
+      </c>
+      <c r="F28" s="39"/>
+      <c r="G28" s="39"/>
+      <c r="H28" s="39"/>
+      <c r="I28" s="39"/>
+      <c r="J28" s="39"/>
+      <c r="K28" s="39"/>
+      <c r="L28" s="39"/>
+      <c r="M28" s="39"/>
     </row>
     <row r="29" spans="1:13" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A29" s="35">
@@ -1775,17 +1760,17 @@
       <c r="D29" s="38">
         <v>4949.59</v>
       </c>
-      <c r="E29" s="39">
-        <v>0</v>
-      </c>
-      <c r="F29" s="40"/>
-      <c r="G29" s="40"/>
-      <c r="H29" s="40"/>
-      <c r="I29" s="40"/>
-      <c r="J29" s="40"/>
-      <c r="K29" s="40"/>
-      <c r="L29" s="40"/>
-      <c r="M29" s="40"/>
+      <c r="E29" s="37">
+        <v>730049</v>
+      </c>
+      <c r="F29" s="39"/>
+      <c r="G29" s="39"/>
+      <c r="H29" s="39"/>
+      <c r="I29" s="39"/>
+      <c r="J29" s="39"/>
+      <c r="K29" s="39"/>
+      <c r="L29" s="39"/>
+      <c r="M29" s="39"/>
     </row>
     <row r="30" spans="1:13" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A30" s="35">
@@ -1800,17 +1785,17 @@
       <c r="D30" s="38">
         <v>5084.8500000000004</v>
       </c>
-      <c r="E30" s="39">
-        <v>0</v>
-      </c>
-      <c r="F30" s="40"/>
-      <c r="G30" s="40"/>
-      <c r="H30" s="40"/>
-      <c r="I30" s="40"/>
-      <c r="J30" s="40"/>
-      <c r="K30" s="40"/>
-      <c r="L30" s="40"/>
-      <c r="M30" s="40"/>
+      <c r="E30" s="37">
+        <v>641680</v>
+      </c>
+      <c r="F30" s="39"/>
+      <c r="G30" s="39"/>
+      <c r="H30" s="39"/>
+      <c r="I30" s="39"/>
+      <c r="J30" s="39"/>
+      <c r="K30" s="39"/>
+      <c r="L30" s="39"/>
+      <c r="M30" s="39"/>
     </row>
     <row r="31" spans="1:13" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A31" s="35">
@@ -1825,17 +1810,17 @@
       <c r="D31" s="38">
         <v>5170.8100000000004</v>
       </c>
-      <c r="E31" s="39">
-        <v>0</v>
-      </c>
-      <c r="F31" s="40"/>
-      <c r="G31" s="40"/>
-      <c r="H31" s="40"/>
-      <c r="I31" s="40"/>
-      <c r="J31" s="40"/>
-      <c r="K31" s="40"/>
-      <c r="L31" s="40"/>
-      <c r="M31" s="40"/>
+      <c r="E31" s="37">
+        <v>280270</v>
+      </c>
+      <c r="F31" s="39"/>
+      <c r="G31" s="39"/>
+      <c r="H31" s="39"/>
+      <c r="I31" s="39"/>
+      <c r="J31" s="39"/>
+      <c r="K31" s="39"/>
+      <c r="L31" s="39"/>
+      <c r="M31" s="39"/>
     </row>
     <row r="32" spans="1:13" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A32" s="35">
@@ -1850,17 +1835,17 @@
       <c r="D32" s="38">
         <v>5221.25</v>
       </c>
-      <c r="E32" s="39">
-        <v>0</v>
-      </c>
-      <c r="F32" s="40"/>
-      <c r="G32" s="40"/>
-      <c r="H32" s="40"/>
-      <c r="I32" s="40"/>
-      <c r="J32" s="40"/>
-      <c r="K32" s="40"/>
-      <c r="L32" s="40"/>
-      <c r="M32" s="40"/>
+      <c r="E32" s="37">
+        <v>166850</v>
+      </c>
+      <c r="F32" s="39"/>
+      <c r="G32" s="39"/>
+      <c r="H32" s="39"/>
+      <c r="I32" s="39"/>
+      <c r="J32" s="39"/>
+      <c r="K32" s="39"/>
+      <c r="L32" s="39"/>
+      <c r="M32" s="39"/>
     </row>
     <row r="33" spans="1:13" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A33" s="35">
@@ -1875,17 +1860,17 @@
       <c r="D33" s="38">
         <v>5224.3599999999997</v>
       </c>
-      <c r="E33" s="39">
-        <v>0</v>
-      </c>
-      <c r="F33" s="40"/>
-      <c r="G33" s="40"/>
-      <c r="H33" s="40"/>
-      <c r="I33" s="40"/>
-      <c r="J33" s="40"/>
-      <c r="K33" s="40"/>
-      <c r="L33" s="40"/>
-      <c r="M33" s="40"/>
+      <c r="E33" s="37">
+        <v>28124</v>
+      </c>
+      <c r="F33" s="39"/>
+      <c r="G33" s="39"/>
+      <c r="H33" s="39"/>
+      <c r="I33" s="39"/>
+      <c r="J33" s="39"/>
+      <c r="K33" s="39"/>
+      <c r="L33" s="39"/>
+      <c r="M33" s="39"/>
     </row>
     <row r="34" spans="1:13" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A34" s="35">
@@ -1900,17 +1885,17 @@
       <c r="D34" s="38">
         <v>5224.3599999999997</v>
       </c>
-      <c r="E34" s="39">
-        <v>7215472</v>
-      </c>
-      <c r="F34" s="40"/>
-      <c r="G34" s="40"/>
-      <c r="H34" s="40"/>
-      <c r="I34" s="40"/>
-      <c r="J34" s="40"/>
-      <c r="K34" s="40"/>
-      <c r="L34" s="40"/>
-      <c r="M34" s="40"/>
+      <c r="E34" s="37">
+        <v>0</v>
+      </c>
+      <c r="F34" s="39"/>
+      <c r="G34" s="39"/>
+      <c r="H34" s="39"/>
+      <c r="I34" s="39"/>
+      <c r="J34" s="39"/>
+      <c r="K34" s="39"/>
+      <c r="L34" s="39"/>
+      <c r="M34" s="39"/>
     </row>
     <row r="35" spans="1:13" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A35" s="35">
@@ -1925,17 +1910,17 @@
       <c r="D35" s="38">
         <v>5224.3599999999997</v>
       </c>
-      <c r="E35" s="39">
-        <v>0</v>
-      </c>
-      <c r="F35" s="40"/>
-      <c r="G35" s="40"/>
-      <c r="H35" s="40"/>
-      <c r="I35" s="40"/>
-      <c r="J35" s="40"/>
-      <c r="K35" s="40"/>
-      <c r="L35" s="40"/>
-      <c r="M35" s="40"/>
+      <c r="E35" s="37">
+        <v>0</v>
+      </c>
+      <c r="F35" s="39"/>
+      <c r="G35" s="39"/>
+      <c r="H35" s="39"/>
+      <c r="I35" s="39"/>
+      <c r="J35" s="39"/>
+      <c r="K35" s="39"/>
+      <c r="L35" s="39"/>
+      <c r="M35" s="39"/>
     </row>
     <row r="36" spans="1:13" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A36" s="35">
@@ -1950,17 +1935,17 @@
       <c r="D36" s="38">
         <v>4949.67</v>
       </c>
-      <c r="E36" s="39">
-        <v>0</v>
-      </c>
-      <c r="F36" s="40"/>
-      <c r="G36" s="40"/>
-      <c r="H36" s="40"/>
-      <c r="I36" s="40"/>
-      <c r="J36" s="40"/>
-      <c r="K36" s="40"/>
-      <c r="L36" s="40"/>
-      <c r="M36" s="40"/>
+      <c r="E36" s="37">
+        <v>0</v>
+      </c>
+      <c r="F36" s="39"/>
+      <c r="G36" s="39"/>
+      <c r="H36" s="39"/>
+      <c r="I36" s="39"/>
+      <c r="J36" s="39"/>
+      <c r="K36" s="39"/>
+      <c r="L36" s="39"/>
+      <c r="M36" s="39"/>
     </row>
     <row r="37" spans="1:13" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A37" s="35">
@@ -1975,17 +1960,17 @@
       <c r="D37" s="38">
         <v>5288.08</v>
       </c>
-      <c r="E37" s="39">
-        <v>0</v>
-      </c>
-      <c r="F37" s="40"/>
-      <c r="G37" s="40"/>
-      <c r="H37" s="40"/>
-      <c r="I37" s="40"/>
-      <c r="J37" s="40"/>
-      <c r="K37" s="40"/>
-      <c r="L37" s="40"/>
-      <c r="M37" s="40"/>
+      <c r="E37" s="37">
+        <v>725738</v>
+      </c>
+      <c r="F37" s="39"/>
+      <c r="G37" s="39"/>
+      <c r="H37" s="39"/>
+      <c r="I37" s="39"/>
+      <c r="J37" s="39"/>
+      <c r="K37" s="39"/>
+      <c r="L37" s="39"/>
+      <c r="M37" s="39"/>
     </row>
     <row r="38" spans="1:13" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A38" s="35">
@@ -2000,17 +1985,17 @@
       <c r="D38" s="38">
         <v>5371.1</v>
       </c>
-      <c r="E38" s="39">
-        <v>0</v>
-      </c>
-      <c r="F38" s="40"/>
-      <c r="G38" s="40"/>
-      <c r="H38" s="40"/>
-      <c r="I38" s="40"/>
-      <c r="J38" s="40"/>
-      <c r="K38" s="40"/>
-      <c r="L38" s="40"/>
-      <c r="M38" s="40"/>
+      <c r="E38" s="37">
+        <v>151025</v>
+      </c>
+      <c r="F38" s="39"/>
+      <c r="G38" s="39"/>
+      <c r="H38" s="39"/>
+      <c r="I38" s="39"/>
+      <c r="J38" s="39"/>
+      <c r="K38" s="39"/>
+      <c r="L38" s="39"/>
+      <c r="M38" s="39"/>
     </row>
     <row r="39" spans="1:13" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A39" s="35">
@@ -2025,17 +2010,17 @@
       <c r="D39" s="38">
         <v>5163.57</v>
       </c>
-      <c r="E39" s="39">
-        <v>0</v>
-      </c>
-      <c r="F39" s="40"/>
-      <c r="G39" s="40"/>
-      <c r="H39" s="40"/>
-      <c r="I39" s="40"/>
-      <c r="J39" s="40"/>
-      <c r="K39" s="40"/>
-      <c r="L39" s="40"/>
-      <c r="M39" s="40"/>
+      <c r="E39" s="37">
+        <v>0</v>
+      </c>
+      <c r="F39" s="39"/>
+      <c r="G39" s="39"/>
+      <c r="H39" s="39"/>
+      <c r="I39" s="39"/>
+      <c r="J39" s="39"/>
+      <c r="K39" s="39"/>
+      <c r="L39" s="39"/>
+      <c r="M39" s="39"/>
     </row>
     <row r="40" spans="1:13" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A40" s="35">
@@ -2050,17 +2035,17 @@
       <c r="D40" s="38">
         <v>5089.1400000000003</v>
       </c>
-      <c r="E40" s="39">
-        <v>0</v>
-      </c>
-      <c r="F40" s="40"/>
-      <c r="G40" s="40"/>
-      <c r="H40" s="40"/>
-      <c r="I40" s="40"/>
-      <c r="J40" s="40"/>
-      <c r="K40" s="40"/>
-      <c r="L40" s="40"/>
-      <c r="M40" s="40"/>
+      <c r="E40" s="37">
+        <v>0</v>
+      </c>
+      <c r="F40" s="39"/>
+      <c r="G40" s="39"/>
+      <c r="H40" s="39"/>
+      <c r="I40" s="39"/>
+      <c r="J40" s="39"/>
+      <c r="K40" s="39"/>
+      <c r="L40" s="39"/>
+      <c r="M40" s="39"/>
     </row>
     <row r="41" spans="1:13" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A41" s="35">
@@ -2075,17 +2060,17 @@
       <c r="D41" s="38">
         <v>5089.1400000000003</v>
       </c>
-      <c r="E41" s="39">
-        <v>0</v>
-      </c>
-      <c r="F41" s="40"/>
-      <c r="G41" s="40"/>
-      <c r="H41" s="40"/>
-      <c r="I41" s="40"/>
-      <c r="J41" s="40"/>
-      <c r="K41" s="40"/>
-      <c r="L41" s="40"/>
-      <c r="M41" s="40"/>
+      <c r="E41" s="37">
+        <v>0</v>
+      </c>
+      <c r="F41" s="39"/>
+      <c r="G41" s="39"/>
+      <c r="H41" s="39"/>
+      <c r="I41" s="39"/>
+      <c r="J41" s="39"/>
+      <c r="K41" s="39"/>
+      <c r="L41" s="39"/>
+      <c r="M41" s="39"/>
     </row>
     <row r="42" spans="1:13" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A42" s="35">
@@ -2100,17 +2085,17 @@
       <c r="D42" s="38">
         <v>5089.1400000000003</v>
       </c>
-      <c r="E42" s="39">
-        <v>0</v>
-      </c>
-      <c r="F42" s="40"/>
-      <c r="G42" s="40"/>
-      <c r="H42" s="40"/>
-      <c r="I42" s="40"/>
-      <c r="J42" s="40"/>
-      <c r="K42" s="40"/>
-      <c r="L42" s="40"/>
-      <c r="M42" s="40"/>
+      <c r="E42" s="37">
+        <v>0</v>
+      </c>
+      <c r="F42" s="39"/>
+      <c r="G42" s="39"/>
+      <c r="H42" s="39"/>
+      <c r="I42" s="39"/>
+      <c r="J42" s="39"/>
+      <c r="K42" s="39"/>
+      <c r="L42" s="39"/>
+      <c r="M42" s="39"/>
     </row>
     <row r="43" spans="1:13" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A43" s="35">
@@ -2125,17 +2110,17 @@
       <c r="D43" s="38">
         <v>5298.04</v>
       </c>
-      <c r="E43" s="39">
-        <v>0</v>
-      </c>
-      <c r="F43" s="40"/>
-      <c r="G43" s="40"/>
-      <c r="H43" s="40"/>
-      <c r="I43" s="40"/>
-      <c r="J43" s="40"/>
-      <c r="K43" s="40"/>
-      <c r="L43" s="40"/>
-      <c r="M43" s="40"/>
+      <c r="E43" s="37">
+        <v>1693361</v>
+      </c>
+      <c r="F43" s="39"/>
+      <c r="G43" s="39"/>
+      <c r="H43" s="39"/>
+      <c r="I43" s="39"/>
+      <c r="J43" s="39"/>
+      <c r="K43" s="39"/>
+      <c r="L43" s="39"/>
+      <c r="M43" s="39"/>
     </row>
     <row r="44" spans="1:13" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A44" s="35">
@@ -2150,17 +2135,17 @@
       <c r="D44" s="38">
         <v>5301.69</v>
       </c>
-      <c r="E44" s="39">
-        <v>0</v>
-      </c>
-      <c r="F44" s="40"/>
-      <c r="G44" s="40"/>
-      <c r="H44" s="40"/>
-      <c r="I44" s="40"/>
-      <c r="J44" s="40"/>
-      <c r="K44" s="40"/>
-      <c r="L44" s="40"/>
-      <c r="M44" s="40"/>
+      <c r="E44" s="37">
+        <v>340677</v>
+      </c>
+      <c r="F44" s="39"/>
+      <c r="G44" s="39"/>
+      <c r="H44" s="39"/>
+      <c r="I44" s="39"/>
+      <c r="J44" s="39"/>
+      <c r="K44" s="39"/>
+      <c r="L44" s="39"/>
+      <c r="M44" s="39"/>
     </row>
     <row r="45" spans="1:13" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A45" s="35">
@@ -2175,17 +2160,17 @@
       <c r="D45" s="38">
         <v>5354.49</v>
       </c>
-      <c r="E45" s="39">
-        <v>0</v>
-      </c>
-      <c r="F45" s="40"/>
-      <c r="G45" s="40"/>
-      <c r="H45" s="40"/>
-      <c r="I45" s="40"/>
-      <c r="J45" s="40"/>
-      <c r="K45" s="40"/>
-      <c r="L45" s="40"/>
-      <c r="M45" s="40"/>
+      <c r="E45" s="37">
+        <v>49798</v>
+      </c>
+      <c r="F45" s="39"/>
+      <c r="G45" s="39"/>
+      <c r="H45" s="39"/>
+      <c r="I45" s="39"/>
+      <c r="J45" s="39"/>
+      <c r="K45" s="39"/>
+      <c r="L45" s="39"/>
+      <c r="M45" s="39"/>
     </row>
     <row r="46" spans="1:13" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A46" s="35">
@@ -2200,17 +2185,17 @@
       <c r="D46" s="38">
         <v>5521.29</v>
       </c>
-      <c r="E46" s="39">
-        <v>0</v>
-      </c>
-      <c r="F46" s="40"/>
-      <c r="G46" s="40"/>
-      <c r="H46" s="40"/>
-      <c r="I46" s="40"/>
-      <c r="J46" s="40"/>
-      <c r="K46" s="40"/>
-      <c r="L46" s="40"/>
-      <c r="M46" s="40"/>
+      <c r="E46" s="37">
+        <v>370225</v>
+      </c>
+      <c r="F46" s="39"/>
+      <c r="G46" s="39"/>
+      <c r="H46" s="39"/>
+      <c r="I46" s="39"/>
+      <c r="J46" s="39"/>
+      <c r="K46" s="39"/>
+      <c r="L46" s="39"/>
+      <c r="M46" s="39"/>
     </row>
     <row r="47" spans="1:13" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A47" s="35">
@@ -2225,17 +2210,17 @@
       <c r="D47" s="38">
         <v>5507.01</v>
       </c>
-      <c r="E47" s="39">
-        <v>0</v>
-      </c>
-      <c r="F47" s="40"/>
-      <c r="G47" s="40"/>
-      <c r="H47" s="40"/>
-      <c r="I47" s="40"/>
-      <c r="J47" s="40"/>
-      <c r="K47" s="40"/>
-      <c r="L47" s="40"/>
-      <c r="M47" s="40"/>
+      <c r="E47" s="37">
+        <v>0</v>
+      </c>
+      <c r="F47" s="39"/>
+      <c r="G47" s="39"/>
+      <c r="H47" s="39"/>
+      <c r="I47" s="39"/>
+      <c r="J47" s="39"/>
+      <c r="K47" s="39"/>
+      <c r="L47" s="39"/>
+      <c r="M47" s="39"/>
     </row>
     <row r="48" spans="1:13" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A48" s="35">
@@ -2250,17 +2235,17 @@
       <c r="D48" s="38">
         <v>5507.01</v>
       </c>
-      <c r="E48" s="39">
-        <v>0</v>
-      </c>
-      <c r="F48" s="40"/>
-      <c r="G48" s="40"/>
-      <c r="H48" s="40"/>
-      <c r="I48" s="40"/>
-      <c r="J48" s="40"/>
-      <c r="K48" s="40"/>
-      <c r="L48" s="40"/>
-      <c r="M48" s="40"/>
+      <c r="E48" s="37">
+        <v>0</v>
+      </c>
+      <c r="F48" s="39"/>
+      <c r="G48" s="39"/>
+      <c r="H48" s="39"/>
+      <c r="I48" s="39"/>
+      <c r="J48" s="39"/>
+      <c r="K48" s="39"/>
+      <c r="L48" s="39"/>
+      <c r="M48" s="39"/>
     </row>
     <row r="49" spans="1:13" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A49" s="35">
@@ -2275,17 +2260,17 @@
       <c r="D49" s="38">
         <v>5507.01</v>
       </c>
-      <c r="E49" s="39">
-        <v>0</v>
-      </c>
-      <c r="F49" s="40"/>
-      <c r="G49" s="40"/>
-      <c r="H49" s="40"/>
-      <c r="I49" s="40"/>
-      <c r="J49" s="40"/>
-      <c r="K49" s="40"/>
-      <c r="L49" s="40"/>
-      <c r="M49" s="40"/>
+      <c r="E49" s="37">
+        <v>0</v>
+      </c>
+      <c r="F49" s="39"/>
+      <c r="G49" s="39"/>
+      <c r="H49" s="39"/>
+      <c r="I49" s="39"/>
+      <c r="J49" s="39"/>
+      <c r="K49" s="39"/>
+      <c r="L49" s="39"/>
+      <c r="M49" s="39"/>
     </row>
     <row r="50" spans="1:13" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A50" s="35">
@@ -2300,17 +2285,17 @@
       <c r="D50" s="38">
         <v>5507.01</v>
       </c>
-      <c r="E50" s="39">
-        <v>0</v>
-      </c>
-      <c r="F50" s="40"/>
-      <c r="G50" s="40"/>
-      <c r="H50" s="40"/>
-      <c r="I50" s="40"/>
-      <c r="J50" s="40"/>
-      <c r="K50" s="40"/>
-      <c r="L50" s="40"/>
-      <c r="M50" s="40"/>
+      <c r="E50" s="37">
+        <v>0</v>
+      </c>
+      <c r="F50" s="39"/>
+      <c r="G50" s="39"/>
+      <c r="H50" s="39"/>
+      <c r="I50" s="39"/>
+      <c r="J50" s="39"/>
+      <c r="K50" s="39"/>
+      <c r="L50" s="39"/>
+      <c r="M50" s="39"/>
     </row>
     <row r="51" spans="1:13" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A51" s="35">
@@ -2325,17 +2310,17 @@
       <c r="D51" s="38">
         <v>5507.01</v>
       </c>
-      <c r="E51" s="39">
-        <v>0</v>
-      </c>
-      <c r="F51" s="40"/>
-      <c r="G51" s="40"/>
-      <c r="H51" s="40"/>
-      <c r="I51" s="40"/>
-      <c r="J51" s="40"/>
-      <c r="K51" s="40"/>
-      <c r="L51" s="40"/>
-      <c r="M51" s="40"/>
+      <c r="E51" s="37">
+        <v>0</v>
+      </c>
+      <c r="F51" s="39"/>
+      <c r="G51" s="39"/>
+      <c r="H51" s="39"/>
+      <c r="I51" s="39"/>
+      <c r="J51" s="39"/>
+      <c r="K51" s="39"/>
+      <c r="L51" s="39"/>
+      <c r="M51" s="39"/>
     </row>
     <row r="52" spans="1:13" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A52" s="35">
@@ -2350,17 +2335,17 @@
       <c r="D52" s="38">
         <v>5507.01</v>
       </c>
-      <c r="E52" s="39">
-        <v>0</v>
-      </c>
-      <c r="F52" s="40"/>
-      <c r="G52" s="40"/>
-      <c r="H52" s="40"/>
-      <c r="I52" s="40"/>
-      <c r="J52" s="40"/>
-      <c r="K52" s="40"/>
-      <c r="L52" s="40"/>
-      <c r="M52" s="40"/>
+      <c r="E52" s="37">
+        <v>0</v>
+      </c>
+      <c r="F52" s="39"/>
+      <c r="G52" s="39"/>
+      <c r="H52" s="39"/>
+      <c r="I52" s="39"/>
+      <c r="J52" s="39"/>
+      <c r="K52" s="39"/>
+      <c r="L52" s="39"/>
+      <c r="M52" s="39"/>
     </row>
     <row r="53" spans="1:13" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A53" s="35">
@@ -2375,17 +2360,17 @@
       <c r="D53" s="38">
         <v>5677.25</v>
       </c>
-      <c r="E53" s="39">
-        <v>0</v>
-      </c>
-      <c r="F53" s="40"/>
-      <c r="G53" s="40"/>
-      <c r="H53" s="40"/>
-      <c r="I53" s="40"/>
-      <c r="J53" s="40"/>
-      <c r="K53" s="40"/>
-      <c r="L53" s="40"/>
-      <c r="M53" s="40"/>
+      <c r="E53" s="37">
+        <v>1961418</v>
+      </c>
+      <c r="F53" s="39"/>
+      <c r="G53" s="39"/>
+      <c r="H53" s="39"/>
+      <c r="I53" s="39"/>
+      <c r="J53" s="39"/>
+      <c r="K53" s="39"/>
+      <c r="L53" s="39"/>
+      <c r="M53" s="39"/>
     </row>
     <row r="54" spans="1:13" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A54" s="35">
@@ -2400,17 +2385,17 @@
       <c r="D54" s="38">
         <v>5808.53</v>
       </c>
-      <c r="E54" s="39">
-        <v>0</v>
-      </c>
-      <c r="F54" s="40"/>
-      <c r="G54" s="40"/>
-      <c r="H54" s="40"/>
-      <c r="I54" s="40"/>
-      <c r="J54" s="40"/>
-      <c r="K54" s="40"/>
-      <c r="L54" s="40"/>
-      <c r="M54" s="40"/>
+      <c r="E54" s="37">
+        <v>106406</v>
+      </c>
+      <c r="F54" s="39"/>
+      <c r="G54" s="39"/>
+      <c r="H54" s="39"/>
+      <c r="I54" s="39"/>
+      <c r="J54" s="39"/>
+      <c r="K54" s="39"/>
+      <c r="L54" s="39"/>
+      <c r="M54" s="39"/>
     </row>
     <row r="55" spans="1:13" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A55" s="35">
@@ -2425,17 +2410,17 @@
       <c r="D55" s="38">
         <v>5808.53</v>
       </c>
-      <c r="E55" s="39">
-        <v>0</v>
-      </c>
-      <c r="F55" s="40"/>
-      <c r="G55" s="40"/>
-      <c r="H55" s="40"/>
-      <c r="I55" s="40"/>
-      <c r="J55" s="40"/>
-      <c r="K55" s="40"/>
-      <c r="L55" s="40"/>
-      <c r="M55" s="40"/>
+      <c r="E55" s="37">
+        <v>0</v>
+      </c>
+      <c r="F55" s="39"/>
+      <c r="G55" s="39"/>
+      <c r="H55" s="39"/>
+      <c r="I55" s="39"/>
+      <c r="J55" s="39"/>
+      <c r="K55" s="39"/>
+      <c r="L55" s="39"/>
+      <c r="M55" s="39"/>
     </row>
     <row r="56" spans="1:13" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A56" s="35">
@@ -2450,17 +2435,17 @@
       <c r="D56" s="38">
         <v>5808.53</v>
       </c>
-      <c r="E56" s="39">
-        <v>0</v>
-      </c>
-      <c r="F56" s="40"/>
-      <c r="G56" s="40"/>
-      <c r="H56" s="40"/>
-      <c r="I56" s="40"/>
-      <c r="J56" s="40"/>
-      <c r="K56" s="40"/>
-      <c r="L56" s="40"/>
-      <c r="M56" s="40"/>
+      <c r="E56" s="37">
+        <v>0</v>
+      </c>
+      <c r="F56" s="39"/>
+      <c r="G56" s="39"/>
+      <c r="H56" s="39"/>
+      <c r="I56" s="39"/>
+      <c r="J56" s="39"/>
+      <c r="K56" s="39"/>
+      <c r="L56" s="39"/>
+      <c r="M56" s="39"/>
     </row>
     <row r="57" spans="1:13" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A57" s="35">
@@ -2475,17 +2460,17 @@
       <c r="D57" s="38">
         <v>5846.09</v>
       </c>
-      <c r="E57" s="39">
-        <v>0</v>
-      </c>
-      <c r="F57" s="40"/>
-      <c r="G57" s="40"/>
-      <c r="H57" s="40"/>
-      <c r="I57" s="40"/>
-      <c r="J57" s="40"/>
-      <c r="K57" s="40"/>
-      <c r="L57" s="40"/>
-      <c r="M57" s="40"/>
+      <c r="E57" s="37">
+        <v>59278</v>
+      </c>
+      <c r="F57" s="39"/>
+      <c r="G57" s="39"/>
+      <c r="H57" s="39"/>
+      <c r="I57" s="39"/>
+      <c r="J57" s="39"/>
+      <c r="K57" s="39"/>
+      <c r="L57" s="39"/>
+      <c r="M57" s="39"/>
     </row>
     <row r="58" spans="1:13" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A58" s="35">
@@ -2500,17 +2485,17 @@
       <c r="D58" s="38">
         <v>5969.64</v>
       </c>
-      <c r="E58" s="39">
-        <v>0</v>
-      </c>
-      <c r="F58" s="40"/>
-      <c r="G58" s="40"/>
-      <c r="H58" s="40"/>
-      <c r="I58" s="40"/>
-      <c r="J58" s="40"/>
-      <c r="K58" s="40"/>
-      <c r="L58" s="40"/>
-      <c r="M58" s="40"/>
+      <c r="E58" s="37">
+        <v>521440</v>
+      </c>
+      <c r="F58" s="39"/>
+      <c r="G58" s="39"/>
+      <c r="H58" s="39"/>
+      <c r="I58" s="39"/>
+      <c r="J58" s="39"/>
+      <c r="K58" s="39"/>
+      <c r="L58" s="39"/>
+      <c r="M58" s="39"/>
     </row>
     <row r="59" spans="1:13" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A59" s="35">
@@ -2525,17 +2510,17 @@
       <c r="D59" s="38">
         <v>6083.86</v>
       </c>
-      <c r="E59" s="39">
-        <v>0</v>
-      </c>
-      <c r="F59" s="40"/>
-      <c r="G59" s="40"/>
-      <c r="H59" s="40"/>
-      <c r="I59" s="40"/>
-      <c r="J59" s="40"/>
-      <c r="K59" s="40"/>
-      <c r="L59" s="40"/>
-      <c r="M59" s="40"/>
+      <c r="E59" s="37">
+        <v>250666</v>
+      </c>
+      <c r="F59" s="39"/>
+      <c r="G59" s="39"/>
+      <c r="H59" s="39"/>
+      <c r="I59" s="39"/>
+      <c r="J59" s="39"/>
+      <c r="K59" s="39"/>
+      <c r="L59" s="39"/>
+      <c r="M59" s="39"/>
     </row>
     <row r="60" spans="1:13" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A60" s="35">
@@ -2550,17 +2535,17 @@
       <c r="D60" s="38">
         <v>6307.27</v>
       </c>
-      <c r="E60" s="39">
-        <v>0</v>
-      </c>
-      <c r="F60" s="40"/>
-      <c r="G60" s="40"/>
-      <c r="H60" s="40"/>
-      <c r="I60" s="40"/>
-      <c r="J60" s="40"/>
-      <c r="K60" s="40"/>
-      <c r="L60" s="40"/>
-      <c r="M60" s="40"/>
+      <c r="E60" s="37">
+        <v>551307</v>
+      </c>
+      <c r="F60" s="39"/>
+      <c r="G60" s="39"/>
+      <c r="H60" s="39"/>
+      <c r="I60" s="39"/>
+      <c r="J60" s="39"/>
+      <c r="K60" s="39"/>
+      <c r="L60" s="39"/>
+      <c r="M60" s="39"/>
     </row>
     <row r="61" spans="1:13" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A61" s="35">
@@ -2575,17 +2560,17 @@
       <c r="D61" s="38">
         <v>6244.13</v>
       </c>
-      <c r="E61" s="39">
-        <v>0</v>
-      </c>
-      <c r="F61" s="40"/>
-      <c r="G61" s="40"/>
-      <c r="H61" s="40"/>
-      <c r="I61" s="40"/>
-      <c r="J61" s="40"/>
-      <c r="K61" s="40"/>
-      <c r="L61" s="40"/>
-      <c r="M61" s="40"/>
+      <c r="E61" s="37">
+        <v>126490</v>
+      </c>
+      <c r="F61" s="39"/>
+      <c r="G61" s="39"/>
+      <c r="H61" s="39"/>
+      <c r="I61" s="39"/>
+      <c r="J61" s="39"/>
+      <c r="K61" s="39"/>
+      <c r="L61" s="39"/>
+      <c r="M61" s="39"/>
     </row>
     <row r="62" spans="1:13" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A62" s="35">
@@ -2600,17 +2585,17 @@
       <c r="D62" s="38">
         <v>6244.13</v>
       </c>
-      <c r="E62" s="39">
-        <v>6907829</v>
-      </c>
-      <c r="F62" s="40"/>
-      <c r="G62" s="40"/>
-      <c r="H62" s="40"/>
-      <c r="I62" s="40"/>
-      <c r="J62" s="40"/>
-      <c r="K62" s="40"/>
-      <c r="L62" s="40"/>
-      <c r="M62" s="40"/>
+      <c r="E62" s="37">
+        <v>0</v>
+      </c>
+      <c r="F62" s="39"/>
+      <c r="G62" s="39"/>
+      <c r="H62" s="39"/>
+      <c r="I62" s="39"/>
+      <c r="J62" s="39"/>
+      <c r="K62" s="39"/>
+      <c r="L62" s="39"/>
+      <c r="M62" s="39"/>
     </row>
     <row r="63" spans="1:13" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A63" s="35">
@@ -2625,17 +2610,17 @@
       <c r="D63" s="38">
         <v>6244.13</v>
       </c>
-      <c r="E63" s="39">
-        <v>0</v>
-      </c>
-      <c r="F63" s="40"/>
-      <c r="G63" s="40"/>
-      <c r="H63" s="40"/>
-      <c r="I63" s="40"/>
-      <c r="J63" s="40"/>
-      <c r="K63" s="40"/>
-      <c r="L63" s="40"/>
-      <c r="M63" s="40"/>
+      <c r="E63" s="37">
+        <v>0</v>
+      </c>
+      <c r="F63" s="39"/>
+      <c r="G63" s="39"/>
+      <c r="H63" s="39"/>
+      <c r="I63" s="39"/>
+      <c r="J63" s="39"/>
+      <c r="K63" s="39"/>
+      <c r="L63" s="39"/>
+      <c r="M63" s="39"/>
     </row>
     <row r="64" spans="1:13" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A64" s="35">
@@ -2650,17 +2635,17 @@
       <c r="D64" s="38">
         <v>6244.13</v>
       </c>
-      <c r="E64" s="39">
-        <v>0</v>
-      </c>
-      <c r="F64" s="40"/>
-      <c r="G64" s="40"/>
-      <c r="H64" s="40"/>
-      <c r="I64" s="40"/>
-      <c r="J64" s="40"/>
-      <c r="K64" s="40"/>
-      <c r="L64" s="40"/>
-      <c r="M64" s="40"/>
+      <c r="E64" s="37">
+        <v>0</v>
+      </c>
+      <c r="F64" s="39"/>
+      <c r="G64" s="39"/>
+      <c r="H64" s="39"/>
+      <c r="I64" s="39"/>
+      <c r="J64" s="39"/>
+      <c r="K64" s="39"/>
+      <c r="L64" s="39"/>
+      <c r="M64" s="39"/>
     </row>
     <row r="65" spans="1:13" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A65" s="35">
@@ -2675,17 +2660,17 @@
       <c r="D65" s="38">
         <v>5791.91</v>
       </c>
-      <c r="E65" s="39">
-        <v>0</v>
-      </c>
-      <c r="F65" s="40"/>
-      <c r="G65" s="40"/>
-      <c r="H65" s="40"/>
-      <c r="I65" s="40"/>
-      <c r="J65" s="40"/>
-      <c r="K65" s="40"/>
-      <c r="L65" s="40"/>
-      <c r="M65" s="40"/>
+      <c r="E65" s="37">
+        <v>0</v>
+      </c>
+      <c r="F65" s="39"/>
+      <c r="G65" s="39"/>
+      <c r="H65" s="39"/>
+      <c r="I65" s="39"/>
+      <c r="J65" s="39"/>
+      <c r="K65" s="39"/>
+      <c r="L65" s="39"/>
+      <c r="M65" s="39"/>
     </row>
     <row r="66" spans="1:13" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A66" s="35">
@@ -2700,17 +2685,17 @@
       <c r="D66" s="38">
         <v>5093.54</v>
       </c>
-      <c r="E66" s="39">
-        <v>0</v>
-      </c>
-      <c r="F66" s="40"/>
-      <c r="G66" s="40"/>
-      <c r="H66" s="40"/>
-      <c r="I66" s="40"/>
-      <c r="J66" s="40"/>
-      <c r="K66" s="40"/>
-      <c r="L66" s="40"/>
-      <c r="M66" s="40"/>
+      <c r="E66" s="37">
+        <v>0</v>
+      </c>
+      <c r="F66" s="39"/>
+      <c r="G66" s="39"/>
+      <c r="H66" s="39"/>
+      <c r="I66" s="39"/>
+      <c r="J66" s="39"/>
+      <c r="K66" s="39"/>
+      <c r="L66" s="39"/>
+      <c r="M66" s="39"/>
     </row>
     <row r="67" spans="1:13" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A67" s="35">
@@ -2725,17 +2710,17 @@
       <c r="D67" s="38">
         <v>5583.9</v>
       </c>
-      <c r="E67" s="39">
-        <v>0</v>
-      </c>
-      <c r="F67" s="40"/>
-      <c r="G67" s="40"/>
-      <c r="H67" s="40"/>
-      <c r="I67" s="40"/>
-      <c r="J67" s="40"/>
-      <c r="K67" s="40"/>
-      <c r="L67" s="40"/>
-      <c r="M67" s="40"/>
+      <c r="E67" s="37">
+        <v>2340462</v>
+      </c>
+      <c r="F67" s="39"/>
+      <c r="G67" s="39"/>
+      <c r="H67" s="39"/>
+      <c r="I67" s="39"/>
+      <c r="J67" s="39"/>
+      <c r="K67" s="39"/>
+      <c r="L67" s="39"/>
+      <c r="M67" s="39"/>
     </row>
     <row r="68" spans="1:13" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A68" s="35">
@@ -2750,17 +2735,17 @@
       <c r="D68" s="38">
         <v>5584.87</v>
       </c>
-      <c r="E68" s="39">
-        <v>0</v>
-      </c>
-      <c r="F68" s="40"/>
-      <c r="G68" s="40"/>
-      <c r="H68" s="40"/>
-      <c r="I68" s="40"/>
-      <c r="J68" s="40"/>
-      <c r="K68" s="40"/>
-      <c r="L68" s="40"/>
-      <c r="M68" s="40"/>
+      <c r="E68" s="37">
+        <v>724725</v>
+      </c>
+      <c r="F68" s="39"/>
+      <c r="G68" s="39"/>
+      <c r="H68" s="39"/>
+      <c r="I68" s="39"/>
+      <c r="J68" s="39"/>
+      <c r="K68" s="39"/>
+      <c r="L68" s="39"/>
+      <c r="M68" s="39"/>
     </row>
     <row r="69" spans="1:13" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A69" s="35">
@@ -2775,17 +2760,17 @@
       <c r="D69" s="38">
         <v>5584.87</v>
       </c>
-      <c r="E69" s="39">
-        <v>0</v>
-      </c>
-      <c r="F69" s="40"/>
-      <c r="G69" s="40"/>
-      <c r="H69" s="40"/>
-      <c r="I69" s="40"/>
-      <c r="J69" s="40"/>
-      <c r="K69" s="40"/>
-      <c r="L69" s="40"/>
-      <c r="M69" s="40"/>
+      <c r="E69" s="37">
+        <v>0</v>
+      </c>
+      <c r="F69" s="39"/>
+      <c r="G69" s="39"/>
+      <c r="H69" s="39"/>
+      <c r="I69" s="39"/>
+      <c r="J69" s="39"/>
+      <c r="K69" s="39"/>
+      <c r="L69" s="39"/>
+      <c r="M69" s="39"/>
     </row>
     <row r="70" spans="1:13" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A70" s="35">
@@ -2800,17 +2785,17 @@
       <c r="D70" s="38">
         <v>5584.87</v>
       </c>
-      <c r="E70" s="39">
-        <v>0</v>
-      </c>
-      <c r="F70" s="40"/>
-      <c r="G70" s="40"/>
-      <c r="H70" s="40"/>
-      <c r="I70" s="40"/>
-      <c r="J70" s="40"/>
-      <c r="K70" s="40"/>
-      <c r="L70" s="40"/>
-      <c r="M70" s="40"/>
+      <c r="E70" s="37">
+        <v>0</v>
+      </c>
+      <c r="F70" s="39"/>
+      <c r="G70" s="39"/>
+      <c r="H70" s="39"/>
+      <c r="I70" s="39"/>
+      <c r="J70" s="39"/>
+      <c r="K70" s="39"/>
+      <c r="L70" s="39"/>
+      <c r="M70" s="39"/>
     </row>
     <row r="71" spans="1:13" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A71" s="35">
@@ -2825,17 +2810,17 @@
       <c r="D71" s="38">
         <v>5251.87</v>
       </c>
-      <c r="E71" s="39">
-        <v>0</v>
-      </c>
-      <c r="F71" s="40"/>
-      <c r="G71" s="40"/>
-      <c r="H71" s="40"/>
-      <c r="I71" s="40"/>
-      <c r="J71" s="40"/>
-      <c r="K71" s="40"/>
-      <c r="L71" s="40"/>
-      <c r="M71" s="40"/>
+      <c r="E71" s="37">
+        <v>0</v>
+      </c>
+      <c r="F71" s="39"/>
+      <c r="G71" s="39"/>
+      <c r="H71" s="39"/>
+      <c r="I71" s="39"/>
+      <c r="J71" s="39"/>
+      <c r="K71" s="39"/>
+      <c r="L71" s="39"/>
+      <c r="M71" s="39"/>
     </row>
     <row r="72" spans="1:13" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A72" s="35">
@@ -2850,17 +2835,17 @@
       <c r="D72" s="38">
         <v>5532.59</v>
       </c>
-      <c r="E72" s="39">
-        <v>0</v>
-      </c>
-      <c r="F72" s="40"/>
-      <c r="G72" s="40"/>
-      <c r="H72" s="40"/>
-      <c r="I72" s="40"/>
-      <c r="J72" s="40"/>
-      <c r="K72" s="40"/>
-      <c r="L72" s="40"/>
-      <c r="M72" s="40"/>
+      <c r="E72" s="37">
+        <v>866851</v>
+      </c>
+      <c r="F72" s="39"/>
+      <c r="G72" s="39"/>
+      <c r="H72" s="39"/>
+      <c r="I72" s="39"/>
+      <c r="J72" s="39"/>
+      <c r="K72" s="39"/>
+      <c r="L72" s="39"/>
+      <c r="M72" s="39"/>
     </row>
     <row r="73" spans="1:13" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A73" s="35">
@@ -2875,17 +2860,17 @@
       <c r="D73" s="38">
         <v>5609.95</v>
       </c>
-      <c r="E73" s="39">
-        <v>0</v>
-      </c>
-      <c r="F73" s="40"/>
-      <c r="G73" s="40"/>
-      <c r="H73" s="40"/>
-      <c r="I73" s="40"/>
-      <c r="J73" s="40"/>
-      <c r="K73" s="40"/>
-      <c r="L73" s="40"/>
-      <c r="M73" s="40"/>
+      <c r="E73" s="37">
+        <v>364486</v>
+      </c>
+      <c r="F73" s="39"/>
+      <c r="G73" s="39"/>
+      <c r="H73" s="39"/>
+      <c r="I73" s="39"/>
+      <c r="J73" s="39"/>
+      <c r="K73" s="39"/>
+      <c r="L73" s="39"/>
+      <c r="M73" s="39"/>
     </row>
     <row r="74" spans="1:13" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A74" s="35">
@@ -2900,17 +2885,17 @@
       <c r="D74" s="38">
         <v>5583.25</v>
       </c>
-      <c r="E74" s="39">
-        <v>0</v>
-      </c>
-      <c r="F74" s="40"/>
-      <c r="G74" s="40"/>
-      <c r="H74" s="40"/>
-      <c r="I74" s="40"/>
-      <c r="J74" s="40"/>
-      <c r="K74" s="40"/>
-      <c r="L74" s="40"/>
-      <c r="M74" s="40"/>
+      <c r="E74" s="37">
+        <v>27300</v>
+      </c>
+      <c r="F74" s="39"/>
+      <c r="G74" s="39"/>
+      <c r="H74" s="39"/>
+      <c r="I74" s="39"/>
+      <c r="J74" s="39"/>
+      <c r="K74" s="39"/>
+      <c r="L74" s="39"/>
+      <c r="M74" s="39"/>
     </row>
     <row r="75" spans="1:13" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A75" s="35">
@@ -2925,17 +2910,17 @@
       <c r="D75" s="38">
         <v>5487.24</v>
       </c>
-      <c r="E75" s="39">
-        <v>0</v>
-      </c>
-      <c r="F75" s="40"/>
-      <c r="G75" s="40"/>
-      <c r="H75" s="40"/>
-      <c r="I75" s="40"/>
-      <c r="J75" s="40"/>
-      <c r="K75" s="40"/>
-      <c r="L75" s="40"/>
-      <c r="M75" s="40"/>
+      <c r="E75" s="37">
+        <v>0</v>
+      </c>
+      <c r="F75" s="39"/>
+      <c r="G75" s="39"/>
+      <c r="H75" s="39"/>
+      <c r="I75" s="39"/>
+      <c r="J75" s="39"/>
+      <c r="K75" s="39"/>
+      <c r="L75" s="39"/>
+      <c r="M75" s="39"/>
     </row>
     <row r="76" spans="1:13" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A76" s="35">
@@ -2950,17 +2935,17 @@
       <c r="D76" s="38">
         <v>5487.24</v>
       </c>
-      <c r="E76" s="39">
-        <v>0</v>
-      </c>
-      <c r="F76" s="40"/>
-      <c r="G76" s="40"/>
-      <c r="H76" s="40"/>
-      <c r="I76" s="40"/>
-      <c r="J76" s="40"/>
-      <c r="K76" s="40"/>
-      <c r="L76" s="40"/>
-      <c r="M76" s="40"/>
+      <c r="E76" s="37">
+        <v>0</v>
+      </c>
+      <c r="F76" s="39"/>
+      <c r="G76" s="39"/>
+      <c r="H76" s="39"/>
+      <c r="I76" s="39"/>
+      <c r="J76" s="39"/>
+      <c r="K76" s="39"/>
+      <c r="L76" s="39"/>
+      <c r="M76" s="39"/>
     </row>
     <row r="77" spans="1:13" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A77" s="35">
@@ -2975,17 +2960,17 @@
       <c r="D77" s="38">
         <v>5487.24</v>
       </c>
-      <c r="E77" s="39">
-        <v>0</v>
-      </c>
-      <c r="F77" s="40"/>
-      <c r="G77" s="40"/>
-      <c r="H77" s="40"/>
-      <c r="I77" s="40"/>
-      <c r="J77" s="40"/>
-      <c r="K77" s="40"/>
-      <c r="L77" s="40"/>
-      <c r="M77" s="40"/>
+      <c r="E77" s="37">
+        <v>0</v>
+      </c>
+      <c r="F77" s="39"/>
+      <c r="G77" s="39"/>
+      <c r="H77" s="39"/>
+      <c r="I77" s="39"/>
+      <c r="J77" s="39"/>
+      <c r="K77" s="39"/>
+      <c r="L77" s="39"/>
+      <c r="M77" s="39"/>
     </row>
     <row r="78" spans="1:13" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A78" s="35">
@@ -3000,17 +2985,17 @@
       <c r="D78" s="38">
         <v>5549.85</v>
       </c>
-      <c r="E78" s="39">
-        <v>0</v>
-      </c>
-      <c r="F78" s="40"/>
-      <c r="G78" s="40"/>
-      <c r="H78" s="40"/>
-      <c r="I78" s="40"/>
-      <c r="J78" s="40"/>
-      <c r="K78" s="40"/>
-      <c r="L78" s="40"/>
-      <c r="M78" s="40"/>
+      <c r="E78" s="37">
+        <v>162293</v>
+      </c>
+      <c r="F78" s="39"/>
+      <c r="G78" s="39"/>
+      <c r="H78" s="39"/>
+      <c r="I78" s="39"/>
+      <c r="J78" s="39"/>
+      <c r="K78" s="39"/>
+      <c r="L78" s="39"/>
+      <c r="M78" s="39"/>
     </row>
     <row r="79" spans="1:13" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A79" s="35">
@@ -3025,17 +3010,17 @@
       <c r="D79" s="38">
         <v>5925.03</v>
       </c>
-      <c r="E79" s="39">
-        <v>0</v>
-      </c>
-      <c r="F79" s="40"/>
-      <c r="G79" s="40"/>
-      <c r="H79" s="40"/>
-      <c r="I79" s="40"/>
-      <c r="J79" s="40"/>
-      <c r="K79" s="40"/>
-      <c r="L79" s="40"/>
-      <c r="M79" s="40"/>
+      <c r="E79" s="37">
+        <v>326423</v>
+      </c>
+      <c r="F79" s="39"/>
+      <c r="G79" s="39"/>
+      <c r="H79" s="39"/>
+      <c r="I79" s="39"/>
+      <c r="J79" s="39"/>
+      <c r="K79" s="39"/>
+      <c r="L79" s="39"/>
+      <c r="M79" s="39"/>
     </row>
     <row r="80" spans="1:13" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A80" s="35">
@@ -3050,17 +3035,17 @@
       <c r="D80" s="38">
         <v>5763.22</v>
       </c>
-      <c r="E80" s="39">
-        <v>0</v>
-      </c>
-      <c r="F80" s="40"/>
-      <c r="G80" s="40"/>
-      <c r="H80" s="40"/>
-      <c r="I80" s="40"/>
-      <c r="J80" s="40"/>
-      <c r="K80" s="40"/>
-      <c r="L80" s="40"/>
-      <c r="M80" s="40"/>
+      <c r="E80" s="37">
+        <v>902676</v>
+      </c>
+      <c r="F80" s="39"/>
+      <c r="G80" s="39"/>
+      <c r="H80" s="39"/>
+      <c r="I80" s="39"/>
+      <c r="J80" s="39"/>
+      <c r="K80" s="39"/>
+      <c r="L80" s="39"/>
+      <c r="M80" s="39"/>
     </row>
     <row r="81" spans="1:13" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A81" s="35">
@@ -3075,17 +3060,17 @@
       <c r="D81" s="38">
         <v>5763.22</v>
       </c>
-      <c r="E81" s="39">
-        <v>0</v>
-      </c>
-      <c r="F81" s="40"/>
-      <c r="G81" s="40"/>
-      <c r="H81" s="40"/>
-      <c r="I81" s="40"/>
-      <c r="J81" s="40"/>
-      <c r="K81" s="40"/>
-      <c r="L81" s="40"/>
-      <c r="M81" s="40"/>
+      <c r="E81" s="37">
+        <v>0</v>
+      </c>
+      <c r="F81" s="39"/>
+      <c r="G81" s="39"/>
+      <c r="H81" s="39"/>
+      <c r="I81" s="39"/>
+      <c r="J81" s="39"/>
+      <c r="K81" s="39"/>
+      <c r="L81" s="39"/>
+      <c r="M81" s="39"/>
     </row>
     <row r="82" spans="1:13" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A82" s="35">
@@ -3100,17 +3085,17 @@
       <c r="D82" s="38">
         <v>5781.2</v>
       </c>
-      <c r="E82" s="39">
-        <v>0</v>
-      </c>
-      <c r="F82" s="40"/>
-      <c r="G82" s="40"/>
-      <c r="H82" s="40"/>
-      <c r="I82" s="40"/>
-      <c r="J82" s="40"/>
-      <c r="K82" s="40"/>
-      <c r="L82" s="40"/>
-      <c r="M82" s="40"/>
+      <c r="E82" s="37">
+        <v>236843</v>
+      </c>
+      <c r="F82" s="39"/>
+      <c r="G82" s="39"/>
+      <c r="H82" s="39"/>
+      <c r="I82" s="39"/>
+      <c r="J82" s="39"/>
+      <c r="K82" s="39"/>
+      <c r="L82" s="39"/>
+      <c r="M82" s="39"/>
     </row>
     <row r="83" spans="1:13" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A83" s="35">
@@ -3125,17 +3110,17 @@
       <c r="D83" s="38">
         <v>5781.2</v>
       </c>
-      <c r="E83" s="39">
-        <v>0</v>
-      </c>
-      <c r="F83" s="40"/>
-      <c r="G83" s="40"/>
-      <c r="H83" s="40"/>
-      <c r="I83" s="40"/>
-      <c r="J83" s="40"/>
-      <c r="K83" s="40"/>
-      <c r="L83" s="40"/>
-      <c r="M83" s="40"/>
+      <c r="E83" s="37">
+        <v>0</v>
+      </c>
+      <c r="F83" s="39"/>
+      <c r="G83" s="39"/>
+      <c r="H83" s="39"/>
+      <c r="I83" s="39"/>
+      <c r="J83" s="39"/>
+      <c r="K83" s="39"/>
+      <c r="L83" s="39"/>
+      <c r="M83" s="39"/>
     </row>
     <row r="84" spans="1:13" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A84" s="35">
@@ -3150,17 +3135,17 @@
       <c r="D84" s="38">
         <v>5781.2</v>
       </c>
-      <c r="E84" s="39">
-        <v>0</v>
-      </c>
-      <c r="F84" s="40"/>
-      <c r="G84" s="40"/>
-      <c r="H84" s="40"/>
-      <c r="I84" s="40"/>
-      <c r="J84" s="40"/>
-      <c r="K84" s="40"/>
-      <c r="L84" s="40"/>
-      <c r="M84" s="40"/>
+      <c r="E84" s="37">
+        <v>0</v>
+      </c>
+      <c r="F84" s="39"/>
+      <c r="G84" s="39"/>
+      <c r="H84" s="39"/>
+      <c r="I84" s="39"/>
+      <c r="J84" s="39"/>
+      <c r="K84" s="39"/>
+      <c r="L84" s="39"/>
+      <c r="M84" s="39"/>
     </row>
     <row r="85" spans="1:13" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A85" s="35">
@@ -3175,17 +3160,17 @@
       <c r="D85" s="38">
         <v>5405.75</v>
       </c>
-      <c r="E85" s="39">
-        <v>0</v>
-      </c>
-      <c r="F85" s="40"/>
-      <c r="G85" s="40"/>
-      <c r="H85" s="40"/>
-      <c r="I85" s="40"/>
-      <c r="J85" s="40"/>
-      <c r="K85" s="40"/>
-      <c r="L85" s="40"/>
-      <c r="M85" s="40"/>
+      <c r="E85" s="37">
+        <v>0</v>
+      </c>
+      <c r="F85" s="39"/>
+      <c r="G85" s="39"/>
+      <c r="H85" s="39"/>
+      <c r="I85" s="39"/>
+      <c r="J85" s="39"/>
+      <c r="K85" s="39"/>
+      <c r="L85" s="39"/>
+      <c r="M85" s="39"/>
     </row>
     <row r="86" spans="1:13" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A86" s="35">
@@ -3200,17 +3185,17 @@
       <c r="D86" s="38">
         <v>5553.92</v>
       </c>
-      <c r="E86" s="39">
-        <v>0</v>
-      </c>
-      <c r="F86" s="40"/>
-      <c r="G86" s="40"/>
-      <c r="H86" s="40"/>
-      <c r="I86" s="40"/>
-      <c r="J86" s="40"/>
-      <c r="K86" s="40"/>
-      <c r="L86" s="40"/>
-      <c r="M86" s="40"/>
+      <c r="E86" s="37">
+        <v>426860</v>
+      </c>
+      <c r="F86" s="39"/>
+      <c r="G86" s="39"/>
+      <c r="H86" s="39"/>
+      <c r="I86" s="39"/>
+      <c r="J86" s="39"/>
+      <c r="K86" s="39"/>
+      <c r="L86" s="39"/>
+      <c r="M86" s="39"/>
     </row>
     <row r="87" spans="1:13" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A87" s="35">
@@ -3225,17 +3210,17 @@
       <c r="D87" s="38">
         <v>5642.21</v>
       </c>
-      <c r="E87" s="39">
-        <v>0</v>
-      </c>
-      <c r="F87" s="40"/>
-      <c r="G87" s="40"/>
-      <c r="H87" s="40"/>
-      <c r="I87" s="40"/>
-      <c r="J87" s="40"/>
-      <c r="K87" s="40"/>
-      <c r="L87" s="40"/>
-      <c r="M87" s="40"/>
+      <c r="E87" s="37">
+        <v>732533</v>
+      </c>
+      <c r="F87" s="39"/>
+      <c r="G87" s="39"/>
+      <c r="H87" s="39"/>
+      <c r="I87" s="39"/>
+      <c r="J87" s="39"/>
+      <c r="K87" s="39"/>
+      <c r="L87" s="39"/>
+      <c r="M87" s="39"/>
     </row>
     <row r="88" spans="1:13" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A88" s="35">
@@ -3250,17 +3235,17 @@
       <c r="D88" s="38">
         <v>5460.46</v>
       </c>
-      <c r="E88" s="39">
-        <v>0</v>
-      </c>
-      <c r="F88" s="40"/>
-      <c r="G88" s="40"/>
-      <c r="H88" s="40"/>
-      <c r="I88" s="40"/>
-      <c r="J88" s="40"/>
-      <c r="K88" s="40"/>
-      <c r="L88" s="40"/>
-      <c r="M88" s="40"/>
+      <c r="E88" s="37">
+        <v>0</v>
+      </c>
+      <c r="F88" s="39"/>
+      <c r="G88" s="39"/>
+      <c r="H88" s="39"/>
+      <c r="I88" s="39"/>
+      <c r="J88" s="39"/>
+      <c r="K88" s="39"/>
+      <c r="L88" s="39"/>
+      <c r="M88" s="39"/>
     </row>
     <row r="89" spans="1:13" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A89" s="35">
@@ -3275,17 +3260,17 @@
       <c r="D89" s="38">
         <v>5438.87</v>
       </c>
-      <c r="E89" s="39">
-        <v>0</v>
-      </c>
-      <c r="F89" s="40"/>
-      <c r="G89" s="40"/>
-      <c r="H89" s="40"/>
-      <c r="I89" s="40"/>
-      <c r="J89" s="40"/>
-      <c r="K89" s="40"/>
-      <c r="L89" s="40"/>
-      <c r="M89" s="40"/>
+      <c r="E89" s="37">
+        <v>48090</v>
+      </c>
+      <c r="F89" s="39"/>
+      <c r="G89" s="39"/>
+      <c r="H89" s="39"/>
+      <c r="I89" s="39"/>
+      <c r="J89" s="39"/>
+      <c r="K89" s="39"/>
+      <c r="L89" s="39"/>
+      <c r="M89" s="39"/>
     </row>
     <row r="90" spans="1:13" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A90" s="35">
@@ -3300,17 +3285,17 @@
       <c r="D90" s="38">
         <v>5438.87</v>
       </c>
-      <c r="E90" s="39">
-        <v>0</v>
-      </c>
-      <c r="F90" s="40"/>
-      <c r="G90" s="40"/>
-      <c r="H90" s="40"/>
-      <c r="I90" s="40"/>
-      <c r="J90" s="40"/>
-      <c r="K90" s="40"/>
-      <c r="L90" s="40"/>
-      <c r="M90" s="40"/>
+      <c r="E90" s="37">
+        <v>0</v>
+      </c>
+      <c r="F90" s="39"/>
+      <c r="G90" s="39"/>
+      <c r="H90" s="39"/>
+      <c r="I90" s="39"/>
+      <c r="J90" s="39"/>
+      <c r="K90" s="39"/>
+      <c r="L90" s="39"/>
+      <c r="M90" s="39"/>
     </row>
     <row r="91" spans="1:13" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A91" s="35">
@@ -3325,17 +3310,17 @@
       <c r="D91" s="38">
         <v>5438.87</v>
       </c>
-      <c r="E91" s="39">
-        <v>0</v>
-      </c>
-      <c r="F91" s="40"/>
-      <c r="G91" s="40"/>
-      <c r="H91" s="40"/>
-      <c r="I91" s="40"/>
-      <c r="J91" s="40"/>
-      <c r="K91" s="40"/>
-      <c r="L91" s="40"/>
-      <c r="M91" s="40"/>
+      <c r="E91" s="37">
+        <v>0</v>
+      </c>
+      <c r="F91" s="39"/>
+      <c r="G91" s="39"/>
+      <c r="H91" s="39"/>
+      <c r="I91" s="39"/>
+      <c r="J91" s="39"/>
+      <c r="K91" s="39"/>
+      <c r="L91" s="39"/>
+      <c r="M91" s="39"/>
     </row>
     <row r="92" spans="1:13" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A92" s="35">
@@ -3350,17 +3335,17 @@
       <c r="D92" s="38">
         <v>5277.3</v>
       </c>
-      <c r="E92" s="39">
-        <v>0</v>
-      </c>
-      <c r="F92" s="40"/>
-      <c r="G92" s="40"/>
-      <c r="H92" s="40"/>
-      <c r="I92" s="40"/>
-      <c r="J92" s="40"/>
-      <c r="K92" s="40"/>
-      <c r="L92" s="40"/>
-      <c r="M92" s="40"/>
+      <c r="E92" s="37">
+        <v>0</v>
+      </c>
+      <c r="F92" s="39"/>
+      <c r="G92" s="39"/>
+      <c r="H92" s="39"/>
+      <c r="I92" s="39"/>
+      <c r="J92" s="39"/>
+      <c r="K92" s="39"/>
+      <c r="L92" s="39"/>
+      <c r="M92" s="39"/>
     </row>
     <row r="93" spans="1:13" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A93" s="35">
@@ -3375,17 +3360,17 @@
       <c r="D93" s="38">
         <v>5052.46</v>
       </c>
-      <c r="E93" s="39">
-        <v>7159542</v>
-      </c>
-      <c r="F93" s="40"/>
-      <c r="G93" s="40"/>
-      <c r="H93" s="40"/>
-      <c r="I93" s="40"/>
-      <c r="J93" s="40"/>
-      <c r="K93" s="40"/>
-      <c r="L93" s="40"/>
-      <c r="M93" s="40"/>
+      <c r="E93" s="37">
+        <v>0</v>
+      </c>
+      <c r="F93" s="39"/>
+      <c r="G93" s="39"/>
+      <c r="H93" s="39"/>
+      <c r="I93" s="39"/>
+      <c r="J93" s="39"/>
+      <c r="K93" s="39"/>
+      <c r="L93" s="39"/>
+      <c r="M93" s="39"/>
     </row>
     <row r="94" spans="1:13" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A94" s="35">
@@ -3400,17 +3385,17 @@
       <c r="D94" s="38">
         <v>5478.7</v>
       </c>
-      <c r="E94" s="39">
-        <v>0</v>
-      </c>
-      <c r="F94" s="40"/>
-      <c r="G94" s="40"/>
-      <c r="H94" s="40"/>
-      <c r="I94" s="40"/>
-      <c r="J94" s="40"/>
-      <c r="K94" s="40"/>
-      <c r="L94" s="40"/>
-      <c r="M94" s="40"/>
+      <c r="E94" s="37">
+        <v>2458304</v>
+      </c>
+      <c r="F94" s="39"/>
+      <c r="G94" s="39"/>
+      <c r="H94" s="39"/>
+      <c r="I94" s="39"/>
+      <c r="J94" s="39"/>
+      <c r="K94" s="39"/>
+      <c r="L94" s="39"/>
+      <c r="M94" s="39"/>
     </row>
     <row r="95" spans="1:13" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A95" s="35">
@@ -3425,17 +3410,17 @@
       <c r="D95" s="38">
         <v>5234.05</v>
       </c>
-      <c r="E95" s="39">
-        <v>0</v>
-      </c>
-      <c r="F95" s="40"/>
-      <c r="G95" s="40"/>
-      <c r="H95" s="40"/>
-      <c r="I95" s="40"/>
-      <c r="J95" s="40"/>
-      <c r="K95" s="40"/>
-      <c r="L95" s="40"/>
-      <c r="M95" s="40"/>
+      <c r="E95" s="37">
+        <v>0</v>
+      </c>
+      <c r="F95" s="39"/>
+      <c r="G95" s="39"/>
+      <c r="H95" s="39"/>
+      <c r="I95" s="39"/>
+      <c r="J95" s="39"/>
+      <c r="K95" s="39"/>
+      <c r="L95" s="39"/>
+      <c r="M95" s="39"/>
     </row>
     <row r="96" spans="1:13" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A96" s="35">
@@ -3450,17 +3435,17 @@
       <c r="D96" s="38">
         <v>5377.3</v>
       </c>
-      <c r="E96" s="39">
-        <v>0</v>
-      </c>
-      <c r="F96" s="40"/>
-      <c r="G96" s="40"/>
-      <c r="H96" s="40"/>
-      <c r="I96" s="40"/>
-      <c r="J96" s="40"/>
-      <c r="K96" s="40"/>
-      <c r="L96" s="40"/>
-      <c r="M96" s="40"/>
+      <c r="E96" s="37">
+        <v>721685</v>
+      </c>
+      <c r="F96" s="39"/>
+      <c r="G96" s="39"/>
+      <c r="H96" s="39"/>
+      <c r="I96" s="39"/>
+      <c r="J96" s="39"/>
+      <c r="K96" s="39"/>
+      <c r="L96" s="39"/>
+      <c r="M96" s="39"/>
     </row>
     <row r="97" spans="1:13" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A97" s="35">
@@ -3475,17 +3460,17 @@
       <c r="D97" s="38">
         <v>5377.3</v>
       </c>
-      <c r="E97" s="39">
-        <v>0</v>
-      </c>
-      <c r="F97" s="40"/>
-      <c r="G97" s="40"/>
-      <c r="H97" s="40"/>
-      <c r="I97" s="40"/>
-      <c r="J97" s="40"/>
-      <c r="K97" s="40"/>
-      <c r="L97" s="40"/>
-      <c r="M97" s="40"/>
+      <c r="E97" s="37">
+        <v>0</v>
+      </c>
+      <c r="F97" s="39"/>
+      <c r="G97" s="39"/>
+      <c r="H97" s="39"/>
+      <c r="I97" s="39"/>
+      <c r="J97" s="39"/>
+      <c r="K97" s="39"/>
+      <c r="L97" s="39"/>
+      <c r="M97" s="39"/>
     </row>
     <row r="98" spans="1:13" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A98" s="35">
@@ -3500,17 +3485,17 @@
       <c r="D98" s="38">
         <v>5377.3</v>
       </c>
-      <c r="E98" s="39">
-        <v>0</v>
-      </c>
-      <c r="F98" s="40"/>
-      <c r="G98" s="40"/>
-      <c r="H98" s="40"/>
-      <c r="I98" s="40"/>
-      <c r="J98" s="40"/>
-      <c r="K98" s="40"/>
-      <c r="L98" s="40"/>
-      <c r="M98" s="40"/>
+      <c r="E98" s="37">
+        <v>0</v>
+      </c>
+      <c r="F98" s="39"/>
+      <c r="G98" s="39"/>
+      <c r="H98" s="39"/>
+      <c r="I98" s="39"/>
+      <c r="J98" s="39"/>
+      <c r="K98" s="39"/>
+      <c r="L98" s="39"/>
+      <c r="M98" s="39"/>
     </row>
     <row r="99" spans="1:13" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A99" s="35">
@@ -3525,17 +3510,17 @@
       <c r="D99" s="38">
         <v>5450.33</v>
       </c>
-      <c r="E99" s="39">
-        <v>0</v>
-      </c>
-      <c r="F99" s="40"/>
-      <c r="G99" s="40"/>
-      <c r="H99" s="40"/>
-      <c r="I99" s="40"/>
-      <c r="J99" s="40"/>
-      <c r="K99" s="40"/>
-      <c r="L99" s="40"/>
-      <c r="M99" s="40"/>
+      <c r="E99" s="37">
+        <v>586978</v>
+      </c>
+      <c r="F99" s="39"/>
+      <c r="G99" s="39"/>
+      <c r="H99" s="39"/>
+      <c r="I99" s="39"/>
+      <c r="J99" s="39"/>
+      <c r="K99" s="39"/>
+      <c r="L99" s="39"/>
+      <c r="M99" s="39"/>
     </row>
     <row r="100" spans="1:13" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A100" s="35">
@@ -3550,17 +3535,17 @@
       <c r="D100" s="38">
         <v>5494.78</v>
       </c>
-      <c r="E100" s="39">
-        <v>0</v>
-      </c>
-      <c r="F100" s="40"/>
-      <c r="G100" s="40"/>
-      <c r="H100" s="40"/>
-      <c r="I100" s="40"/>
-      <c r="J100" s="40"/>
-      <c r="K100" s="40"/>
-      <c r="L100" s="40"/>
-      <c r="M100" s="40"/>
+      <c r="E100" s="37">
+        <v>143653</v>
+      </c>
+      <c r="F100" s="39"/>
+      <c r="G100" s="39"/>
+      <c r="H100" s="39"/>
+      <c r="I100" s="39"/>
+      <c r="J100" s="39"/>
+      <c r="K100" s="39"/>
+      <c r="L100" s="39"/>
+      <c r="M100" s="39"/>
     </row>
     <row r="101" spans="1:13" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A101" s="35">
@@ -3575,17 +3560,17 @@
       <c r="D101" s="38">
         <v>5872.34</v>
       </c>
-      <c r="E101" s="39">
-        <v>0</v>
-      </c>
-      <c r="F101" s="40"/>
-      <c r="G101" s="40"/>
-      <c r="H101" s="40"/>
-      <c r="I101" s="40"/>
-      <c r="J101" s="40"/>
-      <c r="K101" s="40"/>
-      <c r="L101" s="40"/>
-      <c r="M101" s="40"/>
+      <c r="E101" s="37">
+        <v>2425024</v>
+      </c>
+      <c r="F101" s="39"/>
+      <c r="G101" s="39"/>
+      <c r="H101" s="39"/>
+      <c r="I101" s="39"/>
+      <c r="J101" s="39"/>
+      <c r="K101" s="39"/>
+      <c r="L101" s="39"/>
+      <c r="M101" s="39"/>
     </row>
     <row r="102" spans="1:13" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A102" s="35">
@@ -3600,17 +3585,17 @@
       <c r="D102" s="38">
         <v>5778.01</v>
       </c>
-      <c r="E102" s="39">
-        <v>0</v>
-      </c>
-      <c r="F102" s="40"/>
-      <c r="G102" s="40"/>
-      <c r="H102" s="40"/>
-      <c r="I102" s="40"/>
-      <c r="J102" s="40"/>
-      <c r="K102" s="40"/>
-      <c r="L102" s="40"/>
-      <c r="M102" s="40"/>
+      <c r="E102" s="37">
+        <v>0</v>
+      </c>
+      <c r="F102" s="39"/>
+      <c r="G102" s="39"/>
+      <c r="H102" s="39"/>
+      <c r="I102" s="39"/>
+      <c r="J102" s="39"/>
+      <c r="K102" s="39"/>
+      <c r="L102" s="39"/>
+      <c r="M102" s="39"/>
     </row>
     <row r="103" spans="1:13" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A103" s="35">
@@ -3625,17 +3610,17 @@
       <c r="D103" s="38">
         <v>5858.87</v>
       </c>
-      <c r="E103" s="39">
-        <v>0</v>
-      </c>
-      <c r="F103" s="40"/>
-      <c r="G103" s="40"/>
-      <c r="H103" s="40"/>
-      <c r="I103" s="40"/>
-      <c r="J103" s="40"/>
-      <c r="K103" s="40"/>
-      <c r="L103" s="40"/>
-      <c r="M103" s="40"/>
+      <c r="E103" s="37">
+        <v>848960</v>
+      </c>
+      <c r="F103" s="39"/>
+      <c r="G103" s="39"/>
+      <c r="H103" s="39"/>
+      <c r="I103" s="39"/>
+      <c r="J103" s="39"/>
+      <c r="K103" s="39"/>
+      <c r="L103" s="39"/>
+      <c r="M103" s="39"/>
     </row>
     <row r="104" spans="1:13" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A104" s="35">
@@ -3650,17 +3635,17 @@
       <c r="D104" s="38">
         <v>5808.62</v>
       </c>
-      <c r="E104" s="39">
-        <v>0</v>
-      </c>
-      <c r="F104" s="40"/>
-      <c r="G104" s="40"/>
-      <c r="H104" s="40"/>
-      <c r="I104" s="40"/>
-      <c r="J104" s="40"/>
-      <c r="K104" s="40"/>
-      <c r="L104" s="40"/>
-      <c r="M104" s="40"/>
+      <c r="E104" s="37">
+        <v>0</v>
+      </c>
+      <c r="F104" s="39"/>
+      <c r="G104" s="39"/>
+      <c r="H104" s="39"/>
+      <c r="I104" s="39"/>
+      <c r="J104" s="39"/>
+      <c r="K104" s="39"/>
+      <c r="L104" s="39"/>
+      <c r="M104" s="39"/>
     </row>
     <row r="105" spans="1:13" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A105" s="35">
@@ -3675,17 +3660,17 @@
       <c r="D105" s="38">
         <v>5967.74</v>
       </c>
-      <c r="E105" s="39">
-        <v>0</v>
-      </c>
-      <c r="F105" s="40"/>
-      <c r="G105" s="40"/>
-      <c r="H105" s="40"/>
-      <c r="I105" s="40"/>
-      <c r="J105" s="40"/>
-      <c r="K105" s="40"/>
-      <c r="L105" s="40"/>
-      <c r="M105" s="40"/>
+      <c r="E105" s="37">
+        <v>1321896</v>
+      </c>
+      <c r="F105" s="39"/>
+      <c r="G105" s="39"/>
+      <c r="H105" s="39"/>
+      <c r="I105" s="39"/>
+      <c r="J105" s="39"/>
+      <c r="K105" s="39"/>
+      <c r="L105" s="39"/>
+      <c r="M105" s="39"/>
     </row>
     <row r="106" spans="1:13" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A106" s="35">
@@ -3700,17 +3685,17 @@
       <c r="D106" s="38">
         <v>6091.39</v>
       </c>
-      <c r="E106" s="39">
-        <v>0</v>
-      </c>
-      <c r="F106" s="40"/>
-      <c r="G106" s="40"/>
-      <c r="H106" s="40"/>
-      <c r="I106" s="40"/>
-      <c r="J106" s="40"/>
-      <c r="K106" s="40"/>
-      <c r="L106" s="40"/>
-      <c r="M106" s="40"/>
+      <c r="E106" s="37">
+        <v>1479255</v>
+      </c>
+      <c r="F106" s="39"/>
+      <c r="G106" s="39"/>
+      <c r="H106" s="39"/>
+      <c r="I106" s="39"/>
+      <c r="J106" s="39"/>
+      <c r="K106" s="39"/>
+      <c r="L106" s="39"/>
+      <c r="M106" s="39"/>
     </row>
     <row r="107" spans="1:13" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A107" s="35">
@@ -3725,17 +3710,17 @@
       <c r="D107" s="38">
         <v>6226.05</v>
       </c>
-      <c r="E107" s="39">
-        <v>0</v>
-      </c>
-      <c r="F107" s="40"/>
-      <c r="G107" s="40"/>
-      <c r="H107" s="40"/>
-      <c r="I107" s="40"/>
-      <c r="J107" s="40"/>
-      <c r="K107" s="40"/>
-      <c r="L107" s="40"/>
-      <c r="M107" s="40"/>
+      <c r="E107" s="37">
+        <v>572636</v>
+      </c>
+      <c r="F107" s="39"/>
+      <c r="G107" s="39"/>
+      <c r="H107" s="39"/>
+      <c r="I107" s="39"/>
+      <c r="J107" s="39"/>
+      <c r="K107" s="39"/>
+      <c r="L107" s="39"/>
+      <c r="M107" s="39"/>
     </row>
     <row r="108" spans="1:13" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A108" s="35">
@@ -3750,17 +3735,17 @@
       <c r="D108" s="38">
         <v>6191.92</v>
       </c>
-      <c r="E108" s="39">
-        <v>0</v>
-      </c>
-      <c r="F108" s="40"/>
-      <c r="G108" s="40"/>
-      <c r="H108" s="40"/>
-      <c r="I108" s="40"/>
-      <c r="J108" s="40"/>
-      <c r="K108" s="40"/>
-      <c r="L108" s="40"/>
-      <c r="M108" s="40"/>
+      <c r="E108" s="37">
+        <v>0</v>
+      </c>
+      <c r="F108" s="39"/>
+      <c r="G108" s="39"/>
+      <c r="H108" s="39"/>
+      <c r="I108" s="39"/>
+      <c r="J108" s="39"/>
+      <c r="K108" s="39"/>
+      <c r="L108" s="39"/>
+      <c r="M108" s="39"/>
     </row>
     <row r="109" spans="1:13" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A109" s="35">
@@ -3775,17 +3760,17 @@
       <c r="D109" s="38">
         <v>6192.92</v>
       </c>
-      <c r="E109" s="39">
-        <v>0</v>
-      </c>
-      <c r="F109" s="40"/>
-      <c r="G109" s="40"/>
-      <c r="H109" s="40"/>
-      <c r="I109" s="40"/>
-      <c r="J109" s="40"/>
-      <c r="K109" s="40"/>
-      <c r="L109" s="40"/>
-      <c r="M109" s="40"/>
+      <c r="E109" s="37">
+        <v>0</v>
+      </c>
+      <c r="F109" s="39"/>
+      <c r="G109" s="39"/>
+      <c r="H109" s="39"/>
+      <c r="I109" s="39"/>
+      <c r="J109" s="39"/>
+      <c r="K109" s="39"/>
+      <c r="L109" s="39"/>
+      <c r="M109" s="39"/>
     </row>
     <row r="110" spans="1:13" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A110" s="35">
@@ -3800,17 +3785,17 @@
       <c r="D110" s="38">
         <v>6193.92</v>
       </c>
-      <c r="E110" s="39">
-        <v>0</v>
-      </c>
-      <c r="F110" s="40"/>
-      <c r="G110" s="40"/>
-      <c r="H110" s="40"/>
-      <c r="I110" s="40"/>
-      <c r="J110" s="40"/>
-      <c r="K110" s="40"/>
-      <c r="L110" s="40"/>
-      <c r="M110" s="40"/>
+      <c r="E110" s="37">
+        <v>0</v>
+      </c>
+      <c r="F110" s="39"/>
+      <c r="G110" s="39"/>
+      <c r="H110" s="39"/>
+      <c r="I110" s="39"/>
+      <c r="J110" s="39"/>
+      <c r="K110" s="39"/>
+      <c r="L110" s="39"/>
+      <c r="M110" s="39"/>
     </row>
     <row r="111" spans="1:13" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A111" s="35">
@@ -3825,17 +3810,17 @@
       <c r="D111" s="38">
         <v>6219.09</v>
       </c>
-      <c r="E111" s="39">
-        <v>0</v>
-      </c>
-      <c r="F111" s="40"/>
-      <c r="G111" s="40"/>
-      <c r="H111" s="40"/>
-      <c r="I111" s="40"/>
-      <c r="J111" s="40"/>
-      <c r="K111" s="40"/>
-      <c r="L111" s="40"/>
-      <c r="M111" s="40"/>
+      <c r="E111" s="37">
+        <v>399740</v>
+      </c>
+      <c r="F111" s="39"/>
+      <c r="G111" s="39"/>
+      <c r="H111" s="39"/>
+      <c r="I111" s="39"/>
+      <c r="J111" s="39"/>
+      <c r="K111" s="39"/>
+      <c r="L111" s="39"/>
+      <c r="M111" s="39"/>
     </row>
     <row r="112" spans="1:13" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A112" s="35">
@@ -3850,17 +3835,17 @@
       <c r="D112" s="38">
         <v>6388.47</v>
       </c>
-      <c r="E112" s="39">
-        <v>0</v>
-      </c>
-      <c r="F112" s="40"/>
-      <c r="G112" s="40"/>
-      <c r="H112" s="40"/>
-      <c r="I112" s="40"/>
-      <c r="J112" s="40"/>
-      <c r="K112" s="40"/>
-      <c r="L112" s="40"/>
-      <c r="M112" s="40"/>
+      <c r="E112" s="37">
+        <v>376848</v>
+      </c>
+      <c r="F112" s="39"/>
+      <c r="G112" s="39"/>
+      <c r="H112" s="39"/>
+      <c r="I112" s="39"/>
+      <c r="J112" s="39"/>
+      <c r="K112" s="39"/>
+      <c r="L112" s="39"/>
+      <c r="M112" s="39"/>
     </row>
     <row r="113" spans="1:13" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A113" s="35">
@@ -3875,17 +3860,17 @@
       <c r="D113" s="38">
         <v>6417.93</v>
       </c>
-      <c r="E113" s="39">
-        <v>0</v>
-      </c>
-      <c r="F113" s="40"/>
-      <c r="G113" s="40"/>
-      <c r="H113" s="40"/>
-      <c r="I113" s="40"/>
-      <c r="J113" s="40"/>
-      <c r="K113" s="40"/>
-      <c r="L113" s="40"/>
-      <c r="M113" s="40"/>
+      <c r="E113" s="37">
+        <v>106053</v>
+      </c>
+      <c r="F113" s="39"/>
+      <c r="G113" s="39"/>
+      <c r="H113" s="39"/>
+      <c r="I113" s="39"/>
+      <c r="J113" s="39"/>
+      <c r="K113" s="39"/>
+      <c r="L113" s="39"/>
+      <c r="M113" s="39"/>
     </row>
     <row r="114" spans="1:13" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A114" s="35">
@@ -3900,17 +3885,17 @@
       <c r="D114" s="38">
         <v>6475.81</v>
       </c>
-      <c r="E114" s="39">
-        <v>0</v>
-      </c>
-      <c r="F114" s="40"/>
-      <c r="G114" s="40"/>
-      <c r="H114" s="40"/>
-      <c r="I114" s="40"/>
-      <c r="J114" s="40"/>
-      <c r="K114" s="40"/>
-      <c r="L114" s="40"/>
-      <c r="M114" s="40"/>
+      <c r="E114" s="37">
+        <v>56738</v>
+      </c>
+      <c r="F114" s="39"/>
+      <c r="G114" s="39"/>
+      <c r="H114" s="39"/>
+      <c r="I114" s="39"/>
+      <c r="J114" s="39"/>
+      <c r="K114" s="39"/>
+      <c r="L114" s="39"/>
+      <c r="M114" s="39"/>
     </row>
     <row r="115" spans="1:13" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A115" s="35">
@@ -3925,17 +3910,17 @@
       <c r="D115" s="38">
         <v>6475.63</v>
       </c>
-      <c r="E115" s="39">
-        <v>0</v>
-      </c>
-      <c r="F115" s="40"/>
-      <c r="G115" s="40"/>
-      <c r="H115" s="40"/>
-      <c r="I115" s="40"/>
-      <c r="J115" s="40"/>
-      <c r="K115" s="40"/>
-      <c r="L115" s="40"/>
-      <c r="M115" s="40"/>
+      <c r="E115" s="37">
+        <v>751330</v>
+      </c>
+      <c r="F115" s="39"/>
+      <c r="G115" s="39"/>
+      <c r="H115" s="39"/>
+      <c r="I115" s="39"/>
+      <c r="J115" s="39"/>
+      <c r="K115" s="39"/>
+      <c r="L115" s="39"/>
+      <c r="M115" s="39"/>
     </row>
     <row r="116" spans="1:13" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A116" s="35">
@@ -3950,17 +3935,17 @@
       <c r="D116" s="38">
         <v>6475.63</v>
       </c>
-      <c r="E116" s="39">
-        <v>0</v>
-      </c>
-      <c r="F116" s="40"/>
-      <c r="G116" s="40"/>
-      <c r="H116" s="40"/>
-      <c r="I116" s="40"/>
-      <c r="J116" s="40"/>
-      <c r="K116" s="40"/>
-      <c r="L116" s="40"/>
-      <c r="M116" s="40"/>
+      <c r="E116" s="37">
+        <v>0</v>
+      </c>
+      <c r="F116" s="39"/>
+      <c r="G116" s="39"/>
+      <c r="H116" s="39"/>
+      <c r="I116" s="39"/>
+      <c r="J116" s="39"/>
+      <c r="K116" s="39"/>
+      <c r="L116" s="39"/>
+      <c r="M116" s="39"/>
     </row>
     <row r="117" spans="1:13" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A117" s="35">
@@ -3975,17 +3960,17 @@
       <c r="D117" s="38">
         <v>6475.63</v>
       </c>
-      <c r="E117" s="39">
-        <v>0</v>
-      </c>
-      <c r="F117" s="40"/>
-      <c r="G117" s="40"/>
-      <c r="H117" s="40"/>
-      <c r="I117" s="40"/>
-      <c r="J117" s="40"/>
-      <c r="K117" s="40"/>
-      <c r="L117" s="40"/>
-      <c r="M117" s="40"/>
+      <c r="E117" s="37">
+        <v>0</v>
+      </c>
+      <c r="F117" s="39"/>
+      <c r="G117" s="39"/>
+      <c r="H117" s="39"/>
+      <c r="I117" s="39"/>
+      <c r="J117" s="39"/>
+      <c r="K117" s="39"/>
+      <c r="L117" s="39"/>
+      <c r="M117" s="39"/>
     </row>
     <row r="118" spans="1:13" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A118" s="35">
@@ -4000,17 +3985,17 @@
       <c r="D118" s="38">
         <v>6615.03</v>
       </c>
-      <c r="E118" s="39">
-        <v>0</v>
-      </c>
-      <c r="F118" s="40"/>
-      <c r="G118" s="40"/>
-      <c r="H118" s="40"/>
-      <c r="I118" s="40"/>
-      <c r="J118" s="40"/>
-      <c r="K118" s="40"/>
-      <c r="L118" s="40"/>
-      <c r="M118" s="40"/>
+      <c r="E118" s="37">
+        <v>967896</v>
+      </c>
+      <c r="F118" s="39"/>
+      <c r="G118" s="39"/>
+      <c r="H118" s="39"/>
+      <c r="I118" s="39"/>
+      <c r="J118" s="39"/>
+      <c r="K118" s="39"/>
+      <c r="L118" s="39"/>
+      <c r="M118" s="39"/>
     </row>
     <row r="119" spans="1:13" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A119" s="35">
@@ -4025,17 +4010,17 @@
       <c r="D119" s="38">
         <v>6616.03</v>
       </c>
-      <c r="E119" s="39">
-        <v>0</v>
-      </c>
-      <c r="F119" s="40"/>
-      <c r="G119" s="40"/>
-      <c r="H119" s="40"/>
-      <c r="I119" s="40"/>
-      <c r="J119" s="40"/>
-      <c r="K119" s="40"/>
-      <c r="L119" s="40"/>
-      <c r="M119" s="40"/>
+      <c r="E119" s="37">
+        <v>76540</v>
+      </c>
+      <c r="F119" s="39"/>
+      <c r="G119" s="39"/>
+      <c r="H119" s="39"/>
+      <c r="I119" s="39"/>
+      <c r="J119" s="39"/>
+      <c r="K119" s="39"/>
+      <c r="L119" s="39"/>
+      <c r="M119" s="39"/>
     </row>
     <row r="120" spans="1:13" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A120" s="35">
@@ -4050,17 +4035,17 @@
       <c r="D120" s="38">
         <v>6690.9</v>
       </c>
-      <c r="E120" s="39">
-        <v>0</v>
-      </c>
-      <c r="F120" s="40"/>
-      <c r="G120" s="40"/>
-      <c r="H120" s="40"/>
-      <c r="I120" s="40"/>
-      <c r="J120" s="40"/>
-      <c r="K120" s="40"/>
-      <c r="L120" s="40"/>
-      <c r="M120" s="40"/>
+      <c r="E120" s="37">
+        <v>178187</v>
+      </c>
+      <c r="F120" s="39"/>
+      <c r="G120" s="39"/>
+      <c r="H120" s="39"/>
+      <c r="I120" s="39"/>
+      <c r="J120" s="39"/>
+      <c r="K120" s="39"/>
+      <c r="L120" s="39"/>
+      <c r="M120" s="39"/>
     </row>
     <row r="121" spans="1:13" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A121" s="35">
@@ -4075,17 +4060,17 @@
       <c r="D121" s="38">
         <v>6598.87</v>
       </c>
-      <c r="E121" s="39">
-        <v>13471723</v>
-      </c>
-      <c r="F121" s="40"/>
-      <c r="G121" s="40"/>
-      <c r="H121" s="40"/>
-      <c r="I121" s="40"/>
-      <c r="J121" s="40"/>
-      <c r="K121" s="40"/>
-      <c r="L121" s="40"/>
-      <c r="M121" s="40"/>
+      <c r="E121" s="37">
+        <v>0</v>
+      </c>
+      <c r="F121" s="39"/>
+      <c r="G121" s="39"/>
+      <c r="H121" s="39"/>
+      <c r="I121" s="39"/>
+      <c r="J121" s="39"/>
+      <c r="K121" s="39"/>
+      <c r="L121" s="39"/>
+      <c r="M121" s="39"/>
     </row>
     <row r="122" spans="1:13" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A122" s="35">
@@ -4100,17 +4085,17 @@
       <c r="D122" s="38">
         <v>6599.87</v>
       </c>
-      <c r="E122" s="39">
-        <v>0</v>
-      </c>
-      <c r="F122" s="40"/>
-      <c r="G122" s="40"/>
-      <c r="H122" s="40"/>
-      <c r="I122" s="40"/>
-      <c r="J122" s="40"/>
-      <c r="K122" s="40"/>
-      <c r="L122" s="40"/>
-      <c r="M122" s="40"/>
+      <c r="E122" s="37">
+        <v>0</v>
+      </c>
+      <c r="F122" s="39"/>
+      <c r="G122" s="39"/>
+      <c r="H122" s="39"/>
+      <c r="I122" s="39"/>
+      <c r="J122" s="39"/>
+      <c r="K122" s="39"/>
+      <c r="L122" s="39"/>
+      <c r="M122" s="39"/>
     </row>
     <row r="123" spans="1:13" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A123" s="35">
@@ -4125,17 +4110,17 @@
       <c r="D123" s="38">
         <v>6600.87</v>
       </c>
-      <c r="E123" s="39">
-        <v>0</v>
-      </c>
-      <c r="F123" s="40"/>
-      <c r="G123" s="40"/>
-      <c r="H123" s="40"/>
-      <c r="I123" s="40"/>
-      <c r="J123" s="40"/>
-      <c r="K123" s="40"/>
-      <c r="L123" s="40"/>
-      <c r="M123" s="40"/>
+      <c r="E123" s="37">
+        <v>0</v>
+      </c>
+      <c r="F123" s="39"/>
+      <c r="G123" s="39"/>
+      <c r="H123" s="39"/>
+      <c r="I123" s="39"/>
+      <c r="J123" s="39"/>
+      <c r="K123" s="39"/>
+      <c r="L123" s="39"/>
+      <c r="M123" s="39"/>
     </row>
     <row r="124" spans="1:13" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A124" s="35">
@@ -4150,17 +4135,17 @@
       <c r="D124" s="38">
         <v>6601.87</v>
       </c>
-      <c r="E124" s="39">
-        <v>0</v>
-      </c>
-      <c r="F124" s="40"/>
-      <c r="G124" s="40"/>
-      <c r="H124" s="40"/>
-      <c r="I124" s="40"/>
-      <c r="J124" s="40"/>
-      <c r="K124" s="40"/>
-      <c r="L124" s="40"/>
-      <c r="M124" s="40"/>
+      <c r="E124" s="37">
+        <v>0</v>
+      </c>
+      <c r="F124" s="39"/>
+      <c r="G124" s="39"/>
+      <c r="H124" s="39"/>
+      <c r="I124" s="39"/>
+      <c r="J124" s="39"/>
+      <c r="K124" s="39"/>
+      <c r="L124" s="39"/>
+      <c r="M124" s="39"/>
     </row>
     <row r="125" spans="1:13" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A125" s="35">
@@ -4175,17 +4160,17 @@
       <c r="D125" s="38">
         <v>6939.99</v>
       </c>
-      <c r="E125" s="39">
-        <v>0</v>
-      </c>
-      <c r="F125" s="40"/>
-      <c r="G125" s="40"/>
-      <c r="H125" s="40"/>
-      <c r="I125" s="40"/>
-      <c r="J125" s="40"/>
-      <c r="K125" s="40"/>
-      <c r="L125" s="40"/>
-      <c r="M125" s="40"/>
+      <c r="E125" s="37">
+        <v>895918</v>
+      </c>
+      <c r="F125" s="39"/>
+      <c r="G125" s="39"/>
+      <c r="H125" s="39"/>
+      <c r="I125" s="39"/>
+      <c r="J125" s="39"/>
+      <c r="K125" s="39"/>
+      <c r="L125" s="39"/>
+      <c r="M125" s="39"/>
     </row>
     <row r="126" spans="1:13" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A126" s="35">
@@ -4200,17 +4185,17 @@
       <c r="D126" s="38">
         <v>6939.99</v>
       </c>
-      <c r="E126" s="39">
-        <v>0</v>
-      </c>
-      <c r="F126" s="40"/>
-      <c r="G126" s="40"/>
-      <c r="H126" s="40"/>
-      <c r="I126" s="40"/>
-      <c r="J126" s="40"/>
-      <c r="K126" s="40"/>
-      <c r="L126" s="40"/>
-      <c r="M126" s="40"/>
+      <c r="E126" s="37">
+        <v>0</v>
+      </c>
+      <c r="F126" s="39"/>
+      <c r="G126" s="39"/>
+      <c r="H126" s="39"/>
+      <c r="I126" s="39"/>
+      <c r="J126" s="39"/>
+      <c r="K126" s="39"/>
+      <c r="L126" s="39"/>
+      <c r="M126" s="39"/>
     </row>
     <row r="127" spans="1:13" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A127" s="35">
@@ -4225,17 +4210,17 @@
       <c r="D127" s="38">
         <v>7384.56</v>
       </c>
-      <c r="E127" s="39">
-        <v>0</v>
-      </c>
-      <c r="F127" s="40"/>
-      <c r="G127" s="40"/>
-      <c r="H127" s="40"/>
-      <c r="I127" s="40"/>
-      <c r="J127" s="40"/>
-      <c r="K127" s="40"/>
-      <c r="L127" s="40"/>
-      <c r="M127" s="40"/>
+      <c r="E127" s="37">
+        <v>410192</v>
+      </c>
+      <c r="F127" s="39"/>
+      <c r="G127" s="39"/>
+      <c r="H127" s="39"/>
+      <c r="I127" s="39"/>
+      <c r="J127" s="39"/>
+      <c r="K127" s="39"/>
+      <c r="L127" s="39"/>
+      <c r="M127" s="39"/>
     </row>
     <row r="128" spans="1:13" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A128" s="35">
@@ -4250,17 +4235,17 @@
       <c r="D128" s="38">
         <v>7490.05</v>
       </c>
-      <c r="E128" s="39">
-        <v>0</v>
-      </c>
-      <c r="F128" s="40"/>
-      <c r="G128" s="40"/>
-      <c r="H128" s="40"/>
-      <c r="I128" s="40"/>
-      <c r="J128" s="40"/>
-      <c r="K128" s="40"/>
-      <c r="L128" s="40"/>
-      <c r="M128" s="40"/>
+      <c r="E128" s="37">
+        <v>193093</v>
+      </c>
+      <c r="F128" s="39"/>
+      <c r="G128" s="39"/>
+      <c r="H128" s="39"/>
+      <c r="I128" s="39"/>
+      <c r="J128" s="39"/>
+      <c r="K128" s="39"/>
+      <c r="L128" s="39"/>
+      <c r="M128" s="39"/>
     </row>
     <row r="129" spans="1:13" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A129" s="35">
@@ -4275,17 +4260,17 @@
       <c r="D129" s="38">
         <v>7498</v>
       </c>
-      <c r="E129" s="39">
-        <v>0</v>
-      </c>
-      <c r="F129" s="40"/>
-      <c r="G129" s="40"/>
-      <c r="H129" s="40"/>
-      <c r="I129" s="40"/>
-      <c r="J129" s="40"/>
-      <c r="K129" s="40"/>
-      <c r="L129" s="40"/>
-      <c r="M129" s="40"/>
+      <c r="E129" s="37">
+        <v>181254</v>
+      </c>
+      <c r="F129" s="39"/>
+      <c r="G129" s="39"/>
+      <c r="H129" s="39"/>
+      <c r="I129" s="39"/>
+      <c r="J129" s="39"/>
+      <c r="K129" s="39"/>
+      <c r="L129" s="39"/>
+      <c r="M129" s="39"/>
     </row>
     <row r="130" spans="1:13" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A130" s="35">
@@ -4300,17 +4285,17 @@
       <c r="D130" s="38">
         <v>7498</v>
       </c>
-      <c r="E130" s="39">
-        <v>0</v>
-      </c>
-      <c r="F130" s="40"/>
-      <c r="G130" s="40"/>
-      <c r="H130" s="40"/>
-      <c r="I130" s="40"/>
-      <c r="J130" s="40"/>
-      <c r="K130" s="40"/>
-      <c r="L130" s="40"/>
-      <c r="M130" s="40"/>
+      <c r="E130" s="37">
+        <v>0</v>
+      </c>
+      <c r="F130" s="39"/>
+      <c r="G130" s="39"/>
+      <c r="H130" s="39"/>
+      <c r="I130" s="39"/>
+      <c r="J130" s="39"/>
+      <c r="K130" s="39"/>
+      <c r="L130" s="39"/>
+      <c r="M130" s="39"/>
     </row>
     <row r="131" spans="1:13" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A131" s="35">
@@ -4325,17 +4310,17 @@
       <c r="D131" s="38">
         <v>7498</v>
       </c>
-      <c r="E131" s="39">
-        <v>0</v>
-      </c>
-      <c r="F131" s="40"/>
-      <c r="G131" s="40"/>
-      <c r="H131" s="40"/>
-      <c r="I131" s="40"/>
-      <c r="J131" s="40"/>
-      <c r="K131" s="40"/>
-      <c r="L131" s="40"/>
-      <c r="M131" s="40"/>
+      <c r="E131" s="37">
+        <v>0</v>
+      </c>
+      <c r="F131" s="39"/>
+      <c r="G131" s="39"/>
+      <c r="H131" s="39"/>
+      <c r="I131" s="39"/>
+      <c r="J131" s="39"/>
+      <c r="K131" s="39"/>
+      <c r="L131" s="39"/>
+      <c r="M131" s="39"/>
     </row>
     <row r="132" spans="1:13" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A132" s="35">
@@ -4350,17 +4335,17 @@
       <c r="D132" s="38">
         <v>7822.24</v>
       </c>
-      <c r="E132" s="39">
-        <v>0</v>
-      </c>
-      <c r="F132" s="40"/>
-      <c r="G132" s="40"/>
-      <c r="H132" s="40"/>
-      <c r="I132" s="40"/>
-      <c r="J132" s="40"/>
-      <c r="K132" s="40"/>
-      <c r="L132" s="40"/>
-      <c r="M132" s="40"/>
+      <c r="E132" s="37">
+        <v>56247</v>
+      </c>
+      <c r="F132" s="39"/>
+      <c r="G132" s="39"/>
+      <c r="H132" s="39"/>
+      <c r="I132" s="39"/>
+      <c r="J132" s="39"/>
+      <c r="K132" s="39"/>
+      <c r="L132" s="39"/>
+      <c r="M132" s="39"/>
     </row>
     <row r="133" spans="1:13" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A133" s="35">
@@ -4375,17 +4360,17 @@
       <c r="D133" s="38">
         <v>7643.15</v>
       </c>
-      <c r="E133" s="39">
-        <v>0</v>
-      </c>
-      <c r="F133" s="40"/>
-      <c r="G133" s="40"/>
-      <c r="H133" s="40"/>
-      <c r="I133" s="40"/>
-      <c r="J133" s="40"/>
-      <c r="K133" s="40"/>
-      <c r="L133" s="40"/>
-      <c r="M133" s="40"/>
+      <c r="E133" s="37">
+        <v>0</v>
+      </c>
+      <c r="F133" s="39"/>
+      <c r="G133" s="39"/>
+      <c r="H133" s="39"/>
+      <c r="I133" s="39"/>
+      <c r="J133" s="39"/>
+      <c r="K133" s="39"/>
+      <c r="L133" s="39"/>
+      <c r="M133" s="39"/>
     </row>
     <row r="134" spans="1:13" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A134" s="35">
@@ -4400,17 +4385,17 @@
       <c r="D134" s="38">
         <v>7844</v>
       </c>
-      <c r="E134" s="39">
-        <v>0</v>
-      </c>
-      <c r="F134" s="40"/>
-      <c r="G134" s="40"/>
-      <c r="H134" s="40"/>
-      <c r="I134" s="40"/>
-      <c r="J134" s="40"/>
-      <c r="K134" s="40"/>
-      <c r="L134" s="40"/>
-      <c r="M134" s="40"/>
+      <c r="E134" s="37">
+        <v>617587</v>
+      </c>
+      <c r="F134" s="39"/>
+      <c r="G134" s="39"/>
+      <c r="H134" s="39"/>
+      <c r="I134" s="39"/>
+      <c r="J134" s="39"/>
+      <c r="K134" s="39"/>
+      <c r="L134" s="39"/>
+      <c r="M134" s="39"/>
     </row>
     <row r="135" spans="1:13" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A135" s="35">
@@ -4425,17 +4410,17 @@
       <c r="D135" s="38">
         <v>7981.41</v>
       </c>
-      <c r="E135" s="39">
-        <v>0</v>
-      </c>
-      <c r="F135" s="40"/>
-      <c r="G135" s="40"/>
-      <c r="H135" s="40"/>
-      <c r="I135" s="40"/>
-      <c r="J135" s="40"/>
-      <c r="K135" s="40"/>
-      <c r="L135" s="40"/>
-      <c r="M135" s="40"/>
+      <c r="E135" s="37">
+        <v>489774</v>
+      </c>
+      <c r="F135" s="39"/>
+      <c r="G135" s="39"/>
+      <c r="H135" s="39"/>
+      <c r="I135" s="39"/>
+      <c r="J135" s="39"/>
+      <c r="K135" s="39"/>
+      <c r="L135" s="39"/>
+      <c r="M135" s="39"/>
     </row>
     <row r="136" spans="1:13" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A136" s="35">
@@ -4450,17 +4435,17 @@
       <c r="D136" s="38">
         <v>7493.18</v>
       </c>
-      <c r="E136" s="39">
-        <v>0</v>
-      </c>
-      <c r="F136" s="40"/>
-      <c r="G136" s="40"/>
-      <c r="H136" s="40"/>
-      <c r="I136" s="40"/>
-      <c r="J136" s="40"/>
-      <c r="K136" s="40"/>
-      <c r="L136" s="40"/>
-      <c r="M136" s="40"/>
+      <c r="E136" s="37">
+        <v>0</v>
+      </c>
+      <c r="F136" s="39"/>
+      <c r="G136" s="39"/>
+      <c r="H136" s="39"/>
+      <c r="I136" s="39"/>
+      <c r="J136" s="39"/>
+      <c r="K136" s="39"/>
+      <c r="L136" s="39"/>
+      <c r="M136" s="39"/>
     </row>
     <row r="137" spans="1:13" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A137" s="35">
@@ -4475,17 +4460,17 @@
       <c r="D137" s="38">
         <v>7493.18</v>
       </c>
-      <c r="E137" s="39">
-        <v>0</v>
-      </c>
-      <c r="F137" s="40"/>
-      <c r="G137" s="40"/>
-      <c r="H137" s="40"/>
-      <c r="I137" s="40"/>
-      <c r="J137" s="40"/>
-      <c r="K137" s="40"/>
-      <c r="L137" s="40"/>
-      <c r="M137" s="40"/>
+      <c r="E137" s="37">
+        <v>0</v>
+      </c>
+      <c r="F137" s="39"/>
+      <c r="G137" s="39"/>
+      <c r="H137" s="39"/>
+      <c r="I137" s="39"/>
+      <c r="J137" s="39"/>
+      <c r="K137" s="39"/>
+      <c r="L137" s="39"/>
+      <c r="M137" s="39"/>
     </row>
     <row r="138" spans="1:13" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A138" s="35">
@@ -4500,17 +4485,17 @@
       <c r="D138" s="38">
         <v>7493.18</v>
       </c>
-      <c r="E138" s="39">
-        <v>0</v>
-      </c>
-      <c r="F138" s="40"/>
-      <c r="G138" s="40"/>
-      <c r="H138" s="40"/>
-      <c r="I138" s="40"/>
-      <c r="J138" s="40"/>
-      <c r="K138" s="40"/>
-      <c r="L138" s="40"/>
-      <c r="M138" s="40"/>
+      <c r="E138" s="37">
+        <v>0</v>
+      </c>
+      <c r="F138" s="39"/>
+      <c r="G138" s="39"/>
+      <c r="H138" s="39"/>
+      <c r="I138" s="39"/>
+      <c r="J138" s="39"/>
+      <c r="K138" s="39"/>
+      <c r="L138" s="39"/>
+      <c r="M138" s="39"/>
     </row>
     <row r="139" spans="1:13" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A139" s="35">
@@ -4525,17 +4510,17 @@
       <c r="D139" s="38">
         <v>7516.04</v>
       </c>
-      <c r="E139" s="39">
-        <v>0</v>
-      </c>
-      <c r="F139" s="40"/>
-      <c r="G139" s="40"/>
-      <c r="H139" s="40"/>
-      <c r="I139" s="40"/>
-      <c r="J139" s="40"/>
-      <c r="K139" s="40"/>
-      <c r="L139" s="40"/>
-      <c r="M139" s="40"/>
+      <c r="E139" s="37">
+        <v>122049</v>
+      </c>
+      <c r="F139" s="39"/>
+      <c r="G139" s="39"/>
+      <c r="H139" s="39"/>
+      <c r="I139" s="39"/>
+      <c r="J139" s="39"/>
+      <c r="K139" s="39"/>
+      <c r="L139" s="39"/>
+      <c r="M139" s="39"/>
     </row>
     <row r="140" spans="1:13" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A140" s="35">
@@ -4550,17 +4535,17 @@
       <c r="D140" s="38">
         <v>7271.66</v>
       </c>
-      <c r="E140" s="39">
-        <v>0</v>
-      </c>
-      <c r="F140" s="40"/>
-      <c r="G140" s="40"/>
-      <c r="H140" s="40"/>
-      <c r="I140" s="40"/>
-      <c r="J140" s="40"/>
-      <c r="K140" s="40"/>
-      <c r="L140" s="40"/>
-      <c r="M140" s="40"/>
+      <c r="E140" s="37">
+        <v>0</v>
+      </c>
+      <c r="F140" s="39"/>
+      <c r="G140" s="39"/>
+      <c r="H140" s="39"/>
+      <c r="I140" s="39"/>
+      <c r="J140" s="39"/>
+      <c r="K140" s="39"/>
+      <c r="L140" s="39"/>
+      <c r="M140" s="39"/>
     </row>
     <row r="141" spans="1:13" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A141" s="35">
@@ -4575,17 +4560,17 @@
       <c r="D141" s="38">
         <v>7208.95</v>
       </c>
-      <c r="E141" s="39">
-        <v>0</v>
-      </c>
-      <c r="F141" s="40"/>
-      <c r="G141" s="40"/>
-      <c r="H141" s="40"/>
-      <c r="I141" s="40"/>
-      <c r="J141" s="40"/>
-      <c r="K141" s="40"/>
-      <c r="L141" s="40"/>
-      <c r="M141" s="40"/>
+      <c r="E141" s="37">
+        <v>0</v>
+      </c>
+      <c r="F141" s="39"/>
+      <c r="G141" s="39"/>
+      <c r="H141" s="39"/>
+      <c r="I141" s="39"/>
+      <c r="J141" s="39"/>
+      <c r="K141" s="39"/>
+      <c r="L141" s="39"/>
+      <c r="M141" s="39"/>
     </row>
     <row r="142" spans="1:13" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A142" s="35">
@@ -4600,17 +4585,17 @@
       <c r="D142" s="38">
         <v>7209.95</v>
       </c>
-      <c r="E142" s="39">
-        <v>0</v>
-      </c>
-      <c r="F142" s="40"/>
-      <c r="G142" s="40"/>
-      <c r="H142" s="40"/>
-      <c r="I142" s="40"/>
-      <c r="J142" s="40"/>
-      <c r="K142" s="40"/>
-      <c r="L142" s="40"/>
-      <c r="M142" s="40"/>
+      <c r="E142" s="37">
+        <v>4517372</v>
+      </c>
+      <c r="F142" s="39"/>
+      <c r="G142" s="39"/>
+      <c r="H142" s="39"/>
+      <c r="I142" s="39"/>
+      <c r="J142" s="39"/>
+      <c r="K142" s="39"/>
+      <c r="L142" s="39"/>
+      <c r="M142" s="39"/>
     </row>
     <row r="143" spans="1:13" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A143" s="35">
@@ -4625,17 +4610,17 @@
       <c r="D143" s="38">
         <v>7847.71</v>
       </c>
-      <c r="E143" s="39">
-        <v>0</v>
-      </c>
-      <c r="F143" s="40"/>
-      <c r="G143" s="40"/>
-      <c r="H143" s="40"/>
-      <c r="I143" s="40"/>
-      <c r="J143" s="40"/>
-      <c r="K143" s="40"/>
-      <c r="L143" s="40"/>
-      <c r="M143" s="40"/>
+      <c r="E143" s="37">
+        <v>4667317</v>
+      </c>
+      <c r="F143" s="39"/>
+      <c r="G143" s="39"/>
+      <c r="H143" s="39"/>
+      <c r="I143" s="39"/>
+      <c r="J143" s="39"/>
+      <c r="K143" s="39"/>
+      <c r="L143" s="39"/>
+      <c r="M143" s="39"/>
     </row>
     <row r="144" spans="1:13" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A144" s="35">
@@ -4650,17 +4635,17 @@
       <c r="D144" s="38">
         <v>8047.51</v>
       </c>
-      <c r="E144" s="39">
-        <v>0</v>
-      </c>
-      <c r="F144" s="40"/>
-      <c r="G144" s="40"/>
-      <c r="H144" s="40"/>
-      <c r="I144" s="40"/>
-      <c r="J144" s="40"/>
-      <c r="K144" s="40"/>
-      <c r="L144" s="40"/>
-      <c r="M144" s="40"/>
+      <c r="E144" s="37">
+        <v>1552818</v>
+      </c>
+      <c r="F144" s="39"/>
+      <c r="G144" s="39"/>
+      <c r="H144" s="39"/>
+      <c r="I144" s="39"/>
+      <c r="J144" s="39"/>
+      <c r="K144" s="39"/>
+      <c r="L144" s="39"/>
+      <c r="M144" s="39"/>
     </row>
     <row r="145" spans="1:13" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A145" s="35">
@@ -4675,17 +4660,17 @@
       <c r="D145" s="38">
         <v>8228.7000000000007</v>
       </c>
-      <c r="E145" s="39">
-        <v>0</v>
-      </c>
-      <c r="F145" s="40"/>
-      <c r="G145" s="40"/>
-      <c r="H145" s="40"/>
-      <c r="I145" s="40"/>
-      <c r="J145" s="40"/>
-      <c r="K145" s="40"/>
-      <c r="L145" s="40"/>
-      <c r="M145" s="40"/>
+      <c r="E145" s="37">
+        <v>161746</v>
+      </c>
+      <c r="F145" s="39"/>
+      <c r="G145" s="39"/>
+      <c r="H145" s="39"/>
+      <c r="I145" s="39"/>
+      <c r="J145" s="39"/>
+      <c r="K145" s="39"/>
+      <c r="L145" s="39"/>
+      <c r="M145" s="39"/>
     </row>
     <row r="146" spans="1:13" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A146" s="35">
@@ -4700,17 +4685,17 @@
       <c r="D146" s="38">
         <v>8185.3</v>
       </c>
-      <c r="E146" s="39">
-        <v>0</v>
-      </c>
-      <c r="F146" s="40"/>
-      <c r="G146" s="40"/>
-      <c r="H146" s="40"/>
-      <c r="I146" s="40"/>
-      <c r="J146" s="40"/>
-      <c r="K146" s="40"/>
-      <c r="L146" s="40"/>
-      <c r="M146" s="40"/>
+      <c r="E146" s="37">
+        <v>0</v>
+      </c>
+      <c r="F146" s="39"/>
+      <c r="G146" s="39"/>
+      <c r="H146" s="39"/>
+      <c r="I146" s="39"/>
+      <c r="J146" s="39"/>
+      <c r="K146" s="39"/>
+      <c r="L146" s="39"/>
+      <c r="M146" s="39"/>
     </row>
     <row r="147" spans="1:13" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A147" s="35">
@@ -4725,17 +4710,17 @@
       <c r="D147" s="38">
         <v>8476.15</v>
       </c>
-      <c r="E147" s="39">
-        <v>14703327</v>
-      </c>
-      <c r="F147" s="40"/>
-      <c r="G147" s="40"/>
-      <c r="H147" s="40"/>
-      <c r="I147" s="40"/>
-      <c r="J147" s="40"/>
-      <c r="K147" s="40"/>
-      <c r="L147" s="40"/>
-      <c r="M147" s="40"/>
+      <c r="E147" s="37">
+        <v>837960</v>
+      </c>
+      <c r="F147" s="39"/>
+      <c r="G147" s="39"/>
+      <c r="H147" s="39"/>
+      <c r="I147" s="39"/>
+      <c r="J147" s="39"/>
+      <c r="K147" s="39"/>
+      <c r="L147" s="39"/>
+      <c r="M147" s="39"/>
     </row>
     <row r="148" spans="1:13" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A148" s="35">
@@ -4753,14 +4738,14 @@
       <c r="E148" s="37">
         <v>370630</v>
       </c>
-      <c r="F148" s="40"/>
-      <c r="G148" s="40"/>
-      <c r="H148" s="40"/>
-      <c r="I148" s="40"/>
-      <c r="J148" s="40"/>
-      <c r="K148" s="40"/>
-      <c r="L148" s="40"/>
-      <c r="M148" s="40"/>
+      <c r="F148" s="39"/>
+      <c r="G148" s="39"/>
+      <c r="H148" s="39"/>
+      <c r="I148" s="39"/>
+      <c r="J148" s="39"/>
+      <c r="K148" s="39"/>
+      <c r="L148" s="39"/>
+      <c r="M148" s="39"/>
     </row>
     <row r="149" spans="1:13" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A149" s="35">
@@ -4775,17 +4760,17 @@
       <c r="D149" s="38">
         <v>8801.49</v>
       </c>
-      <c r="E149" s="39">
-        <v>0</v>
-      </c>
-      <c r="F149" s="40"/>
-      <c r="G149" s="40"/>
-      <c r="H149" s="40"/>
-      <c r="I149" s="40"/>
-      <c r="J149" s="40"/>
-      <c r="K149" s="40"/>
-      <c r="L149" s="40"/>
-      <c r="M149" s="40"/>
+      <c r="E149" s="37">
+        <v>0</v>
+      </c>
+      <c r="F149" s="39"/>
+      <c r="G149" s="39"/>
+      <c r="H149" s="39"/>
+      <c r="I149" s="39"/>
+      <c r="J149" s="39"/>
+      <c r="K149" s="39"/>
+      <c r="L149" s="39"/>
+      <c r="M149" s="39"/>
     </row>
     <row r="150" spans="1:13" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A150" s="35">
@@ -4803,14 +4788,14 @@
       <c r="E150" s="37">
         <v>981658</v>
       </c>
-      <c r="F150" s="40"/>
-      <c r="G150" s="40"/>
-      <c r="H150" s="40"/>
-      <c r="I150" s="40"/>
-      <c r="J150" s="40"/>
-      <c r="K150" s="40"/>
-      <c r="L150" s="40"/>
-      <c r="M150" s="40"/>
+      <c r="F150" s="39"/>
+      <c r="G150" s="39"/>
+      <c r="H150" s="39"/>
+      <c r="I150" s="39"/>
+      <c r="J150" s="39"/>
+      <c r="K150" s="39"/>
+      <c r="L150" s="39"/>
+      <c r="M150" s="39"/>
     </row>
     <row r="151" spans="1:13" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A151" s="35">
@@ -4825,17 +4810,17 @@
       <c r="D151" s="38">
         <v>8160.59</v>
       </c>
-      <c r="E151" s="39">
-        <v>0</v>
-      </c>
-      <c r="F151" s="40"/>
-      <c r="G151" s="40"/>
-      <c r="H151" s="40"/>
-      <c r="I151" s="40"/>
-      <c r="J151" s="40"/>
-      <c r="K151" s="40"/>
-      <c r="L151" s="40"/>
-      <c r="M151" s="40"/>
+      <c r="E151" s="37">
+        <v>0</v>
+      </c>
+      <c r="F151" s="39"/>
+      <c r="G151" s="39"/>
+      <c r="H151" s="39"/>
+      <c r="I151" s="39"/>
+      <c r="J151" s="39"/>
+      <c r="K151" s="39"/>
+      <c r="L151" s="39"/>
+      <c r="M151" s="39"/>
     </row>
     <row r="152" spans="1:13" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A152" s="35">
@@ -4853,14 +4838,14 @@
       <c r="E152" s="37">
         <v>-1798870</v>
       </c>
-      <c r="F152" s="40"/>
-      <c r="G152" s="40"/>
-      <c r="H152" s="40"/>
-      <c r="I152" s="40"/>
-      <c r="J152" s="40"/>
-      <c r="K152" s="40"/>
-      <c r="L152" s="40"/>
-      <c r="M152" s="40"/>
+      <c r="F152" s="39"/>
+      <c r="G152" s="39"/>
+      <c r="H152" s="39"/>
+      <c r="I152" s="39"/>
+      <c r="J152" s="39"/>
+      <c r="K152" s="39"/>
+      <c r="L152" s="39"/>
+      <c r="M152" s="39"/>
     </row>
     <row r="153" spans="1:13" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A153" s="35">
@@ -4878,28 +4863,28 @@
       <c r="E153" s="37">
         <v>2043292</v>
       </c>
-      <c r="F153" s="41">
+      <c r="F153" s="40">
         <v>12949860</v>
       </c>
-      <c r="G153" s="41">
+      <c r="G153" s="40">
         <v>13594870</v>
       </c>
-      <c r="H153" s="41">
+      <c r="H153" s="40">
         <v>20767620</v>
       </c>
-      <c r="I153" s="41">
+      <c r="I153" s="40">
         <v>27353485</v>
       </c>
-      <c r="J153" s="41">
+      <c r="J153" s="40">
         <v>21735745</v>
       </c>
-      <c r="K153" s="41">
+      <c r="K153" s="40">
         <v>13521425</v>
       </c>
-      <c r="L153" s="41">
+      <c r="L153" s="40">
         <v>15501550</v>
       </c>
-      <c r="M153" s="41">
+      <c r="M153" s="40">
         <v>7250270</v>
       </c>
     </row>
@@ -4919,28 +4904,28 @@
       <c r="E154" s="37">
         <v>0</v>
       </c>
-      <c r="F154" s="41">
+      <c r="F154" s="40">
         <v>12127600</v>
       </c>
-      <c r="G154" s="41">
+      <c r="G154" s="40">
         <v>12434900</v>
       </c>
-      <c r="H154" s="41">
+      <c r="H154" s="40">
         <v>19299400</v>
       </c>
-      <c r="I154" s="41">
+      <c r="I154" s="40">
         <v>26302990</v>
       </c>
-      <c r="J154" s="41">
+      <c r="J154" s="40">
         <v>21467115</v>
       </c>
-      <c r="K154" s="41">
+      <c r="K154" s="40">
         <v>13204750</v>
       </c>
-      <c r="L154" s="41">
+      <c r="L154" s="40">
         <v>24122150</v>
       </c>
-      <c r="M154" s="41">
+      <c r="M154" s="40">
         <v>8983650</v>
       </c>
     </row>
@@ -4960,28 +4945,28 @@
       <c r="E155" s="37">
         <v>1438756</v>
       </c>
-      <c r="F155" s="41">
+      <c r="F155" s="40">
         <v>12931670</v>
       </c>
-      <c r="G155" s="41">
+      <c r="G155" s="40">
         <v>12744060</v>
       </c>
-      <c r="H155" s="41">
+      <c r="H155" s="40">
         <v>20319260</v>
       </c>
-      <c r="I155" s="41">
+      <c r="I155" s="40">
         <v>27594910</v>
       </c>
-      <c r="J155" s="41">
+      <c r="J155" s="40">
         <v>29644530</v>
       </c>
-      <c r="K155" s="41">
+      <c r="K155" s="40">
         <v>23024190</v>
       </c>
-      <c r="L155" s="41">
+      <c r="L155" s="40">
         <v>27438530</v>
       </c>
-      <c r="M155" s="41">
+      <c r="M155" s="40">
         <v>10218090</v>
       </c>
     </row>
@@ -5001,28 +4986,28 @@
       <c r="E156" s="37">
         <v>2767377</v>
       </c>
-      <c r="F156" s="41">
+      <c r="F156" s="40">
         <v>13741690</v>
       </c>
-      <c r="G156" s="41">
+      <c r="G156" s="40">
         <v>13776200</v>
       </c>
-      <c r="H156" s="41">
+      <c r="H156" s="40">
         <v>21709900</v>
       </c>
-      <c r="I156" s="41">
+      <c r="I156" s="40">
         <v>29451950</v>
       </c>
-      <c r="J156" s="41">
+      <c r="J156" s="40">
         <v>31611390</v>
       </c>
-      <c r="K156" s="41">
+      <c r="K156" s="40">
         <v>24287630</v>
       </c>
-      <c r="L156" s="41">
+      <c r="L156" s="40">
         <v>27906250</v>
       </c>
-      <c r="M156" s="41">
+      <c r="M156" s="40">
         <v>10218090</v>
       </c>
     </row>
@@ -5049,72 +5034,72 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:21" x14ac:dyDescent="0.45">
-      <c r="A1" s="45" t="s">
+      <c r="A1" s="46" t="s">
         <v>17</v>
       </c>
-      <c r="B1" s="45" t="s">
+      <c r="B1" s="46" t="s">
         <v>16</v>
       </c>
-      <c r="C1" s="45" t="s">
+      <c r="C1" s="46" t="s">
         <v>18</v>
       </c>
-      <c r="D1" s="45" t="s">
+      <c r="D1" s="46" t="s">
         <v>19</v>
       </c>
-      <c r="E1" s="49" t="s">
+      <c r="E1" s="56" t="s">
         <v>20</v>
       </c>
-      <c r="F1" s="53" t="s">
+      <c r="F1" s="49" t="s">
         <v>21</v>
       </c>
-      <c r="G1" s="54"/>
-      <c r="H1" s="54"/>
-      <c r="I1" s="54"/>
-      <c r="J1" s="54"/>
-      <c r="K1" s="54"/>
-      <c r="L1" s="48">
+      <c r="G1" s="50"/>
+      <c r="H1" s="50"/>
+      <c r="I1" s="50"/>
+      <c r="J1" s="50"/>
+      <c r="K1" s="50"/>
+      <c r="L1" s="54">
         <v>0.7</v>
       </c>
-      <c r="M1" s="45" t="s">
+      <c r="M1" s="46" t="s">
         <v>22</v>
       </c>
-      <c r="N1" s="51"/>
-      <c r="O1" s="50"/>
-      <c r="P1" s="48">
+      <c r="N1" s="55"/>
+      <c r="O1" s="45"/>
+      <c r="P1" s="54">
         <v>0.25</v>
       </c>
-      <c r="Q1" s="50"/>
+      <c r="Q1" s="45"/>
       <c r="R1" s="1"/>
       <c r="S1" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="T1" s="45" t="s">
+      <c r="T1" s="46" t="s">
         <v>23</v>
       </c>
-      <c r="U1" s="50"/>
+      <c r="U1" s="45"/>
     </row>
     <row r="2" spans="1:21" x14ac:dyDescent="0.45">
-      <c r="A2" s="46"/>
-      <c r="B2" s="46"/>
-      <c r="C2" s="46"/>
-      <c r="D2" s="46"/>
-      <c r="E2" s="46"/>
-      <c r="F2" s="55"/>
-      <c r="G2" s="43"/>
-      <c r="H2" s="43"/>
-      <c r="I2" s="43"/>
-      <c r="J2" s="43"/>
-      <c r="K2" s="43"/>
-      <c r="L2" s="47"/>
+      <c r="A2" s="47"/>
+      <c r="B2" s="47"/>
+      <c r="C2" s="47"/>
+      <c r="D2" s="47"/>
+      <c r="E2" s="47"/>
+      <c r="F2" s="51"/>
+      <c r="G2" s="42"/>
+      <c r="H2" s="42"/>
+      <c r="I2" s="42"/>
+      <c r="J2" s="42"/>
+      <c r="K2" s="42"/>
+      <c r="L2" s="48"/>
       <c r="M2" s="3"/>
-      <c r="N2" s="48" t="s">
+      <c r="N2" s="54" t="s">
         <v>15</v>
       </c>
-      <c r="O2" s="50"/>
-      <c r="P2" s="45" t="s">
+      <c r="O2" s="45"/>
+      <c r="P2" s="46" t="s">
         <v>24</v>
       </c>
-      <c r="Q2" s="50"/>
+      <c r="Q2" s="45"/>
       <c r="R2" s="1"/>
       <c r="S2" s="4" t="s">
         <v>25</v>
@@ -5127,31 +5112,31 @@
       </c>
     </row>
     <row r="3" spans="1:21" x14ac:dyDescent="0.45">
-      <c r="A3" s="46"/>
-      <c r="B3" s="46"/>
-      <c r="C3" s="46"/>
-      <c r="D3" s="46"/>
-      <c r="E3" s="46"/>
-      <c r="F3" s="55"/>
-      <c r="G3" s="43"/>
-      <c r="H3" s="43"/>
-      <c r="I3" s="43"/>
-      <c r="J3" s="43"/>
-      <c r="K3" s="43"/>
-      <c r="L3" s="52">
+      <c r="A3" s="47"/>
+      <c r="B3" s="47"/>
+      <c r="C3" s="47"/>
+      <c r="D3" s="47"/>
+      <c r="E3" s="47"/>
+      <c r="F3" s="51"/>
+      <c r="G3" s="42"/>
+      <c r="H3" s="42"/>
+      <c r="I3" s="42"/>
+      <c r="J3" s="42"/>
+      <c r="K3" s="42"/>
+      <c r="L3" s="44">
         <v>17485</v>
       </c>
       <c r="M3" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="N3" s="52">
+      <c r="N3" s="44">
         <v>14760</v>
       </c>
-      <c r="O3" s="50"/>
-      <c r="P3" s="52">
+      <c r="O3" s="45"/>
+      <c r="P3" s="44">
         <v>8125</v>
       </c>
-      <c r="Q3" s="50"/>
+      <c r="Q3" s="45"/>
       <c r="R3" s="1"/>
       <c r="S3" s="4" t="s">
         <v>27</v>
@@ -5164,29 +5149,29 @@
       </c>
     </row>
     <row r="4" spans="1:21" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A4" s="47"/>
-      <c r="B4" s="47"/>
-      <c r="C4" s="47"/>
-      <c r="D4" s="47"/>
-      <c r="E4" s="47"/>
-      <c r="F4" s="55"/>
-      <c r="G4" s="43"/>
-      <c r="H4" s="43"/>
-      <c r="I4" s="43"/>
-      <c r="J4" s="43"/>
-      <c r="K4" s="43"/>
-      <c r="L4" s="47"/>
+      <c r="A4" s="48"/>
+      <c r="B4" s="48"/>
+      <c r="C4" s="48"/>
+      <c r="D4" s="48"/>
+      <c r="E4" s="48"/>
+      <c r="F4" s="51"/>
+      <c r="G4" s="42"/>
+      <c r="H4" s="42"/>
+      <c r="I4" s="42"/>
+      <c r="J4" s="42"/>
+      <c r="K4" s="42"/>
+      <c r="L4" s="48"/>
       <c r="M4" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="N4" s="56">
+      <c r="N4" s="52">
         <v>34705</v>
       </c>
-      <c r="O4" s="57"/>
-      <c r="P4" s="52">
+      <c r="O4" s="53"/>
+      <c r="P4" s="44">
         <v>13230</v>
       </c>
-      <c r="Q4" s="50"/>
+      <c r="Q4" s="45"/>
       <c r="R4" s="1"/>
       <c r="S4" s="4" t="s">
         <v>29</v>
@@ -5624,6 +5609,16 @@
     </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="A1:A4"/>
+    <mergeCell ref="D1:D4"/>
+    <mergeCell ref="B1:B4"/>
+    <mergeCell ref="L1:L2"/>
+    <mergeCell ref="E1:E4"/>
+    <mergeCell ref="T1:U1"/>
+    <mergeCell ref="N2:O2"/>
+    <mergeCell ref="P2:Q2"/>
+    <mergeCell ref="M1:O1"/>
+    <mergeCell ref="P1:Q1"/>
     <mergeCell ref="P4:Q4"/>
     <mergeCell ref="P3:Q3"/>
     <mergeCell ref="N3:O3"/>
@@ -5631,16 +5626,6 @@
     <mergeCell ref="F1:K4"/>
     <mergeCell ref="L3:L4"/>
     <mergeCell ref="N4:O4"/>
-    <mergeCell ref="T1:U1"/>
-    <mergeCell ref="N2:O2"/>
-    <mergeCell ref="P2:Q2"/>
-    <mergeCell ref="M1:O1"/>
-    <mergeCell ref="P1:Q1"/>
-    <mergeCell ref="A1:A4"/>
-    <mergeCell ref="D1:D4"/>
-    <mergeCell ref="B1:B4"/>
-    <mergeCell ref="L1:L2"/>
-    <mergeCell ref="E1:E4"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="E5:E10">

--- a/input.xlsx
+++ b/input.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\backup01\Desktop\병아리\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B42681A8-CF1E-4C8C-94D6-4ACC9C829703}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EEA04C5F-3847-4457-884C-FBC71E63C8A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="25490" yWindow="690" windowWidth="25820" windowHeight="13900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="INPUT" sheetId="1" r:id="rId1"/>
@@ -730,15 +730,22 @@
     <xf numFmtId="0" fontId="10" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="4" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="9" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="41" fontId="4" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -748,13 +755,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="9" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="백분율" xfId="2" builtinId="5"/>
@@ -1037,7 +1037,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M156"/>
+  <dimension ref="A1:M157"/>
   <sheetFormatPr defaultRowHeight="16" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="12" style="31" customWidth="1"/>
@@ -5009,6 +5009,47 @@
       </c>
       <c r="M156" s="40">
         <v>10218090</v>
+      </c>
+    </row>
+    <row r="157" spans="1:13" ht="16.5" x14ac:dyDescent="0.45">
+      <c r="A157" s="35">
+        <v>46188</v>
+      </c>
+      <c r="B157" s="36">
+        <v>156136900</v>
+      </c>
+      <c r="C157" s="37">
+        <v>-23930180</v>
+      </c>
+      <c r="D157" s="38">
+        <v>8545.98</v>
+      </c>
+      <c r="E157" s="37">
+        <v>2508340</v>
+      </c>
+      <c r="F157" s="40">
+        <v>14732070</v>
+      </c>
+      <c r="G157" s="40">
+        <v>15107360</v>
+      </c>
+      <c r="H157" s="40">
+        <v>23445060</v>
+      </c>
+      <c r="I157" s="40">
+        <v>30811210</v>
+      </c>
+      <c r="J157" s="40">
+        <v>33057510</v>
+      </c>
+      <c r="K157" s="40">
+        <v>24789530</v>
+      </c>
+      <c r="L157" s="40">
+        <v>14194160</v>
+      </c>
+      <c r="M157" s="40">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -5034,72 +5075,72 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:21" x14ac:dyDescent="0.45">
-      <c r="A1" s="46" t="s">
+      <c r="A1" s="44" t="s">
         <v>17</v>
       </c>
-      <c r="B1" s="46" t="s">
+      <c r="B1" s="44" t="s">
         <v>16</v>
       </c>
-      <c r="C1" s="46" t="s">
+      <c r="C1" s="44" t="s">
         <v>18</v>
       </c>
-      <c r="D1" s="46" t="s">
+      <c r="D1" s="44" t="s">
         <v>19</v>
       </c>
-      <c r="E1" s="56" t="s">
+      <c r="E1" s="48" t="s">
         <v>20</v>
       </c>
-      <c r="F1" s="49" t="s">
+      <c r="F1" s="52" t="s">
         <v>21</v>
       </c>
-      <c r="G1" s="50"/>
-      <c r="H1" s="50"/>
-      <c r="I1" s="50"/>
-      <c r="J1" s="50"/>
-      <c r="K1" s="50"/>
-      <c r="L1" s="54">
+      <c r="G1" s="53"/>
+      <c r="H1" s="53"/>
+      <c r="I1" s="53"/>
+      <c r="J1" s="53"/>
+      <c r="K1" s="53"/>
+      <c r="L1" s="47">
         <v>0.7</v>
       </c>
-      <c r="M1" s="46" t="s">
+      <c r="M1" s="44" t="s">
         <v>22</v>
       </c>
-      <c r="N1" s="55"/>
-      <c r="O1" s="45"/>
-      <c r="P1" s="54">
+      <c r="N1" s="50"/>
+      <c r="O1" s="49"/>
+      <c r="P1" s="47">
         <v>0.25</v>
       </c>
-      <c r="Q1" s="45"/>
+      <c r="Q1" s="49"/>
       <c r="R1" s="1"/>
       <c r="S1" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="T1" s="46" t="s">
+      <c r="T1" s="44" t="s">
         <v>23</v>
       </c>
-      <c r="U1" s="45"/>
+      <c r="U1" s="49"/>
     </row>
     <row r="2" spans="1:21" x14ac:dyDescent="0.45">
-      <c r="A2" s="47"/>
-      <c r="B2" s="47"/>
-      <c r="C2" s="47"/>
-      <c r="D2" s="47"/>
-      <c r="E2" s="47"/>
-      <c r="F2" s="51"/>
+      <c r="A2" s="45"/>
+      <c r="B2" s="45"/>
+      <c r="C2" s="45"/>
+      <c r="D2" s="45"/>
+      <c r="E2" s="45"/>
+      <c r="F2" s="54"/>
       <c r="G2" s="42"/>
       <c r="H2" s="42"/>
       <c r="I2" s="42"/>
       <c r="J2" s="42"/>
       <c r="K2" s="42"/>
-      <c r="L2" s="48"/>
+      <c r="L2" s="46"/>
       <c r="M2" s="3"/>
-      <c r="N2" s="54" t="s">
+      <c r="N2" s="47" t="s">
         <v>15</v>
       </c>
-      <c r="O2" s="45"/>
-      <c r="P2" s="46" t="s">
+      <c r="O2" s="49"/>
+      <c r="P2" s="44" t="s">
         <v>24</v>
       </c>
-      <c r="Q2" s="45"/>
+      <c r="Q2" s="49"/>
       <c r="R2" s="1"/>
       <c r="S2" s="4" t="s">
         <v>25</v>
@@ -5112,31 +5153,31 @@
       </c>
     </row>
     <row r="3" spans="1:21" x14ac:dyDescent="0.45">
-      <c r="A3" s="47"/>
-      <c r="B3" s="47"/>
-      <c r="C3" s="47"/>
-      <c r="D3" s="47"/>
-      <c r="E3" s="47"/>
-      <c r="F3" s="51"/>
+      <c r="A3" s="45"/>
+      <c r="B3" s="45"/>
+      <c r="C3" s="45"/>
+      <c r="D3" s="45"/>
+      <c r="E3" s="45"/>
+      <c r="F3" s="54"/>
       <c r="G3" s="42"/>
       <c r="H3" s="42"/>
       <c r="I3" s="42"/>
       <c r="J3" s="42"/>
       <c r="K3" s="42"/>
-      <c r="L3" s="44">
+      <c r="L3" s="51">
         <v>17485</v>
       </c>
       <c r="M3" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="N3" s="44">
+      <c r="N3" s="51">
         <v>14760</v>
       </c>
-      <c r="O3" s="45"/>
-      <c r="P3" s="44">
+      <c r="O3" s="49"/>
+      <c r="P3" s="51">
         <v>8125</v>
       </c>
-      <c r="Q3" s="45"/>
+      <c r="Q3" s="49"/>
       <c r="R3" s="1"/>
       <c r="S3" s="4" t="s">
         <v>27</v>
@@ -5149,29 +5190,29 @@
       </c>
     </row>
     <row r="4" spans="1:21" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A4" s="48"/>
-      <c r="B4" s="48"/>
-      <c r="C4" s="48"/>
-      <c r="D4" s="48"/>
-      <c r="E4" s="48"/>
-      <c r="F4" s="51"/>
+      <c r="A4" s="46"/>
+      <c r="B4" s="46"/>
+      <c r="C4" s="46"/>
+      <c r="D4" s="46"/>
+      <c r="E4" s="46"/>
+      <c r="F4" s="54"/>
       <c r="G4" s="42"/>
       <c r="H4" s="42"/>
       <c r="I4" s="42"/>
       <c r="J4" s="42"/>
       <c r="K4" s="42"/>
-      <c r="L4" s="48"/>
+      <c r="L4" s="46"/>
       <c r="M4" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="N4" s="52">
+      <c r="N4" s="55">
         <v>34705</v>
       </c>
-      <c r="O4" s="53"/>
-      <c r="P4" s="44">
+      <c r="O4" s="56"/>
+      <c r="P4" s="51">
         <v>13230</v>
       </c>
-      <c r="Q4" s="45"/>
+      <c r="Q4" s="49"/>
       <c r="R4" s="1"/>
       <c r="S4" s="4" t="s">
         <v>29</v>
@@ -5609,16 +5650,6 @@
     </row>
   </sheetData>
   <mergeCells count="17">
-    <mergeCell ref="A1:A4"/>
-    <mergeCell ref="D1:D4"/>
-    <mergeCell ref="B1:B4"/>
-    <mergeCell ref="L1:L2"/>
-    <mergeCell ref="E1:E4"/>
-    <mergeCell ref="T1:U1"/>
-    <mergeCell ref="N2:O2"/>
-    <mergeCell ref="P2:Q2"/>
-    <mergeCell ref="M1:O1"/>
-    <mergeCell ref="P1:Q1"/>
     <mergeCell ref="P4:Q4"/>
     <mergeCell ref="P3:Q3"/>
     <mergeCell ref="N3:O3"/>
@@ -5626,6 +5657,16 @@
     <mergeCell ref="F1:K4"/>
     <mergeCell ref="L3:L4"/>
     <mergeCell ref="N4:O4"/>
+    <mergeCell ref="T1:U1"/>
+    <mergeCell ref="N2:O2"/>
+    <mergeCell ref="P2:Q2"/>
+    <mergeCell ref="M1:O1"/>
+    <mergeCell ref="P1:Q1"/>
+    <mergeCell ref="A1:A4"/>
+    <mergeCell ref="D1:D4"/>
+    <mergeCell ref="B1:B4"/>
+    <mergeCell ref="L1:L2"/>
+    <mergeCell ref="E1:E4"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="E5:E10">

--- a/input.xlsx
+++ b/input.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\backup01\Desktop\병아리\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EEA04C5F-3847-4457-884C-FBC71E63C8A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F72B77D5-22CC-4EBE-AFB9-D39690DB75CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="25490" yWindow="690" windowWidth="25820" windowHeight="13900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="INPUT" sheetId="1" r:id="rId1"/>
@@ -730,22 +730,15 @@
     <xf numFmtId="0" fontId="10" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="41" fontId="4" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="9" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="41" fontId="4" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -755,6 +748,13 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="9" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="백분율" xfId="2" builtinId="5"/>
@@ -1037,7 +1037,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M157"/>
+  <dimension ref="A1:M158"/>
   <sheetFormatPr defaultRowHeight="16" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="12" style="31" customWidth="1"/>
@@ -5049,6 +5049,47 @@
         <v>14194160</v>
       </c>
       <c r="M157" s="40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="158" spans="1:13" ht="16.5" x14ac:dyDescent="0.45">
+      <c r="A158" s="35">
+        <v>46189</v>
+      </c>
+      <c r="B158" s="36">
+        <v>132121045</v>
+      </c>
+      <c r="C158" s="37">
+        <v>-22075380</v>
+      </c>
+      <c r="D158" s="38">
+        <v>8726.6</v>
+      </c>
+      <c r="E158" s="37">
+        <v>1307810</v>
+      </c>
+      <c r="F158" s="40">
+        <v>14639640</v>
+      </c>
+      <c r="G158" s="40">
+        <v>15451570</v>
+      </c>
+      <c r="H158" s="40">
+        <v>23518260</v>
+      </c>
+      <c r="I158" s="40">
+        <v>21881565</v>
+      </c>
+      <c r="J158" s="40">
+        <v>23485705</v>
+      </c>
+      <c r="K158" s="40">
+        <v>24139490</v>
+      </c>
+      <c r="L158" s="40">
+        <v>9004815</v>
+      </c>
+      <c r="M158" s="40">
         <v>0</v>
       </c>
     </row>
@@ -5075,72 +5116,72 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:21" x14ac:dyDescent="0.45">
-      <c r="A1" s="44" t="s">
+      <c r="A1" s="46" t="s">
         <v>17</v>
       </c>
-      <c r="B1" s="44" t="s">
+      <c r="B1" s="46" t="s">
         <v>16</v>
       </c>
-      <c r="C1" s="44" t="s">
+      <c r="C1" s="46" t="s">
         <v>18</v>
       </c>
-      <c r="D1" s="44" t="s">
+      <c r="D1" s="46" t="s">
         <v>19</v>
       </c>
-      <c r="E1" s="48" t="s">
+      <c r="E1" s="56" t="s">
         <v>20</v>
       </c>
-      <c r="F1" s="52" t="s">
+      <c r="F1" s="49" t="s">
         <v>21</v>
       </c>
-      <c r="G1" s="53"/>
-      <c r="H1" s="53"/>
-      <c r="I1" s="53"/>
-      <c r="J1" s="53"/>
-      <c r="K1" s="53"/>
-      <c r="L1" s="47">
+      <c r="G1" s="50"/>
+      <c r="H1" s="50"/>
+      <c r="I1" s="50"/>
+      <c r="J1" s="50"/>
+      <c r="K1" s="50"/>
+      <c r="L1" s="54">
         <v>0.7</v>
       </c>
-      <c r="M1" s="44" t="s">
+      <c r="M1" s="46" t="s">
         <v>22</v>
       </c>
-      <c r="N1" s="50"/>
-      <c r="O1" s="49"/>
-      <c r="P1" s="47">
+      <c r="N1" s="55"/>
+      <c r="O1" s="45"/>
+      <c r="P1" s="54">
         <v>0.25</v>
       </c>
-      <c r="Q1" s="49"/>
+      <c r="Q1" s="45"/>
       <c r="R1" s="1"/>
       <c r="S1" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="T1" s="44" t="s">
+      <c r="T1" s="46" t="s">
         <v>23</v>
       </c>
-      <c r="U1" s="49"/>
+      <c r="U1" s="45"/>
     </row>
     <row r="2" spans="1:21" x14ac:dyDescent="0.45">
-      <c r="A2" s="45"/>
-      <c r="B2" s="45"/>
-      <c r="C2" s="45"/>
-      <c r="D2" s="45"/>
-      <c r="E2" s="45"/>
-      <c r="F2" s="54"/>
+      <c r="A2" s="47"/>
+      <c r="B2" s="47"/>
+      <c r="C2" s="47"/>
+      <c r="D2" s="47"/>
+      <c r="E2" s="47"/>
+      <c r="F2" s="51"/>
       <c r="G2" s="42"/>
       <c r="H2" s="42"/>
       <c r="I2" s="42"/>
       <c r="J2" s="42"/>
       <c r="K2" s="42"/>
-      <c r="L2" s="46"/>
+      <c r="L2" s="48"/>
       <c r="M2" s="3"/>
-      <c r="N2" s="47" t="s">
+      <c r="N2" s="54" t="s">
         <v>15</v>
       </c>
-      <c r="O2" s="49"/>
-      <c r="P2" s="44" t="s">
+      <c r="O2" s="45"/>
+      <c r="P2" s="46" t="s">
         <v>24</v>
       </c>
-      <c r="Q2" s="49"/>
+      <c r="Q2" s="45"/>
       <c r="R2" s="1"/>
       <c r="S2" s="4" t="s">
         <v>25</v>
@@ -5153,31 +5194,31 @@
       </c>
     </row>
     <row r="3" spans="1:21" x14ac:dyDescent="0.45">
-      <c r="A3" s="45"/>
-      <c r="B3" s="45"/>
-      <c r="C3" s="45"/>
-      <c r="D3" s="45"/>
-      <c r="E3" s="45"/>
-      <c r="F3" s="54"/>
+      <c r="A3" s="47"/>
+      <c r="B3" s="47"/>
+      <c r="C3" s="47"/>
+      <c r="D3" s="47"/>
+      <c r="E3" s="47"/>
+      <c r="F3" s="51"/>
       <c r="G3" s="42"/>
       <c r="H3" s="42"/>
       <c r="I3" s="42"/>
       <c r="J3" s="42"/>
       <c r="K3" s="42"/>
-      <c r="L3" s="51">
+      <c r="L3" s="44">
         <v>17485</v>
       </c>
       <c r="M3" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="N3" s="51">
+      <c r="N3" s="44">
         <v>14760</v>
       </c>
-      <c r="O3" s="49"/>
-      <c r="P3" s="51">
+      <c r="O3" s="45"/>
+      <c r="P3" s="44">
         <v>8125</v>
       </c>
-      <c r="Q3" s="49"/>
+      <c r="Q3" s="45"/>
       <c r="R3" s="1"/>
       <c r="S3" s="4" t="s">
         <v>27</v>
@@ -5190,29 +5231,29 @@
       </c>
     </row>
     <row r="4" spans="1:21" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A4" s="46"/>
-      <c r="B4" s="46"/>
-      <c r="C4" s="46"/>
-      <c r="D4" s="46"/>
-      <c r="E4" s="46"/>
-      <c r="F4" s="54"/>
+      <c r="A4" s="48"/>
+      <c r="B4" s="48"/>
+      <c r="C4" s="48"/>
+      <c r="D4" s="48"/>
+      <c r="E4" s="48"/>
+      <c r="F4" s="51"/>
       <c r="G4" s="42"/>
       <c r="H4" s="42"/>
       <c r="I4" s="42"/>
       <c r="J4" s="42"/>
       <c r="K4" s="42"/>
-      <c r="L4" s="46"/>
+      <c r="L4" s="48"/>
       <c r="M4" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="N4" s="55">
+      <c r="N4" s="52">
         <v>34705</v>
       </c>
-      <c r="O4" s="56"/>
-      <c r="P4" s="51">
+      <c r="O4" s="53"/>
+      <c r="P4" s="44">
         <v>13230</v>
       </c>
-      <c r="Q4" s="49"/>
+      <c r="Q4" s="45"/>
       <c r="R4" s="1"/>
       <c r="S4" s="4" t="s">
         <v>29</v>
@@ -5650,6 +5691,16 @@
     </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="A1:A4"/>
+    <mergeCell ref="D1:D4"/>
+    <mergeCell ref="B1:B4"/>
+    <mergeCell ref="L1:L2"/>
+    <mergeCell ref="E1:E4"/>
+    <mergeCell ref="T1:U1"/>
+    <mergeCell ref="N2:O2"/>
+    <mergeCell ref="P2:Q2"/>
+    <mergeCell ref="M1:O1"/>
+    <mergeCell ref="P1:Q1"/>
     <mergeCell ref="P4:Q4"/>
     <mergeCell ref="P3:Q3"/>
     <mergeCell ref="N3:O3"/>
@@ -5657,16 +5708,6 @@
     <mergeCell ref="F1:K4"/>
     <mergeCell ref="L3:L4"/>
     <mergeCell ref="N4:O4"/>
-    <mergeCell ref="T1:U1"/>
-    <mergeCell ref="N2:O2"/>
-    <mergeCell ref="P2:Q2"/>
-    <mergeCell ref="M1:O1"/>
-    <mergeCell ref="P1:Q1"/>
-    <mergeCell ref="A1:A4"/>
-    <mergeCell ref="D1:D4"/>
-    <mergeCell ref="B1:B4"/>
-    <mergeCell ref="L1:L2"/>
-    <mergeCell ref="E1:E4"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="E5:E10">

--- a/input.xlsx
+++ b/input.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\backup01\Desktop\병아리\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F72B77D5-22CC-4EBE-AFB9-D39690DB75CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B279A95-D9F7-4364-8191-3F82B01DCAB9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -730,15 +730,22 @@
     <xf numFmtId="0" fontId="10" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="4" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="9" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="41" fontId="4" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -748,13 +755,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="9" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="백분율" xfId="2" builtinId="5"/>
@@ -1037,7 +1037,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M158"/>
+  <dimension ref="A1:M159"/>
   <sheetFormatPr defaultRowHeight="16" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="12" style="31" customWidth="1"/>
@@ -5090,6 +5090,47 @@
         <v>9004815</v>
       </c>
       <c r="M158" s="40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="159" spans="1:13" ht="16.5" x14ac:dyDescent="0.45">
+      <c r="A159" s="35">
+        <v>46190</v>
+      </c>
+      <c r="B159" s="36">
+        <v>122387060</v>
+      </c>
+      <c r="C159" s="37">
+        <v>-14413270</v>
+      </c>
+      <c r="D159" s="38">
+        <v>8864.24</v>
+      </c>
+      <c r="E159" s="37">
+        <v>1031930</v>
+      </c>
+      <c r="F159" s="40">
+        <v>15251125</v>
+      </c>
+      <c r="G159" s="40">
+        <v>16053780</v>
+      </c>
+      <c r="H159" s="40">
+        <v>24202255</v>
+      </c>
+      <c r="I159" s="40">
+        <v>17792600</v>
+      </c>
+      <c r="J159" s="40">
+        <v>14387100</v>
+      </c>
+      <c r="K159" s="40">
+        <v>25273560</v>
+      </c>
+      <c r="L159" s="40">
+        <v>9426640</v>
+      </c>
+      <c r="M159" s="40">
         <v>0</v>
       </c>
     </row>
@@ -5116,72 +5157,72 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:21" x14ac:dyDescent="0.45">
-      <c r="A1" s="46" t="s">
+      <c r="A1" s="44" t="s">
         <v>17</v>
       </c>
-      <c r="B1" s="46" t="s">
+      <c r="B1" s="44" t="s">
         <v>16</v>
       </c>
-      <c r="C1" s="46" t="s">
+      <c r="C1" s="44" t="s">
         <v>18</v>
       </c>
-      <c r="D1" s="46" t="s">
+      <c r="D1" s="44" t="s">
         <v>19</v>
       </c>
-      <c r="E1" s="56" t="s">
+      <c r="E1" s="48" t="s">
         <v>20</v>
       </c>
-      <c r="F1" s="49" t="s">
+      <c r="F1" s="52" t="s">
         <v>21</v>
       </c>
-      <c r="G1" s="50"/>
-      <c r="H1" s="50"/>
-      <c r="I1" s="50"/>
-      <c r="J1" s="50"/>
-      <c r="K1" s="50"/>
-      <c r="L1" s="54">
+      <c r="G1" s="53"/>
+      <c r="H1" s="53"/>
+      <c r="I1" s="53"/>
+      <c r="J1" s="53"/>
+      <c r="K1" s="53"/>
+      <c r="L1" s="47">
         <v>0.7</v>
       </c>
-      <c r="M1" s="46" t="s">
+      <c r="M1" s="44" t="s">
         <v>22</v>
       </c>
-      <c r="N1" s="55"/>
-      <c r="O1" s="45"/>
-      <c r="P1" s="54">
+      <c r="N1" s="50"/>
+      <c r="O1" s="49"/>
+      <c r="P1" s="47">
         <v>0.25</v>
       </c>
-      <c r="Q1" s="45"/>
+      <c r="Q1" s="49"/>
       <c r="R1" s="1"/>
       <c r="S1" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="T1" s="46" t="s">
+      <c r="T1" s="44" t="s">
         <v>23</v>
       </c>
-      <c r="U1" s="45"/>
+      <c r="U1" s="49"/>
     </row>
     <row r="2" spans="1:21" x14ac:dyDescent="0.45">
-      <c r="A2" s="47"/>
-      <c r="B2" s="47"/>
-      <c r="C2" s="47"/>
-      <c r="D2" s="47"/>
-      <c r="E2" s="47"/>
-      <c r="F2" s="51"/>
+      <c r="A2" s="45"/>
+      <c r="B2" s="45"/>
+      <c r="C2" s="45"/>
+      <c r="D2" s="45"/>
+      <c r="E2" s="45"/>
+      <c r="F2" s="54"/>
       <c r="G2" s="42"/>
       <c r="H2" s="42"/>
       <c r="I2" s="42"/>
       <c r="J2" s="42"/>
       <c r="K2" s="42"/>
-      <c r="L2" s="48"/>
+      <c r="L2" s="46"/>
       <c r="M2" s="3"/>
-      <c r="N2" s="54" t="s">
+      <c r="N2" s="47" t="s">
         <v>15</v>
       </c>
-      <c r="O2" s="45"/>
-      <c r="P2" s="46" t="s">
+      <c r="O2" s="49"/>
+      <c r="P2" s="44" t="s">
         <v>24</v>
       </c>
-      <c r="Q2" s="45"/>
+      <c r="Q2" s="49"/>
       <c r="R2" s="1"/>
       <c r="S2" s="4" t="s">
         <v>25</v>
@@ -5194,31 +5235,31 @@
       </c>
     </row>
     <row r="3" spans="1:21" x14ac:dyDescent="0.45">
-      <c r="A3" s="47"/>
-      <c r="B3" s="47"/>
-      <c r="C3" s="47"/>
-      <c r="D3" s="47"/>
-      <c r="E3" s="47"/>
-      <c r="F3" s="51"/>
+      <c r="A3" s="45"/>
+      <c r="B3" s="45"/>
+      <c r="C3" s="45"/>
+      <c r="D3" s="45"/>
+      <c r="E3" s="45"/>
+      <c r="F3" s="54"/>
       <c r="G3" s="42"/>
       <c r="H3" s="42"/>
       <c r="I3" s="42"/>
       <c r="J3" s="42"/>
       <c r="K3" s="42"/>
-      <c r="L3" s="44">
+      <c r="L3" s="51">
         <v>17485</v>
       </c>
       <c r="M3" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="N3" s="44">
+      <c r="N3" s="51">
         <v>14760</v>
       </c>
-      <c r="O3" s="45"/>
-      <c r="P3" s="44">
+      <c r="O3" s="49"/>
+      <c r="P3" s="51">
         <v>8125</v>
       </c>
-      <c r="Q3" s="45"/>
+      <c r="Q3" s="49"/>
       <c r="R3" s="1"/>
       <c r="S3" s="4" t="s">
         <v>27</v>
@@ -5231,29 +5272,29 @@
       </c>
     </row>
     <row r="4" spans="1:21" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A4" s="48"/>
-      <c r="B4" s="48"/>
-      <c r="C4" s="48"/>
-      <c r="D4" s="48"/>
-      <c r="E4" s="48"/>
-      <c r="F4" s="51"/>
+      <c r="A4" s="46"/>
+      <c r="B4" s="46"/>
+      <c r="C4" s="46"/>
+      <c r="D4" s="46"/>
+      <c r="E4" s="46"/>
+      <c r="F4" s="54"/>
       <c r="G4" s="42"/>
       <c r="H4" s="42"/>
       <c r="I4" s="42"/>
       <c r="J4" s="42"/>
       <c r="K4" s="42"/>
-      <c r="L4" s="48"/>
+      <c r="L4" s="46"/>
       <c r="M4" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="N4" s="52">
+      <c r="N4" s="55">
         <v>34705</v>
       </c>
-      <c r="O4" s="53"/>
-      <c r="P4" s="44">
+      <c r="O4" s="56"/>
+      <c r="P4" s="51">
         <v>13230</v>
       </c>
-      <c r="Q4" s="45"/>
+      <c r="Q4" s="49"/>
       <c r="R4" s="1"/>
       <c r="S4" s="4" t="s">
         <v>29</v>
@@ -5691,16 +5732,6 @@
     </row>
   </sheetData>
   <mergeCells count="17">
-    <mergeCell ref="A1:A4"/>
-    <mergeCell ref="D1:D4"/>
-    <mergeCell ref="B1:B4"/>
-    <mergeCell ref="L1:L2"/>
-    <mergeCell ref="E1:E4"/>
-    <mergeCell ref="T1:U1"/>
-    <mergeCell ref="N2:O2"/>
-    <mergeCell ref="P2:Q2"/>
-    <mergeCell ref="M1:O1"/>
-    <mergeCell ref="P1:Q1"/>
     <mergeCell ref="P4:Q4"/>
     <mergeCell ref="P3:Q3"/>
     <mergeCell ref="N3:O3"/>
@@ -5708,6 +5739,16 @@
     <mergeCell ref="F1:K4"/>
     <mergeCell ref="L3:L4"/>
     <mergeCell ref="N4:O4"/>
+    <mergeCell ref="T1:U1"/>
+    <mergeCell ref="N2:O2"/>
+    <mergeCell ref="P2:Q2"/>
+    <mergeCell ref="M1:O1"/>
+    <mergeCell ref="P1:Q1"/>
+    <mergeCell ref="A1:A4"/>
+    <mergeCell ref="D1:D4"/>
+    <mergeCell ref="B1:B4"/>
+    <mergeCell ref="L1:L2"/>
+    <mergeCell ref="E1:E4"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="E5:E10">

--- a/input.xlsx
+++ b/input.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\backup01\Desktop\병아리\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B279A95-D9F7-4364-8191-3F82B01DCAB9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3254C54B-94B6-44DD-A1F4-E6B141019EC0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="25490" yWindow="690" windowWidth="25820" windowHeight="13900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="INPUT" sheetId="1" r:id="rId1"/>
@@ -730,22 +730,15 @@
     <xf numFmtId="0" fontId="10" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="41" fontId="4" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="9" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="41" fontId="4" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -755,6 +748,13 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="9" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="백분율" xfId="2" builtinId="5"/>
@@ -1037,7 +1037,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M159"/>
+  <dimension ref="A1:M160"/>
   <sheetFormatPr defaultRowHeight="16" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="12" style="31" customWidth="1"/>
@@ -5131,6 +5131,47 @@
         <v>9426640</v>
       </c>
       <c r="M159" s="40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="160" spans="1:13" ht="16.5" x14ac:dyDescent="0.45">
+      <c r="A160" s="35">
+        <v>46191</v>
+      </c>
+      <c r="B160" s="36">
+        <v>116049660</v>
+      </c>
+      <c r="C160" s="37">
+        <v>-3340090</v>
+      </c>
+      <c r="D160" s="38">
+        <v>9063.84</v>
+      </c>
+      <c r="E160" s="37">
+        <v>1298538</v>
+      </c>
+      <c r="F160" s="40">
+        <v>15375325</v>
+      </c>
+      <c r="G160" s="40">
+        <v>16797410</v>
+      </c>
+      <c r="H160" s="40">
+        <v>16229325</v>
+      </c>
+      <c r="I160" s="40">
+        <v>12119250</v>
+      </c>
+      <c r="J160" s="40">
+        <v>13486550</v>
+      </c>
+      <c r="K160" s="40">
+        <v>32616320</v>
+      </c>
+      <c r="L160" s="40">
+        <v>9425480</v>
+      </c>
+      <c r="M160" s="40">
         <v>0</v>
       </c>
     </row>
@@ -5157,72 +5198,72 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:21" x14ac:dyDescent="0.45">
-      <c r="A1" s="44" t="s">
+      <c r="A1" s="46" t="s">
         <v>17</v>
       </c>
-      <c r="B1" s="44" t="s">
+      <c r="B1" s="46" t="s">
         <v>16</v>
       </c>
-      <c r="C1" s="44" t="s">
+      <c r="C1" s="46" t="s">
         <v>18</v>
       </c>
-      <c r="D1" s="44" t="s">
+      <c r="D1" s="46" t="s">
         <v>19</v>
       </c>
-      <c r="E1" s="48" t="s">
+      <c r="E1" s="56" t="s">
         <v>20</v>
       </c>
-      <c r="F1" s="52" t="s">
+      <c r="F1" s="49" t="s">
         <v>21</v>
       </c>
-      <c r="G1" s="53"/>
-      <c r="H1" s="53"/>
-      <c r="I1" s="53"/>
-      <c r="J1" s="53"/>
-      <c r="K1" s="53"/>
-      <c r="L1" s="47">
+      <c r="G1" s="50"/>
+      <c r="H1" s="50"/>
+      <c r="I1" s="50"/>
+      <c r="J1" s="50"/>
+      <c r="K1" s="50"/>
+      <c r="L1" s="54">
         <v>0.7</v>
       </c>
-      <c r="M1" s="44" t="s">
+      <c r="M1" s="46" t="s">
         <v>22</v>
       </c>
-      <c r="N1" s="50"/>
-      <c r="O1" s="49"/>
-      <c r="P1" s="47">
+      <c r="N1" s="55"/>
+      <c r="O1" s="45"/>
+      <c r="P1" s="54">
         <v>0.25</v>
       </c>
-      <c r="Q1" s="49"/>
+      <c r="Q1" s="45"/>
       <c r="R1" s="1"/>
       <c r="S1" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="T1" s="44" t="s">
+      <c r="T1" s="46" t="s">
         <v>23</v>
       </c>
-      <c r="U1" s="49"/>
+      <c r="U1" s="45"/>
     </row>
     <row r="2" spans="1:21" x14ac:dyDescent="0.45">
-      <c r="A2" s="45"/>
-      <c r="B2" s="45"/>
-      <c r="C2" s="45"/>
-      <c r="D2" s="45"/>
-      <c r="E2" s="45"/>
-      <c r="F2" s="54"/>
+      <c r="A2" s="47"/>
+      <c r="B2" s="47"/>
+      <c r="C2" s="47"/>
+      <c r="D2" s="47"/>
+      <c r="E2" s="47"/>
+      <c r="F2" s="51"/>
       <c r="G2" s="42"/>
       <c r="H2" s="42"/>
       <c r="I2" s="42"/>
       <c r="J2" s="42"/>
       <c r="K2" s="42"/>
-      <c r="L2" s="46"/>
+      <c r="L2" s="48"/>
       <c r="M2" s="3"/>
-      <c r="N2" s="47" t="s">
+      <c r="N2" s="54" t="s">
         <v>15</v>
       </c>
-      <c r="O2" s="49"/>
-      <c r="P2" s="44" t="s">
+      <c r="O2" s="45"/>
+      <c r="P2" s="46" t="s">
         <v>24</v>
       </c>
-      <c r="Q2" s="49"/>
+      <c r="Q2" s="45"/>
       <c r="R2" s="1"/>
       <c r="S2" s="4" t="s">
         <v>25</v>
@@ -5235,31 +5276,31 @@
       </c>
     </row>
     <row r="3" spans="1:21" x14ac:dyDescent="0.45">
-      <c r="A3" s="45"/>
-      <c r="B3" s="45"/>
-      <c r="C3" s="45"/>
-      <c r="D3" s="45"/>
-      <c r="E3" s="45"/>
-      <c r="F3" s="54"/>
+      <c r="A3" s="47"/>
+      <c r="B3" s="47"/>
+      <c r="C3" s="47"/>
+      <c r="D3" s="47"/>
+      <c r="E3" s="47"/>
+      <c r="F3" s="51"/>
       <c r="G3" s="42"/>
       <c r="H3" s="42"/>
       <c r="I3" s="42"/>
       <c r="J3" s="42"/>
       <c r="K3" s="42"/>
-      <c r="L3" s="51">
+      <c r="L3" s="44">
         <v>17485</v>
       </c>
       <c r="M3" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="N3" s="51">
+      <c r="N3" s="44">
         <v>14760</v>
       </c>
-      <c r="O3" s="49"/>
-      <c r="P3" s="51">
+      <c r="O3" s="45"/>
+      <c r="P3" s="44">
         <v>8125</v>
       </c>
-      <c r="Q3" s="49"/>
+      <c r="Q3" s="45"/>
       <c r="R3" s="1"/>
       <c r="S3" s="4" t="s">
         <v>27</v>
@@ -5272,29 +5313,29 @@
       </c>
     </row>
     <row r="4" spans="1:21" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A4" s="46"/>
-      <c r="B4" s="46"/>
-      <c r="C4" s="46"/>
-      <c r="D4" s="46"/>
-      <c r="E4" s="46"/>
-      <c r="F4" s="54"/>
+      <c r="A4" s="48"/>
+      <c r="B4" s="48"/>
+      <c r="C4" s="48"/>
+      <c r="D4" s="48"/>
+      <c r="E4" s="48"/>
+      <c r="F4" s="51"/>
       <c r="G4" s="42"/>
       <c r="H4" s="42"/>
       <c r="I4" s="42"/>
       <c r="J4" s="42"/>
       <c r="K4" s="42"/>
-      <c r="L4" s="46"/>
+      <c r="L4" s="48"/>
       <c r="M4" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="N4" s="55">
+      <c r="N4" s="52">
         <v>34705</v>
       </c>
-      <c r="O4" s="56"/>
-      <c r="P4" s="51">
+      <c r="O4" s="53"/>
+      <c r="P4" s="44">
         <v>13230</v>
       </c>
-      <c r="Q4" s="49"/>
+      <c r="Q4" s="45"/>
       <c r="R4" s="1"/>
       <c r="S4" s="4" t="s">
         <v>29</v>
@@ -5732,6 +5773,16 @@
     </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="A1:A4"/>
+    <mergeCell ref="D1:D4"/>
+    <mergeCell ref="B1:B4"/>
+    <mergeCell ref="L1:L2"/>
+    <mergeCell ref="E1:E4"/>
+    <mergeCell ref="T1:U1"/>
+    <mergeCell ref="N2:O2"/>
+    <mergeCell ref="P2:Q2"/>
+    <mergeCell ref="M1:O1"/>
+    <mergeCell ref="P1:Q1"/>
     <mergeCell ref="P4:Q4"/>
     <mergeCell ref="P3:Q3"/>
     <mergeCell ref="N3:O3"/>
@@ -5739,16 +5790,6 @@
     <mergeCell ref="F1:K4"/>
     <mergeCell ref="L3:L4"/>
     <mergeCell ref="N4:O4"/>
-    <mergeCell ref="T1:U1"/>
-    <mergeCell ref="N2:O2"/>
-    <mergeCell ref="P2:Q2"/>
-    <mergeCell ref="M1:O1"/>
-    <mergeCell ref="P1:Q1"/>
-    <mergeCell ref="A1:A4"/>
-    <mergeCell ref="D1:D4"/>
-    <mergeCell ref="B1:B4"/>
-    <mergeCell ref="L1:L2"/>
-    <mergeCell ref="E1:E4"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="E5:E10">

--- a/input.xlsx
+++ b/input.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\backup01\Desktop\병아리\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3254C54B-94B6-44DD-A1F4-E6B141019EC0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A2CB89A1-BEA7-4898-9A50-98998EA12976}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="25490" yWindow="690" windowWidth="25820" windowHeight="13900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="INPUT" sheetId="1" r:id="rId1"/>
@@ -730,15 +730,22 @@
     <xf numFmtId="0" fontId="10" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="4" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="9" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="41" fontId="4" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -748,13 +755,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="9" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="백분율" xfId="2" builtinId="5"/>
@@ -1037,7 +1037,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M160"/>
+  <dimension ref="A1:M161"/>
   <sheetFormatPr defaultRowHeight="16" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="12" style="31" customWidth="1"/>
@@ -5173,6 +5173,47 @@
       </c>
       <c r="M160" s="40">
         <v>0</v>
+      </c>
+    </row>
+    <row r="161" spans="1:13" ht="16.5" x14ac:dyDescent="0.45">
+      <c r="A161" s="35">
+        <v>46192</v>
+      </c>
+      <c r="B161" s="36">
+        <v>119889400</v>
+      </c>
+      <c r="C161" s="37">
+        <v>9826805</v>
+      </c>
+      <c r="D161" s="38">
+        <v>9052.42</v>
+      </c>
+      <c r="E161" s="37">
+        <v>193084</v>
+      </c>
+      <c r="F161" s="40">
+        <v>14910100</v>
+      </c>
+      <c r="G161" s="40">
+        <v>16606660</v>
+      </c>
+      <c r="H161" s="40">
+        <v>7949840</v>
+      </c>
+      <c r="I161" s="40">
+        <v>11266125</v>
+      </c>
+      <c r="J161" s="40">
+        <v>12537175</v>
+      </c>
+      <c r="K161" s="40">
+        <v>30320320</v>
+      </c>
+      <c r="L161" s="40">
+        <v>17297835</v>
+      </c>
+      <c r="M161" s="40">
+        <v>9001345</v>
       </c>
     </row>
   </sheetData>
@@ -5198,72 +5239,72 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:21" x14ac:dyDescent="0.45">
-      <c r="A1" s="46" t="s">
+      <c r="A1" s="44" t="s">
         <v>17</v>
       </c>
-      <c r="B1" s="46" t="s">
+      <c r="B1" s="44" t="s">
         <v>16</v>
       </c>
-      <c r="C1" s="46" t="s">
+      <c r="C1" s="44" t="s">
         <v>18</v>
       </c>
-      <c r="D1" s="46" t="s">
+      <c r="D1" s="44" t="s">
         <v>19</v>
       </c>
-      <c r="E1" s="56" t="s">
+      <c r="E1" s="48" t="s">
         <v>20</v>
       </c>
-      <c r="F1" s="49" t="s">
+      <c r="F1" s="52" t="s">
         <v>21</v>
       </c>
-      <c r="G1" s="50"/>
-      <c r="H1" s="50"/>
-      <c r="I1" s="50"/>
-      <c r="J1" s="50"/>
-      <c r="K1" s="50"/>
-      <c r="L1" s="54">
+      <c r="G1" s="53"/>
+      <c r="H1" s="53"/>
+      <c r="I1" s="53"/>
+      <c r="J1" s="53"/>
+      <c r="K1" s="53"/>
+      <c r="L1" s="47">
         <v>0.7</v>
       </c>
-      <c r="M1" s="46" t="s">
+      <c r="M1" s="44" t="s">
         <v>22</v>
       </c>
-      <c r="N1" s="55"/>
-      <c r="O1" s="45"/>
-      <c r="P1" s="54">
+      <c r="N1" s="50"/>
+      <c r="O1" s="49"/>
+      <c r="P1" s="47">
         <v>0.25</v>
       </c>
-      <c r="Q1" s="45"/>
+      <c r="Q1" s="49"/>
       <c r="R1" s="1"/>
       <c r="S1" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="T1" s="46" t="s">
+      <c r="T1" s="44" t="s">
         <v>23</v>
       </c>
-      <c r="U1" s="45"/>
+      <c r="U1" s="49"/>
     </row>
     <row r="2" spans="1:21" x14ac:dyDescent="0.45">
-      <c r="A2" s="47"/>
-      <c r="B2" s="47"/>
-      <c r="C2" s="47"/>
-      <c r="D2" s="47"/>
-      <c r="E2" s="47"/>
-      <c r="F2" s="51"/>
+      <c r="A2" s="45"/>
+      <c r="B2" s="45"/>
+      <c r="C2" s="45"/>
+      <c r="D2" s="45"/>
+      <c r="E2" s="45"/>
+      <c r="F2" s="54"/>
       <c r="G2" s="42"/>
       <c r="H2" s="42"/>
       <c r="I2" s="42"/>
       <c r="J2" s="42"/>
       <c r="K2" s="42"/>
-      <c r="L2" s="48"/>
+      <c r="L2" s="46"/>
       <c r="M2" s="3"/>
-      <c r="N2" s="54" t="s">
+      <c r="N2" s="47" t="s">
         <v>15</v>
       </c>
-      <c r="O2" s="45"/>
-      <c r="P2" s="46" t="s">
+      <c r="O2" s="49"/>
+      <c r="P2" s="44" t="s">
         <v>24</v>
       </c>
-      <c r="Q2" s="45"/>
+      <c r="Q2" s="49"/>
       <c r="R2" s="1"/>
       <c r="S2" s="4" t="s">
         <v>25</v>
@@ -5276,31 +5317,31 @@
       </c>
     </row>
     <row r="3" spans="1:21" x14ac:dyDescent="0.45">
-      <c r="A3" s="47"/>
-      <c r="B3" s="47"/>
-      <c r="C3" s="47"/>
-      <c r="D3" s="47"/>
-      <c r="E3" s="47"/>
-      <c r="F3" s="51"/>
+      <c r="A3" s="45"/>
+      <c r="B3" s="45"/>
+      <c r="C3" s="45"/>
+      <c r="D3" s="45"/>
+      <c r="E3" s="45"/>
+      <c r="F3" s="54"/>
       <c r="G3" s="42"/>
       <c r="H3" s="42"/>
       <c r="I3" s="42"/>
       <c r="J3" s="42"/>
       <c r="K3" s="42"/>
-      <c r="L3" s="44">
+      <c r="L3" s="51">
         <v>17485</v>
       </c>
       <c r="M3" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="N3" s="44">
+      <c r="N3" s="51">
         <v>14760</v>
       </c>
-      <c r="O3" s="45"/>
-      <c r="P3" s="44">
+      <c r="O3" s="49"/>
+      <c r="P3" s="51">
         <v>8125</v>
       </c>
-      <c r="Q3" s="45"/>
+      <c r="Q3" s="49"/>
       <c r="R3" s="1"/>
       <c r="S3" s="4" t="s">
         <v>27</v>
@@ -5313,29 +5354,29 @@
       </c>
     </row>
     <row r="4" spans="1:21" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A4" s="48"/>
-      <c r="B4" s="48"/>
-      <c r="C4" s="48"/>
-      <c r="D4" s="48"/>
-      <c r="E4" s="48"/>
-      <c r="F4" s="51"/>
+      <c r="A4" s="46"/>
+      <c r="B4" s="46"/>
+      <c r="C4" s="46"/>
+      <c r="D4" s="46"/>
+      <c r="E4" s="46"/>
+      <c r="F4" s="54"/>
       <c r="G4" s="42"/>
       <c r="H4" s="42"/>
       <c r="I4" s="42"/>
       <c r="J4" s="42"/>
       <c r="K4" s="42"/>
-      <c r="L4" s="48"/>
+      <c r="L4" s="46"/>
       <c r="M4" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="N4" s="52">
+      <c r="N4" s="55">
         <v>34705</v>
       </c>
-      <c r="O4" s="53"/>
-      <c r="P4" s="44">
+      <c r="O4" s="56"/>
+      <c r="P4" s="51">
         <v>13230</v>
       </c>
-      <c r="Q4" s="45"/>
+      <c r="Q4" s="49"/>
       <c r="R4" s="1"/>
       <c r="S4" s="4" t="s">
         <v>29</v>
@@ -5773,16 +5814,6 @@
     </row>
   </sheetData>
   <mergeCells count="17">
-    <mergeCell ref="A1:A4"/>
-    <mergeCell ref="D1:D4"/>
-    <mergeCell ref="B1:B4"/>
-    <mergeCell ref="L1:L2"/>
-    <mergeCell ref="E1:E4"/>
-    <mergeCell ref="T1:U1"/>
-    <mergeCell ref="N2:O2"/>
-    <mergeCell ref="P2:Q2"/>
-    <mergeCell ref="M1:O1"/>
-    <mergeCell ref="P1:Q1"/>
     <mergeCell ref="P4:Q4"/>
     <mergeCell ref="P3:Q3"/>
     <mergeCell ref="N3:O3"/>
@@ -5790,6 +5821,16 @@
     <mergeCell ref="F1:K4"/>
     <mergeCell ref="L3:L4"/>
     <mergeCell ref="N4:O4"/>
+    <mergeCell ref="T1:U1"/>
+    <mergeCell ref="N2:O2"/>
+    <mergeCell ref="P2:Q2"/>
+    <mergeCell ref="M1:O1"/>
+    <mergeCell ref="P1:Q1"/>
+    <mergeCell ref="A1:A4"/>
+    <mergeCell ref="D1:D4"/>
+    <mergeCell ref="B1:B4"/>
+    <mergeCell ref="L1:L2"/>
+    <mergeCell ref="E1:E4"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="E5:E10">

--- a/input.xlsx
+++ b/input.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\backup01\Desktop\병아리\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A2CB89A1-BEA7-4898-9A50-98998EA12976}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9EE35406-3A60-44F5-911A-DF5076888888}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -730,22 +730,15 @@
     <xf numFmtId="0" fontId="10" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="41" fontId="4" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="9" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="41" fontId="4" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -755,6 +748,13 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="9" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="백분율" xfId="2" builtinId="5"/>
@@ -1037,7 +1037,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M161"/>
+  <dimension ref="A1:M162"/>
   <sheetFormatPr defaultRowHeight="16" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="12" style="31" customWidth="1"/>
@@ -5214,6 +5214,47 @@
       </c>
       <c r="M161" s="40">
         <v>9001345</v>
+      </c>
+    </row>
+    <row r="162" spans="1:13" ht="16.5" x14ac:dyDescent="0.45">
+      <c r="A162" s="35">
+        <v>46195</v>
+      </c>
+      <c r="B162" s="36">
+        <v>106065700</v>
+      </c>
+      <c r="C162" s="37">
+        <v>-18313980</v>
+      </c>
+      <c r="D162" s="38">
+        <v>9114.5499999999993</v>
+      </c>
+      <c r="E162" s="37">
+        <v>617290</v>
+      </c>
+      <c r="F162" s="40">
+        <v>11007480</v>
+      </c>
+      <c r="G162" s="40">
+        <v>2634530</v>
+      </c>
+      <c r="H162" s="40">
+        <v>8314480</v>
+      </c>
+      <c r="I162" s="40">
+        <v>11782875</v>
+      </c>
+      <c r="J162" s="40">
+        <v>13112225</v>
+      </c>
+      <c r="K162" s="40">
+        <v>31711040</v>
+      </c>
+      <c r="L162" s="40">
+        <v>18090075</v>
+      </c>
+      <c r="M162" s="40">
+        <v>9412995</v>
       </c>
     </row>
   </sheetData>
@@ -5239,72 +5280,72 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:21" x14ac:dyDescent="0.45">
-      <c r="A1" s="44" t="s">
+      <c r="A1" s="46" t="s">
         <v>17</v>
       </c>
-      <c r="B1" s="44" t="s">
+      <c r="B1" s="46" t="s">
         <v>16</v>
       </c>
-      <c r="C1" s="44" t="s">
+      <c r="C1" s="46" t="s">
         <v>18</v>
       </c>
-      <c r="D1" s="44" t="s">
+      <c r="D1" s="46" t="s">
         <v>19</v>
       </c>
-      <c r="E1" s="48" t="s">
+      <c r="E1" s="56" t="s">
         <v>20</v>
       </c>
-      <c r="F1" s="52" t="s">
+      <c r="F1" s="49" t="s">
         <v>21</v>
       </c>
-      <c r="G1" s="53"/>
-      <c r="H1" s="53"/>
-      <c r="I1" s="53"/>
-      <c r="J1" s="53"/>
-      <c r="K1" s="53"/>
-      <c r="L1" s="47">
+      <c r="G1" s="50"/>
+      <c r="H1" s="50"/>
+      <c r="I1" s="50"/>
+      <c r="J1" s="50"/>
+      <c r="K1" s="50"/>
+      <c r="L1" s="54">
         <v>0.7</v>
       </c>
-      <c r="M1" s="44" t="s">
+      <c r="M1" s="46" t="s">
         <v>22</v>
       </c>
-      <c r="N1" s="50"/>
-      <c r="O1" s="49"/>
-      <c r="P1" s="47">
+      <c r="N1" s="55"/>
+      <c r="O1" s="45"/>
+      <c r="P1" s="54">
         <v>0.25</v>
       </c>
-      <c r="Q1" s="49"/>
+      <c r="Q1" s="45"/>
       <c r="R1" s="1"/>
       <c r="S1" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="T1" s="44" t="s">
+      <c r="T1" s="46" t="s">
         <v>23</v>
       </c>
-      <c r="U1" s="49"/>
+      <c r="U1" s="45"/>
     </row>
     <row r="2" spans="1:21" x14ac:dyDescent="0.45">
-      <c r="A2" s="45"/>
-      <c r="B2" s="45"/>
-      <c r="C2" s="45"/>
-      <c r="D2" s="45"/>
-      <c r="E2" s="45"/>
-      <c r="F2" s="54"/>
+      <c r="A2" s="47"/>
+      <c r="B2" s="47"/>
+      <c r="C2" s="47"/>
+      <c r="D2" s="47"/>
+      <c r="E2" s="47"/>
+      <c r="F2" s="51"/>
       <c r="G2" s="42"/>
       <c r="H2" s="42"/>
       <c r="I2" s="42"/>
       <c r="J2" s="42"/>
       <c r="K2" s="42"/>
-      <c r="L2" s="46"/>
+      <c r="L2" s="48"/>
       <c r="M2" s="3"/>
-      <c r="N2" s="47" t="s">
+      <c r="N2" s="54" t="s">
         <v>15</v>
       </c>
-      <c r="O2" s="49"/>
-      <c r="P2" s="44" t="s">
+      <c r="O2" s="45"/>
+      <c r="P2" s="46" t="s">
         <v>24</v>
       </c>
-      <c r="Q2" s="49"/>
+      <c r="Q2" s="45"/>
       <c r="R2" s="1"/>
       <c r="S2" s="4" t="s">
         <v>25</v>
@@ -5317,31 +5358,31 @@
       </c>
     </row>
     <row r="3" spans="1:21" x14ac:dyDescent="0.45">
-      <c r="A3" s="45"/>
-      <c r="B3" s="45"/>
-      <c r="C3" s="45"/>
-      <c r="D3" s="45"/>
-      <c r="E3" s="45"/>
-      <c r="F3" s="54"/>
+      <c r="A3" s="47"/>
+      <c r="B3" s="47"/>
+      <c r="C3" s="47"/>
+      <c r="D3" s="47"/>
+      <c r="E3" s="47"/>
+      <c r="F3" s="51"/>
       <c r="G3" s="42"/>
       <c r="H3" s="42"/>
       <c r="I3" s="42"/>
       <c r="J3" s="42"/>
       <c r="K3" s="42"/>
-      <c r="L3" s="51">
+      <c r="L3" s="44">
         <v>17485</v>
       </c>
       <c r="M3" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="N3" s="51">
+      <c r="N3" s="44">
         <v>14760</v>
       </c>
-      <c r="O3" s="49"/>
-      <c r="P3" s="51">
+      <c r="O3" s="45"/>
+      <c r="P3" s="44">
         <v>8125</v>
       </c>
-      <c r="Q3" s="49"/>
+      <c r="Q3" s="45"/>
       <c r="R3" s="1"/>
       <c r="S3" s="4" t="s">
         <v>27</v>
@@ -5354,29 +5395,29 @@
       </c>
     </row>
     <row r="4" spans="1:21" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A4" s="46"/>
-      <c r="B4" s="46"/>
-      <c r="C4" s="46"/>
-      <c r="D4" s="46"/>
-      <c r="E4" s="46"/>
-      <c r="F4" s="54"/>
+      <c r="A4" s="48"/>
+      <c r="B4" s="48"/>
+      <c r="C4" s="48"/>
+      <c r="D4" s="48"/>
+      <c r="E4" s="48"/>
+      <c r="F4" s="51"/>
       <c r="G4" s="42"/>
       <c r="H4" s="42"/>
       <c r="I4" s="42"/>
       <c r="J4" s="42"/>
       <c r="K4" s="42"/>
-      <c r="L4" s="46"/>
+      <c r="L4" s="48"/>
       <c r="M4" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="N4" s="55">
+      <c r="N4" s="52">
         <v>34705</v>
       </c>
-      <c r="O4" s="56"/>
-      <c r="P4" s="51">
+      <c r="O4" s="53"/>
+      <c r="P4" s="44">
         <v>13230</v>
       </c>
-      <c r="Q4" s="49"/>
+      <c r="Q4" s="45"/>
       <c r="R4" s="1"/>
       <c r="S4" s="4" t="s">
         <v>29</v>
@@ -5814,6 +5855,16 @@
     </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="A1:A4"/>
+    <mergeCell ref="D1:D4"/>
+    <mergeCell ref="B1:B4"/>
+    <mergeCell ref="L1:L2"/>
+    <mergeCell ref="E1:E4"/>
+    <mergeCell ref="T1:U1"/>
+    <mergeCell ref="N2:O2"/>
+    <mergeCell ref="P2:Q2"/>
+    <mergeCell ref="M1:O1"/>
+    <mergeCell ref="P1:Q1"/>
     <mergeCell ref="P4:Q4"/>
     <mergeCell ref="P3:Q3"/>
     <mergeCell ref="N3:O3"/>
@@ -5821,16 +5872,6 @@
     <mergeCell ref="F1:K4"/>
     <mergeCell ref="L3:L4"/>
     <mergeCell ref="N4:O4"/>
-    <mergeCell ref="T1:U1"/>
-    <mergeCell ref="N2:O2"/>
-    <mergeCell ref="P2:Q2"/>
-    <mergeCell ref="M1:O1"/>
-    <mergeCell ref="P1:Q1"/>
-    <mergeCell ref="A1:A4"/>
-    <mergeCell ref="D1:D4"/>
-    <mergeCell ref="B1:B4"/>
-    <mergeCell ref="L1:L2"/>
-    <mergeCell ref="E1:E4"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="E5:E10">

--- a/input.xlsx
+++ b/input.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\backup01\Desktop\병아리\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9EE35406-3A60-44F5-911A-DF5076888888}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1250C40-765D-429F-8B8F-4936EE965BFC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -730,15 +730,22 @@
     <xf numFmtId="0" fontId="10" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="4" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="9" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="41" fontId="4" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -748,13 +755,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="9" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="백분율" xfId="2" builtinId="5"/>
@@ -1037,7 +1037,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M162"/>
+  <dimension ref="A1:M163"/>
   <sheetFormatPr defaultRowHeight="16" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="12" style="31" customWidth="1"/>
@@ -5255,6 +5255,47 @@
       </c>
       <c r="M162" s="40">
         <v>9412995</v>
+      </c>
+    </row>
+    <row r="163" spans="1:13" ht="16.5" x14ac:dyDescent="0.45">
+      <c r="A163" s="35">
+        <v>46196</v>
+      </c>
+      <c r="B163" s="36">
+        <v>101085650</v>
+      </c>
+      <c r="C163" s="37">
+        <v>8408150</v>
+      </c>
+      <c r="D163" s="38">
+        <v>8203.84</v>
+      </c>
+      <c r="E163" s="37">
+        <v>0</v>
+      </c>
+      <c r="F163" s="40">
+        <v>12277790</v>
+      </c>
+      <c r="G163" s="40">
+        <v>8076840</v>
+      </c>
+      <c r="H163" s="40">
+        <v>7000400</v>
+      </c>
+      <c r="I163" s="40">
+        <v>9920625</v>
+      </c>
+      <c r="J163" s="40">
+        <v>11039875</v>
+      </c>
+      <c r="K163" s="40">
+        <v>26699200</v>
+      </c>
+      <c r="L163" s="40">
+        <v>16658705</v>
+      </c>
+      <c r="M163" s="40">
+        <v>9412215</v>
       </c>
     </row>
   </sheetData>
@@ -5280,72 +5321,72 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:21" x14ac:dyDescent="0.45">
-      <c r="A1" s="46" t="s">
+      <c r="A1" s="44" t="s">
         <v>17</v>
       </c>
-      <c r="B1" s="46" t="s">
+      <c r="B1" s="44" t="s">
         <v>16</v>
       </c>
-      <c r="C1" s="46" t="s">
+      <c r="C1" s="44" t="s">
         <v>18</v>
       </c>
-      <c r="D1" s="46" t="s">
+      <c r="D1" s="44" t="s">
         <v>19</v>
       </c>
-      <c r="E1" s="56" t="s">
+      <c r="E1" s="48" t="s">
         <v>20</v>
       </c>
-      <c r="F1" s="49" t="s">
+      <c r="F1" s="52" t="s">
         <v>21</v>
       </c>
-      <c r="G1" s="50"/>
-      <c r="H1" s="50"/>
-      <c r="I1" s="50"/>
-      <c r="J1" s="50"/>
-      <c r="K1" s="50"/>
-      <c r="L1" s="54">
+      <c r="G1" s="53"/>
+      <c r="H1" s="53"/>
+      <c r="I1" s="53"/>
+      <c r="J1" s="53"/>
+      <c r="K1" s="53"/>
+      <c r="L1" s="47">
         <v>0.7</v>
       </c>
-      <c r="M1" s="46" t="s">
+      <c r="M1" s="44" t="s">
         <v>22</v>
       </c>
-      <c r="N1" s="55"/>
-      <c r="O1" s="45"/>
-      <c r="P1" s="54">
+      <c r="N1" s="50"/>
+      <c r="O1" s="49"/>
+      <c r="P1" s="47">
         <v>0.25</v>
       </c>
-      <c r="Q1" s="45"/>
+      <c r="Q1" s="49"/>
       <c r="R1" s="1"/>
       <c r="S1" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="T1" s="46" t="s">
+      <c r="T1" s="44" t="s">
         <v>23</v>
       </c>
-      <c r="U1" s="45"/>
+      <c r="U1" s="49"/>
     </row>
     <row r="2" spans="1:21" x14ac:dyDescent="0.45">
-      <c r="A2" s="47"/>
-      <c r="B2" s="47"/>
-      <c r="C2" s="47"/>
-      <c r="D2" s="47"/>
-      <c r="E2" s="47"/>
-      <c r="F2" s="51"/>
+      <c r="A2" s="45"/>
+      <c r="B2" s="45"/>
+      <c r="C2" s="45"/>
+      <c r="D2" s="45"/>
+      <c r="E2" s="45"/>
+      <c r="F2" s="54"/>
       <c r="G2" s="42"/>
       <c r="H2" s="42"/>
       <c r="I2" s="42"/>
       <c r="J2" s="42"/>
       <c r="K2" s="42"/>
-      <c r="L2" s="48"/>
+      <c r="L2" s="46"/>
       <c r="M2" s="3"/>
-      <c r="N2" s="54" t="s">
+      <c r="N2" s="47" t="s">
         <v>15</v>
       </c>
-      <c r="O2" s="45"/>
-      <c r="P2" s="46" t="s">
+      <c r="O2" s="49"/>
+      <c r="P2" s="44" t="s">
         <v>24</v>
       </c>
-      <c r="Q2" s="45"/>
+      <c r="Q2" s="49"/>
       <c r="R2" s="1"/>
       <c r="S2" s="4" t="s">
         <v>25</v>
@@ -5358,31 +5399,31 @@
       </c>
     </row>
     <row r="3" spans="1:21" x14ac:dyDescent="0.45">
-      <c r="A3" s="47"/>
-      <c r="B3" s="47"/>
-      <c r="C3" s="47"/>
-      <c r="D3" s="47"/>
-      <c r="E3" s="47"/>
-      <c r="F3" s="51"/>
+      <c r="A3" s="45"/>
+      <c r="B3" s="45"/>
+      <c r="C3" s="45"/>
+      <c r="D3" s="45"/>
+      <c r="E3" s="45"/>
+      <c r="F3" s="54"/>
       <c r="G3" s="42"/>
       <c r="H3" s="42"/>
       <c r="I3" s="42"/>
       <c r="J3" s="42"/>
       <c r="K3" s="42"/>
-      <c r="L3" s="44">
+      <c r="L3" s="51">
         <v>17485</v>
       </c>
       <c r="M3" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="N3" s="44">
+      <c r="N3" s="51">
         <v>14760</v>
       </c>
-      <c r="O3" s="45"/>
-      <c r="P3" s="44">
+      <c r="O3" s="49"/>
+      <c r="P3" s="51">
         <v>8125</v>
       </c>
-      <c r="Q3" s="45"/>
+      <c r="Q3" s="49"/>
       <c r="R3" s="1"/>
       <c r="S3" s="4" t="s">
         <v>27</v>
@@ -5395,29 +5436,29 @@
       </c>
     </row>
     <row r="4" spans="1:21" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A4" s="48"/>
-      <c r="B4" s="48"/>
-      <c r="C4" s="48"/>
-      <c r="D4" s="48"/>
-      <c r="E4" s="48"/>
-      <c r="F4" s="51"/>
+      <c r="A4" s="46"/>
+      <c r="B4" s="46"/>
+      <c r="C4" s="46"/>
+      <c r="D4" s="46"/>
+      <c r="E4" s="46"/>
+      <c r="F4" s="54"/>
       <c r="G4" s="42"/>
       <c r="H4" s="42"/>
       <c r="I4" s="42"/>
       <c r="J4" s="42"/>
       <c r="K4" s="42"/>
-      <c r="L4" s="48"/>
+      <c r="L4" s="46"/>
       <c r="M4" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="N4" s="52">
+      <c r="N4" s="55">
         <v>34705</v>
       </c>
-      <c r="O4" s="53"/>
-      <c r="P4" s="44">
+      <c r="O4" s="56"/>
+      <c r="P4" s="51">
         <v>13230</v>
       </c>
-      <c r="Q4" s="45"/>
+      <c r="Q4" s="49"/>
       <c r="R4" s="1"/>
       <c r="S4" s="4" t="s">
         <v>29</v>
@@ -5855,16 +5896,6 @@
     </row>
   </sheetData>
   <mergeCells count="17">
-    <mergeCell ref="A1:A4"/>
-    <mergeCell ref="D1:D4"/>
-    <mergeCell ref="B1:B4"/>
-    <mergeCell ref="L1:L2"/>
-    <mergeCell ref="E1:E4"/>
-    <mergeCell ref="T1:U1"/>
-    <mergeCell ref="N2:O2"/>
-    <mergeCell ref="P2:Q2"/>
-    <mergeCell ref="M1:O1"/>
-    <mergeCell ref="P1:Q1"/>
     <mergeCell ref="P4:Q4"/>
     <mergeCell ref="P3:Q3"/>
     <mergeCell ref="N3:O3"/>
@@ -5872,6 +5903,16 @@
     <mergeCell ref="F1:K4"/>
     <mergeCell ref="L3:L4"/>
     <mergeCell ref="N4:O4"/>
+    <mergeCell ref="T1:U1"/>
+    <mergeCell ref="N2:O2"/>
+    <mergeCell ref="P2:Q2"/>
+    <mergeCell ref="M1:O1"/>
+    <mergeCell ref="P1:Q1"/>
+    <mergeCell ref="A1:A4"/>
+    <mergeCell ref="D1:D4"/>
+    <mergeCell ref="B1:B4"/>
+    <mergeCell ref="L1:L2"/>
+    <mergeCell ref="E1:E4"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="E5:E10">

--- a/input.xlsx
+++ b/input.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\backup01\Desktop\병아리\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1250C40-765D-429F-8B8F-4936EE965BFC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7AB5A71-8351-4754-A3B5-230621E33BE7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -730,22 +730,15 @@
     <xf numFmtId="0" fontId="10" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="41" fontId="4" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="9" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="41" fontId="4" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -755,6 +748,13 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="9" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="백분율" xfId="2" builtinId="5"/>
@@ -1037,7 +1037,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M163"/>
+  <dimension ref="A1:M164"/>
   <sheetFormatPr defaultRowHeight="16" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="12" style="31" customWidth="1"/>
@@ -5296,6 +5296,47 @@
       </c>
       <c r="M163" s="40">
         <v>9412215</v>
+      </c>
+    </row>
+    <row r="164" spans="1:13" ht="16.5" x14ac:dyDescent="0.45">
+      <c r="A164" s="35">
+        <v>46197</v>
+      </c>
+      <c r="B164" s="36">
+        <v>98741000</v>
+      </c>
+      <c r="C164" s="37">
+        <v>-6422995</v>
+      </c>
+      <c r="D164" s="38">
+        <v>8507.81</v>
+      </c>
+      <c r="E164" s="37">
+        <v>823904</v>
+      </c>
+      <c r="F164" s="40">
+        <v>12971870</v>
+      </c>
+      <c r="G164" s="40">
+        <v>8577230</v>
+      </c>
+      <c r="H164" s="40">
+        <v>7272160</v>
+      </c>
+      <c r="I164" s="40">
+        <v>10305750</v>
+      </c>
+      <c r="J164" s="40">
+        <v>11468450</v>
+      </c>
+      <c r="K164" s="40">
+        <v>27735680</v>
+      </c>
+      <c r="L164" s="40">
+        <v>14163800</v>
+      </c>
+      <c r="M164" s="40">
+        <v>6246060</v>
       </c>
     </row>
   </sheetData>
@@ -5321,72 +5362,72 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:21" x14ac:dyDescent="0.45">
-      <c r="A1" s="44" t="s">
+      <c r="A1" s="46" t="s">
         <v>17</v>
       </c>
-      <c r="B1" s="44" t="s">
+      <c r="B1" s="46" t="s">
         <v>16</v>
       </c>
-      <c r="C1" s="44" t="s">
+      <c r="C1" s="46" t="s">
         <v>18</v>
       </c>
-      <c r="D1" s="44" t="s">
+      <c r="D1" s="46" t="s">
         <v>19</v>
       </c>
-      <c r="E1" s="48" t="s">
+      <c r="E1" s="56" t="s">
         <v>20</v>
       </c>
-      <c r="F1" s="52" t="s">
+      <c r="F1" s="49" t="s">
         <v>21</v>
       </c>
-      <c r="G1" s="53"/>
-      <c r="H1" s="53"/>
-      <c r="I1" s="53"/>
-      <c r="J1" s="53"/>
-      <c r="K1" s="53"/>
-      <c r="L1" s="47">
+      <c r="G1" s="50"/>
+      <c r="H1" s="50"/>
+      <c r="I1" s="50"/>
+      <c r="J1" s="50"/>
+      <c r="K1" s="50"/>
+      <c r="L1" s="54">
         <v>0.7</v>
       </c>
-      <c r="M1" s="44" t="s">
+      <c r="M1" s="46" t="s">
         <v>22</v>
       </c>
-      <c r="N1" s="50"/>
-      <c r="O1" s="49"/>
-      <c r="P1" s="47">
+      <c r="N1" s="55"/>
+      <c r="O1" s="45"/>
+      <c r="P1" s="54">
         <v>0.25</v>
       </c>
-      <c r="Q1" s="49"/>
+      <c r="Q1" s="45"/>
       <c r="R1" s="1"/>
       <c r="S1" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="T1" s="44" t="s">
+      <c r="T1" s="46" t="s">
         <v>23</v>
       </c>
-      <c r="U1" s="49"/>
+      <c r="U1" s="45"/>
     </row>
     <row r="2" spans="1:21" x14ac:dyDescent="0.45">
-      <c r="A2" s="45"/>
-      <c r="B2" s="45"/>
-      <c r="C2" s="45"/>
-      <c r="D2" s="45"/>
-      <c r="E2" s="45"/>
-      <c r="F2" s="54"/>
+      <c r="A2" s="47"/>
+      <c r="B2" s="47"/>
+      <c r="C2" s="47"/>
+      <c r="D2" s="47"/>
+      <c r="E2" s="47"/>
+      <c r="F2" s="51"/>
       <c r="G2" s="42"/>
       <c r="H2" s="42"/>
       <c r="I2" s="42"/>
       <c r="J2" s="42"/>
       <c r="K2" s="42"/>
-      <c r="L2" s="46"/>
+      <c r="L2" s="48"/>
       <c r="M2" s="3"/>
-      <c r="N2" s="47" t="s">
+      <c r="N2" s="54" t="s">
         <v>15</v>
       </c>
-      <c r="O2" s="49"/>
-      <c r="P2" s="44" t="s">
+      <c r="O2" s="45"/>
+      <c r="P2" s="46" t="s">
         <v>24</v>
       </c>
-      <c r="Q2" s="49"/>
+      <c r="Q2" s="45"/>
       <c r="R2" s="1"/>
       <c r="S2" s="4" t="s">
         <v>25</v>
@@ -5399,31 +5440,31 @@
       </c>
     </row>
     <row r="3" spans="1:21" x14ac:dyDescent="0.45">
-      <c r="A3" s="45"/>
-      <c r="B3" s="45"/>
-      <c r="C3" s="45"/>
-      <c r="D3" s="45"/>
-      <c r="E3" s="45"/>
-      <c r="F3" s="54"/>
+      <c r="A3" s="47"/>
+      <c r="B3" s="47"/>
+      <c r="C3" s="47"/>
+      <c r="D3" s="47"/>
+      <c r="E3" s="47"/>
+      <c r="F3" s="51"/>
       <c r="G3" s="42"/>
       <c r="H3" s="42"/>
       <c r="I3" s="42"/>
       <c r="J3" s="42"/>
       <c r="K3" s="42"/>
-      <c r="L3" s="51">
+      <c r="L3" s="44">
         <v>17485</v>
       </c>
       <c r="M3" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="N3" s="51">
+      <c r="N3" s="44">
         <v>14760</v>
       </c>
-      <c r="O3" s="49"/>
-      <c r="P3" s="51">
+      <c r="O3" s="45"/>
+      <c r="P3" s="44">
         <v>8125</v>
       </c>
-      <c r="Q3" s="49"/>
+      <c r="Q3" s="45"/>
       <c r="R3" s="1"/>
       <c r="S3" s="4" t="s">
         <v>27</v>
@@ -5436,29 +5477,29 @@
       </c>
     </row>
     <row r="4" spans="1:21" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A4" s="46"/>
-      <c r="B4" s="46"/>
-      <c r="C4" s="46"/>
-      <c r="D4" s="46"/>
-      <c r="E4" s="46"/>
-      <c r="F4" s="54"/>
+      <c r="A4" s="48"/>
+      <c r="B4" s="48"/>
+      <c r="C4" s="48"/>
+      <c r="D4" s="48"/>
+      <c r="E4" s="48"/>
+      <c r="F4" s="51"/>
       <c r="G4" s="42"/>
       <c r="H4" s="42"/>
       <c r="I4" s="42"/>
       <c r="J4" s="42"/>
       <c r="K4" s="42"/>
-      <c r="L4" s="46"/>
+      <c r="L4" s="48"/>
       <c r="M4" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="N4" s="55">
+      <c r="N4" s="52">
         <v>34705</v>
       </c>
-      <c r="O4" s="56"/>
-      <c r="P4" s="51">
+      <c r="O4" s="53"/>
+      <c r="P4" s="44">
         <v>13230</v>
       </c>
-      <c r="Q4" s="49"/>
+      <c r="Q4" s="45"/>
       <c r="R4" s="1"/>
       <c r="S4" s="4" t="s">
         <v>29</v>
@@ -5896,6 +5937,16 @@
     </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="A1:A4"/>
+    <mergeCell ref="D1:D4"/>
+    <mergeCell ref="B1:B4"/>
+    <mergeCell ref="L1:L2"/>
+    <mergeCell ref="E1:E4"/>
+    <mergeCell ref="T1:U1"/>
+    <mergeCell ref="N2:O2"/>
+    <mergeCell ref="P2:Q2"/>
+    <mergeCell ref="M1:O1"/>
+    <mergeCell ref="P1:Q1"/>
     <mergeCell ref="P4:Q4"/>
     <mergeCell ref="P3:Q3"/>
     <mergeCell ref="N3:O3"/>
@@ -5903,16 +5954,6 @@
     <mergeCell ref="F1:K4"/>
     <mergeCell ref="L3:L4"/>
     <mergeCell ref="N4:O4"/>
-    <mergeCell ref="T1:U1"/>
-    <mergeCell ref="N2:O2"/>
-    <mergeCell ref="P2:Q2"/>
-    <mergeCell ref="M1:O1"/>
-    <mergeCell ref="P1:Q1"/>
-    <mergeCell ref="A1:A4"/>
-    <mergeCell ref="D1:D4"/>
-    <mergeCell ref="B1:B4"/>
-    <mergeCell ref="L1:L2"/>
-    <mergeCell ref="E1:E4"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="E5:E10">

--- a/input.xlsx
+++ b/input.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\backup01\Desktop\병아리\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7AB5A71-8351-4754-A3B5-230621E33BE7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30EB9794-8DDC-4E72-BA35-621E73302DA6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="25490" yWindow="690" windowWidth="25820" windowHeight="13900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="INPUT" sheetId="1" r:id="rId1"/>
@@ -730,15 +730,22 @@
     <xf numFmtId="0" fontId="10" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="4" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="9" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="41" fontId="4" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -748,13 +755,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="9" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="백분율" xfId="2" builtinId="5"/>
@@ -1037,7 +1037,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M164"/>
+  <dimension ref="A1:M165"/>
   <sheetFormatPr defaultRowHeight="16" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="12" style="31" customWidth="1"/>
@@ -5337,6 +5337,47 @@
       </c>
       <c r="M164" s="40">
         <v>6246060</v>
+      </c>
+    </row>
+    <row r="165" spans="1:13" ht="16.5" x14ac:dyDescent="0.45">
+      <c r="A165" s="35">
+        <v>46198</v>
+      </c>
+      <c r="B165" s="36">
+        <v>101114800</v>
+      </c>
+      <c r="C165" s="37">
+        <v>5958590</v>
+      </c>
+      <c r="D165" s="38">
+        <v>8930.2999999999993</v>
+      </c>
+      <c r="E165" s="37">
+        <v>5958590</v>
+      </c>
+      <c r="F165" s="40">
+        <v>13130820</v>
+      </c>
+      <c r="G165" s="40">
+        <v>8459510</v>
+      </c>
+      <c r="H165" s="40">
+        <v>6900640</v>
+      </c>
+      <c r="I165" s="40">
+        <v>9779250</v>
+      </c>
+      <c r="J165" s="40">
+        <v>10882550</v>
+      </c>
+      <c r="K165" s="40">
+        <v>26318720</v>
+      </c>
+      <c r="L165" s="40">
+        <v>19398020</v>
+      </c>
+      <c r="M165" s="40">
+        <v>6245290</v>
       </c>
     </row>
   </sheetData>
@@ -5362,72 +5403,72 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:21" x14ac:dyDescent="0.45">
-      <c r="A1" s="46" t="s">
+      <c r="A1" s="44" t="s">
         <v>17</v>
       </c>
-      <c r="B1" s="46" t="s">
+      <c r="B1" s="44" t="s">
         <v>16</v>
       </c>
-      <c r="C1" s="46" t="s">
+      <c r="C1" s="44" t="s">
         <v>18</v>
       </c>
-      <c r="D1" s="46" t="s">
+      <c r="D1" s="44" t="s">
         <v>19</v>
       </c>
-      <c r="E1" s="56" t="s">
+      <c r="E1" s="48" t="s">
         <v>20</v>
       </c>
-      <c r="F1" s="49" t="s">
+      <c r="F1" s="52" t="s">
         <v>21</v>
       </c>
-      <c r="G1" s="50"/>
-      <c r="H1" s="50"/>
-      <c r="I1" s="50"/>
-      <c r="J1" s="50"/>
-      <c r="K1" s="50"/>
-      <c r="L1" s="54">
+      <c r="G1" s="53"/>
+      <c r="H1" s="53"/>
+      <c r="I1" s="53"/>
+      <c r="J1" s="53"/>
+      <c r="K1" s="53"/>
+      <c r="L1" s="47">
         <v>0.7</v>
       </c>
-      <c r="M1" s="46" t="s">
+      <c r="M1" s="44" t="s">
         <v>22</v>
       </c>
-      <c r="N1" s="55"/>
-      <c r="O1" s="45"/>
-      <c r="P1" s="54">
+      <c r="N1" s="50"/>
+      <c r="O1" s="49"/>
+      <c r="P1" s="47">
         <v>0.25</v>
       </c>
-      <c r="Q1" s="45"/>
+      <c r="Q1" s="49"/>
       <c r="R1" s="1"/>
       <c r="S1" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="T1" s="46" t="s">
+      <c r="T1" s="44" t="s">
         <v>23</v>
       </c>
-      <c r="U1" s="45"/>
+      <c r="U1" s="49"/>
     </row>
     <row r="2" spans="1:21" x14ac:dyDescent="0.45">
-      <c r="A2" s="47"/>
-      <c r="B2" s="47"/>
-      <c r="C2" s="47"/>
-      <c r="D2" s="47"/>
-      <c r="E2" s="47"/>
-      <c r="F2" s="51"/>
+      <c r="A2" s="45"/>
+      <c r="B2" s="45"/>
+      <c r="C2" s="45"/>
+      <c r="D2" s="45"/>
+      <c r="E2" s="45"/>
+      <c r="F2" s="54"/>
       <c r="G2" s="42"/>
       <c r="H2" s="42"/>
       <c r="I2" s="42"/>
       <c r="J2" s="42"/>
       <c r="K2" s="42"/>
-      <c r="L2" s="48"/>
+      <c r="L2" s="46"/>
       <c r="M2" s="3"/>
-      <c r="N2" s="54" t="s">
+      <c r="N2" s="47" t="s">
         <v>15</v>
       </c>
-      <c r="O2" s="45"/>
-      <c r="P2" s="46" t="s">
+      <c r="O2" s="49"/>
+      <c r="P2" s="44" t="s">
         <v>24</v>
       </c>
-      <c r="Q2" s="45"/>
+      <c r="Q2" s="49"/>
       <c r="R2" s="1"/>
       <c r="S2" s="4" t="s">
         <v>25</v>
@@ -5440,31 +5481,31 @@
       </c>
     </row>
     <row r="3" spans="1:21" x14ac:dyDescent="0.45">
-      <c r="A3" s="47"/>
-      <c r="B3" s="47"/>
-      <c r="C3" s="47"/>
-      <c r="D3" s="47"/>
-      <c r="E3" s="47"/>
-      <c r="F3" s="51"/>
+      <c r="A3" s="45"/>
+      <c r="B3" s="45"/>
+      <c r="C3" s="45"/>
+      <c r="D3" s="45"/>
+      <c r="E3" s="45"/>
+      <c r="F3" s="54"/>
       <c r="G3" s="42"/>
       <c r="H3" s="42"/>
       <c r="I3" s="42"/>
       <c r="J3" s="42"/>
       <c r="K3" s="42"/>
-      <c r="L3" s="44">
+      <c r="L3" s="51">
         <v>17485</v>
       </c>
       <c r="M3" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="N3" s="44">
+      <c r="N3" s="51">
         <v>14760</v>
       </c>
-      <c r="O3" s="45"/>
-      <c r="P3" s="44">
+      <c r="O3" s="49"/>
+      <c r="P3" s="51">
         <v>8125</v>
       </c>
-      <c r="Q3" s="45"/>
+      <c r="Q3" s="49"/>
       <c r="R3" s="1"/>
       <c r="S3" s="4" t="s">
         <v>27</v>
@@ -5477,29 +5518,29 @@
       </c>
     </row>
     <row r="4" spans="1:21" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A4" s="48"/>
-      <c r="B4" s="48"/>
-      <c r="C4" s="48"/>
-      <c r="D4" s="48"/>
-      <c r="E4" s="48"/>
-      <c r="F4" s="51"/>
+      <c r="A4" s="46"/>
+      <c r="B4" s="46"/>
+      <c r="C4" s="46"/>
+      <c r="D4" s="46"/>
+      <c r="E4" s="46"/>
+      <c r="F4" s="54"/>
       <c r="G4" s="42"/>
       <c r="H4" s="42"/>
       <c r="I4" s="42"/>
       <c r="J4" s="42"/>
       <c r="K4" s="42"/>
-      <c r="L4" s="48"/>
+      <c r="L4" s="46"/>
       <c r="M4" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="N4" s="52">
+      <c r="N4" s="55">
         <v>34705</v>
       </c>
-      <c r="O4" s="53"/>
-      <c r="P4" s="44">
+      <c r="O4" s="56"/>
+      <c r="P4" s="51">
         <v>13230</v>
       </c>
-      <c r="Q4" s="45"/>
+      <c r="Q4" s="49"/>
       <c r="R4" s="1"/>
       <c r="S4" s="4" t="s">
         <v>29</v>
@@ -5937,16 +5978,6 @@
     </row>
   </sheetData>
   <mergeCells count="17">
-    <mergeCell ref="A1:A4"/>
-    <mergeCell ref="D1:D4"/>
-    <mergeCell ref="B1:B4"/>
-    <mergeCell ref="L1:L2"/>
-    <mergeCell ref="E1:E4"/>
-    <mergeCell ref="T1:U1"/>
-    <mergeCell ref="N2:O2"/>
-    <mergeCell ref="P2:Q2"/>
-    <mergeCell ref="M1:O1"/>
-    <mergeCell ref="P1:Q1"/>
     <mergeCell ref="P4:Q4"/>
     <mergeCell ref="P3:Q3"/>
     <mergeCell ref="N3:O3"/>
@@ -5954,6 +5985,16 @@
     <mergeCell ref="F1:K4"/>
     <mergeCell ref="L3:L4"/>
     <mergeCell ref="N4:O4"/>
+    <mergeCell ref="T1:U1"/>
+    <mergeCell ref="N2:O2"/>
+    <mergeCell ref="P2:Q2"/>
+    <mergeCell ref="M1:O1"/>
+    <mergeCell ref="P1:Q1"/>
+    <mergeCell ref="A1:A4"/>
+    <mergeCell ref="D1:D4"/>
+    <mergeCell ref="B1:B4"/>
+    <mergeCell ref="L1:L2"/>
+    <mergeCell ref="E1:E4"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="E5:E10">

--- a/input.xlsx
+++ b/input.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\backup01\Desktop\병아리\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30EB9794-8DDC-4E72-BA35-621E73302DA6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F1282F6-A30E-4E65-8700-859F455AB7FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="25490" yWindow="690" windowWidth="25820" windowHeight="13900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="INPUT" sheetId="1" r:id="rId1"/>
@@ -730,22 +730,15 @@
     <xf numFmtId="0" fontId="10" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="41" fontId="4" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="9" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="41" fontId="4" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -755,6 +748,13 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="9" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="백분율" xfId="2" builtinId="5"/>
@@ -5353,7 +5353,7 @@
         <v>8930.2999999999993</v>
       </c>
       <c r="E165" s="37">
-        <v>5958590</v>
+        <v>314105</v>
       </c>
       <c r="F165" s="40">
         <v>13130820</v>
@@ -5403,72 +5403,72 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:21" x14ac:dyDescent="0.45">
-      <c r="A1" s="44" t="s">
+      <c r="A1" s="46" t="s">
         <v>17</v>
       </c>
-      <c r="B1" s="44" t="s">
+      <c r="B1" s="46" t="s">
         <v>16</v>
       </c>
-      <c r="C1" s="44" t="s">
+      <c r="C1" s="46" t="s">
         <v>18</v>
       </c>
-      <c r="D1" s="44" t="s">
+      <c r="D1" s="46" t="s">
         <v>19</v>
       </c>
-      <c r="E1" s="48" t="s">
+      <c r="E1" s="56" t="s">
         <v>20</v>
       </c>
-      <c r="F1" s="52" t="s">
+      <c r="F1" s="49" t="s">
         <v>21</v>
       </c>
-      <c r="G1" s="53"/>
-      <c r="H1" s="53"/>
-      <c r="I1" s="53"/>
-      <c r="J1" s="53"/>
-      <c r="K1" s="53"/>
-      <c r="L1" s="47">
+      <c r="G1" s="50"/>
+      <c r="H1" s="50"/>
+      <c r="I1" s="50"/>
+      <c r="J1" s="50"/>
+      <c r="K1" s="50"/>
+      <c r="L1" s="54">
         <v>0.7</v>
       </c>
-      <c r="M1" s="44" t="s">
+      <c r="M1" s="46" t="s">
         <v>22</v>
       </c>
-      <c r="N1" s="50"/>
-      <c r="O1" s="49"/>
-      <c r="P1" s="47">
+      <c r="N1" s="55"/>
+      <c r="O1" s="45"/>
+      <c r="P1" s="54">
         <v>0.25</v>
       </c>
-      <c r="Q1" s="49"/>
+      <c r="Q1" s="45"/>
       <c r="R1" s="1"/>
       <c r="S1" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="T1" s="44" t="s">
+      <c r="T1" s="46" t="s">
         <v>23</v>
       </c>
-      <c r="U1" s="49"/>
+      <c r="U1" s="45"/>
     </row>
     <row r="2" spans="1:21" x14ac:dyDescent="0.45">
-      <c r="A2" s="45"/>
-      <c r="B2" s="45"/>
-      <c r="C2" s="45"/>
-      <c r="D2" s="45"/>
-      <c r="E2" s="45"/>
-      <c r="F2" s="54"/>
+      <c r="A2" s="47"/>
+      <c r="B2" s="47"/>
+      <c r="C2" s="47"/>
+      <c r="D2" s="47"/>
+      <c r="E2" s="47"/>
+      <c r="F2" s="51"/>
       <c r="G2" s="42"/>
       <c r="H2" s="42"/>
       <c r="I2" s="42"/>
       <c r="J2" s="42"/>
       <c r="K2" s="42"/>
-      <c r="L2" s="46"/>
+      <c r="L2" s="48"/>
       <c r="M2" s="3"/>
-      <c r="N2" s="47" t="s">
+      <c r="N2" s="54" t="s">
         <v>15</v>
       </c>
-      <c r="O2" s="49"/>
-      <c r="P2" s="44" t="s">
+      <c r="O2" s="45"/>
+      <c r="P2" s="46" t="s">
         <v>24</v>
       </c>
-      <c r="Q2" s="49"/>
+      <c r="Q2" s="45"/>
       <c r="R2" s="1"/>
       <c r="S2" s="4" t="s">
         <v>25</v>
@@ -5481,31 +5481,31 @@
       </c>
     </row>
     <row r="3" spans="1:21" x14ac:dyDescent="0.45">
-      <c r="A3" s="45"/>
-      <c r="B3" s="45"/>
-      <c r="C3" s="45"/>
-      <c r="D3" s="45"/>
-      <c r="E3" s="45"/>
-      <c r="F3" s="54"/>
+      <c r="A3" s="47"/>
+      <c r="B3" s="47"/>
+      <c r="C3" s="47"/>
+      <c r="D3" s="47"/>
+      <c r="E3" s="47"/>
+      <c r="F3" s="51"/>
       <c r="G3" s="42"/>
       <c r="H3" s="42"/>
       <c r="I3" s="42"/>
       <c r="J3" s="42"/>
       <c r="K3" s="42"/>
-      <c r="L3" s="51">
+      <c r="L3" s="44">
         <v>17485</v>
       </c>
       <c r="M3" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="N3" s="51">
+      <c r="N3" s="44">
         <v>14760</v>
       </c>
-      <c r="O3" s="49"/>
-      <c r="P3" s="51">
+      <c r="O3" s="45"/>
+      <c r="P3" s="44">
         <v>8125</v>
       </c>
-      <c r="Q3" s="49"/>
+      <c r="Q3" s="45"/>
       <c r="R3" s="1"/>
       <c r="S3" s="4" t="s">
         <v>27</v>
@@ -5518,29 +5518,29 @@
       </c>
     </row>
     <row r="4" spans="1:21" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A4" s="46"/>
-      <c r="B4" s="46"/>
-      <c r="C4" s="46"/>
-      <c r="D4" s="46"/>
-      <c r="E4" s="46"/>
-      <c r="F4" s="54"/>
+      <c r="A4" s="48"/>
+      <c r="B4" s="48"/>
+      <c r="C4" s="48"/>
+      <c r="D4" s="48"/>
+      <c r="E4" s="48"/>
+      <c r="F4" s="51"/>
       <c r="G4" s="42"/>
       <c r="H4" s="42"/>
       <c r="I4" s="42"/>
       <c r="J4" s="42"/>
       <c r="K4" s="42"/>
-      <c r="L4" s="46"/>
+      <c r="L4" s="48"/>
       <c r="M4" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="N4" s="55">
+      <c r="N4" s="52">
         <v>34705</v>
       </c>
-      <c r="O4" s="56"/>
-      <c r="P4" s="51">
+      <c r="O4" s="53"/>
+      <c r="P4" s="44">
         <v>13230</v>
       </c>
-      <c r="Q4" s="49"/>
+      <c r="Q4" s="45"/>
       <c r="R4" s="1"/>
       <c r="S4" s="4" t="s">
         <v>29</v>
@@ -5978,6 +5978,16 @@
     </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="A1:A4"/>
+    <mergeCell ref="D1:D4"/>
+    <mergeCell ref="B1:B4"/>
+    <mergeCell ref="L1:L2"/>
+    <mergeCell ref="E1:E4"/>
+    <mergeCell ref="T1:U1"/>
+    <mergeCell ref="N2:O2"/>
+    <mergeCell ref="P2:Q2"/>
+    <mergeCell ref="M1:O1"/>
+    <mergeCell ref="P1:Q1"/>
     <mergeCell ref="P4:Q4"/>
     <mergeCell ref="P3:Q3"/>
     <mergeCell ref="N3:O3"/>
@@ -5985,16 +5995,6 @@
     <mergeCell ref="F1:K4"/>
     <mergeCell ref="L3:L4"/>
     <mergeCell ref="N4:O4"/>
-    <mergeCell ref="T1:U1"/>
-    <mergeCell ref="N2:O2"/>
-    <mergeCell ref="P2:Q2"/>
-    <mergeCell ref="M1:O1"/>
-    <mergeCell ref="P1:Q1"/>
-    <mergeCell ref="A1:A4"/>
-    <mergeCell ref="D1:D4"/>
-    <mergeCell ref="B1:B4"/>
-    <mergeCell ref="L1:L2"/>
-    <mergeCell ref="E1:E4"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="E5:E10">

--- a/input.xlsx
+++ b/input.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\backup01\Desktop\병아리\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F1282F6-A30E-4E65-8700-859F455AB7FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A95090AB-FC02-4DA7-A95D-787FA4691E3E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -730,15 +730,22 @@
     <xf numFmtId="0" fontId="10" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="4" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="9" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="41" fontId="4" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -748,13 +755,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="9" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="백분율" xfId="2" builtinId="5"/>
@@ -1037,7 +1037,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M165"/>
+  <dimension ref="A1:M166"/>
   <sheetFormatPr defaultRowHeight="16" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="12" style="31" customWidth="1"/>
@@ -5378,6 +5378,47 @@
       </c>
       <c r="M165" s="40">
         <v>6245290</v>
+      </c>
+    </row>
+    <row r="166" spans="1:13" ht="16.5" x14ac:dyDescent="0.45">
+      <c r="A166" s="35">
+        <v>46199</v>
+      </c>
+      <c r="B166" s="36">
+        <v>99721380</v>
+      </c>
+      <c r="C166" s="37">
+        <v>5780075</v>
+      </c>
+      <c r="D166" s="38">
+        <v>8411.2099999999991</v>
+      </c>
+      <c r="E166" s="37">
+        <v>0</v>
+      </c>
+      <c r="F166" s="40">
+        <v>12765350</v>
+      </c>
+      <c r="G166" s="40">
+        <v>8011840</v>
+      </c>
+      <c r="H166" s="40">
+        <v>6350240</v>
+      </c>
+      <c r="I166" s="40">
+        <v>8999250</v>
+      </c>
+      <c r="J166" s="40">
+        <v>10014550</v>
+      </c>
+      <c r="K166" s="40">
+        <v>24219520</v>
+      </c>
+      <c r="L166" s="40">
+        <v>17850820</v>
+      </c>
+      <c r="M166" s="40">
+        <v>11509810</v>
       </c>
     </row>
   </sheetData>
@@ -5403,72 +5444,72 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:21" x14ac:dyDescent="0.45">
-      <c r="A1" s="46" t="s">
+      <c r="A1" s="44" t="s">
         <v>17</v>
       </c>
-      <c r="B1" s="46" t="s">
+      <c r="B1" s="44" t="s">
         <v>16</v>
       </c>
-      <c r="C1" s="46" t="s">
+      <c r="C1" s="44" t="s">
         <v>18</v>
       </c>
-      <c r="D1" s="46" t="s">
+      <c r="D1" s="44" t="s">
         <v>19</v>
       </c>
-      <c r="E1" s="56" t="s">
+      <c r="E1" s="48" t="s">
         <v>20</v>
       </c>
-      <c r="F1" s="49" t="s">
+      <c r="F1" s="52" t="s">
         <v>21</v>
       </c>
-      <c r="G1" s="50"/>
-      <c r="H1" s="50"/>
-      <c r="I1" s="50"/>
-      <c r="J1" s="50"/>
-      <c r="K1" s="50"/>
-      <c r="L1" s="54">
+      <c r="G1" s="53"/>
+      <c r="H1" s="53"/>
+      <c r="I1" s="53"/>
+      <c r="J1" s="53"/>
+      <c r="K1" s="53"/>
+      <c r="L1" s="47">
         <v>0.7</v>
       </c>
-      <c r="M1" s="46" t="s">
+      <c r="M1" s="44" t="s">
         <v>22</v>
       </c>
-      <c r="N1" s="55"/>
-      <c r="O1" s="45"/>
-      <c r="P1" s="54">
+      <c r="N1" s="50"/>
+      <c r="O1" s="49"/>
+      <c r="P1" s="47">
         <v>0.25</v>
       </c>
-      <c r="Q1" s="45"/>
+      <c r="Q1" s="49"/>
       <c r="R1" s="1"/>
       <c r="S1" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="T1" s="46" t="s">
+      <c r="T1" s="44" t="s">
         <v>23</v>
       </c>
-      <c r="U1" s="45"/>
+      <c r="U1" s="49"/>
     </row>
     <row r="2" spans="1:21" x14ac:dyDescent="0.45">
-      <c r="A2" s="47"/>
-      <c r="B2" s="47"/>
-      <c r="C2" s="47"/>
-      <c r="D2" s="47"/>
-      <c r="E2" s="47"/>
-      <c r="F2" s="51"/>
+      <c r="A2" s="45"/>
+      <c r="B2" s="45"/>
+      <c r="C2" s="45"/>
+      <c r="D2" s="45"/>
+      <c r="E2" s="45"/>
+      <c r="F2" s="54"/>
       <c r="G2" s="42"/>
       <c r="H2" s="42"/>
       <c r="I2" s="42"/>
       <c r="J2" s="42"/>
       <c r="K2" s="42"/>
-      <c r="L2" s="48"/>
+      <c r="L2" s="46"/>
       <c r="M2" s="3"/>
-      <c r="N2" s="54" t="s">
+      <c r="N2" s="47" t="s">
         <v>15</v>
       </c>
-      <c r="O2" s="45"/>
-      <c r="P2" s="46" t="s">
+      <c r="O2" s="49"/>
+      <c r="P2" s="44" t="s">
         <v>24</v>
       </c>
-      <c r="Q2" s="45"/>
+      <c r="Q2" s="49"/>
       <c r="R2" s="1"/>
       <c r="S2" s="4" t="s">
         <v>25</v>
@@ -5481,31 +5522,31 @@
       </c>
     </row>
     <row r="3" spans="1:21" x14ac:dyDescent="0.45">
-      <c r="A3" s="47"/>
-      <c r="B3" s="47"/>
-      <c r="C3" s="47"/>
-      <c r="D3" s="47"/>
-      <c r="E3" s="47"/>
-      <c r="F3" s="51"/>
+      <c r="A3" s="45"/>
+      <c r="B3" s="45"/>
+      <c r="C3" s="45"/>
+      <c r="D3" s="45"/>
+      <c r="E3" s="45"/>
+      <c r="F3" s="54"/>
       <c r="G3" s="42"/>
       <c r="H3" s="42"/>
       <c r="I3" s="42"/>
       <c r="J3" s="42"/>
       <c r="K3" s="42"/>
-      <c r="L3" s="44">
+      <c r="L3" s="51">
         <v>17485</v>
       </c>
       <c r="M3" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="N3" s="44">
+      <c r="N3" s="51">
         <v>14760</v>
       </c>
-      <c r="O3" s="45"/>
-      <c r="P3" s="44">
+      <c r="O3" s="49"/>
+      <c r="P3" s="51">
         <v>8125</v>
       </c>
-      <c r="Q3" s="45"/>
+      <c r="Q3" s="49"/>
       <c r="R3" s="1"/>
       <c r="S3" s="4" t="s">
         <v>27</v>
@@ -5518,29 +5559,29 @@
       </c>
     </row>
     <row r="4" spans="1:21" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A4" s="48"/>
-      <c r="B4" s="48"/>
-      <c r="C4" s="48"/>
-      <c r="D4" s="48"/>
-      <c r="E4" s="48"/>
-      <c r="F4" s="51"/>
+      <c r="A4" s="46"/>
+      <c r="B4" s="46"/>
+      <c r="C4" s="46"/>
+      <c r="D4" s="46"/>
+      <c r="E4" s="46"/>
+      <c r="F4" s="54"/>
       <c r="G4" s="42"/>
       <c r="H4" s="42"/>
       <c r="I4" s="42"/>
       <c r="J4" s="42"/>
       <c r="K4" s="42"/>
-      <c r="L4" s="48"/>
+      <c r="L4" s="46"/>
       <c r="M4" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="N4" s="52">
+      <c r="N4" s="55">
         <v>34705</v>
       </c>
-      <c r="O4" s="53"/>
-      <c r="P4" s="44">
+      <c r="O4" s="56"/>
+      <c r="P4" s="51">
         <v>13230</v>
       </c>
-      <c r="Q4" s="45"/>
+      <c r="Q4" s="49"/>
       <c r="R4" s="1"/>
       <c r="S4" s="4" t="s">
         <v>29</v>
@@ -5978,16 +6019,6 @@
     </row>
   </sheetData>
   <mergeCells count="17">
-    <mergeCell ref="A1:A4"/>
-    <mergeCell ref="D1:D4"/>
-    <mergeCell ref="B1:B4"/>
-    <mergeCell ref="L1:L2"/>
-    <mergeCell ref="E1:E4"/>
-    <mergeCell ref="T1:U1"/>
-    <mergeCell ref="N2:O2"/>
-    <mergeCell ref="P2:Q2"/>
-    <mergeCell ref="M1:O1"/>
-    <mergeCell ref="P1:Q1"/>
     <mergeCell ref="P4:Q4"/>
     <mergeCell ref="P3:Q3"/>
     <mergeCell ref="N3:O3"/>
@@ -5995,6 +6026,16 @@
     <mergeCell ref="F1:K4"/>
     <mergeCell ref="L3:L4"/>
     <mergeCell ref="N4:O4"/>
+    <mergeCell ref="T1:U1"/>
+    <mergeCell ref="N2:O2"/>
+    <mergeCell ref="P2:Q2"/>
+    <mergeCell ref="M1:O1"/>
+    <mergeCell ref="P1:Q1"/>
+    <mergeCell ref="A1:A4"/>
+    <mergeCell ref="D1:D4"/>
+    <mergeCell ref="B1:B4"/>
+    <mergeCell ref="L1:L2"/>
+    <mergeCell ref="E1:E4"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="E5:E10">

--- a/input.xlsx
+++ b/input.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\backup01\Desktop\병아리\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A95090AB-FC02-4DA7-A95D-787FA4691E3E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B696E254-C559-4C0C-84C3-89B7197386D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -730,22 +730,15 @@
     <xf numFmtId="0" fontId="10" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="41" fontId="4" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="9" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="41" fontId="4" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -755,6 +748,13 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="9" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="백분율" xfId="2" builtinId="5"/>
@@ -1037,7 +1037,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M166"/>
+  <dimension ref="A1:M167"/>
   <sheetFormatPr defaultRowHeight="16" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="12" style="31" customWidth="1"/>
@@ -5419,6 +5419,47 @@
       </c>
       <c r="M166" s="40">
         <v>11509810</v>
+      </c>
+    </row>
+    <row r="167" spans="1:13" ht="16.5" x14ac:dyDescent="0.45">
+      <c r="A167" s="35">
+        <v>46200</v>
+      </c>
+      <c r="B167" s="36">
+        <v>129270440</v>
+      </c>
+      <c r="C167" s="37">
+        <v>13910800</v>
+      </c>
+      <c r="D167" s="38">
+        <v>8394.65</v>
+      </c>
+      <c r="E167" s="37">
+        <v>1715684</v>
+      </c>
+      <c r="F167" s="40">
+        <v>13624260</v>
+      </c>
+      <c r="G167" s="40">
+        <v>15296060</v>
+      </c>
+      <c r="H167" s="40">
+        <v>14467460</v>
+      </c>
+      <c r="I167" s="40">
+        <v>10647000</v>
+      </c>
+      <c r="J167" s="40">
+        <v>11848200</v>
+      </c>
+      <c r="K167" s="40">
+        <v>28654080</v>
+      </c>
+      <c r="L167" s="40">
+        <v>21117910</v>
+      </c>
+      <c r="M167" s="40">
+        <v>13615470</v>
       </c>
     </row>
   </sheetData>
@@ -5444,72 +5485,72 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:21" x14ac:dyDescent="0.45">
-      <c r="A1" s="44" t="s">
+      <c r="A1" s="46" t="s">
         <v>17</v>
       </c>
-      <c r="B1" s="44" t="s">
+      <c r="B1" s="46" t="s">
         <v>16</v>
       </c>
-      <c r="C1" s="44" t="s">
+      <c r="C1" s="46" t="s">
         <v>18</v>
       </c>
-      <c r="D1" s="44" t="s">
+      <c r="D1" s="46" t="s">
         <v>19</v>
       </c>
-      <c r="E1" s="48" t="s">
+      <c r="E1" s="56" t="s">
         <v>20</v>
       </c>
-      <c r="F1" s="52" t="s">
+      <c r="F1" s="49" t="s">
         <v>21</v>
       </c>
-      <c r="G1" s="53"/>
-      <c r="H1" s="53"/>
-      <c r="I1" s="53"/>
-      <c r="J1" s="53"/>
-      <c r="K1" s="53"/>
-      <c r="L1" s="47">
+      <c r="G1" s="50"/>
+      <c r="H1" s="50"/>
+      <c r="I1" s="50"/>
+      <c r="J1" s="50"/>
+      <c r="K1" s="50"/>
+      <c r="L1" s="54">
         <v>0.7</v>
       </c>
-      <c r="M1" s="44" t="s">
+      <c r="M1" s="46" t="s">
         <v>22</v>
       </c>
-      <c r="N1" s="50"/>
-      <c r="O1" s="49"/>
-      <c r="P1" s="47">
+      <c r="N1" s="55"/>
+      <c r="O1" s="45"/>
+      <c r="P1" s="54">
         <v>0.25</v>
       </c>
-      <c r="Q1" s="49"/>
+      <c r="Q1" s="45"/>
       <c r="R1" s="1"/>
       <c r="S1" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="T1" s="44" t="s">
+      <c r="T1" s="46" t="s">
         <v>23</v>
       </c>
-      <c r="U1" s="49"/>
+      <c r="U1" s="45"/>
     </row>
     <row r="2" spans="1:21" x14ac:dyDescent="0.45">
-      <c r="A2" s="45"/>
-      <c r="B2" s="45"/>
-      <c r="C2" s="45"/>
-      <c r="D2" s="45"/>
-      <c r="E2" s="45"/>
-      <c r="F2" s="54"/>
+      <c r="A2" s="47"/>
+      <c r="B2" s="47"/>
+      <c r="C2" s="47"/>
+      <c r="D2" s="47"/>
+      <c r="E2" s="47"/>
+      <c r="F2" s="51"/>
       <c r="G2" s="42"/>
       <c r="H2" s="42"/>
       <c r="I2" s="42"/>
       <c r="J2" s="42"/>
       <c r="K2" s="42"/>
-      <c r="L2" s="46"/>
+      <c r="L2" s="48"/>
       <c r="M2" s="3"/>
-      <c r="N2" s="47" t="s">
+      <c r="N2" s="54" t="s">
         <v>15</v>
       </c>
-      <c r="O2" s="49"/>
-      <c r="P2" s="44" t="s">
+      <c r="O2" s="45"/>
+      <c r="P2" s="46" t="s">
         <v>24</v>
       </c>
-      <c r="Q2" s="49"/>
+      <c r="Q2" s="45"/>
       <c r="R2" s="1"/>
       <c r="S2" s="4" t="s">
         <v>25</v>
@@ -5522,31 +5563,31 @@
       </c>
     </row>
     <row r="3" spans="1:21" x14ac:dyDescent="0.45">
-      <c r="A3" s="45"/>
-      <c r="B3" s="45"/>
-      <c r="C3" s="45"/>
-      <c r="D3" s="45"/>
-      <c r="E3" s="45"/>
-      <c r="F3" s="54"/>
+      <c r="A3" s="47"/>
+      <c r="B3" s="47"/>
+      <c r="C3" s="47"/>
+      <c r="D3" s="47"/>
+      <c r="E3" s="47"/>
+      <c r="F3" s="51"/>
       <c r="G3" s="42"/>
       <c r="H3" s="42"/>
       <c r="I3" s="42"/>
       <c r="J3" s="42"/>
       <c r="K3" s="42"/>
-      <c r="L3" s="51">
+      <c r="L3" s="44">
         <v>17485</v>
       </c>
       <c r="M3" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="N3" s="51">
+      <c r="N3" s="44">
         <v>14760</v>
       </c>
-      <c r="O3" s="49"/>
-      <c r="P3" s="51">
+      <c r="O3" s="45"/>
+      <c r="P3" s="44">
         <v>8125</v>
       </c>
-      <c r="Q3" s="49"/>
+      <c r="Q3" s="45"/>
       <c r="R3" s="1"/>
       <c r="S3" s="4" t="s">
         <v>27</v>
@@ -5559,29 +5600,29 @@
       </c>
     </row>
     <row r="4" spans="1:21" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A4" s="46"/>
-      <c r="B4" s="46"/>
-      <c r="C4" s="46"/>
-      <c r="D4" s="46"/>
-      <c r="E4" s="46"/>
-      <c r="F4" s="54"/>
+      <c r="A4" s="48"/>
+      <c r="B4" s="48"/>
+      <c r="C4" s="48"/>
+      <c r="D4" s="48"/>
+      <c r="E4" s="48"/>
+      <c r="F4" s="51"/>
       <c r="G4" s="42"/>
       <c r="H4" s="42"/>
       <c r="I4" s="42"/>
       <c r="J4" s="42"/>
       <c r="K4" s="42"/>
-      <c r="L4" s="46"/>
+      <c r="L4" s="48"/>
       <c r="M4" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="N4" s="55">
+      <c r="N4" s="52">
         <v>34705</v>
       </c>
-      <c r="O4" s="56"/>
-      <c r="P4" s="51">
+      <c r="O4" s="53"/>
+      <c r="P4" s="44">
         <v>13230</v>
       </c>
-      <c r="Q4" s="49"/>
+      <c r="Q4" s="45"/>
       <c r="R4" s="1"/>
       <c r="S4" s="4" t="s">
         <v>29</v>
@@ -6019,6 +6060,16 @@
     </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="A1:A4"/>
+    <mergeCell ref="D1:D4"/>
+    <mergeCell ref="B1:B4"/>
+    <mergeCell ref="L1:L2"/>
+    <mergeCell ref="E1:E4"/>
+    <mergeCell ref="T1:U1"/>
+    <mergeCell ref="N2:O2"/>
+    <mergeCell ref="P2:Q2"/>
+    <mergeCell ref="M1:O1"/>
+    <mergeCell ref="P1:Q1"/>
     <mergeCell ref="P4:Q4"/>
     <mergeCell ref="P3:Q3"/>
     <mergeCell ref="N3:O3"/>
@@ -6026,16 +6077,6 @@
     <mergeCell ref="F1:K4"/>
     <mergeCell ref="L3:L4"/>
     <mergeCell ref="N4:O4"/>
-    <mergeCell ref="T1:U1"/>
-    <mergeCell ref="N2:O2"/>
-    <mergeCell ref="P2:Q2"/>
-    <mergeCell ref="M1:O1"/>
-    <mergeCell ref="P1:Q1"/>
-    <mergeCell ref="A1:A4"/>
-    <mergeCell ref="D1:D4"/>
-    <mergeCell ref="B1:B4"/>
-    <mergeCell ref="L1:L2"/>
-    <mergeCell ref="E1:E4"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="E5:E10">

--- a/input.xlsx
+++ b/input.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\backup01\Desktop\병아리\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B696E254-C559-4C0C-84C3-89B7197386D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{235C8165-9D4F-4E0F-89DD-DD9C3CCF98BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -730,15 +730,22 @@
     <xf numFmtId="0" fontId="10" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="4" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="9" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="41" fontId="4" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -748,13 +755,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="9" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="백분율" xfId="2" builtinId="5"/>
@@ -5423,7 +5423,7 @@
     </row>
     <row r="167" spans="1:13" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A167" s="35">
-        <v>46200</v>
+        <v>46202</v>
       </c>
       <c r="B167" s="36">
         <v>129270440</v>
@@ -5485,72 +5485,72 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:21" x14ac:dyDescent="0.45">
-      <c r="A1" s="46" t="s">
+      <c r="A1" s="44" t="s">
         <v>17</v>
       </c>
-      <c r="B1" s="46" t="s">
+      <c r="B1" s="44" t="s">
         <v>16</v>
       </c>
-      <c r="C1" s="46" t="s">
+      <c r="C1" s="44" t="s">
         <v>18</v>
       </c>
-      <c r="D1" s="46" t="s">
+      <c r="D1" s="44" t="s">
         <v>19</v>
       </c>
-      <c r="E1" s="56" t="s">
+      <c r="E1" s="48" t="s">
         <v>20</v>
       </c>
-      <c r="F1" s="49" t="s">
+      <c r="F1" s="52" t="s">
         <v>21</v>
       </c>
-      <c r="G1" s="50"/>
-      <c r="H1" s="50"/>
-      <c r="I1" s="50"/>
-      <c r="J1" s="50"/>
-      <c r="K1" s="50"/>
-      <c r="L1" s="54">
+      <c r="G1" s="53"/>
+      <c r="H1" s="53"/>
+      <c r="I1" s="53"/>
+      <c r="J1" s="53"/>
+      <c r="K1" s="53"/>
+      <c r="L1" s="47">
         <v>0.7</v>
       </c>
-      <c r="M1" s="46" t="s">
+      <c r="M1" s="44" t="s">
         <v>22</v>
       </c>
-      <c r="N1" s="55"/>
-      <c r="O1" s="45"/>
-      <c r="P1" s="54">
+      <c r="N1" s="50"/>
+      <c r="O1" s="49"/>
+      <c r="P1" s="47">
         <v>0.25</v>
       </c>
-      <c r="Q1" s="45"/>
+      <c r="Q1" s="49"/>
       <c r="R1" s="1"/>
       <c r="S1" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="T1" s="46" t="s">
+      <c r="T1" s="44" t="s">
         <v>23</v>
       </c>
-      <c r="U1" s="45"/>
+      <c r="U1" s="49"/>
     </row>
     <row r="2" spans="1:21" x14ac:dyDescent="0.45">
-      <c r="A2" s="47"/>
-      <c r="B2" s="47"/>
-      <c r="C2" s="47"/>
-      <c r="D2" s="47"/>
-      <c r="E2" s="47"/>
-      <c r="F2" s="51"/>
+      <c r="A2" s="45"/>
+      <c r="B2" s="45"/>
+      <c r="C2" s="45"/>
+      <c r="D2" s="45"/>
+      <c r="E2" s="45"/>
+      <c r="F2" s="54"/>
       <c r="G2" s="42"/>
       <c r="H2" s="42"/>
       <c r="I2" s="42"/>
       <c r="J2" s="42"/>
       <c r="K2" s="42"/>
-      <c r="L2" s="48"/>
+      <c r="L2" s="46"/>
       <c r="M2" s="3"/>
-      <c r="N2" s="54" t="s">
+      <c r="N2" s="47" t="s">
         <v>15</v>
       </c>
-      <c r="O2" s="45"/>
-      <c r="P2" s="46" t="s">
+      <c r="O2" s="49"/>
+      <c r="P2" s="44" t="s">
         <v>24</v>
       </c>
-      <c r="Q2" s="45"/>
+      <c r="Q2" s="49"/>
       <c r="R2" s="1"/>
       <c r="S2" s="4" t="s">
         <v>25</v>
@@ -5563,31 +5563,31 @@
       </c>
     </row>
     <row r="3" spans="1:21" x14ac:dyDescent="0.45">
-      <c r="A3" s="47"/>
-      <c r="B3" s="47"/>
-      <c r="C3" s="47"/>
-      <c r="D3" s="47"/>
-      <c r="E3" s="47"/>
-      <c r="F3" s="51"/>
+      <c r="A3" s="45"/>
+      <c r="B3" s="45"/>
+      <c r="C3" s="45"/>
+      <c r="D3" s="45"/>
+      <c r="E3" s="45"/>
+      <c r="F3" s="54"/>
       <c r="G3" s="42"/>
       <c r="H3" s="42"/>
       <c r="I3" s="42"/>
       <c r="J3" s="42"/>
       <c r="K3" s="42"/>
-      <c r="L3" s="44">
+      <c r="L3" s="51">
         <v>17485</v>
       </c>
       <c r="M3" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="N3" s="44">
+      <c r="N3" s="51">
         <v>14760</v>
       </c>
-      <c r="O3" s="45"/>
-      <c r="P3" s="44">
+      <c r="O3" s="49"/>
+      <c r="P3" s="51">
         <v>8125</v>
       </c>
-      <c r="Q3" s="45"/>
+      <c r="Q3" s="49"/>
       <c r="R3" s="1"/>
       <c r="S3" s="4" t="s">
         <v>27</v>
@@ -5600,29 +5600,29 @@
       </c>
     </row>
     <row r="4" spans="1:21" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A4" s="48"/>
-      <c r="B4" s="48"/>
-      <c r="C4" s="48"/>
-      <c r="D4" s="48"/>
-      <c r="E4" s="48"/>
-      <c r="F4" s="51"/>
+      <c r="A4" s="46"/>
+      <c r="B4" s="46"/>
+      <c r="C4" s="46"/>
+      <c r="D4" s="46"/>
+      <c r="E4" s="46"/>
+      <c r="F4" s="54"/>
       <c r="G4" s="42"/>
       <c r="H4" s="42"/>
       <c r="I4" s="42"/>
       <c r="J4" s="42"/>
       <c r="K4" s="42"/>
-      <c r="L4" s="48"/>
+      <c r="L4" s="46"/>
       <c r="M4" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="N4" s="52">
+      <c r="N4" s="55">
         <v>34705</v>
       </c>
-      <c r="O4" s="53"/>
-      <c r="P4" s="44">
+      <c r="O4" s="56"/>
+      <c r="P4" s="51">
         <v>13230</v>
       </c>
-      <c r="Q4" s="45"/>
+      <c r="Q4" s="49"/>
       <c r="R4" s="1"/>
       <c r="S4" s="4" t="s">
         <v>29</v>
@@ -6060,16 +6060,6 @@
     </row>
   </sheetData>
   <mergeCells count="17">
-    <mergeCell ref="A1:A4"/>
-    <mergeCell ref="D1:D4"/>
-    <mergeCell ref="B1:B4"/>
-    <mergeCell ref="L1:L2"/>
-    <mergeCell ref="E1:E4"/>
-    <mergeCell ref="T1:U1"/>
-    <mergeCell ref="N2:O2"/>
-    <mergeCell ref="P2:Q2"/>
-    <mergeCell ref="M1:O1"/>
-    <mergeCell ref="P1:Q1"/>
     <mergeCell ref="P4:Q4"/>
     <mergeCell ref="P3:Q3"/>
     <mergeCell ref="N3:O3"/>
@@ -6077,6 +6067,16 @@
     <mergeCell ref="F1:K4"/>
     <mergeCell ref="L3:L4"/>
     <mergeCell ref="N4:O4"/>
+    <mergeCell ref="T1:U1"/>
+    <mergeCell ref="N2:O2"/>
+    <mergeCell ref="P2:Q2"/>
+    <mergeCell ref="M1:O1"/>
+    <mergeCell ref="P1:Q1"/>
+    <mergeCell ref="A1:A4"/>
+    <mergeCell ref="D1:D4"/>
+    <mergeCell ref="B1:B4"/>
+    <mergeCell ref="L1:L2"/>
+    <mergeCell ref="E1:E4"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="E5:E10">

--- a/input.xlsx
+++ b/input.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\backup01\Desktop\병아리\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{235C8165-9D4F-4E0F-89DD-DD9C3CCF98BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D4D7FF7-46C9-4643-91F2-FFE1E10D4E55}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -730,22 +730,15 @@
     <xf numFmtId="0" fontId="10" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="41" fontId="4" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="9" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="41" fontId="4" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -755,6 +748,13 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="9" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="백분율" xfId="2" builtinId="5"/>
@@ -1037,7 +1037,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M167"/>
+  <dimension ref="A1:M168"/>
   <sheetFormatPr defaultRowHeight="16" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="12" style="31" customWidth="1"/>
@@ -5460,6 +5460,47 @@
       </c>
       <c r="M167" s="40">
         <v>13615470</v>
+      </c>
+    </row>
+    <row r="168" spans="1:13" ht="16.5" x14ac:dyDescent="0.45">
+      <c r="A168" s="35">
+        <v>46203</v>
+      </c>
+      <c r="B168" s="36">
+        <v>128466290</v>
+      </c>
+      <c r="C168" s="37">
+        <v>0</v>
+      </c>
+      <c r="D168" s="38">
+        <v>8476.48</v>
+      </c>
+      <c r="E168" s="37">
+        <v>302123</v>
+      </c>
+      <c r="F168" s="40">
+        <v>13667955</v>
+      </c>
+      <c r="G168" s="40">
+        <v>15494415</v>
+      </c>
+      <c r="H168" s="40">
+        <v>14468235</v>
+      </c>
+      <c r="I168" s="40">
+        <v>10466625</v>
+      </c>
+      <c r="J168" s="40">
+        <v>11647475</v>
+      </c>
+      <c r="K168" s="40">
+        <v>28168640</v>
+      </c>
+      <c r="L168" s="40">
+        <v>20938245</v>
+      </c>
+      <c r="M168" s="40">
+        <v>13614700</v>
       </c>
     </row>
   </sheetData>
@@ -5485,72 +5526,72 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:21" x14ac:dyDescent="0.45">
-      <c r="A1" s="44" t="s">
+      <c r="A1" s="46" t="s">
         <v>17</v>
       </c>
-      <c r="B1" s="44" t="s">
+      <c r="B1" s="46" t="s">
         <v>16</v>
       </c>
-      <c r="C1" s="44" t="s">
+      <c r="C1" s="46" t="s">
         <v>18</v>
       </c>
-      <c r="D1" s="44" t="s">
+      <c r="D1" s="46" t="s">
         <v>19</v>
       </c>
-      <c r="E1" s="48" t="s">
+      <c r="E1" s="56" t="s">
         <v>20</v>
       </c>
-      <c r="F1" s="52" t="s">
+      <c r="F1" s="49" t="s">
         <v>21</v>
       </c>
-      <c r="G1" s="53"/>
-      <c r="H1" s="53"/>
-      <c r="I1" s="53"/>
-      <c r="J1" s="53"/>
-      <c r="K1" s="53"/>
-      <c r="L1" s="47">
+      <c r="G1" s="50"/>
+      <c r="H1" s="50"/>
+      <c r="I1" s="50"/>
+      <c r="J1" s="50"/>
+      <c r="K1" s="50"/>
+      <c r="L1" s="54">
         <v>0.7</v>
       </c>
-      <c r="M1" s="44" t="s">
+      <c r="M1" s="46" t="s">
         <v>22</v>
       </c>
-      <c r="N1" s="50"/>
-      <c r="O1" s="49"/>
-      <c r="P1" s="47">
+      <c r="N1" s="55"/>
+      <c r="O1" s="45"/>
+      <c r="P1" s="54">
         <v>0.25</v>
       </c>
-      <c r="Q1" s="49"/>
+      <c r="Q1" s="45"/>
       <c r="R1" s="1"/>
       <c r="S1" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="T1" s="44" t="s">
+      <c r="T1" s="46" t="s">
         <v>23</v>
       </c>
-      <c r="U1" s="49"/>
+      <c r="U1" s="45"/>
     </row>
     <row r="2" spans="1:21" x14ac:dyDescent="0.45">
-      <c r="A2" s="45"/>
-      <c r="B2" s="45"/>
-      <c r="C2" s="45"/>
-      <c r="D2" s="45"/>
-      <c r="E2" s="45"/>
-      <c r="F2" s="54"/>
+      <c r="A2" s="47"/>
+      <c r="B2" s="47"/>
+      <c r="C2" s="47"/>
+      <c r="D2" s="47"/>
+      <c r="E2" s="47"/>
+      <c r="F2" s="51"/>
       <c r="G2" s="42"/>
       <c r="H2" s="42"/>
       <c r="I2" s="42"/>
       <c r="J2" s="42"/>
       <c r="K2" s="42"/>
-      <c r="L2" s="46"/>
+      <c r="L2" s="48"/>
       <c r="M2" s="3"/>
-      <c r="N2" s="47" t="s">
+      <c r="N2" s="54" t="s">
         <v>15</v>
       </c>
-      <c r="O2" s="49"/>
-      <c r="P2" s="44" t="s">
+      <c r="O2" s="45"/>
+      <c r="P2" s="46" t="s">
         <v>24</v>
       </c>
-      <c r="Q2" s="49"/>
+      <c r="Q2" s="45"/>
       <c r="R2" s="1"/>
       <c r="S2" s="4" t="s">
         <v>25</v>
@@ -5563,31 +5604,31 @@
       </c>
     </row>
     <row r="3" spans="1:21" x14ac:dyDescent="0.45">
-      <c r="A3" s="45"/>
-      <c r="B3" s="45"/>
-      <c r="C3" s="45"/>
-      <c r="D3" s="45"/>
-      <c r="E3" s="45"/>
-      <c r="F3" s="54"/>
+      <c r="A3" s="47"/>
+      <c r="B3" s="47"/>
+      <c r="C3" s="47"/>
+      <c r="D3" s="47"/>
+      <c r="E3" s="47"/>
+      <c r="F3" s="51"/>
       <c r="G3" s="42"/>
       <c r="H3" s="42"/>
       <c r="I3" s="42"/>
       <c r="J3" s="42"/>
       <c r="K3" s="42"/>
-      <c r="L3" s="51">
+      <c r="L3" s="44">
         <v>17485</v>
       </c>
       <c r="M3" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="N3" s="51">
+      <c r="N3" s="44">
         <v>14760</v>
       </c>
-      <c r="O3" s="49"/>
-      <c r="P3" s="51">
+      <c r="O3" s="45"/>
+      <c r="P3" s="44">
         <v>8125</v>
       </c>
-      <c r="Q3" s="49"/>
+      <c r="Q3" s="45"/>
       <c r="R3" s="1"/>
       <c r="S3" s="4" t="s">
         <v>27</v>
@@ -5600,29 +5641,29 @@
       </c>
     </row>
     <row r="4" spans="1:21" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A4" s="46"/>
-      <c r="B4" s="46"/>
-      <c r="C4" s="46"/>
-      <c r="D4" s="46"/>
-      <c r="E4" s="46"/>
-      <c r="F4" s="54"/>
+      <c r="A4" s="48"/>
+      <c r="B4" s="48"/>
+      <c r="C4" s="48"/>
+      <c r="D4" s="48"/>
+      <c r="E4" s="48"/>
+      <c r="F4" s="51"/>
       <c r="G4" s="42"/>
       <c r="H4" s="42"/>
       <c r="I4" s="42"/>
       <c r="J4" s="42"/>
       <c r="K4" s="42"/>
-      <c r="L4" s="46"/>
+      <c r="L4" s="48"/>
       <c r="M4" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="N4" s="55">
+      <c r="N4" s="52">
         <v>34705</v>
       </c>
-      <c r="O4" s="56"/>
-      <c r="P4" s="51">
+      <c r="O4" s="53"/>
+      <c r="P4" s="44">
         <v>13230</v>
       </c>
-      <c r="Q4" s="49"/>
+      <c r="Q4" s="45"/>
       <c r="R4" s="1"/>
       <c r="S4" s="4" t="s">
         <v>29</v>
@@ -6060,6 +6101,16 @@
     </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="A1:A4"/>
+    <mergeCell ref="D1:D4"/>
+    <mergeCell ref="B1:B4"/>
+    <mergeCell ref="L1:L2"/>
+    <mergeCell ref="E1:E4"/>
+    <mergeCell ref="T1:U1"/>
+    <mergeCell ref="N2:O2"/>
+    <mergeCell ref="P2:Q2"/>
+    <mergeCell ref="M1:O1"/>
+    <mergeCell ref="P1:Q1"/>
     <mergeCell ref="P4:Q4"/>
     <mergeCell ref="P3:Q3"/>
     <mergeCell ref="N3:O3"/>
@@ -6067,16 +6118,6 @@
     <mergeCell ref="F1:K4"/>
     <mergeCell ref="L3:L4"/>
     <mergeCell ref="N4:O4"/>
-    <mergeCell ref="T1:U1"/>
-    <mergeCell ref="N2:O2"/>
-    <mergeCell ref="P2:Q2"/>
-    <mergeCell ref="M1:O1"/>
-    <mergeCell ref="P1:Q1"/>
-    <mergeCell ref="A1:A4"/>
-    <mergeCell ref="D1:D4"/>
-    <mergeCell ref="B1:B4"/>
-    <mergeCell ref="L1:L2"/>
-    <mergeCell ref="E1:E4"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="E5:E10">

--- a/input.xlsx
+++ b/input.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\backup01\Desktop\병아리\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D4D7FF7-46C9-4643-91F2-FFE1E10D4E55}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1269CF0C-6CF5-42BA-A758-0D39C1B58B7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -730,15 +730,22 @@
     <xf numFmtId="0" fontId="10" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="4" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="9" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="41" fontId="4" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -748,13 +755,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="9" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="백분율" xfId="2" builtinId="5"/>
@@ -1037,7 +1037,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M168"/>
+  <dimension ref="A1:M169"/>
   <sheetFormatPr defaultRowHeight="16" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="12" style="31" customWidth="1"/>
@@ -5501,6 +5501,47 @@
       </c>
       <c r="M168" s="40">
         <v>13614700</v>
+      </c>
+    </row>
+    <row r="169" spans="1:13" ht="16.5" x14ac:dyDescent="0.45">
+      <c r="A169" s="35">
+        <v>46204</v>
+      </c>
+      <c r="B169" s="36">
+        <v>116943335</v>
+      </c>
+      <c r="C169" s="37">
+        <v>-11844090</v>
+      </c>
+      <c r="D169" s="38">
+        <v>8303.41</v>
+      </c>
+      <c r="E169" s="37">
+        <v>103105</v>
+      </c>
+      <c r="F169" s="40">
+        <v>13496225</v>
+      </c>
+      <c r="G169" s="40">
+        <v>15523945</v>
+      </c>
+      <c r="H169" s="40">
+        <v>14546465</v>
+      </c>
+      <c r="I169" s="40">
+        <v>10578750</v>
+      </c>
+      <c r="J169" s="40">
+        <v>11772250</v>
+      </c>
+      <c r="K169" s="40">
+        <v>28470400</v>
+      </c>
+      <c r="L169" s="40">
+        <v>16523480</v>
+      </c>
+      <c r="M169" s="40">
+        <v>6031820</v>
       </c>
     </row>
   </sheetData>
@@ -5526,72 +5567,72 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:21" x14ac:dyDescent="0.45">
-      <c r="A1" s="46" t="s">
+      <c r="A1" s="44" t="s">
         <v>17</v>
       </c>
-      <c r="B1" s="46" t="s">
+      <c r="B1" s="44" t="s">
         <v>16</v>
       </c>
-      <c r="C1" s="46" t="s">
+      <c r="C1" s="44" t="s">
         <v>18</v>
       </c>
-      <c r="D1" s="46" t="s">
+      <c r="D1" s="44" t="s">
         <v>19</v>
       </c>
-      <c r="E1" s="56" t="s">
+      <c r="E1" s="48" t="s">
         <v>20</v>
       </c>
-      <c r="F1" s="49" t="s">
+      <c r="F1" s="52" t="s">
         <v>21</v>
       </c>
-      <c r="G1" s="50"/>
-      <c r="H1" s="50"/>
-      <c r="I1" s="50"/>
-      <c r="J1" s="50"/>
-      <c r="K1" s="50"/>
-      <c r="L1" s="54">
+      <c r="G1" s="53"/>
+      <c r="H1" s="53"/>
+      <c r="I1" s="53"/>
+      <c r="J1" s="53"/>
+      <c r="K1" s="53"/>
+      <c r="L1" s="47">
         <v>0.7</v>
       </c>
-      <c r="M1" s="46" t="s">
+      <c r="M1" s="44" t="s">
         <v>22</v>
       </c>
-      <c r="N1" s="55"/>
-      <c r="O1" s="45"/>
-      <c r="P1" s="54">
+      <c r="N1" s="50"/>
+      <c r="O1" s="49"/>
+      <c r="P1" s="47">
         <v>0.25</v>
       </c>
-      <c r="Q1" s="45"/>
+      <c r="Q1" s="49"/>
       <c r="R1" s="1"/>
       <c r="S1" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="T1" s="46" t="s">
+      <c r="T1" s="44" t="s">
         <v>23</v>
       </c>
-      <c r="U1" s="45"/>
+      <c r="U1" s="49"/>
     </row>
     <row r="2" spans="1:21" x14ac:dyDescent="0.45">
-      <c r="A2" s="47"/>
-      <c r="B2" s="47"/>
-      <c r="C2" s="47"/>
-      <c r="D2" s="47"/>
-      <c r="E2" s="47"/>
-      <c r="F2" s="51"/>
+      <c r="A2" s="45"/>
+      <c r="B2" s="45"/>
+      <c r="C2" s="45"/>
+      <c r="D2" s="45"/>
+      <c r="E2" s="45"/>
+      <c r="F2" s="54"/>
       <c r="G2" s="42"/>
       <c r="H2" s="42"/>
       <c r="I2" s="42"/>
       <c r="J2" s="42"/>
       <c r="K2" s="42"/>
-      <c r="L2" s="48"/>
+      <c r="L2" s="46"/>
       <c r="M2" s="3"/>
-      <c r="N2" s="54" t="s">
+      <c r="N2" s="47" t="s">
         <v>15</v>
       </c>
-      <c r="O2" s="45"/>
-      <c r="P2" s="46" t="s">
+      <c r="O2" s="49"/>
+      <c r="P2" s="44" t="s">
         <v>24</v>
       </c>
-      <c r="Q2" s="45"/>
+      <c r="Q2" s="49"/>
       <c r="R2" s="1"/>
       <c r="S2" s="4" t="s">
         <v>25</v>
@@ -5604,31 +5645,31 @@
       </c>
     </row>
     <row r="3" spans="1:21" x14ac:dyDescent="0.45">
-      <c r="A3" s="47"/>
-      <c r="B3" s="47"/>
-      <c r="C3" s="47"/>
-      <c r="D3" s="47"/>
-      <c r="E3" s="47"/>
-      <c r="F3" s="51"/>
+      <c r="A3" s="45"/>
+      <c r="B3" s="45"/>
+      <c r="C3" s="45"/>
+      <c r="D3" s="45"/>
+      <c r="E3" s="45"/>
+      <c r="F3" s="54"/>
       <c r="G3" s="42"/>
       <c r="H3" s="42"/>
       <c r="I3" s="42"/>
       <c r="J3" s="42"/>
       <c r="K3" s="42"/>
-      <c r="L3" s="44">
+      <c r="L3" s="51">
         <v>17485</v>
       </c>
       <c r="M3" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="N3" s="44">
+      <c r="N3" s="51">
         <v>14760</v>
       </c>
-      <c r="O3" s="45"/>
-      <c r="P3" s="44">
+      <c r="O3" s="49"/>
+      <c r="P3" s="51">
         <v>8125</v>
       </c>
-      <c r="Q3" s="45"/>
+      <c r="Q3" s="49"/>
       <c r="R3" s="1"/>
       <c r="S3" s="4" t="s">
         <v>27</v>
@@ -5641,29 +5682,29 @@
       </c>
     </row>
     <row r="4" spans="1:21" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A4" s="48"/>
-      <c r="B4" s="48"/>
-      <c r="C4" s="48"/>
-      <c r="D4" s="48"/>
-      <c r="E4" s="48"/>
-      <c r="F4" s="51"/>
+      <c r="A4" s="46"/>
+      <c r="B4" s="46"/>
+      <c r="C4" s="46"/>
+      <c r="D4" s="46"/>
+      <c r="E4" s="46"/>
+      <c r="F4" s="54"/>
       <c r="G4" s="42"/>
       <c r="H4" s="42"/>
       <c r="I4" s="42"/>
       <c r="J4" s="42"/>
       <c r="K4" s="42"/>
-      <c r="L4" s="48"/>
+      <c r="L4" s="46"/>
       <c r="M4" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="N4" s="52">
+      <c r="N4" s="55">
         <v>34705</v>
       </c>
-      <c r="O4" s="53"/>
-      <c r="P4" s="44">
+      <c r="O4" s="56"/>
+      <c r="P4" s="51">
         <v>13230</v>
       </c>
-      <c r="Q4" s="45"/>
+      <c r="Q4" s="49"/>
       <c r="R4" s="1"/>
       <c r="S4" s="4" t="s">
         <v>29</v>
@@ -6101,16 +6142,6 @@
     </row>
   </sheetData>
   <mergeCells count="17">
-    <mergeCell ref="A1:A4"/>
-    <mergeCell ref="D1:D4"/>
-    <mergeCell ref="B1:B4"/>
-    <mergeCell ref="L1:L2"/>
-    <mergeCell ref="E1:E4"/>
-    <mergeCell ref="T1:U1"/>
-    <mergeCell ref="N2:O2"/>
-    <mergeCell ref="P2:Q2"/>
-    <mergeCell ref="M1:O1"/>
-    <mergeCell ref="P1:Q1"/>
     <mergeCell ref="P4:Q4"/>
     <mergeCell ref="P3:Q3"/>
     <mergeCell ref="N3:O3"/>
@@ -6118,6 +6149,16 @@
     <mergeCell ref="F1:K4"/>
     <mergeCell ref="L3:L4"/>
     <mergeCell ref="N4:O4"/>
+    <mergeCell ref="T1:U1"/>
+    <mergeCell ref="N2:O2"/>
+    <mergeCell ref="P2:Q2"/>
+    <mergeCell ref="M1:O1"/>
+    <mergeCell ref="P1:Q1"/>
+    <mergeCell ref="A1:A4"/>
+    <mergeCell ref="D1:D4"/>
+    <mergeCell ref="B1:B4"/>
+    <mergeCell ref="L1:L2"/>
+    <mergeCell ref="E1:E4"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="E5:E10">

--- a/input.xlsx
+++ b/input.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\backup01\Desktop\병아리\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1269CF0C-6CF5-42BA-A758-0D39C1B58B7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4EE7B3F6-1ABB-4D5C-8394-FB0E3F8CBBBA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="25490" yWindow="690" windowWidth="25820" windowHeight="13900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="INPUT" sheetId="1" r:id="rId1"/>
@@ -730,22 +730,15 @@
     <xf numFmtId="0" fontId="10" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="41" fontId="4" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="9" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="41" fontId="4" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -755,6 +748,13 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="9" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="백분율" xfId="2" builtinId="5"/>
@@ -1037,7 +1037,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M169"/>
+  <dimension ref="A1:M170"/>
   <sheetFormatPr defaultRowHeight="16" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="12" style="31" customWidth="1"/>
@@ -5542,6 +5542,47 @@
       </c>
       <c r="M169" s="40">
         <v>6031820</v>
+      </c>
+    </row>
+    <row r="170" spans="1:13" ht="16.5" x14ac:dyDescent="0.45">
+      <c r="A170" s="35">
+        <v>46205</v>
+      </c>
+      <c r="B170" s="36">
+        <v>112310425</v>
+      </c>
+      <c r="C170" s="37">
+        <v>9720880</v>
+      </c>
+      <c r="D170" s="38">
+        <v>7648.09</v>
+      </c>
+      <c r="E170" s="37">
+        <v>0</v>
+      </c>
+      <c r="F170" s="40">
+        <v>8218860</v>
+      </c>
+      <c r="G170" s="40">
+        <v>13087975</v>
+      </c>
+      <c r="H170" s="40">
+        <v>19070725</v>
+      </c>
+      <c r="I170" s="40">
+        <v>15977105</v>
+      </c>
+      <c r="J170" s="40">
+        <v>10112200</v>
+      </c>
+      <c r="K170" s="40">
+        <v>24455680</v>
+      </c>
+      <c r="L170" s="40">
+        <v>15356840</v>
+      </c>
+      <c r="M170" s="40">
+        <v>6031040</v>
       </c>
     </row>
   </sheetData>
@@ -5567,72 +5608,72 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:21" x14ac:dyDescent="0.45">
-      <c r="A1" s="44" t="s">
+      <c r="A1" s="46" t="s">
         <v>17</v>
       </c>
-      <c r="B1" s="44" t="s">
+      <c r="B1" s="46" t="s">
         <v>16</v>
       </c>
-      <c r="C1" s="44" t="s">
+      <c r="C1" s="46" t="s">
         <v>18</v>
       </c>
-      <c r="D1" s="44" t="s">
+      <c r="D1" s="46" t="s">
         <v>19</v>
       </c>
-      <c r="E1" s="48" t="s">
+      <c r="E1" s="56" t="s">
         <v>20</v>
       </c>
-      <c r="F1" s="52" t="s">
+      <c r="F1" s="49" t="s">
         <v>21</v>
       </c>
-      <c r="G1" s="53"/>
-      <c r="H1" s="53"/>
-      <c r="I1" s="53"/>
-      <c r="J1" s="53"/>
-      <c r="K1" s="53"/>
-      <c r="L1" s="47">
+      <c r="G1" s="50"/>
+      <c r="H1" s="50"/>
+      <c r="I1" s="50"/>
+      <c r="J1" s="50"/>
+      <c r="K1" s="50"/>
+      <c r="L1" s="54">
         <v>0.7</v>
       </c>
-      <c r="M1" s="44" t="s">
+      <c r="M1" s="46" t="s">
         <v>22</v>
       </c>
-      <c r="N1" s="50"/>
-      <c r="O1" s="49"/>
-      <c r="P1" s="47">
+      <c r="N1" s="55"/>
+      <c r="O1" s="45"/>
+      <c r="P1" s="54">
         <v>0.25</v>
       </c>
-      <c r="Q1" s="49"/>
+      <c r="Q1" s="45"/>
       <c r="R1" s="1"/>
       <c r="S1" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="T1" s="44" t="s">
+      <c r="T1" s="46" t="s">
         <v>23</v>
       </c>
-      <c r="U1" s="49"/>
+      <c r="U1" s="45"/>
     </row>
     <row r="2" spans="1:21" x14ac:dyDescent="0.45">
-      <c r="A2" s="45"/>
-      <c r="B2" s="45"/>
-      <c r="C2" s="45"/>
-      <c r="D2" s="45"/>
-      <c r="E2" s="45"/>
-      <c r="F2" s="54"/>
+      <c r="A2" s="47"/>
+      <c r="B2" s="47"/>
+      <c r="C2" s="47"/>
+      <c r="D2" s="47"/>
+      <c r="E2" s="47"/>
+      <c r="F2" s="51"/>
       <c r="G2" s="42"/>
       <c r="H2" s="42"/>
       <c r="I2" s="42"/>
       <c r="J2" s="42"/>
       <c r="K2" s="42"/>
-      <c r="L2" s="46"/>
+      <c r="L2" s="48"/>
       <c r="M2" s="3"/>
-      <c r="N2" s="47" t="s">
+      <c r="N2" s="54" t="s">
         <v>15</v>
       </c>
-      <c r="O2" s="49"/>
-      <c r="P2" s="44" t="s">
+      <c r="O2" s="45"/>
+      <c r="P2" s="46" t="s">
         <v>24</v>
       </c>
-      <c r="Q2" s="49"/>
+      <c r="Q2" s="45"/>
       <c r="R2" s="1"/>
       <c r="S2" s="4" t="s">
         <v>25</v>
@@ -5645,31 +5686,31 @@
       </c>
     </row>
     <row r="3" spans="1:21" x14ac:dyDescent="0.45">
-      <c r="A3" s="45"/>
-      <c r="B3" s="45"/>
-      <c r="C3" s="45"/>
-      <c r="D3" s="45"/>
-      <c r="E3" s="45"/>
-      <c r="F3" s="54"/>
+      <c r="A3" s="47"/>
+      <c r="B3" s="47"/>
+      <c r="C3" s="47"/>
+      <c r="D3" s="47"/>
+      <c r="E3" s="47"/>
+      <c r="F3" s="51"/>
       <c r="G3" s="42"/>
       <c r="H3" s="42"/>
       <c r="I3" s="42"/>
       <c r="J3" s="42"/>
       <c r="K3" s="42"/>
-      <c r="L3" s="51">
+      <c r="L3" s="44">
         <v>17485</v>
       </c>
       <c r="M3" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="N3" s="51">
+      <c r="N3" s="44">
         <v>14760</v>
       </c>
-      <c r="O3" s="49"/>
-      <c r="P3" s="51">
+      <c r="O3" s="45"/>
+      <c r="P3" s="44">
         <v>8125</v>
       </c>
-      <c r="Q3" s="49"/>
+      <c r="Q3" s="45"/>
       <c r="R3" s="1"/>
       <c r="S3" s="4" t="s">
         <v>27</v>
@@ -5682,29 +5723,29 @@
       </c>
     </row>
     <row r="4" spans="1:21" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A4" s="46"/>
-      <c r="B4" s="46"/>
-      <c r="C4" s="46"/>
-      <c r="D4" s="46"/>
-      <c r="E4" s="46"/>
-      <c r="F4" s="54"/>
+      <c r="A4" s="48"/>
+      <c r="B4" s="48"/>
+      <c r="C4" s="48"/>
+      <c r="D4" s="48"/>
+      <c r="E4" s="48"/>
+      <c r="F4" s="51"/>
       <c r="G4" s="42"/>
       <c r="H4" s="42"/>
       <c r="I4" s="42"/>
       <c r="J4" s="42"/>
       <c r="K4" s="42"/>
-      <c r="L4" s="46"/>
+      <c r="L4" s="48"/>
       <c r="M4" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="N4" s="55">
+      <c r="N4" s="52">
         <v>34705</v>
       </c>
-      <c r="O4" s="56"/>
-      <c r="P4" s="51">
+      <c r="O4" s="53"/>
+      <c r="P4" s="44">
         <v>13230</v>
       </c>
-      <c r="Q4" s="49"/>
+      <c r="Q4" s="45"/>
       <c r="R4" s="1"/>
       <c r="S4" s="4" t="s">
         <v>29</v>
@@ -6142,6 +6183,16 @@
     </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="A1:A4"/>
+    <mergeCell ref="D1:D4"/>
+    <mergeCell ref="B1:B4"/>
+    <mergeCell ref="L1:L2"/>
+    <mergeCell ref="E1:E4"/>
+    <mergeCell ref="T1:U1"/>
+    <mergeCell ref="N2:O2"/>
+    <mergeCell ref="P2:Q2"/>
+    <mergeCell ref="M1:O1"/>
+    <mergeCell ref="P1:Q1"/>
     <mergeCell ref="P4:Q4"/>
     <mergeCell ref="P3:Q3"/>
     <mergeCell ref="N3:O3"/>
@@ -6149,16 +6200,6 @@
     <mergeCell ref="F1:K4"/>
     <mergeCell ref="L3:L4"/>
     <mergeCell ref="N4:O4"/>
-    <mergeCell ref="T1:U1"/>
-    <mergeCell ref="N2:O2"/>
-    <mergeCell ref="P2:Q2"/>
-    <mergeCell ref="M1:O1"/>
-    <mergeCell ref="P1:Q1"/>
-    <mergeCell ref="A1:A4"/>
-    <mergeCell ref="D1:D4"/>
-    <mergeCell ref="B1:B4"/>
-    <mergeCell ref="L1:L2"/>
-    <mergeCell ref="E1:E4"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="E5:E10">

--- a/input.xlsx
+++ b/input.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\backup01\Desktop\병아리\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4EE7B3F6-1ABB-4D5C-8394-FB0E3F8CBBBA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DFE398A1-8927-4FDA-96AF-667803C9B668}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="25490" yWindow="690" windowWidth="25820" windowHeight="13900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="INPUT" sheetId="1" r:id="rId1"/>
@@ -730,15 +730,22 @@
     <xf numFmtId="0" fontId="10" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="4" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="9" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="41" fontId="4" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -748,13 +755,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="9" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="백분율" xfId="2" builtinId="5"/>
@@ -1037,7 +1037,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M170"/>
+  <dimension ref="A1:M171"/>
   <sheetFormatPr defaultRowHeight="16" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="12" style="31" customWidth="1"/>
@@ -5583,6 +5583,47 @@
       </c>
       <c r="M170" s="40">
         <v>6031040</v>
+      </c>
+    </row>
+    <row r="171" spans="1:13" ht="16.5" x14ac:dyDescent="0.45">
+      <c r="A171" s="35">
+        <v>46206</v>
+      </c>
+      <c r="B171" s="36">
+        <v>111850960</v>
+      </c>
+      <c r="C171" s="37">
+        <v>-2263240</v>
+      </c>
+      <c r="D171" s="38">
+        <v>8088.34</v>
+      </c>
+      <c r="E171" s="37">
+        <v>1014864</v>
+      </c>
+      <c r="F171" s="40">
+        <v>8454100</v>
+      </c>
+      <c r="G171" s="40">
+        <v>14341840</v>
+      </c>
+      <c r="H171" s="40">
+        <v>20387040</v>
+      </c>
+      <c r="I171" s="40">
+        <v>16530930</v>
+      </c>
+      <c r="J171" s="40">
+        <v>9819250</v>
+      </c>
+      <c r="K171" s="40">
+        <v>23747200</v>
+      </c>
+      <c r="L171" s="40">
+        <v>12733350</v>
+      </c>
+      <c r="M171" s="40">
+        <v>5837250</v>
       </c>
     </row>
   </sheetData>
@@ -5608,72 +5649,72 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:21" x14ac:dyDescent="0.45">
-      <c r="A1" s="46" t="s">
+      <c r="A1" s="44" t="s">
         <v>17</v>
       </c>
-      <c r="B1" s="46" t="s">
+      <c r="B1" s="44" t="s">
         <v>16</v>
       </c>
-      <c r="C1" s="46" t="s">
+      <c r="C1" s="44" t="s">
         <v>18</v>
       </c>
-      <c r="D1" s="46" t="s">
+      <c r="D1" s="44" t="s">
         <v>19</v>
       </c>
-      <c r="E1" s="56" t="s">
+      <c r="E1" s="48" t="s">
         <v>20</v>
       </c>
-      <c r="F1" s="49" t="s">
+      <c r="F1" s="52" t="s">
         <v>21</v>
       </c>
-      <c r="G1" s="50"/>
-      <c r="H1" s="50"/>
-      <c r="I1" s="50"/>
-      <c r="J1" s="50"/>
-      <c r="K1" s="50"/>
-      <c r="L1" s="54">
+      <c r="G1" s="53"/>
+      <c r="H1" s="53"/>
+      <c r="I1" s="53"/>
+      <c r="J1" s="53"/>
+      <c r="K1" s="53"/>
+      <c r="L1" s="47">
         <v>0.7</v>
       </c>
-      <c r="M1" s="46" t="s">
+      <c r="M1" s="44" t="s">
         <v>22</v>
       </c>
-      <c r="N1" s="55"/>
-      <c r="O1" s="45"/>
-      <c r="P1" s="54">
+      <c r="N1" s="50"/>
+      <c r="O1" s="49"/>
+      <c r="P1" s="47">
         <v>0.25</v>
       </c>
-      <c r="Q1" s="45"/>
+      <c r="Q1" s="49"/>
       <c r="R1" s="1"/>
       <c r="S1" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="T1" s="46" t="s">
+      <c r="T1" s="44" t="s">
         <v>23</v>
       </c>
-      <c r="U1" s="45"/>
+      <c r="U1" s="49"/>
     </row>
     <row r="2" spans="1:21" x14ac:dyDescent="0.45">
-      <c r="A2" s="47"/>
-      <c r="B2" s="47"/>
-      <c r="C2" s="47"/>
-      <c r="D2" s="47"/>
-      <c r="E2" s="47"/>
-      <c r="F2" s="51"/>
+      <c r="A2" s="45"/>
+      <c r="B2" s="45"/>
+      <c r="C2" s="45"/>
+      <c r="D2" s="45"/>
+      <c r="E2" s="45"/>
+      <c r="F2" s="54"/>
       <c r="G2" s="42"/>
       <c r="H2" s="42"/>
       <c r="I2" s="42"/>
       <c r="J2" s="42"/>
       <c r="K2" s="42"/>
-      <c r="L2" s="48"/>
+      <c r="L2" s="46"/>
       <c r="M2" s="3"/>
-      <c r="N2" s="54" t="s">
+      <c r="N2" s="47" t="s">
         <v>15</v>
       </c>
-      <c r="O2" s="45"/>
-      <c r="P2" s="46" t="s">
+      <c r="O2" s="49"/>
+      <c r="P2" s="44" t="s">
         <v>24</v>
       </c>
-      <c r="Q2" s="45"/>
+      <c r="Q2" s="49"/>
       <c r="R2" s="1"/>
       <c r="S2" s="4" t="s">
         <v>25</v>
@@ -5686,31 +5727,31 @@
       </c>
     </row>
     <row r="3" spans="1:21" x14ac:dyDescent="0.45">
-      <c r="A3" s="47"/>
-      <c r="B3" s="47"/>
-      <c r="C3" s="47"/>
-      <c r="D3" s="47"/>
-      <c r="E3" s="47"/>
-      <c r="F3" s="51"/>
+      <c r="A3" s="45"/>
+      <c r="B3" s="45"/>
+      <c r="C3" s="45"/>
+      <c r="D3" s="45"/>
+      <c r="E3" s="45"/>
+      <c r="F3" s="54"/>
       <c r="G3" s="42"/>
       <c r="H3" s="42"/>
       <c r="I3" s="42"/>
       <c r="J3" s="42"/>
       <c r="K3" s="42"/>
-      <c r="L3" s="44">
+      <c r="L3" s="51">
         <v>17485</v>
       </c>
       <c r="M3" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="N3" s="44">
+      <c r="N3" s="51">
         <v>14760</v>
       </c>
-      <c r="O3" s="45"/>
-      <c r="P3" s="44">
+      <c r="O3" s="49"/>
+      <c r="P3" s="51">
         <v>8125</v>
       </c>
-      <c r="Q3" s="45"/>
+      <c r="Q3" s="49"/>
       <c r="R3" s="1"/>
       <c r="S3" s="4" t="s">
         <v>27</v>
@@ -5723,29 +5764,29 @@
       </c>
     </row>
     <row r="4" spans="1:21" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A4" s="48"/>
-      <c r="B4" s="48"/>
-      <c r="C4" s="48"/>
-      <c r="D4" s="48"/>
-      <c r="E4" s="48"/>
-      <c r="F4" s="51"/>
+      <c r="A4" s="46"/>
+      <c r="B4" s="46"/>
+      <c r="C4" s="46"/>
+      <c r="D4" s="46"/>
+      <c r="E4" s="46"/>
+      <c r="F4" s="54"/>
       <c r="G4" s="42"/>
       <c r="H4" s="42"/>
       <c r="I4" s="42"/>
       <c r="J4" s="42"/>
       <c r="K4" s="42"/>
-      <c r="L4" s="48"/>
+      <c r="L4" s="46"/>
       <c r="M4" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="N4" s="52">
+      <c r="N4" s="55">
         <v>34705</v>
       </c>
-      <c r="O4" s="53"/>
-      <c r="P4" s="44">
+      <c r="O4" s="56"/>
+      <c r="P4" s="51">
         <v>13230</v>
       </c>
-      <c r="Q4" s="45"/>
+      <c r="Q4" s="49"/>
       <c r="R4" s="1"/>
       <c r="S4" s="4" t="s">
         <v>29</v>
@@ -6183,16 +6224,6 @@
     </row>
   </sheetData>
   <mergeCells count="17">
-    <mergeCell ref="A1:A4"/>
-    <mergeCell ref="D1:D4"/>
-    <mergeCell ref="B1:B4"/>
-    <mergeCell ref="L1:L2"/>
-    <mergeCell ref="E1:E4"/>
-    <mergeCell ref="T1:U1"/>
-    <mergeCell ref="N2:O2"/>
-    <mergeCell ref="P2:Q2"/>
-    <mergeCell ref="M1:O1"/>
-    <mergeCell ref="P1:Q1"/>
     <mergeCell ref="P4:Q4"/>
     <mergeCell ref="P3:Q3"/>
     <mergeCell ref="N3:O3"/>
@@ -6200,6 +6231,16 @@
     <mergeCell ref="F1:K4"/>
     <mergeCell ref="L3:L4"/>
     <mergeCell ref="N4:O4"/>
+    <mergeCell ref="T1:U1"/>
+    <mergeCell ref="N2:O2"/>
+    <mergeCell ref="P2:Q2"/>
+    <mergeCell ref="M1:O1"/>
+    <mergeCell ref="P1:Q1"/>
+    <mergeCell ref="A1:A4"/>
+    <mergeCell ref="D1:D4"/>
+    <mergeCell ref="B1:B4"/>
+    <mergeCell ref="L1:L2"/>
+    <mergeCell ref="E1:E4"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="E5:E10">

--- a/input.xlsx
+++ b/input.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\backup01\Desktop\병아리\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DFE398A1-8927-4FDA-96AF-667803C9B668}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D359954-28D6-475B-8F62-C83AF0350456}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -730,22 +730,15 @@
     <xf numFmtId="0" fontId="10" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="41" fontId="4" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="9" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="41" fontId="4" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -755,6 +748,13 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="9" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="백분율" xfId="2" builtinId="5"/>
@@ -1037,7 +1037,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M171"/>
+  <dimension ref="A1:M172"/>
   <sheetFormatPr defaultRowHeight="16" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="12" style="31" customWidth="1"/>
@@ -5624,6 +5624,47 @@
       </c>
       <c r="M171" s="40">
         <v>5837250</v>
+      </c>
+    </row>
+    <row r="172" spans="1:13" ht="16.5" x14ac:dyDescent="0.45">
+      <c r="A172" s="35">
+        <v>46209</v>
+      </c>
+      <c r="B172" s="36">
+        <v>112743225</v>
+      </c>
+      <c r="C172" s="37">
+        <v>6019395</v>
+      </c>
+      <c r="D172" s="38">
+        <v>8051.33</v>
+      </c>
+      <c r="E172" s="37">
+        <v>0</v>
+      </c>
+      <c r="F172" s="40">
+        <v>8086770</v>
+      </c>
+      <c r="G172" s="40">
+        <v>14032840</v>
+      </c>
+      <c r="H172" s="40">
+        <v>19878470</v>
+      </c>
+      <c r="I172" s="40">
+        <v>15959665</v>
+      </c>
+      <c r="J172" s="40">
+        <v>9184525</v>
+      </c>
+      <c r="K172" s="40">
+        <v>22212160</v>
+      </c>
+      <c r="L172" s="40">
+        <v>11910255</v>
+      </c>
+      <c r="M172" s="40">
+        <v>11478540</v>
       </c>
     </row>
   </sheetData>
@@ -5649,72 +5690,72 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:21" x14ac:dyDescent="0.45">
-      <c r="A1" s="44" t="s">
+      <c r="A1" s="46" t="s">
         <v>17</v>
       </c>
-      <c r="B1" s="44" t="s">
+      <c r="B1" s="46" t="s">
         <v>16</v>
       </c>
-      <c r="C1" s="44" t="s">
+      <c r="C1" s="46" t="s">
         <v>18</v>
       </c>
-      <c r="D1" s="44" t="s">
+      <c r="D1" s="46" t="s">
         <v>19</v>
       </c>
-      <c r="E1" s="48" t="s">
+      <c r="E1" s="56" t="s">
         <v>20</v>
       </c>
-      <c r="F1" s="52" t="s">
+      <c r="F1" s="49" t="s">
         <v>21</v>
       </c>
-      <c r="G1" s="53"/>
-      <c r="H1" s="53"/>
-      <c r="I1" s="53"/>
-      <c r="J1" s="53"/>
-      <c r="K1" s="53"/>
-      <c r="L1" s="47">
+      <c r="G1" s="50"/>
+      <c r="H1" s="50"/>
+      <c r="I1" s="50"/>
+      <c r="J1" s="50"/>
+      <c r="K1" s="50"/>
+      <c r="L1" s="54">
         <v>0.7</v>
       </c>
-      <c r="M1" s="44" t="s">
+      <c r="M1" s="46" t="s">
         <v>22</v>
       </c>
-      <c r="N1" s="50"/>
-      <c r="O1" s="49"/>
-      <c r="P1" s="47">
+      <c r="N1" s="55"/>
+      <c r="O1" s="45"/>
+      <c r="P1" s="54">
         <v>0.25</v>
       </c>
-      <c r="Q1" s="49"/>
+      <c r="Q1" s="45"/>
       <c r="R1" s="1"/>
       <c r="S1" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="T1" s="44" t="s">
+      <c r="T1" s="46" t="s">
         <v>23</v>
       </c>
-      <c r="U1" s="49"/>
+      <c r="U1" s="45"/>
     </row>
     <row r="2" spans="1:21" x14ac:dyDescent="0.45">
-      <c r="A2" s="45"/>
-      <c r="B2" s="45"/>
-      <c r="C2" s="45"/>
-      <c r="D2" s="45"/>
-      <c r="E2" s="45"/>
-      <c r="F2" s="54"/>
+      <c r="A2" s="47"/>
+      <c r="B2" s="47"/>
+      <c r="C2" s="47"/>
+      <c r="D2" s="47"/>
+      <c r="E2" s="47"/>
+      <c r="F2" s="51"/>
       <c r="G2" s="42"/>
       <c r="H2" s="42"/>
       <c r="I2" s="42"/>
       <c r="J2" s="42"/>
       <c r="K2" s="42"/>
-      <c r="L2" s="46"/>
+      <c r="L2" s="48"/>
       <c r="M2" s="3"/>
-      <c r="N2" s="47" t="s">
+      <c r="N2" s="54" t="s">
         <v>15</v>
       </c>
-      <c r="O2" s="49"/>
-      <c r="P2" s="44" t="s">
+      <c r="O2" s="45"/>
+      <c r="P2" s="46" t="s">
         <v>24</v>
       </c>
-      <c r="Q2" s="49"/>
+      <c r="Q2" s="45"/>
       <c r="R2" s="1"/>
       <c r="S2" s="4" t="s">
         <v>25</v>
@@ -5727,31 +5768,31 @@
       </c>
     </row>
     <row r="3" spans="1:21" x14ac:dyDescent="0.45">
-      <c r="A3" s="45"/>
-      <c r="B3" s="45"/>
-      <c r="C3" s="45"/>
-      <c r="D3" s="45"/>
-      <c r="E3" s="45"/>
-      <c r="F3" s="54"/>
+      <c r="A3" s="47"/>
+      <c r="B3" s="47"/>
+      <c r="C3" s="47"/>
+      <c r="D3" s="47"/>
+      <c r="E3" s="47"/>
+      <c r="F3" s="51"/>
       <c r="G3" s="42"/>
       <c r="H3" s="42"/>
       <c r="I3" s="42"/>
       <c r="J3" s="42"/>
       <c r="K3" s="42"/>
-      <c r="L3" s="51">
+      <c r="L3" s="44">
         <v>17485</v>
       </c>
       <c r="M3" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="N3" s="51">
+      <c r="N3" s="44">
         <v>14760</v>
       </c>
-      <c r="O3" s="49"/>
-      <c r="P3" s="51">
+      <c r="O3" s="45"/>
+      <c r="P3" s="44">
         <v>8125</v>
       </c>
-      <c r="Q3" s="49"/>
+      <c r="Q3" s="45"/>
       <c r="R3" s="1"/>
       <c r="S3" s="4" t="s">
         <v>27</v>
@@ -5764,29 +5805,29 @@
       </c>
     </row>
     <row r="4" spans="1:21" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A4" s="46"/>
-      <c r="B4" s="46"/>
-      <c r="C4" s="46"/>
-      <c r="D4" s="46"/>
-      <c r="E4" s="46"/>
-      <c r="F4" s="54"/>
+      <c r="A4" s="48"/>
+      <c r="B4" s="48"/>
+      <c r="C4" s="48"/>
+      <c r="D4" s="48"/>
+      <c r="E4" s="48"/>
+      <c r="F4" s="51"/>
       <c r="G4" s="42"/>
       <c r="H4" s="42"/>
       <c r="I4" s="42"/>
       <c r="J4" s="42"/>
       <c r="K4" s="42"/>
-      <c r="L4" s="46"/>
+      <c r="L4" s="48"/>
       <c r="M4" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="N4" s="55">
+      <c r="N4" s="52">
         <v>34705</v>
       </c>
-      <c r="O4" s="56"/>
-      <c r="P4" s="51">
+      <c r="O4" s="53"/>
+      <c r="P4" s="44">
         <v>13230</v>
       </c>
-      <c r="Q4" s="49"/>
+      <c r="Q4" s="45"/>
       <c r="R4" s="1"/>
       <c r="S4" s="4" t="s">
         <v>29</v>
@@ -6224,6 +6265,16 @@
     </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="A1:A4"/>
+    <mergeCell ref="D1:D4"/>
+    <mergeCell ref="B1:B4"/>
+    <mergeCell ref="L1:L2"/>
+    <mergeCell ref="E1:E4"/>
+    <mergeCell ref="T1:U1"/>
+    <mergeCell ref="N2:O2"/>
+    <mergeCell ref="P2:Q2"/>
+    <mergeCell ref="M1:O1"/>
+    <mergeCell ref="P1:Q1"/>
     <mergeCell ref="P4:Q4"/>
     <mergeCell ref="P3:Q3"/>
     <mergeCell ref="N3:O3"/>
@@ -6231,16 +6282,6 @@
     <mergeCell ref="F1:K4"/>
     <mergeCell ref="L3:L4"/>
     <mergeCell ref="N4:O4"/>
-    <mergeCell ref="T1:U1"/>
-    <mergeCell ref="N2:O2"/>
-    <mergeCell ref="P2:Q2"/>
-    <mergeCell ref="M1:O1"/>
-    <mergeCell ref="P1:Q1"/>
-    <mergeCell ref="A1:A4"/>
-    <mergeCell ref="D1:D4"/>
-    <mergeCell ref="B1:B4"/>
-    <mergeCell ref="L1:L2"/>
-    <mergeCell ref="E1:E4"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="E5:E10">

--- a/input.xlsx
+++ b/input.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\backup01\Desktop\병아리\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D359954-28D6-475B-8F62-C83AF0350456}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B9990C94-09F7-47E2-B485-1A07BA60710D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -730,15 +730,22 @@
     <xf numFmtId="0" fontId="10" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="4" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="9" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="41" fontId="4" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -748,13 +755,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="9" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="백분율" xfId="2" builtinId="5"/>
@@ -1037,7 +1037,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M172"/>
+  <dimension ref="A1:M173"/>
   <sheetFormatPr defaultRowHeight="16" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="12" style="31" customWidth="1"/>
@@ -5665,6 +5665,47 @@
       </c>
       <c r="M172" s="40">
         <v>11478540</v>
+      </c>
+    </row>
+    <row r="173" spans="1:13" ht="16.5" x14ac:dyDescent="0.45">
+      <c r="A173" s="35">
+        <v>46210</v>
+      </c>
+      <c r="B173" s="36">
+        <v>127921715</v>
+      </c>
+      <c r="C173" s="37">
+        <v>20986315</v>
+      </c>
+      <c r="D173" s="38">
+        <v>7656.31</v>
+      </c>
+      <c r="E173" s="37">
+        <v>0</v>
+      </c>
+      <c r="F173" s="40">
+        <v>7602950</v>
+      </c>
+      <c r="G173" s="40">
+        <v>12756805</v>
+      </c>
+      <c r="H173" s="40">
+        <v>18211505</v>
+      </c>
+      <c r="I173" s="40">
+        <v>22161030</v>
+      </c>
+      <c r="J173" s="40">
+        <v>16868875</v>
+      </c>
+      <c r="K173" s="40">
+        <v>21582400</v>
+      </c>
+      <c r="L173" s="40">
+        <v>11572575</v>
+      </c>
+      <c r="M173" s="40">
+        <v>17165575</v>
       </c>
     </row>
   </sheetData>
@@ -5690,72 +5731,72 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:21" x14ac:dyDescent="0.45">
-      <c r="A1" s="46" t="s">
+      <c r="A1" s="44" t="s">
         <v>17</v>
       </c>
-      <c r="B1" s="46" t="s">
+      <c r="B1" s="44" t="s">
         <v>16</v>
       </c>
-      <c r="C1" s="46" t="s">
+      <c r="C1" s="44" t="s">
         <v>18</v>
       </c>
-      <c r="D1" s="46" t="s">
+      <c r="D1" s="44" t="s">
         <v>19</v>
       </c>
-      <c r="E1" s="56" t="s">
+      <c r="E1" s="48" t="s">
         <v>20</v>
       </c>
-      <c r="F1" s="49" t="s">
+      <c r="F1" s="52" t="s">
         <v>21</v>
       </c>
-      <c r="G1" s="50"/>
-      <c r="H1" s="50"/>
-      <c r="I1" s="50"/>
-      <c r="J1" s="50"/>
-      <c r="K1" s="50"/>
-      <c r="L1" s="54">
+      <c r="G1" s="53"/>
+      <c r="H1" s="53"/>
+      <c r="I1" s="53"/>
+      <c r="J1" s="53"/>
+      <c r="K1" s="53"/>
+      <c r="L1" s="47">
         <v>0.7</v>
       </c>
-      <c r="M1" s="46" t="s">
+      <c r="M1" s="44" t="s">
         <v>22</v>
       </c>
-      <c r="N1" s="55"/>
-      <c r="O1" s="45"/>
-      <c r="P1" s="54">
+      <c r="N1" s="50"/>
+      <c r="O1" s="49"/>
+      <c r="P1" s="47">
         <v>0.25</v>
       </c>
-      <c r="Q1" s="45"/>
+      <c r="Q1" s="49"/>
       <c r="R1" s="1"/>
       <c r="S1" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="T1" s="46" t="s">
+      <c r="T1" s="44" t="s">
         <v>23</v>
       </c>
-      <c r="U1" s="45"/>
+      <c r="U1" s="49"/>
     </row>
     <row r="2" spans="1:21" x14ac:dyDescent="0.45">
-      <c r="A2" s="47"/>
-      <c r="B2" s="47"/>
-      <c r="C2" s="47"/>
-      <c r="D2" s="47"/>
-      <c r="E2" s="47"/>
-      <c r="F2" s="51"/>
+      <c r="A2" s="45"/>
+      <c r="B2" s="45"/>
+      <c r="C2" s="45"/>
+      <c r="D2" s="45"/>
+      <c r="E2" s="45"/>
+      <c r="F2" s="54"/>
       <c r="G2" s="42"/>
       <c r="H2" s="42"/>
       <c r="I2" s="42"/>
       <c r="J2" s="42"/>
       <c r="K2" s="42"/>
-      <c r="L2" s="48"/>
+      <c r="L2" s="46"/>
       <c r="M2" s="3"/>
-      <c r="N2" s="54" t="s">
+      <c r="N2" s="47" t="s">
         <v>15</v>
       </c>
-      <c r="O2" s="45"/>
-      <c r="P2" s="46" t="s">
+      <c r="O2" s="49"/>
+      <c r="P2" s="44" t="s">
         <v>24</v>
       </c>
-      <c r="Q2" s="45"/>
+      <c r="Q2" s="49"/>
       <c r="R2" s="1"/>
       <c r="S2" s="4" t="s">
         <v>25</v>
@@ -5768,31 +5809,31 @@
       </c>
     </row>
     <row r="3" spans="1:21" x14ac:dyDescent="0.45">
-      <c r="A3" s="47"/>
-      <c r="B3" s="47"/>
-      <c r="C3" s="47"/>
-      <c r="D3" s="47"/>
-      <c r="E3" s="47"/>
-      <c r="F3" s="51"/>
+      <c r="A3" s="45"/>
+      <c r="B3" s="45"/>
+      <c r="C3" s="45"/>
+      <c r="D3" s="45"/>
+      <c r="E3" s="45"/>
+      <c r="F3" s="54"/>
       <c r="G3" s="42"/>
       <c r="H3" s="42"/>
       <c r="I3" s="42"/>
       <c r="J3" s="42"/>
       <c r="K3" s="42"/>
-      <c r="L3" s="44">
+      <c r="L3" s="51">
         <v>17485</v>
       </c>
       <c r="M3" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="N3" s="44">
+      <c r="N3" s="51">
         <v>14760</v>
       </c>
-      <c r="O3" s="45"/>
-      <c r="P3" s="44">
+      <c r="O3" s="49"/>
+      <c r="P3" s="51">
         <v>8125</v>
       </c>
-      <c r="Q3" s="45"/>
+      <c r="Q3" s="49"/>
       <c r="R3" s="1"/>
       <c r="S3" s="4" t="s">
         <v>27</v>
@@ -5805,29 +5846,29 @@
       </c>
     </row>
     <row r="4" spans="1:21" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A4" s="48"/>
-      <c r="B4" s="48"/>
-      <c r="C4" s="48"/>
-      <c r="D4" s="48"/>
-      <c r="E4" s="48"/>
-      <c r="F4" s="51"/>
+      <c r="A4" s="46"/>
+      <c r="B4" s="46"/>
+      <c r="C4" s="46"/>
+      <c r="D4" s="46"/>
+      <c r="E4" s="46"/>
+      <c r="F4" s="54"/>
       <c r="G4" s="42"/>
       <c r="H4" s="42"/>
       <c r="I4" s="42"/>
       <c r="J4" s="42"/>
       <c r="K4" s="42"/>
-      <c r="L4" s="48"/>
+      <c r="L4" s="46"/>
       <c r="M4" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="N4" s="52">
+      <c r="N4" s="55">
         <v>34705</v>
       </c>
-      <c r="O4" s="53"/>
-      <c r="P4" s="44">
+      <c r="O4" s="56"/>
+      <c r="P4" s="51">
         <v>13230</v>
       </c>
-      <c r="Q4" s="45"/>
+      <c r="Q4" s="49"/>
       <c r="R4" s="1"/>
       <c r="S4" s="4" t="s">
         <v>29</v>
@@ -6265,16 +6306,6 @@
     </row>
   </sheetData>
   <mergeCells count="17">
-    <mergeCell ref="A1:A4"/>
-    <mergeCell ref="D1:D4"/>
-    <mergeCell ref="B1:B4"/>
-    <mergeCell ref="L1:L2"/>
-    <mergeCell ref="E1:E4"/>
-    <mergeCell ref="T1:U1"/>
-    <mergeCell ref="N2:O2"/>
-    <mergeCell ref="P2:Q2"/>
-    <mergeCell ref="M1:O1"/>
-    <mergeCell ref="P1:Q1"/>
     <mergeCell ref="P4:Q4"/>
     <mergeCell ref="P3:Q3"/>
     <mergeCell ref="N3:O3"/>
@@ -6282,6 +6313,16 @@
     <mergeCell ref="F1:K4"/>
     <mergeCell ref="L3:L4"/>
     <mergeCell ref="N4:O4"/>
+    <mergeCell ref="T1:U1"/>
+    <mergeCell ref="N2:O2"/>
+    <mergeCell ref="P2:Q2"/>
+    <mergeCell ref="M1:O1"/>
+    <mergeCell ref="P1:Q1"/>
+    <mergeCell ref="A1:A4"/>
+    <mergeCell ref="D1:D4"/>
+    <mergeCell ref="B1:B4"/>
+    <mergeCell ref="L1:L2"/>
+    <mergeCell ref="E1:E4"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="E5:E10">

--- a/input.xlsx
+++ b/input.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\backup01\Desktop\병아리\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B9990C94-09F7-47E2-B485-1A07BA60710D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F3F6FE8-6644-4D7E-B349-484ECE6BD0FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -730,22 +730,15 @@
     <xf numFmtId="0" fontId="10" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="41" fontId="4" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="9" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="41" fontId="4" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -755,6 +748,13 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="9" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="백분율" xfId="2" builtinId="5"/>
@@ -1037,7 +1037,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M173"/>
+  <dimension ref="A1:M174"/>
   <sheetFormatPr defaultRowHeight="16" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="12" style="31" customWidth="1"/>
@@ -5706,6 +5706,47 @@
       </c>
       <c r="M173" s="40">
         <v>17165575</v>
+      </c>
+    </row>
+    <row r="174" spans="1:13" ht="16.5" x14ac:dyDescent="0.45">
+      <c r="A174" s="35">
+        <v>46211</v>
+      </c>
+      <c r="B174" s="36">
+        <v>128983950</v>
+      </c>
+      <c r="C174" s="37">
+        <v>15962060</v>
+      </c>
+      <c r="D174" s="38">
+        <v>7246.79</v>
+      </c>
+      <c r="E174" s="37">
+        <v>-3020380</v>
+      </c>
+      <c r="F174" s="40">
+        <v>6723600</v>
+      </c>
+      <c r="G174" s="40">
+        <v>11402100</v>
+      </c>
+      <c r="H174" s="40">
+        <v>16211100</v>
+      </c>
+      <c r="I174" s="40">
+        <v>19702500</v>
+      </c>
+      <c r="J174" s="40">
+        <v>22917000</v>
+      </c>
+      <c r="K174" s="40">
+        <v>26872800</v>
+      </c>
+      <c r="L174" s="40">
+        <v>10130400</v>
+      </c>
+      <c r="M174" s="40">
+        <v>15024450</v>
       </c>
     </row>
   </sheetData>
@@ -5731,72 +5772,72 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:21" x14ac:dyDescent="0.45">
-      <c r="A1" s="44" t="s">
+      <c r="A1" s="46" t="s">
         <v>17</v>
       </c>
-      <c r="B1" s="44" t="s">
+      <c r="B1" s="46" t="s">
         <v>16</v>
       </c>
-      <c r="C1" s="44" t="s">
+      <c r="C1" s="46" t="s">
         <v>18</v>
       </c>
-      <c r="D1" s="44" t="s">
+      <c r="D1" s="46" t="s">
         <v>19</v>
       </c>
-      <c r="E1" s="48" t="s">
+      <c r="E1" s="56" t="s">
         <v>20</v>
       </c>
-      <c r="F1" s="52" t="s">
+      <c r="F1" s="49" t="s">
         <v>21</v>
       </c>
-      <c r="G1" s="53"/>
-      <c r="H1" s="53"/>
-      <c r="I1" s="53"/>
-      <c r="J1" s="53"/>
-      <c r="K1" s="53"/>
-      <c r="L1" s="47">
+      <c r="G1" s="50"/>
+      <c r="H1" s="50"/>
+      <c r="I1" s="50"/>
+      <c r="J1" s="50"/>
+      <c r="K1" s="50"/>
+      <c r="L1" s="54">
         <v>0.7</v>
       </c>
-      <c r="M1" s="44" t="s">
+      <c r="M1" s="46" t="s">
         <v>22</v>
       </c>
-      <c r="N1" s="50"/>
-      <c r="O1" s="49"/>
-      <c r="P1" s="47">
+      <c r="N1" s="55"/>
+      <c r="O1" s="45"/>
+      <c r="P1" s="54">
         <v>0.25</v>
       </c>
-      <c r="Q1" s="49"/>
+      <c r="Q1" s="45"/>
       <c r="R1" s="1"/>
       <c r="S1" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="T1" s="44" t="s">
+      <c r="T1" s="46" t="s">
         <v>23</v>
       </c>
-      <c r="U1" s="49"/>
+      <c r="U1" s="45"/>
     </row>
     <row r="2" spans="1:21" x14ac:dyDescent="0.45">
-      <c r="A2" s="45"/>
-      <c r="B2" s="45"/>
-      <c r="C2" s="45"/>
-      <c r="D2" s="45"/>
-      <c r="E2" s="45"/>
-      <c r="F2" s="54"/>
+      <c r="A2" s="47"/>
+      <c r="B2" s="47"/>
+      <c r="C2" s="47"/>
+      <c r="D2" s="47"/>
+      <c r="E2" s="47"/>
+      <c r="F2" s="51"/>
       <c r="G2" s="42"/>
       <c r="H2" s="42"/>
       <c r="I2" s="42"/>
       <c r="J2" s="42"/>
       <c r="K2" s="42"/>
-      <c r="L2" s="46"/>
+      <c r="L2" s="48"/>
       <c r="M2" s="3"/>
-      <c r="N2" s="47" t="s">
+      <c r="N2" s="54" t="s">
         <v>15</v>
       </c>
-      <c r="O2" s="49"/>
-      <c r="P2" s="44" t="s">
+      <c r="O2" s="45"/>
+      <c r="P2" s="46" t="s">
         <v>24</v>
       </c>
-      <c r="Q2" s="49"/>
+      <c r="Q2" s="45"/>
       <c r="R2" s="1"/>
       <c r="S2" s="4" t="s">
         <v>25</v>
@@ -5809,31 +5850,31 @@
       </c>
     </row>
     <row r="3" spans="1:21" x14ac:dyDescent="0.45">
-      <c r="A3" s="45"/>
-      <c r="B3" s="45"/>
-      <c r="C3" s="45"/>
-      <c r="D3" s="45"/>
-      <c r="E3" s="45"/>
-      <c r="F3" s="54"/>
+      <c r="A3" s="47"/>
+      <c r="B3" s="47"/>
+      <c r="C3" s="47"/>
+      <c r="D3" s="47"/>
+      <c r="E3" s="47"/>
+      <c r="F3" s="51"/>
       <c r="G3" s="42"/>
       <c r="H3" s="42"/>
       <c r="I3" s="42"/>
       <c r="J3" s="42"/>
       <c r="K3" s="42"/>
-      <c r="L3" s="51">
+      <c r="L3" s="44">
         <v>17485</v>
       </c>
       <c r="M3" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="N3" s="51">
+      <c r="N3" s="44">
         <v>14760</v>
       </c>
-      <c r="O3" s="49"/>
-      <c r="P3" s="51">
+      <c r="O3" s="45"/>
+      <c r="P3" s="44">
         <v>8125</v>
       </c>
-      <c r="Q3" s="49"/>
+      <c r="Q3" s="45"/>
       <c r="R3" s="1"/>
       <c r="S3" s="4" t="s">
         <v>27</v>
@@ -5846,29 +5887,29 @@
       </c>
     </row>
     <row r="4" spans="1:21" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A4" s="46"/>
-      <c r="B4" s="46"/>
-      <c r="C4" s="46"/>
-      <c r="D4" s="46"/>
-      <c r="E4" s="46"/>
-      <c r="F4" s="54"/>
+      <c r="A4" s="48"/>
+      <c r="B4" s="48"/>
+      <c r="C4" s="48"/>
+      <c r="D4" s="48"/>
+      <c r="E4" s="48"/>
+      <c r="F4" s="51"/>
       <c r="G4" s="42"/>
       <c r="H4" s="42"/>
       <c r="I4" s="42"/>
       <c r="J4" s="42"/>
       <c r="K4" s="42"/>
-      <c r="L4" s="46"/>
+      <c r="L4" s="48"/>
       <c r="M4" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="N4" s="55">
+      <c r="N4" s="52">
         <v>34705</v>
       </c>
-      <c r="O4" s="56"/>
-      <c r="P4" s="51">
+      <c r="O4" s="53"/>
+      <c r="P4" s="44">
         <v>13230</v>
       </c>
-      <c r="Q4" s="49"/>
+      <c r="Q4" s="45"/>
       <c r="R4" s="1"/>
       <c r="S4" s="4" t="s">
         <v>29</v>
@@ -6306,6 +6347,16 @@
     </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="A1:A4"/>
+    <mergeCell ref="D1:D4"/>
+    <mergeCell ref="B1:B4"/>
+    <mergeCell ref="L1:L2"/>
+    <mergeCell ref="E1:E4"/>
+    <mergeCell ref="T1:U1"/>
+    <mergeCell ref="N2:O2"/>
+    <mergeCell ref="P2:Q2"/>
+    <mergeCell ref="M1:O1"/>
+    <mergeCell ref="P1:Q1"/>
     <mergeCell ref="P4:Q4"/>
     <mergeCell ref="P3:Q3"/>
     <mergeCell ref="N3:O3"/>
@@ -6313,16 +6364,6 @@
     <mergeCell ref="F1:K4"/>
     <mergeCell ref="L3:L4"/>
     <mergeCell ref="N4:O4"/>
-    <mergeCell ref="T1:U1"/>
-    <mergeCell ref="N2:O2"/>
-    <mergeCell ref="P2:Q2"/>
-    <mergeCell ref="M1:O1"/>
-    <mergeCell ref="P1:Q1"/>
-    <mergeCell ref="A1:A4"/>
-    <mergeCell ref="D1:D4"/>
-    <mergeCell ref="B1:B4"/>
-    <mergeCell ref="L1:L2"/>
-    <mergeCell ref="E1:E4"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="E5:E10">

--- a/input.xlsx
+++ b/input.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\backup01\Desktop\병아리\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F3F6FE8-6644-4D7E-B349-484ECE6BD0FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{529C8A48-7875-4B24-9E04-3AFD1FE8FFEC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -730,15 +730,22 @@
     <xf numFmtId="0" fontId="10" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="4" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="9" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="41" fontId="4" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -748,13 +755,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="9" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="백분율" xfId="2" builtinId="5"/>
@@ -1037,7 +1037,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M174"/>
+  <dimension ref="A1:M175"/>
   <sheetFormatPr defaultRowHeight="16" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="12" style="31" customWidth="1"/>
@@ -5746,6 +5746,45 @@
         <v>10130400</v>
       </c>
       <c r="M174" s="40">
+        <v>15024450</v>
+      </c>
+    </row>
+    <row r="175" spans="1:13" ht="16.5" x14ac:dyDescent="0.45">
+      <c r="A175" s="35">
+        <v>46212</v>
+      </c>
+      <c r="B175" s="36">
+        <v>130879955</v>
+      </c>
+      <c r="C175" s="37"/>
+      <c r="D175" s="38">
+        <v>7283.11</v>
+      </c>
+      <c r="E175" s="37">
+        <v>105440</v>
+      </c>
+      <c r="F175" s="40">
+        <v>6840010</v>
+      </c>
+      <c r="G175" s="40">
+        <v>11566190</v>
+      </c>
+      <c r="H175" s="40">
+        <v>16462540</v>
+      </c>
+      <c r="I175" s="40">
+        <v>20014755</v>
+      </c>
+      <c r="J175" s="40">
+        <v>23277845</v>
+      </c>
+      <c r="K175" s="40">
+        <v>27359750</v>
+      </c>
+      <c r="L175" s="40">
+        <v>10334415</v>
+      </c>
+      <c r="M175" s="40">
         <v>15024450</v>
       </c>
     </row>
@@ -5772,72 +5811,72 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:21" x14ac:dyDescent="0.45">
-      <c r="A1" s="46" t="s">
+      <c r="A1" s="44" t="s">
         <v>17</v>
       </c>
-      <c r="B1" s="46" t="s">
+      <c r="B1" s="44" t="s">
         <v>16</v>
       </c>
-      <c r="C1" s="46" t="s">
+      <c r="C1" s="44" t="s">
         <v>18</v>
       </c>
-      <c r="D1" s="46" t="s">
+      <c r="D1" s="44" t="s">
         <v>19</v>
       </c>
-      <c r="E1" s="56" t="s">
+      <c r="E1" s="48" t="s">
         <v>20</v>
       </c>
-      <c r="F1" s="49" t="s">
+      <c r="F1" s="52" t="s">
         <v>21</v>
       </c>
-      <c r="G1" s="50"/>
-      <c r="H1" s="50"/>
-      <c r="I1" s="50"/>
-      <c r="J1" s="50"/>
-      <c r="K1" s="50"/>
-      <c r="L1" s="54">
+      <c r="G1" s="53"/>
+      <c r="H1" s="53"/>
+      <c r="I1" s="53"/>
+      <c r="J1" s="53"/>
+      <c r="K1" s="53"/>
+      <c r="L1" s="47">
         <v>0.7</v>
       </c>
-      <c r="M1" s="46" t="s">
+      <c r="M1" s="44" t="s">
         <v>22</v>
       </c>
-      <c r="N1" s="55"/>
-      <c r="O1" s="45"/>
-      <c r="P1" s="54">
+      <c r="N1" s="50"/>
+      <c r="O1" s="49"/>
+      <c r="P1" s="47">
         <v>0.25</v>
       </c>
-      <c r="Q1" s="45"/>
+      <c r="Q1" s="49"/>
       <c r="R1" s="1"/>
       <c r="S1" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="T1" s="46" t="s">
+      <c r="T1" s="44" t="s">
         <v>23</v>
       </c>
-      <c r="U1" s="45"/>
+      <c r="U1" s="49"/>
     </row>
     <row r="2" spans="1:21" x14ac:dyDescent="0.45">
-      <c r="A2" s="47"/>
-      <c r="B2" s="47"/>
-      <c r="C2" s="47"/>
-      <c r="D2" s="47"/>
-      <c r="E2" s="47"/>
-      <c r="F2" s="51"/>
+      <c r="A2" s="45"/>
+      <c r="B2" s="45"/>
+      <c r="C2" s="45"/>
+      <c r="D2" s="45"/>
+      <c r="E2" s="45"/>
+      <c r="F2" s="54"/>
       <c r="G2" s="42"/>
       <c r="H2" s="42"/>
       <c r="I2" s="42"/>
       <c r="J2" s="42"/>
       <c r="K2" s="42"/>
-      <c r="L2" s="48"/>
+      <c r="L2" s="46"/>
       <c r="M2" s="3"/>
-      <c r="N2" s="54" t="s">
+      <c r="N2" s="47" t="s">
         <v>15</v>
       </c>
-      <c r="O2" s="45"/>
-      <c r="P2" s="46" t="s">
+      <c r="O2" s="49"/>
+      <c r="P2" s="44" t="s">
         <v>24</v>
       </c>
-      <c r="Q2" s="45"/>
+      <c r="Q2" s="49"/>
       <c r="R2" s="1"/>
       <c r="S2" s="4" t="s">
         <v>25</v>
@@ -5850,31 +5889,31 @@
       </c>
     </row>
     <row r="3" spans="1:21" x14ac:dyDescent="0.45">
-      <c r="A3" s="47"/>
-      <c r="B3" s="47"/>
-      <c r="C3" s="47"/>
-      <c r="D3" s="47"/>
-      <c r="E3" s="47"/>
-      <c r="F3" s="51"/>
+      <c r="A3" s="45"/>
+      <c r="B3" s="45"/>
+      <c r="C3" s="45"/>
+      <c r="D3" s="45"/>
+      <c r="E3" s="45"/>
+      <c r="F3" s="54"/>
       <c r="G3" s="42"/>
       <c r="H3" s="42"/>
       <c r="I3" s="42"/>
       <c r="J3" s="42"/>
       <c r="K3" s="42"/>
-      <c r="L3" s="44">
+      <c r="L3" s="51">
         <v>17485</v>
       </c>
       <c r="M3" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="N3" s="44">
+      <c r="N3" s="51">
         <v>14760</v>
       </c>
-      <c r="O3" s="45"/>
-      <c r="P3" s="44">
+      <c r="O3" s="49"/>
+      <c r="P3" s="51">
         <v>8125</v>
       </c>
-      <c r="Q3" s="45"/>
+      <c r="Q3" s="49"/>
       <c r="R3" s="1"/>
       <c r="S3" s="4" t="s">
         <v>27</v>
@@ -5887,29 +5926,29 @@
       </c>
     </row>
     <row r="4" spans="1:21" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A4" s="48"/>
-      <c r="B4" s="48"/>
-      <c r="C4" s="48"/>
-      <c r="D4" s="48"/>
-      <c r="E4" s="48"/>
-      <c r="F4" s="51"/>
+      <c r="A4" s="46"/>
+      <c r="B4" s="46"/>
+      <c r="C4" s="46"/>
+      <c r="D4" s="46"/>
+      <c r="E4" s="46"/>
+      <c r="F4" s="54"/>
       <c r="G4" s="42"/>
       <c r="H4" s="42"/>
       <c r="I4" s="42"/>
       <c r="J4" s="42"/>
       <c r="K4" s="42"/>
-      <c r="L4" s="48"/>
+      <c r="L4" s="46"/>
       <c r="M4" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="N4" s="52">
+      <c r="N4" s="55">
         <v>34705</v>
       </c>
-      <c r="O4" s="53"/>
-      <c r="P4" s="44">
+      <c r="O4" s="56"/>
+      <c r="P4" s="51">
         <v>13230</v>
       </c>
-      <c r="Q4" s="45"/>
+      <c r="Q4" s="49"/>
       <c r="R4" s="1"/>
       <c r="S4" s="4" t="s">
         <v>29</v>
@@ -6347,16 +6386,6 @@
     </row>
   </sheetData>
   <mergeCells count="17">
-    <mergeCell ref="A1:A4"/>
-    <mergeCell ref="D1:D4"/>
-    <mergeCell ref="B1:B4"/>
-    <mergeCell ref="L1:L2"/>
-    <mergeCell ref="E1:E4"/>
-    <mergeCell ref="T1:U1"/>
-    <mergeCell ref="N2:O2"/>
-    <mergeCell ref="P2:Q2"/>
-    <mergeCell ref="M1:O1"/>
-    <mergeCell ref="P1:Q1"/>
     <mergeCell ref="P4:Q4"/>
     <mergeCell ref="P3:Q3"/>
     <mergeCell ref="N3:O3"/>
@@ -6364,6 +6393,16 @@
     <mergeCell ref="F1:K4"/>
     <mergeCell ref="L3:L4"/>
     <mergeCell ref="N4:O4"/>
+    <mergeCell ref="T1:U1"/>
+    <mergeCell ref="N2:O2"/>
+    <mergeCell ref="P2:Q2"/>
+    <mergeCell ref="M1:O1"/>
+    <mergeCell ref="P1:Q1"/>
+    <mergeCell ref="A1:A4"/>
+    <mergeCell ref="D1:D4"/>
+    <mergeCell ref="B1:B4"/>
+    <mergeCell ref="L1:L2"/>
+    <mergeCell ref="E1:E4"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="E5:E10">

--- a/input.xlsx
+++ b/input.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\backup01\Desktop\병아리\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{529C8A48-7875-4B24-9E04-3AFD1FE8FFEC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E3CABFC-7994-41E8-9B16-81608EA693FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -730,22 +730,15 @@
     <xf numFmtId="0" fontId="10" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="41" fontId="4" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="9" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="41" fontId="4" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -755,6 +748,13 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="9" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="백분율" xfId="2" builtinId="5"/>
@@ -1037,7 +1037,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M175"/>
+  <dimension ref="A1:M176"/>
   <sheetFormatPr defaultRowHeight="16" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="12" style="31" customWidth="1"/>
@@ -5786,6 +5786,47 @@
       </c>
       <c r="M175" s="40">
         <v>15024450</v>
+      </c>
+    </row>
+    <row r="176" spans="1:13" ht="16.5" x14ac:dyDescent="0.45">
+      <c r="A176" s="35">
+        <v>46213</v>
+      </c>
+      <c r="B176" s="36">
+        <v>122993405</v>
+      </c>
+      <c r="C176" s="37">
+        <v>-15024450</v>
+      </c>
+      <c r="D176" s="38">
+        <v>7475.94</v>
+      </c>
+      <c r="E176" s="37">
+        <v>0</v>
+      </c>
+      <c r="F176" s="40">
+        <v>7312520</v>
+      </c>
+      <c r="G176" s="40">
+        <v>12139775</v>
+      </c>
+      <c r="H176" s="40">
+        <v>17402025</v>
+      </c>
+      <c r="I176" s="40">
+        <v>21202105</v>
+      </c>
+      <c r="J176" s="40">
+        <v>24642820</v>
+      </c>
+      <c r="K176" s="40">
+        <v>29052230</v>
+      </c>
+      <c r="L176" s="40">
+        <v>11241930</v>
+      </c>
+      <c r="M176" s="40">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -5811,72 +5852,72 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:21" x14ac:dyDescent="0.45">
-      <c r="A1" s="44" t="s">
+      <c r="A1" s="46" t="s">
         <v>17</v>
       </c>
-      <c r="B1" s="44" t="s">
+      <c r="B1" s="46" t="s">
         <v>16</v>
       </c>
-      <c r="C1" s="44" t="s">
+      <c r="C1" s="46" t="s">
         <v>18</v>
       </c>
-      <c r="D1" s="44" t="s">
+      <c r="D1" s="46" t="s">
         <v>19</v>
       </c>
-      <c r="E1" s="48" t="s">
+      <c r="E1" s="56" t="s">
         <v>20</v>
       </c>
-      <c r="F1" s="52" t="s">
+      <c r="F1" s="49" t="s">
         <v>21</v>
       </c>
-      <c r="G1" s="53"/>
-      <c r="H1" s="53"/>
-      <c r="I1" s="53"/>
-      <c r="J1" s="53"/>
-      <c r="K1" s="53"/>
-      <c r="L1" s="47">
+      <c r="G1" s="50"/>
+      <c r="H1" s="50"/>
+      <c r="I1" s="50"/>
+      <c r="J1" s="50"/>
+      <c r="K1" s="50"/>
+      <c r="L1" s="54">
         <v>0.7</v>
       </c>
-      <c r="M1" s="44" t="s">
+      <c r="M1" s="46" t="s">
         <v>22</v>
       </c>
-      <c r="N1" s="50"/>
-      <c r="O1" s="49"/>
-      <c r="P1" s="47">
+      <c r="N1" s="55"/>
+      <c r="O1" s="45"/>
+      <c r="P1" s="54">
         <v>0.25</v>
       </c>
-      <c r="Q1" s="49"/>
+      <c r="Q1" s="45"/>
       <c r="R1" s="1"/>
       <c r="S1" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="T1" s="44" t="s">
+      <c r="T1" s="46" t="s">
         <v>23</v>
       </c>
-      <c r="U1" s="49"/>
+      <c r="U1" s="45"/>
     </row>
     <row r="2" spans="1:21" x14ac:dyDescent="0.45">
-      <c r="A2" s="45"/>
-      <c r="B2" s="45"/>
-      <c r="C2" s="45"/>
-      <c r="D2" s="45"/>
-      <c r="E2" s="45"/>
-      <c r="F2" s="54"/>
+      <c r="A2" s="47"/>
+      <c r="B2" s="47"/>
+      <c r="C2" s="47"/>
+      <c r="D2" s="47"/>
+      <c r="E2" s="47"/>
+      <c r="F2" s="51"/>
       <c r="G2" s="42"/>
       <c r="H2" s="42"/>
       <c r="I2" s="42"/>
       <c r="J2" s="42"/>
       <c r="K2" s="42"/>
-      <c r="L2" s="46"/>
+      <c r="L2" s="48"/>
       <c r="M2" s="3"/>
-      <c r="N2" s="47" t="s">
+      <c r="N2" s="54" t="s">
         <v>15</v>
       </c>
-      <c r="O2" s="49"/>
-      <c r="P2" s="44" t="s">
+      <c r="O2" s="45"/>
+      <c r="P2" s="46" t="s">
         <v>24</v>
       </c>
-      <c r="Q2" s="49"/>
+      <c r="Q2" s="45"/>
       <c r="R2" s="1"/>
       <c r="S2" s="4" t="s">
         <v>25</v>
@@ -5889,31 +5930,31 @@
       </c>
     </row>
     <row r="3" spans="1:21" x14ac:dyDescent="0.45">
-      <c r="A3" s="45"/>
-      <c r="B3" s="45"/>
-      <c r="C3" s="45"/>
-      <c r="D3" s="45"/>
-      <c r="E3" s="45"/>
-      <c r="F3" s="54"/>
+      <c r="A3" s="47"/>
+      <c r="B3" s="47"/>
+      <c r="C3" s="47"/>
+      <c r="D3" s="47"/>
+      <c r="E3" s="47"/>
+      <c r="F3" s="51"/>
       <c r="G3" s="42"/>
       <c r="H3" s="42"/>
       <c r="I3" s="42"/>
       <c r="J3" s="42"/>
       <c r="K3" s="42"/>
-      <c r="L3" s="51">
+      <c r="L3" s="44">
         <v>17485</v>
       </c>
       <c r="M3" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="N3" s="51">
+      <c r="N3" s="44">
         <v>14760</v>
       </c>
-      <c r="O3" s="49"/>
-      <c r="P3" s="51">
+      <c r="O3" s="45"/>
+      <c r="P3" s="44">
         <v>8125</v>
       </c>
-      <c r="Q3" s="49"/>
+      <c r="Q3" s="45"/>
       <c r="R3" s="1"/>
       <c r="S3" s="4" t="s">
         <v>27</v>
@@ -5926,29 +5967,29 @@
       </c>
     </row>
     <row r="4" spans="1:21" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A4" s="46"/>
-      <c r="B4" s="46"/>
-      <c r="C4" s="46"/>
-      <c r="D4" s="46"/>
-      <c r="E4" s="46"/>
-      <c r="F4" s="54"/>
+      <c r="A4" s="48"/>
+      <c r="B4" s="48"/>
+      <c r="C4" s="48"/>
+      <c r="D4" s="48"/>
+      <c r="E4" s="48"/>
+      <c r="F4" s="51"/>
       <c r="G4" s="42"/>
       <c r="H4" s="42"/>
       <c r="I4" s="42"/>
       <c r="J4" s="42"/>
       <c r="K4" s="42"/>
-      <c r="L4" s="46"/>
+      <c r="L4" s="48"/>
       <c r="M4" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="N4" s="55">
+      <c r="N4" s="52">
         <v>34705</v>
       </c>
-      <c r="O4" s="56"/>
-      <c r="P4" s="51">
+      <c r="O4" s="53"/>
+      <c r="P4" s="44">
         <v>13230</v>
       </c>
-      <c r="Q4" s="49"/>
+      <c r="Q4" s="45"/>
       <c r="R4" s="1"/>
       <c r="S4" s="4" t="s">
         <v>29</v>
@@ -6386,6 +6427,16 @@
     </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="A1:A4"/>
+    <mergeCell ref="D1:D4"/>
+    <mergeCell ref="B1:B4"/>
+    <mergeCell ref="L1:L2"/>
+    <mergeCell ref="E1:E4"/>
+    <mergeCell ref="T1:U1"/>
+    <mergeCell ref="N2:O2"/>
+    <mergeCell ref="P2:Q2"/>
+    <mergeCell ref="M1:O1"/>
+    <mergeCell ref="P1:Q1"/>
     <mergeCell ref="P4:Q4"/>
     <mergeCell ref="P3:Q3"/>
     <mergeCell ref="N3:O3"/>
@@ -6393,16 +6444,6 @@
     <mergeCell ref="F1:K4"/>
     <mergeCell ref="L3:L4"/>
     <mergeCell ref="N4:O4"/>
-    <mergeCell ref="T1:U1"/>
-    <mergeCell ref="N2:O2"/>
-    <mergeCell ref="P2:Q2"/>
-    <mergeCell ref="M1:O1"/>
-    <mergeCell ref="P1:Q1"/>
-    <mergeCell ref="A1:A4"/>
-    <mergeCell ref="D1:D4"/>
-    <mergeCell ref="B1:B4"/>
-    <mergeCell ref="L1:L2"/>
-    <mergeCell ref="E1:E4"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="E5:E10">

--- a/input.xlsx
+++ b/input.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\backup01\Desktop\병아리\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E3CABFC-7994-41E8-9B16-81608EA693FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34E29070-223E-4643-9D70-C23D834A96D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -730,15 +730,22 @@
     <xf numFmtId="0" fontId="10" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="4" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="9" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="41" fontId="4" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -748,13 +755,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="9" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="백분율" xfId="2" builtinId="5"/>
@@ -1037,7 +1037,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M176"/>
+  <dimension ref="A1:M177"/>
   <sheetFormatPr defaultRowHeight="16" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="12" style="31" customWidth="1"/>
@@ -5827,6 +5827,47 @@
       </c>
       <c r="M176" s="40">
         <v>0</v>
+      </c>
+    </row>
+    <row r="177" spans="1:13" ht="16.5" x14ac:dyDescent="0.45">
+      <c r="A177" s="35">
+        <v>46216</v>
+      </c>
+      <c r="B177" s="36">
+        <v>127397160</v>
+      </c>
+      <c r="C177" s="37">
+        <v>19757690</v>
+      </c>
+      <c r="D177" s="38">
+        <v>6806.93</v>
+      </c>
+      <c r="E177" s="37">
+        <v>0</v>
+      </c>
+      <c r="F177" s="40">
+        <v>6386920</v>
+      </c>
+      <c r="G177" s="40">
+        <v>10011220</v>
+      </c>
+      <c r="H177" s="40">
+        <v>14680020</v>
+      </c>
+      <c r="I177" s="40">
+        <v>18005600</v>
+      </c>
+      <c r="J177" s="40">
+        <v>28808800</v>
+      </c>
+      <c r="K177" s="40">
+        <v>27183660</v>
+      </c>
+      <c r="L177" s="40">
+        <v>16324160</v>
+      </c>
+      <c r="M177" s="40">
+        <v>5996780</v>
       </c>
     </row>
   </sheetData>
@@ -5852,72 +5893,72 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:21" x14ac:dyDescent="0.45">
-      <c r="A1" s="46" t="s">
+      <c r="A1" s="44" t="s">
         <v>17</v>
       </c>
-      <c r="B1" s="46" t="s">
+      <c r="B1" s="44" t="s">
         <v>16</v>
       </c>
-      <c r="C1" s="46" t="s">
+      <c r="C1" s="44" t="s">
         <v>18</v>
       </c>
-      <c r="D1" s="46" t="s">
+      <c r="D1" s="44" t="s">
         <v>19</v>
       </c>
-      <c r="E1" s="56" t="s">
+      <c r="E1" s="48" t="s">
         <v>20</v>
       </c>
-      <c r="F1" s="49" t="s">
+      <c r="F1" s="52" t="s">
         <v>21</v>
       </c>
-      <c r="G1" s="50"/>
-      <c r="H1" s="50"/>
-      <c r="I1" s="50"/>
-      <c r="J1" s="50"/>
-      <c r="K1" s="50"/>
-      <c r="L1" s="54">
+      <c r="G1" s="53"/>
+      <c r="H1" s="53"/>
+      <c r="I1" s="53"/>
+      <c r="J1" s="53"/>
+      <c r="K1" s="53"/>
+      <c r="L1" s="47">
         <v>0.7</v>
       </c>
-      <c r="M1" s="46" t="s">
+      <c r="M1" s="44" t="s">
         <v>22</v>
       </c>
-      <c r="N1" s="55"/>
-      <c r="O1" s="45"/>
-      <c r="P1" s="54">
+      <c r="N1" s="50"/>
+      <c r="O1" s="49"/>
+      <c r="P1" s="47">
         <v>0.25</v>
       </c>
-      <c r="Q1" s="45"/>
+      <c r="Q1" s="49"/>
       <c r="R1" s="1"/>
       <c r="S1" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="T1" s="46" t="s">
+      <c r="T1" s="44" t="s">
         <v>23</v>
       </c>
-      <c r="U1" s="45"/>
+      <c r="U1" s="49"/>
     </row>
     <row r="2" spans="1:21" x14ac:dyDescent="0.45">
-      <c r="A2" s="47"/>
-      <c r="B2" s="47"/>
-      <c r="C2" s="47"/>
-      <c r="D2" s="47"/>
-      <c r="E2" s="47"/>
-      <c r="F2" s="51"/>
+      <c r="A2" s="45"/>
+      <c r="B2" s="45"/>
+      <c r="C2" s="45"/>
+      <c r="D2" s="45"/>
+      <c r="E2" s="45"/>
+      <c r="F2" s="54"/>
       <c r="G2" s="42"/>
       <c r="H2" s="42"/>
       <c r="I2" s="42"/>
       <c r="J2" s="42"/>
       <c r="K2" s="42"/>
-      <c r="L2" s="48"/>
+      <c r="L2" s="46"/>
       <c r="M2" s="3"/>
-      <c r="N2" s="54" t="s">
+      <c r="N2" s="47" t="s">
         <v>15</v>
       </c>
-      <c r="O2" s="45"/>
-      <c r="P2" s="46" t="s">
+      <c r="O2" s="49"/>
+      <c r="P2" s="44" t="s">
         <v>24</v>
       </c>
-      <c r="Q2" s="45"/>
+      <c r="Q2" s="49"/>
       <c r="R2" s="1"/>
       <c r="S2" s="4" t="s">
         <v>25</v>
@@ -5930,31 +5971,31 @@
       </c>
     </row>
     <row r="3" spans="1:21" x14ac:dyDescent="0.45">
-      <c r="A3" s="47"/>
-      <c r="B3" s="47"/>
-      <c r="C3" s="47"/>
-      <c r="D3" s="47"/>
-      <c r="E3" s="47"/>
-      <c r="F3" s="51"/>
+      <c r="A3" s="45"/>
+      <c r="B3" s="45"/>
+      <c r="C3" s="45"/>
+      <c r="D3" s="45"/>
+      <c r="E3" s="45"/>
+      <c r="F3" s="54"/>
       <c r="G3" s="42"/>
       <c r="H3" s="42"/>
       <c r="I3" s="42"/>
       <c r="J3" s="42"/>
       <c r="K3" s="42"/>
-      <c r="L3" s="44">
+      <c r="L3" s="51">
         <v>17485</v>
       </c>
       <c r="M3" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="N3" s="44">
+      <c r="N3" s="51">
         <v>14760</v>
       </c>
-      <c r="O3" s="45"/>
-      <c r="P3" s="44">
+      <c r="O3" s="49"/>
+      <c r="P3" s="51">
         <v>8125</v>
       </c>
-      <c r="Q3" s="45"/>
+      <c r="Q3" s="49"/>
       <c r="R3" s="1"/>
       <c r="S3" s="4" t="s">
         <v>27</v>
@@ -5967,29 +6008,29 @@
       </c>
     </row>
     <row r="4" spans="1:21" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A4" s="48"/>
-      <c r="B4" s="48"/>
-      <c r="C4" s="48"/>
-      <c r="D4" s="48"/>
-      <c r="E4" s="48"/>
-      <c r="F4" s="51"/>
+      <c r="A4" s="46"/>
+      <c r="B4" s="46"/>
+      <c r="C4" s="46"/>
+      <c r="D4" s="46"/>
+      <c r="E4" s="46"/>
+      <c r="F4" s="54"/>
       <c r="G4" s="42"/>
       <c r="H4" s="42"/>
       <c r="I4" s="42"/>
       <c r="J4" s="42"/>
       <c r="K4" s="42"/>
-      <c r="L4" s="48"/>
+      <c r="L4" s="46"/>
       <c r="M4" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="N4" s="52">
+      <c r="N4" s="55">
         <v>34705</v>
       </c>
-      <c r="O4" s="53"/>
-      <c r="P4" s="44">
+      <c r="O4" s="56"/>
+      <c r="P4" s="51">
         <v>13230</v>
       </c>
-      <c r="Q4" s="45"/>
+      <c r="Q4" s="49"/>
       <c r="R4" s="1"/>
       <c r="S4" s="4" t="s">
         <v>29</v>
@@ -6427,16 +6468,6 @@
     </row>
   </sheetData>
   <mergeCells count="17">
-    <mergeCell ref="A1:A4"/>
-    <mergeCell ref="D1:D4"/>
-    <mergeCell ref="B1:B4"/>
-    <mergeCell ref="L1:L2"/>
-    <mergeCell ref="E1:E4"/>
-    <mergeCell ref="T1:U1"/>
-    <mergeCell ref="N2:O2"/>
-    <mergeCell ref="P2:Q2"/>
-    <mergeCell ref="M1:O1"/>
-    <mergeCell ref="P1:Q1"/>
     <mergeCell ref="P4:Q4"/>
     <mergeCell ref="P3:Q3"/>
     <mergeCell ref="N3:O3"/>
@@ -6444,6 +6475,16 @@
     <mergeCell ref="F1:K4"/>
     <mergeCell ref="L3:L4"/>
     <mergeCell ref="N4:O4"/>
+    <mergeCell ref="T1:U1"/>
+    <mergeCell ref="N2:O2"/>
+    <mergeCell ref="P2:Q2"/>
+    <mergeCell ref="M1:O1"/>
+    <mergeCell ref="P1:Q1"/>
+    <mergeCell ref="A1:A4"/>
+    <mergeCell ref="D1:D4"/>
+    <mergeCell ref="B1:B4"/>
+    <mergeCell ref="L1:L2"/>
+    <mergeCell ref="E1:E4"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="E5:E10">

--- a/input.xlsx
+++ b/input.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\backup01\Desktop\병아리\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34E29070-223E-4643-9D70-C23D834A96D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71852C12-F7D0-47D4-8B1B-D95BD75DDEB1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -730,22 +730,15 @@
     <xf numFmtId="0" fontId="10" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="41" fontId="4" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="9" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="41" fontId="4" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -755,6 +748,13 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="9" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="백분율" xfId="2" builtinId="5"/>
@@ -1037,7 +1037,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M177"/>
+  <dimension ref="A1:M178"/>
   <sheetFormatPr defaultRowHeight="16" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="12" style="31" customWidth="1"/>
@@ -5868,6 +5868,47 @@
       </c>
       <c r="M177" s="40">
         <v>5996780</v>
+      </c>
+    </row>
+    <row r="178" spans="1:13" ht="16.5" x14ac:dyDescent="0.45">
+      <c r="A178" s="35">
+        <v>46217</v>
+      </c>
+      <c r="B178" s="36">
+        <v>130459520</v>
+      </c>
+      <c r="C178" s="37">
+        <v>5995220</v>
+      </c>
+      <c r="D178" s="38">
+        <v>6856.83</v>
+      </c>
+      <c r="E178" s="37">
+        <v>107130</v>
+      </c>
+      <c r="F178" s="40">
+        <v>6199940</v>
+      </c>
+      <c r="G178" s="40">
+        <v>10037760</v>
+      </c>
+      <c r="H178" s="40">
+        <v>14530660</v>
+      </c>
+      <c r="I178" s="40">
+        <v>17755370</v>
+      </c>
+      <c r="J178" s="40">
+        <v>28651230</v>
+      </c>
+      <c r="K178" s="40">
+        <v>26215980</v>
+      </c>
+      <c r="L178" s="40">
+        <v>15412320</v>
+      </c>
+      <c r="M178" s="40">
+        <v>11656260</v>
       </c>
     </row>
   </sheetData>
@@ -5893,72 +5934,72 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:21" x14ac:dyDescent="0.45">
-      <c r="A1" s="44" t="s">
+      <c r="A1" s="46" t="s">
         <v>17</v>
       </c>
-      <c r="B1" s="44" t="s">
+      <c r="B1" s="46" t="s">
         <v>16</v>
       </c>
-      <c r="C1" s="44" t="s">
+      <c r="C1" s="46" t="s">
         <v>18</v>
       </c>
-      <c r="D1" s="44" t="s">
+      <c r="D1" s="46" t="s">
         <v>19</v>
       </c>
-      <c r="E1" s="48" t="s">
+      <c r="E1" s="56" t="s">
         <v>20</v>
       </c>
-      <c r="F1" s="52" t="s">
+      <c r="F1" s="49" t="s">
         <v>21</v>
       </c>
-      <c r="G1" s="53"/>
-      <c r="H1" s="53"/>
-      <c r="I1" s="53"/>
-      <c r="J1" s="53"/>
-      <c r="K1" s="53"/>
-      <c r="L1" s="47">
+      <c r="G1" s="50"/>
+      <c r="H1" s="50"/>
+      <c r="I1" s="50"/>
+      <c r="J1" s="50"/>
+      <c r="K1" s="50"/>
+      <c r="L1" s="54">
         <v>0.7</v>
       </c>
-      <c r="M1" s="44" t="s">
+      <c r="M1" s="46" t="s">
         <v>22</v>
       </c>
-      <c r="N1" s="50"/>
-      <c r="O1" s="49"/>
-      <c r="P1" s="47">
+      <c r="N1" s="55"/>
+      <c r="O1" s="45"/>
+      <c r="P1" s="54">
         <v>0.25</v>
       </c>
-      <c r="Q1" s="49"/>
+      <c r="Q1" s="45"/>
       <c r="R1" s="1"/>
       <c r="S1" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="T1" s="44" t="s">
+      <c r="T1" s="46" t="s">
         <v>23</v>
       </c>
-      <c r="U1" s="49"/>
+      <c r="U1" s="45"/>
     </row>
     <row r="2" spans="1:21" x14ac:dyDescent="0.45">
-      <c r="A2" s="45"/>
-      <c r="B2" s="45"/>
-      <c r="C2" s="45"/>
-      <c r="D2" s="45"/>
-      <c r="E2" s="45"/>
-      <c r="F2" s="54"/>
+      <c r="A2" s="47"/>
+      <c r="B2" s="47"/>
+      <c r="C2" s="47"/>
+      <c r="D2" s="47"/>
+      <c r="E2" s="47"/>
+      <c r="F2" s="51"/>
       <c r="G2" s="42"/>
       <c r="H2" s="42"/>
       <c r="I2" s="42"/>
       <c r="J2" s="42"/>
       <c r="K2" s="42"/>
-      <c r="L2" s="46"/>
+      <c r="L2" s="48"/>
       <c r="M2" s="3"/>
-      <c r="N2" s="47" t="s">
+      <c r="N2" s="54" t="s">
         <v>15</v>
       </c>
-      <c r="O2" s="49"/>
-      <c r="P2" s="44" t="s">
+      <c r="O2" s="45"/>
+      <c r="P2" s="46" t="s">
         <v>24</v>
       </c>
-      <c r="Q2" s="49"/>
+      <c r="Q2" s="45"/>
       <c r="R2" s="1"/>
       <c r="S2" s="4" t="s">
         <v>25</v>
@@ -5971,31 +6012,31 @@
       </c>
     </row>
     <row r="3" spans="1:21" x14ac:dyDescent="0.45">
-      <c r="A3" s="45"/>
-      <c r="B3" s="45"/>
-      <c r="C3" s="45"/>
-      <c r="D3" s="45"/>
-      <c r="E3" s="45"/>
-      <c r="F3" s="54"/>
+      <c r="A3" s="47"/>
+      <c r="B3" s="47"/>
+      <c r="C3" s="47"/>
+      <c r="D3" s="47"/>
+      <c r="E3" s="47"/>
+      <c r="F3" s="51"/>
       <c r="G3" s="42"/>
       <c r="H3" s="42"/>
       <c r="I3" s="42"/>
       <c r="J3" s="42"/>
       <c r="K3" s="42"/>
-      <c r="L3" s="51">
+      <c r="L3" s="44">
         <v>17485</v>
       </c>
       <c r="M3" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="N3" s="51">
+      <c r="N3" s="44">
         <v>14760</v>
       </c>
-      <c r="O3" s="49"/>
-      <c r="P3" s="51">
+      <c r="O3" s="45"/>
+      <c r="P3" s="44">
         <v>8125</v>
       </c>
-      <c r="Q3" s="49"/>
+      <c r="Q3" s="45"/>
       <c r="R3" s="1"/>
       <c r="S3" s="4" t="s">
         <v>27</v>
@@ -6008,29 +6049,29 @@
       </c>
     </row>
     <row r="4" spans="1:21" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A4" s="46"/>
-      <c r="B4" s="46"/>
-      <c r="C4" s="46"/>
-      <c r="D4" s="46"/>
-      <c r="E4" s="46"/>
-      <c r="F4" s="54"/>
+      <c r="A4" s="48"/>
+      <c r="B4" s="48"/>
+      <c r="C4" s="48"/>
+      <c r="D4" s="48"/>
+      <c r="E4" s="48"/>
+      <c r="F4" s="51"/>
       <c r="G4" s="42"/>
       <c r="H4" s="42"/>
       <c r="I4" s="42"/>
       <c r="J4" s="42"/>
       <c r="K4" s="42"/>
-      <c r="L4" s="46"/>
+      <c r="L4" s="48"/>
       <c r="M4" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="N4" s="55">
+      <c r="N4" s="52">
         <v>34705</v>
       </c>
-      <c r="O4" s="56"/>
-      <c r="P4" s="51">
+      <c r="O4" s="53"/>
+      <c r="P4" s="44">
         <v>13230</v>
       </c>
-      <c r="Q4" s="49"/>
+      <c r="Q4" s="45"/>
       <c r="R4" s="1"/>
       <c r="S4" s="4" t="s">
         <v>29</v>
@@ -6468,6 +6509,16 @@
     </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="A1:A4"/>
+    <mergeCell ref="D1:D4"/>
+    <mergeCell ref="B1:B4"/>
+    <mergeCell ref="L1:L2"/>
+    <mergeCell ref="E1:E4"/>
+    <mergeCell ref="T1:U1"/>
+    <mergeCell ref="N2:O2"/>
+    <mergeCell ref="P2:Q2"/>
+    <mergeCell ref="M1:O1"/>
+    <mergeCell ref="P1:Q1"/>
     <mergeCell ref="P4:Q4"/>
     <mergeCell ref="P3:Q3"/>
     <mergeCell ref="N3:O3"/>
@@ -6475,16 +6526,6 @@
     <mergeCell ref="F1:K4"/>
     <mergeCell ref="L3:L4"/>
     <mergeCell ref="N4:O4"/>
-    <mergeCell ref="T1:U1"/>
-    <mergeCell ref="N2:O2"/>
-    <mergeCell ref="P2:Q2"/>
-    <mergeCell ref="M1:O1"/>
-    <mergeCell ref="P1:Q1"/>
-    <mergeCell ref="A1:A4"/>
-    <mergeCell ref="D1:D4"/>
-    <mergeCell ref="B1:B4"/>
-    <mergeCell ref="L1:L2"/>
-    <mergeCell ref="E1:E4"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="E5:E10">

--- a/input.xlsx
+++ b/input.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\backup01\Desktop\병아리\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71852C12-F7D0-47D4-8B1B-D95BD75DDEB1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{467C616B-3AA6-458F-A9A6-C812A5795B94}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -730,15 +730,22 @@
     <xf numFmtId="0" fontId="10" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="4" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="9" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="41" fontId="4" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -748,13 +755,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="9" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="백분율" xfId="2" builtinId="5"/>
@@ -1037,7 +1037,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M178"/>
+  <dimension ref="A1:M179"/>
   <sheetFormatPr defaultRowHeight="16" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="12" style="31" customWidth="1"/>
@@ -5909,6 +5909,45 @@
       </c>
       <c r="M178" s="40">
         <v>11656260</v>
+      </c>
+    </row>
+    <row r="179" spans="1:13" ht="16.5" x14ac:dyDescent="0.45">
+      <c r="A179" s="35">
+        <v>46218</v>
+      </c>
+      <c r="B179" s="36">
+        <v>146490010</v>
+      </c>
+      <c r="C179" s="37"/>
+      <c r="D179" s="38">
+        <v>7284.41</v>
+      </c>
+      <c r="E179" s="37">
+        <v>1209220</v>
+      </c>
+      <c r="F179" s="40">
+        <v>7012700</v>
+      </c>
+      <c r="G179" s="40">
+        <v>11334730</v>
+      </c>
+      <c r="H179" s="40">
+        <v>16418930</v>
+      </c>
+      <c r="I179" s="40">
+        <v>20066580</v>
+      </c>
+      <c r="J179" s="40">
+        <v>32366620</v>
+      </c>
+      <c r="K179" s="40">
+        <v>28630060</v>
+      </c>
+      <c r="L179" s="40">
+        <v>17458400</v>
+      </c>
+      <c r="M179" s="40">
+        <v>13201990</v>
       </c>
     </row>
   </sheetData>
@@ -5934,72 +5973,72 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:21" x14ac:dyDescent="0.45">
-      <c r="A1" s="46" t="s">
+      <c r="A1" s="44" t="s">
         <v>17</v>
       </c>
-      <c r="B1" s="46" t="s">
+      <c r="B1" s="44" t="s">
         <v>16</v>
       </c>
-      <c r="C1" s="46" t="s">
+      <c r="C1" s="44" t="s">
         <v>18</v>
       </c>
-      <c r="D1" s="46" t="s">
+      <c r="D1" s="44" t="s">
         <v>19</v>
       </c>
-      <c r="E1" s="56" t="s">
+      <c r="E1" s="48" t="s">
         <v>20</v>
       </c>
-      <c r="F1" s="49" t="s">
+      <c r="F1" s="52" t="s">
         <v>21</v>
       </c>
-      <c r="G1" s="50"/>
-      <c r="H1" s="50"/>
-      <c r="I1" s="50"/>
-      <c r="J1" s="50"/>
-      <c r="K1" s="50"/>
-      <c r="L1" s="54">
+      <c r="G1" s="53"/>
+      <c r="H1" s="53"/>
+      <c r="I1" s="53"/>
+      <c r="J1" s="53"/>
+      <c r="K1" s="53"/>
+      <c r="L1" s="47">
         <v>0.7</v>
       </c>
-      <c r="M1" s="46" t="s">
+      <c r="M1" s="44" t="s">
         <v>22</v>
       </c>
-      <c r="N1" s="55"/>
-      <c r="O1" s="45"/>
-      <c r="P1" s="54">
+      <c r="N1" s="50"/>
+      <c r="O1" s="49"/>
+      <c r="P1" s="47">
         <v>0.25</v>
       </c>
-      <c r="Q1" s="45"/>
+      <c r="Q1" s="49"/>
       <c r="R1" s="1"/>
       <c r="S1" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="T1" s="46" t="s">
+      <c r="T1" s="44" t="s">
         <v>23</v>
       </c>
-      <c r="U1" s="45"/>
+      <c r="U1" s="49"/>
     </row>
     <row r="2" spans="1:21" x14ac:dyDescent="0.45">
-      <c r="A2" s="47"/>
-      <c r="B2" s="47"/>
-      <c r="C2" s="47"/>
-      <c r="D2" s="47"/>
-      <c r="E2" s="47"/>
-      <c r="F2" s="51"/>
+      <c r="A2" s="45"/>
+      <c r="B2" s="45"/>
+      <c r="C2" s="45"/>
+      <c r="D2" s="45"/>
+      <c r="E2" s="45"/>
+      <c r="F2" s="54"/>
       <c r="G2" s="42"/>
       <c r="H2" s="42"/>
       <c r="I2" s="42"/>
       <c r="J2" s="42"/>
       <c r="K2" s="42"/>
-      <c r="L2" s="48"/>
+      <c r="L2" s="46"/>
       <c r="M2" s="3"/>
-      <c r="N2" s="54" t="s">
+      <c r="N2" s="47" t="s">
         <v>15</v>
       </c>
-      <c r="O2" s="45"/>
-      <c r="P2" s="46" t="s">
+      <c r="O2" s="49"/>
+      <c r="P2" s="44" t="s">
         <v>24</v>
       </c>
-      <c r="Q2" s="45"/>
+      <c r="Q2" s="49"/>
       <c r="R2" s="1"/>
       <c r="S2" s="4" t="s">
         <v>25</v>
@@ -6012,31 +6051,31 @@
       </c>
     </row>
     <row r="3" spans="1:21" x14ac:dyDescent="0.45">
-      <c r="A3" s="47"/>
-      <c r="B3" s="47"/>
-      <c r="C3" s="47"/>
-      <c r="D3" s="47"/>
-      <c r="E3" s="47"/>
-      <c r="F3" s="51"/>
+      <c r="A3" s="45"/>
+      <c r="B3" s="45"/>
+      <c r="C3" s="45"/>
+      <c r="D3" s="45"/>
+      <c r="E3" s="45"/>
+      <c r="F3" s="54"/>
       <c r="G3" s="42"/>
       <c r="H3" s="42"/>
       <c r="I3" s="42"/>
       <c r="J3" s="42"/>
       <c r="K3" s="42"/>
-      <c r="L3" s="44">
+      <c r="L3" s="51">
         <v>17485</v>
       </c>
       <c r="M3" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="N3" s="44">
+      <c r="N3" s="51">
         <v>14760</v>
       </c>
-      <c r="O3" s="45"/>
-      <c r="P3" s="44">
+      <c r="O3" s="49"/>
+      <c r="P3" s="51">
         <v>8125</v>
       </c>
-      <c r="Q3" s="45"/>
+      <c r="Q3" s="49"/>
       <c r="R3" s="1"/>
       <c r="S3" s="4" t="s">
         <v>27</v>
@@ -6049,29 +6088,29 @@
       </c>
     </row>
     <row r="4" spans="1:21" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A4" s="48"/>
-      <c r="B4" s="48"/>
-      <c r="C4" s="48"/>
-      <c r="D4" s="48"/>
-      <c r="E4" s="48"/>
-      <c r="F4" s="51"/>
+      <c r="A4" s="46"/>
+      <c r="B4" s="46"/>
+      <c r="C4" s="46"/>
+      <c r="D4" s="46"/>
+      <c r="E4" s="46"/>
+      <c r="F4" s="54"/>
       <c r="G4" s="42"/>
       <c r="H4" s="42"/>
       <c r="I4" s="42"/>
       <c r="J4" s="42"/>
       <c r="K4" s="42"/>
-      <c r="L4" s="48"/>
+      <c r="L4" s="46"/>
       <c r="M4" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="N4" s="52">
+      <c r="N4" s="55">
         <v>34705</v>
       </c>
-      <c r="O4" s="53"/>
-      <c r="P4" s="44">
+      <c r="O4" s="56"/>
+      <c r="P4" s="51">
         <v>13230</v>
       </c>
-      <c r="Q4" s="45"/>
+      <c r="Q4" s="49"/>
       <c r="R4" s="1"/>
       <c r="S4" s="4" t="s">
         <v>29</v>
@@ -6509,16 +6548,6 @@
     </row>
   </sheetData>
   <mergeCells count="17">
-    <mergeCell ref="A1:A4"/>
-    <mergeCell ref="D1:D4"/>
-    <mergeCell ref="B1:B4"/>
-    <mergeCell ref="L1:L2"/>
-    <mergeCell ref="E1:E4"/>
-    <mergeCell ref="T1:U1"/>
-    <mergeCell ref="N2:O2"/>
-    <mergeCell ref="P2:Q2"/>
-    <mergeCell ref="M1:O1"/>
-    <mergeCell ref="P1:Q1"/>
     <mergeCell ref="P4:Q4"/>
     <mergeCell ref="P3:Q3"/>
     <mergeCell ref="N3:O3"/>
@@ -6526,6 +6555,16 @@
     <mergeCell ref="F1:K4"/>
     <mergeCell ref="L3:L4"/>
     <mergeCell ref="N4:O4"/>
+    <mergeCell ref="T1:U1"/>
+    <mergeCell ref="N2:O2"/>
+    <mergeCell ref="P2:Q2"/>
+    <mergeCell ref="M1:O1"/>
+    <mergeCell ref="P1:Q1"/>
+    <mergeCell ref="A1:A4"/>
+    <mergeCell ref="D1:D4"/>
+    <mergeCell ref="B1:B4"/>
+    <mergeCell ref="L1:L2"/>
+    <mergeCell ref="E1:E4"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="E5:E10">

--- a/input.xlsx
+++ b/input.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\backup01\Desktop\병아리\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{467C616B-3AA6-458F-A9A6-C812A5795B94}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AEEA0C87-A2DF-4BB0-9279-9301A1334C04}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -730,22 +730,15 @@
     <xf numFmtId="0" fontId="10" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="41" fontId="4" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="9" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="41" fontId="4" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -755,6 +748,13 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="9" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="백분율" xfId="2" builtinId="5"/>
@@ -1037,7 +1037,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M179"/>
+  <dimension ref="A1:M180"/>
   <sheetFormatPr defaultRowHeight="16" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="12" style="31" customWidth="1"/>
@@ -5948,6 +5948,47 @@
       </c>
       <c r="M179" s="40">
         <v>13201990</v>
+      </c>
+    </row>
+    <row r="180" spans="1:13" ht="16.5" x14ac:dyDescent="0.45">
+      <c r="A180" s="35">
+        <v>46219</v>
+      </c>
+      <c r="B180" s="36">
+        <v>145013070</v>
+      </c>
+      <c r="C180" s="37">
+        <v>13870300</v>
+      </c>
+      <c r="D180" s="38">
+        <v>6820.6</v>
+      </c>
+      <c r="E180" s="37">
+        <v>0</v>
+      </c>
+      <c r="F180" s="40">
+        <v>6167930</v>
+      </c>
+      <c r="G180" s="40">
+        <v>9837230</v>
+      </c>
+      <c r="H180" s="40">
+        <v>14325180</v>
+      </c>
+      <c r="I180" s="40">
+        <v>17534875</v>
+      </c>
+      <c r="J180" s="40">
+        <v>36137225</v>
+      </c>
+      <c r="K180" s="40">
+        <v>26281640</v>
+      </c>
+      <c r="L180" s="40">
+        <v>21527770</v>
+      </c>
+      <c r="M180" s="40">
+        <v>13201220</v>
       </c>
     </row>
   </sheetData>
@@ -5973,72 +6014,72 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:21" x14ac:dyDescent="0.45">
-      <c r="A1" s="44" t="s">
+      <c r="A1" s="46" t="s">
         <v>17</v>
       </c>
-      <c r="B1" s="44" t="s">
+      <c r="B1" s="46" t="s">
         <v>16</v>
       </c>
-      <c r="C1" s="44" t="s">
+      <c r="C1" s="46" t="s">
         <v>18</v>
       </c>
-      <c r="D1" s="44" t="s">
+      <c r="D1" s="46" t="s">
         <v>19</v>
       </c>
-      <c r="E1" s="48" t="s">
+      <c r="E1" s="56" t="s">
         <v>20</v>
       </c>
-      <c r="F1" s="52" t="s">
+      <c r="F1" s="49" t="s">
         <v>21</v>
       </c>
-      <c r="G1" s="53"/>
-      <c r="H1" s="53"/>
-      <c r="I1" s="53"/>
-      <c r="J1" s="53"/>
-      <c r="K1" s="53"/>
-      <c r="L1" s="47">
+      <c r="G1" s="50"/>
+      <c r="H1" s="50"/>
+      <c r="I1" s="50"/>
+      <c r="J1" s="50"/>
+      <c r="K1" s="50"/>
+      <c r="L1" s="54">
         <v>0.7</v>
       </c>
-      <c r="M1" s="44" t="s">
+      <c r="M1" s="46" t="s">
         <v>22</v>
       </c>
-      <c r="N1" s="50"/>
-      <c r="O1" s="49"/>
-      <c r="P1" s="47">
+      <c r="N1" s="55"/>
+      <c r="O1" s="45"/>
+      <c r="P1" s="54">
         <v>0.25</v>
       </c>
-      <c r="Q1" s="49"/>
+      <c r="Q1" s="45"/>
       <c r="R1" s="1"/>
       <c r="S1" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="T1" s="44" t="s">
+      <c r="T1" s="46" t="s">
         <v>23</v>
       </c>
-      <c r="U1" s="49"/>
+      <c r="U1" s="45"/>
     </row>
     <row r="2" spans="1:21" x14ac:dyDescent="0.45">
-      <c r="A2" s="45"/>
-      <c r="B2" s="45"/>
-      <c r="C2" s="45"/>
-      <c r="D2" s="45"/>
-      <c r="E2" s="45"/>
-      <c r="F2" s="54"/>
+      <c r="A2" s="47"/>
+      <c r="B2" s="47"/>
+      <c r="C2" s="47"/>
+      <c r="D2" s="47"/>
+      <c r="E2" s="47"/>
+      <c r="F2" s="51"/>
       <c r="G2" s="42"/>
       <c r="H2" s="42"/>
       <c r="I2" s="42"/>
       <c r="J2" s="42"/>
       <c r="K2" s="42"/>
-      <c r="L2" s="46"/>
+      <c r="L2" s="48"/>
       <c r="M2" s="3"/>
-      <c r="N2" s="47" t="s">
+      <c r="N2" s="54" t="s">
         <v>15</v>
       </c>
-      <c r="O2" s="49"/>
-      <c r="P2" s="44" t="s">
+      <c r="O2" s="45"/>
+      <c r="P2" s="46" t="s">
         <v>24</v>
       </c>
-      <c r="Q2" s="49"/>
+      <c r="Q2" s="45"/>
       <c r="R2" s="1"/>
       <c r="S2" s="4" t="s">
         <v>25</v>
@@ -6051,31 +6092,31 @@
       </c>
     </row>
     <row r="3" spans="1:21" x14ac:dyDescent="0.45">
-      <c r="A3" s="45"/>
-      <c r="B3" s="45"/>
-      <c r="C3" s="45"/>
-      <c r="D3" s="45"/>
-      <c r="E3" s="45"/>
-      <c r="F3" s="54"/>
+      <c r="A3" s="47"/>
+      <c r="B3" s="47"/>
+      <c r="C3" s="47"/>
+      <c r="D3" s="47"/>
+      <c r="E3" s="47"/>
+      <c r="F3" s="51"/>
       <c r="G3" s="42"/>
       <c r="H3" s="42"/>
       <c r="I3" s="42"/>
       <c r="J3" s="42"/>
       <c r="K3" s="42"/>
-      <c r="L3" s="51">
+      <c r="L3" s="44">
         <v>17485</v>
       </c>
       <c r="M3" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="N3" s="51">
+      <c r="N3" s="44">
         <v>14760</v>
       </c>
-      <c r="O3" s="49"/>
-      <c r="P3" s="51">
+      <c r="O3" s="45"/>
+      <c r="P3" s="44">
         <v>8125</v>
       </c>
-      <c r="Q3" s="49"/>
+      <c r="Q3" s="45"/>
       <c r="R3" s="1"/>
       <c r="S3" s="4" t="s">
         <v>27</v>
@@ -6088,29 +6129,29 @@
       </c>
     </row>
     <row r="4" spans="1:21" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A4" s="46"/>
-      <c r="B4" s="46"/>
-      <c r="C4" s="46"/>
-      <c r="D4" s="46"/>
-      <c r="E4" s="46"/>
-      <c r="F4" s="54"/>
+      <c r="A4" s="48"/>
+      <c r="B4" s="48"/>
+      <c r="C4" s="48"/>
+      <c r="D4" s="48"/>
+      <c r="E4" s="48"/>
+      <c r="F4" s="51"/>
       <c r="G4" s="42"/>
       <c r="H4" s="42"/>
       <c r="I4" s="42"/>
       <c r="J4" s="42"/>
       <c r="K4" s="42"/>
-      <c r="L4" s="46"/>
+      <c r="L4" s="48"/>
       <c r="M4" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="N4" s="55">
+      <c r="N4" s="52">
         <v>34705</v>
       </c>
-      <c r="O4" s="56"/>
-      <c r="P4" s="51">
+      <c r="O4" s="53"/>
+      <c r="P4" s="44">
         <v>13230</v>
       </c>
-      <c r="Q4" s="49"/>
+      <c r="Q4" s="45"/>
       <c r="R4" s="1"/>
       <c r="S4" s="4" t="s">
         <v>29</v>
@@ -6548,6 +6589,16 @@
     </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="A1:A4"/>
+    <mergeCell ref="D1:D4"/>
+    <mergeCell ref="B1:B4"/>
+    <mergeCell ref="L1:L2"/>
+    <mergeCell ref="E1:E4"/>
+    <mergeCell ref="T1:U1"/>
+    <mergeCell ref="N2:O2"/>
+    <mergeCell ref="P2:Q2"/>
+    <mergeCell ref="M1:O1"/>
+    <mergeCell ref="P1:Q1"/>
     <mergeCell ref="P4:Q4"/>
     <mergeCell ref="P3:Q3"/>
     <mergeCell ref="N3:O3"/>
@@ -6555,16 +6606,6 @@
     <mergeCell ref="F1:K4"/>
     <mergeCell ref="L3:L4"/>
     <mergeCell ref="N4:O4"/>
-    <mergeCell ref="T1:U1"/>
-    <mergeCell ref="N2:O2"/>
-    <mergeCell ref="P2:Q2"/>
-    <mergeCell ref="M1:O1"/>
-    <mergeCell ref="P1:Q1"/>
-    <mergeCell ref="A1:A4"/>
-    <mergeCell ref="D1:D4"/>
-    <mergeCell ref="B1:B4"/>
-    <mergeCell ref="L1:L2"/>
-    <mergeCell ref="E1:E4"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="E5:E10">

--- a/input.xlsx
+++ b/input.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\backup01\Desktop\병아리\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AEEA0C87-A2DF-4BB0-9279-9301A1334C04}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EDA851A2-C98D-4523-9C7A-5AF8892C9655}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -730,15 +730,22 @@
     <xf numFmtId="0" fontId="10" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="4" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="9" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="41" fontId="4" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -748,13 +755,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="9" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="백분율" xfId="2" builtinId="5"/>
@@ -1037,7 +1037,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M180"/>
+  <dimension ref="A1:M181"/>
   <sheetFormatPr defaultRowHeight="16" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="12" style="31" customWidth="1"/>
@@ -5989,6 +5989,47 @@
       </c>
       <c r="M180" s="40">
         <v>13201220</v>
+      </c>
+    </row>
+    <row r="181" spans="1:13" ht="16.5" x14ac:dyDescent="0.45">
+      <c r="A181" s="35">
+        <v>46223</v>
+      </c>
+      <c r="B181" s="36">
+        <v>122043980</v>
+      </c>
+      <c r="C181" s="37">
+        <v>-7208090</v>
+      </c>
+      <c r="D181" s="38">
+        <v>6516.27</v>
+      </c>
+      <c r="E181" s="37">
+        <v>0</v>
+      </c>
+      <c r="F181" s="40">
+        <v>5435530</v>
+      </c>
+      <c r="G181" s="40">
+        <v>8866645</v>
+      </c>
+      <c r="H181" s="40">
+        <v>12797445</v>
+      </c>
+      <c r="I181" s="40">
+        <v>15623840</v>
+      </c>
+      <c r="J181" s="40">
+        <v>32484070</v>
+      </c>
+      <c r="K181" s="40">
+        <v>23058550</v>
+      </c>
+      <c r="L181" s="40">
+        <v>18599870</v>
+      </c>
+      <c r="M181" s="40">
+        <v>5178030</v>
       </c>
     </row>
   </sheetData>
@@ -6014,72 +6055,72 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:21" x14ac:dyDescent="0.45">
-      <c r="A1" s="46" t="s">
+      <c r="A1" s="44" t="s">
         <v>17</v>
       </c>
-      <c r="B1" s="46" t="s">
+      <c r="B1" s="44" t="s">
         <v>16</v>
       </c>
-      <c r="C1" s="46" t="s">
+      <c r="C1" s="44" t="s">
         <v>18</v>
       </c>
-      <c r="D1" s="46" t="s">
+      <c r="D1" s="44" t="s">
         <v>19</v>
       </c>
-      <c r="E1" s="56" t="s">
+      <c r="E1" s="48" t="s">
         <v>20</v>
       </c>
-      <c r="F1" s="49" t="s">
+      <c r="F1" s="52" t="s">
         <v>21</v>
       </c>
-      <c r="G1" s="50"/>
-      <c r="H1" s="50"/>
-      <c r="I1" s="50"/>
-      <c r="J1" s="50"/>
-      <c r="K1" s="50"/>
-      <c r="L1" s="54">
+      <c r="G1" s="53"/>
+      <c r="H1" s="53"/>
+      <c r="I1" s="53"/>
+      <c r="J1" s="53"/>
+      <c r="K1" s="53"/>
+      <c r="L1" s="47">
         <v>0.7</v>
       </c>
-      <c r="M1" s="46" t="s">
+      <c r="M1" s="44" t="s">
         <v>22</v>
       </c>
-      <c r="N1" s="55"/>
-      <c r="O1" s="45"/>
-      <c r="P1" s="54">
+      <c r="N1" s="50"/>
+      <c r="O1" s="49"/>
+      <c r="P1" s="47">
         <v>0.25</v>
       </c>
-      <c r="Q1" s="45"/>
+      <c r="Q1" s="49"/>
       <c r="R1" s="1"/>
       <c r="S1" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="T1" s="46" t="s">
+      <c r="T1" s="44" t="s">
         <v>23</v>
       </c>
-      <c r="U1" s="45"/>
+      <c r="U1" s="49"/>
     </row>
     <row r="2" spans="1:21" x14ac:dyDescent="0.45">
-      <c r="A2" s="47"/>
-      <c r="B2" s="47"/>
-      <c r="C2" s="47"/>
-      <c r="D2" s="47"/>
-      <c r="E2" s="47"/>
-      <c r="F2" s="51"/>
+      <c r="A2" s="45"/>
+      <c r="B2" s="45"/>
+      <c r="C2" s="45"/>
+      <c r="D2" s="45"/>
+      <c r="E2" s="45"/>
+      <c r="F2" s="54"/>
       <c r="G2" s="42"/>
       <c r="H2" s="42"/>
       <c r="I2" s="42"/>
       <c r="J2" s="42"/>
       <c r="K2" s="42"/>
-      <c r="L2" s="48"/>
+      <c r="L2" s="46"/>
       <c r="M2" s="3"/>
-      <c r="N2" s="54" t="s">
+      <c r="N2" s="47" t="s">
         <v>15</v>
       </c>
-      <c r="O2" s="45"/>
-      <c r="P2" s="46" t="s">
+      <c r="O2" s="49"/>
+      <c r="P2" s="44" t="s">
         <v>24</v>
       </c>
-      <c r="Q2" s="45"/>
+      <c r="Q2" s="49"/>
       <c r="R2" s="1"/>
       <c r="S2" s="4" t="s">
         <v>25</v>
@@ -6092,31 +6133,31 @@
       </c>
     </row>
     <row r="3" spans="1:21" x14ac:dyDescent="0.45">
-      <c r="A3" s="47"/>
-      <c r="B3" s="47"/>
-      <c r="C3" s="47"/>
-      <c r="D3" s="47"/>
-      <c r="E3" s="47"/>
-      <c r="F3" s="51"/>
+      <c r="A3" s="45"/>
+      <c r="B3" s="45"/>
+      <c r="C3" s="45"/>
+      <c r="D3" s="45"/>
+      <c r="E3" s="45"/>
+      <c r="F3" s="54"/>
       <c r="G3" s="42"/>
       <c r="H3" s="42"/>
       <c r="I3" s="42"/>
       <c r="J3" s="42"/>
       <c r="K3" s="42"/>
-      <c r="L3" s="44">
+      <c r="L3" s="51">
         <v>17485</v>
       </c>
       <c r="M3" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="N3" s="44">
+      <c r="N3" s="51">
         <v>14760</v>
       </c>
-      <c r="O3" s="45"/>
-      <c r="P3" s="44">
+      <c r="O3" s="49"/>
+      <c r="P3" s="51">
         <v>8125</v>
       </c>
-      <c r="Q3" s="45"/>
+      <c r="Q3" s="49"/>
       <c r="R3" s="1"/>
       <c r="S3" s="4" t="s">
         <v>27</v>
@@ -6129,29 +6170,29 @@
       </c>
     </row>
     <row r="4" spans="1:21" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A4" s="48"/>
-      <c r="B4" s="48"/>
-      <c r="C4" s="48"/>
-      <c r="D4" s="48"/>
-      <c r="E4" s="48"/>
-      <c r="F4" s="51"/>
+      <c r="A4" s="46"/>
+      <c r="B4" s="46"/>
+      <c r="C4" s="46"/>
+      <c r="D4" s="46"/>
+      <c r="E4" s="46"/>
+      <c r="F4" s="54"/>
       <c r="G4" s="42"/>
       <c r="H4" s="42"/>
       <c r="I4" s="42"/>
       <c r="J4" s="42"/>
       <c r="K4" s="42"/>
-      <c r="L4" s="48"/>
+      <c r="L4" s="46"/>
       <c r="M4" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="N4" s="52">
+      <c r="N4" s="55">
         <v>34705</v>
       </c>
-      <c r="O4" s="53"/>
-      <c r="P4" s="44">
+      <c r="O4" s="56"/>
+      <c r="P4" s="51">
         <v>13230</v>
       </c>
-      <c r="Q4" s="45"/>
+      <c r="Q4" s="49"/>
       <c r="R4" s="1"/>
       <c r="S4" s="4" t="s">
         <v>29</v>
@@ -6589,16 +6630,6 @@
     </row>
   </sheetData>
   <mergeCells count="17">
-    <mergeCell ref="A1:A4"/>
-    <mergeCell ref="D1:D4"/>
-    <mergeCell ref="B1:B4"/>
-    <mergeCell ref="L1:L2"/>
-    <mergeCell ref="E1:E4"/>
-    <mergeCell ref="T1:U1"/>
-    <mergeCell ref="N2:O2"/>
-    <mergeCell ref="P2:Q2"/>
-    <mergeCell ref="M1:O1"/>
-    <mergeCell ref="P1:Q1"/>
     <mergeCell ref="P4:Q4"/>
     <mergeCell ref="P3:Q3"/>
     <mergeCell ref="N3:O3"/>
@@ -6606,6 +6637,16 @@
     <mergeCell ref="F1:K4"/>
     <mergeCell ref="L3:L4"/>
     <mergeCell ref="N4:O4"/>
+    <mergeCell ref="T1:U1"/>
+    <mergeCell ref="N2:O2"/>
+    <mergeCell ref="P2:Q2"/>
+    <mergeCell ref="M1:O1"/>
+    <mergeCell ref="P1:Q1"/>
+    <mergeCell ref="A1:A4"/>
+    <mergeCell ref="D1:D4"/>
+    <mergeCell ref="B1:B4"/>
+    <mergeCell ref="L1:L2"/>
+    <mergeCell ref="E1:E4"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="E5:E10">

--- a/input.xlsx
+++ b/input.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\backup01\Desktop\병아리\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EDA851A2-C98D-4523-9C7A-5AF8892C9655}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B52FD1C-5DC7-4A78-B420-CD64C9DB0C92}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="25490" yWindow="690" windowWidth="25820" windowHeight="13900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="INPUT" sheetId="1" r:id="rId1"/>
@@ -730,22 +730,15 @@
     <xf numFmtId="0" fontId="10" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="41" fontId="4" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="9" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="41" fontId="4" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -755,6 +748,13 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="9" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="백분율" xfId="2" builtinId="5"/>
@@ -1037,7 +1037,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M181"/>
+  <dimension ref="A1:M182"/>
   <sheetFormatPr defaultRowHeight="16" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="12" style="31" customWidth="1"/>
@@ -6030,6 +6030,45 @@
       </c>
       <c r="M181" s="40">
         <v>5178030</v>
+      </c>
+    </row>
+    <row r="182" spans="1:13" ht="16.5" x14ac:dyDescent="0.45">
+      <c r="A182" s="35">
+        <v>46224</v>
+      </c>
+      <c r="B182" s="36">
+        <v>127128480</v>
+      </c>
+      <c r="C182" s="37"/>
+      <c r="D182" s="38">
+        <v>6747.95</v>
+      </c>
+      <c r="E182" s="37">
+        <v>0</v>
+      </c>
+      <c r="F182" s="40">
+        <v>5621580</v>
+      </c>
+      <c r="G182" s="40">
+        <v>9467565</v>
+      </c>
+      <c r="H182" s="40">
+        <v>13496415</v>
+      </c>
+      <c r="I182" s="40">
+        <v>16416285</v>
+      </c>
+      <c r="J182" s="40">
+        <v>34556505</v>
+      </c>
+      <c r="K182" s="40">
+        <v>23693730</v>
+      </c>
+      <c r="L182" s="40">
+        <v>18676920</v>
+      </c>
+      <c r="M182" s="40">
+        <v>5199480</v>
       </c>
     </row>
   </sheetData>
@@ -6055,72 +6094,72 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:21" x14ac:dyDescent="0.45">
-      <c r="A1" s="44" t="s">
+      <c r="A1" s="46" t="s">
         <v>17</v>
       </c>
-      <c r="B1" s="44" t="s">
+      <c r="B1" s="46" t="s">
         <v>16</v>
       </c>
-      <c r="C1" s="44" t="s">
+      <c r="C1" s="46" t="s">
         <v>18</v>
       </c>
-      <c r="D1" s="44" t="s">
+      <c r="D1" s="46" t="s">
         <v>19</v>
       </c>
-      <c r="E1" s="48" t="s">
+      <c r="E1" s="56" t="s">
         <v>20</v>
       </c>
-      <c r="F1" s="52" t="s">
+      <c r="F1" s="49" t="s">
         <v>21</v>
       </c>
-      <c r="G1" s="53"/>
-      <c r="H1" s="53"/>
-      <c r="I1" s="53"/>
-      <c r="J1" s="53"/>
-      <c r="K1" s="53"/>
-      <c r="L1" s="47">
+      <c r="G1" s="50"/>
+      <c r="H1" s="50"/>
+      <c r="I1" s="50"/>
+      <c r="J1" s="50"/>
+      <c r="K1" s="50"/>
+      <c r="L1" s="54">
         <v>0.7</v>
       </c>
-      <c r="M1" s="44" t="s">
+      <c r="M1" s="46" t="s">
         <v>22</v>
       </c>
-      <c r="N1" s="50"/>
-      <c r="O1" s="49"/>
-      <c r="P1" s="47">
+      <c r="N1" s="55"/>
+      <c r="O1" s="45"/>
+      <c r="P1" s="54">
         <v>0.25</v>
       </c>
-      <c r="Q1" s="49"/>
+      <c r="Q1" s="45"/>
       <c r="R1" s="1"/>
       <c r="S1" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="T1" s="44" t="s">
+      <c r="T1" s="46" t="s">
         <v>23</v>
       </c>
-      <c r="U1" s="49"/>
+      <c r="U1" s="45"/>
     </row>
     <row r="2" spans="1:21" x14ac:dyDescent="0.45">
-      <c r="A2" s="45"/>
-      <c r="B2" s="45"/>
-      <c r="C2" s="45"/>
-      <c r="D2" s="45"/>
-      <c r="E2" s="45"/>
-      <c r="F2" s="54"/>
+      <c r="A2" s="47"/>
+      <c r="B2" s="47"/>
+      <c r="C2" s="47"/>
+      <c r="D2" s="47"/>
+      <c r="E2" s="47"/>
+      <c r="F2" s="51"/>
       <c r="G2" s="42"/>
       <c r="H2" s="42"/>
       <c r="I2" s="42"/>
       <c r="J2" s="42"/>
       <c r="K2" s="42"/>
-      <c r="L2" s="46"/>
+      <c r="L2" s="48"/>
       <c r="M2" s="3"/>
-      <c r="N2" s="47" t="s">
+      <c r="N2" s="54" t="s">
         <v>15</v>
       </c>
-      <c r="O2" s="49"/>
-      <c r="P2" s="44" t="s">
+      <c r="O2" s="45"/>
+      <c r="P2" s="46" t="s">
         <v>24</v>
       </c>
-      <c r="Q2" s="49"/>
+      <c r="Q2" s="45"/>
       <c r="R2" s="1"/>
       <c r="S2" s="4" t="s">
         <v>25</v>
@@ -6133,31 +6172,31 @@
       </c>
     </row>
     <row r="3" spans="1:21" x14ac:dyDescent="0.45">
-      <c r="A3" s="45"/>
-      <c r="B3" s="45"/>
-      <c r="C3" s="45"/>
-      <c r="D3" s="45"/>
-      <c r="E3" s="45"/>
-      <c r="F3" s="54"/>
+      <c r="A3" s="47"/>
+      <c r="B3" s="47"/>
+      <c r="C3" s="47"/>
+      <c r="D3" s="47"/>
+      <c r="E3" s="47"/>
+      <c r="F3" s="51"/>
       <c r="G3" s="42"/>
       <c r="H3" s="42"/>
       <c r="I3" s="42"/>
       <c r="J3" s="42"/>
       <c r="K3" s="42"/>
-      <c r="L3" s="51">
+      <c r="L3" s="44">
         <v>17485</v>
       </c>
       <c r="M3" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="N3" s="51">
+      <c r="N3" s="44">
         <v>14760</v>
       </c>
-      <c r="O3" s="49"/>
-      <c r="P3" s="51">
+      <c r="O3" s="45"/>
+      <c r="P3" s="44">
         <v>8125</v>
       </c>
-      <c r="Q3" s="49"/>
+      <c r="Q3" s="45"/>
       <c r="R3" s="1"/>
       <c r="S3" s="4" t="s">
         <v>27</v>
@@ -6170,29 +6209,29 @@
       </c>
     </row>
     <row r="4" spans="1:21" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A4" s="46"/>
-      <c r="B4" s="46"/>
-      <c r="C4" s="46"/>
-      <c r="D4" s="46"/>
-      <c r="E4" s="46"/>
-      <c r="F4" s="54"/>
+      <c r="A4" s="48"/>
+      <c r="B4" s="48"/>
+      <c r="C4" s="48"/>
+      <c r="D4" s="48"/>
+      <c r="E4" s="48"/>
+      <c r="F4" s="51"/>
       <c r="G4" s="42"/>
       <c r="H4" s="42"/>
       <c r="I4" s="42"/>
       <c r="J4" s="42"/>
       <c r="K4" s="42"/>
-      <c r="L4" s="46"/>
+      <c r="L4" s="48"/>
       <c r="M4" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="N4" s="55">
+      <c r="N4" s="52">
         <v>34705</v>
       </c>
-      <c r="O4" s="56"/>
-      <c r="P4" s="51">
+      <c r="O4" s="53"/>
+      <c r="P4" s="44">
         <v>13230</v>
       </c>
-      <c r="Q4" s="49"/>
+      <c r="Q4" s="45"/>
       <c r="R4" s="1"/>
       <c r="S4" s="4" t="s">
         <v>29</v>
@@ -6630,6 +6669,16 @@
     </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="A1:A4"/>
+    <mergeCell ref="D1:D4"/>
+    <mergeCell ref="B1:B4"/>
+    <mergeCell ref="L1:L2"/>
+    <mergeCell ref="E1:E4"/>
+    <mergeCell ref="T1:U1"/>
+    <mergeCell ref="N2:O2"/>
+    <mergeCell ref="P2:Q2"/>
+    <mergeCell ref="M1:O1"/>
+    <mergeCell ref="P1:Q1"/>
     <mergeCell ref="P4:Q4"/>
     <mergeCell ref="P3:Q3"/>
     <mergeCell ref="N3:O3"/>
@@ -6637,16 +6686,6 @@
     <mergeCell ref="F1:K4"/>
     <mergeCell ref="L3:L4"/>
     <mergeCell ref="N4:O4"/>
-    <mergeCell ref="T1:U1"/>
-    <mergeCell ref="N2:O2"/>
-    <mergeCell ref="P2:Q2"/>
-    <mergeCell ref="M1:O1"/>
-    <mergeCell ref="P1:Q1"/>
-    <mergeCell ref="A1:A4"/>
-    <mergeCell ref="D1:D4"/>
-    <mergeCell ref="B1:B4"/>
-    <mergeCell ref="L1:L2"/>
-    <mergeCell ref="E1:E4"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="E5:E10">

--- a/input.xlsx
+++ b/input.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\backup01\Desktop\병아리\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B52FD1C-5DC7-4A78-B420-CD64C9DB0C92}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{961306BA-A59C-4496-B20C-F29F85993D4B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="25490" yWindow="690" windowWidth="25820" windowHeight="13900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -730,15 +730,22 @@
     <xf numFmtId="0" fontId="10" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="4" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="9" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="41" fontId="4" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -748,13 +755,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="9" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="백분율" xfId="2" builtinId="5"/>
@@ -1037,7 +1037,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M182"/>
+  <dimension ref="A1:M183"/>
   <sheetFormatPr defaultRowHeight="16" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="12" style="31" customWidth="1"/>
@@ -6069,6 +6069,45 @@
       </c>
       <c r="M182" s="40">
         <v>5199480</v>
+      </c>
+    </row>
+    <row r="183" spans="1:13" ht="16.5" x14ac:dyDescent="0.45">
+      <c r="A183" s="35">
+        <v>46225</v>
+      </c>
+      <c r="B183" s="36">
+        <v>126052040</v>
+      </c>
+      <c r="C183" s="37"/>
+      <c r="D183" s="38">
+        <v>6797.7</v>
+      </c>
+      <c r="E183" s="37">
+        <v>0</v>
+      </c>
+      <c r="F183" s="40">
+        <v>5559940</v>
+      </c>
+      <c r="G183" s="40">
+        <v>9467860</v>
+      </c>
+      <c r="H183" s="40">
+        <v>13439760</v>
+      </c>
+      <c r="I183" s="40">
+        <v>16326470</v>
+      </c>
+      <c r="J183" s="40">
+        <v>34513810</v>
+      </c>
+      <c r="K183" s="40">
+        <v>23380000</v>
+      </c>
+      <c r="L183" s="40">
+        <v>18276260</v>
+      </c>
+      <c r="M183" s="40">
+        <v>5087940</v>
       </c>
     </row>
   </sheetData>
@@ -6094,72 +6133,72 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:21" x14ac:dyDescent="0.45">
-      <c r="A1" s="46" t="s">
+      <c r="A1" s="44" t="s">
         <v>17</v>
       </c>
-      <c r="B1" s="46" t="s">
+      <c r="B1" s="44" t="s">
         <v>16</v>
       </c>
-      <c r="C1" s="46" t="s">
+      <c r="C1" s="44" t="s">
         <v>18</v>
       </c>
-      <c r="D1" s="46" t="s">
+      <c r="D1" s="44" t="s">
         <v>19</v>
       </c>
-      <c r="E1" s="56" t="s">
+      <c r="E1" s="48" t="s">
         <v>20</v>
       </c>
-      <c r="F1" s="49" t="s">
+      <c r="F1" s="52" t="s">
         <v>21</v>
       </c>
-      <c r="G1" s="50"/>
-      <c r="H1" s="50"/>
-      <c r="I1" s="50"/>
-      <c r="J1" s="50"/>
-      <c r="K1" s="50"/>
-      <c r="L1" s="54">
+      <c r="G1" s="53"/>
+      <c r="H1" s="53"/>
+      <c r="I1" s="53"/>
+      <c r="J1" s="53"/>
+      <c r="K1" s="53"/>
+      <c r="L1" s="47">
         <v>0.7</v>
       </c>
-      <c r="M1" s="46" t="s">
+      <c r="M1" s="44" t="s">
         <v>22</v>
       </c>
-      <c r="N1" s="55"/>
-      <c r="O1" s="45"/>
-      <c r="P1" s="54">
+      <c r="N1" s="50"/>
+      <c r="O1" s="49"/>
+      <c r="P1" s="47">
         <v>0.25</v>
       </c>
-      <c r="Q1" s="45"/>
+      <c r="Q1" s="49"/>
       <c r="R1" s="1"/>
       <c r="S1" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="T1" s="46" t="s">
+      <c r="T1" s="44" t="s">
         <v>23</v>
       </c>
-      <c r="U1" s="45"/>
+      <c r="U1" s="49"/>
     </row>
     <row r="2" spans="1:21" x14ac:dyDescent="0.45">
-      <c r="A2" s="47"/>
-      <c r="B2" s="47"/>
-      <c r="C2" s="47"/>
-      <c r="D2" s="47"/>
-      <c r="E2" s="47"/>
-      <c r="F2" s="51"/>
+      <c r="A2" s="45"/>
+      <c r="B2" s="45"/>
+      <c r="C2" s="45"/>
+      <c r="D2" s="45"/>
+      <c r="E2" s="45"/>
+      <c r="F2" s="54"/>
       <c r="G2" s="42"/>
       <c r="H2" s="42"/>
       <c r="I2" s="42"/>
       <c r="J2" s="42"/>
       <c r="K2" s="42"/>
-      <c r="L2" s="48"/>
+      <c r="L2" s="46"/>
       <c r="M2" s="3"/>
-      <c r="N2" s="54" t="s">
+      <c r="N2" s="47" t="s">
         <v>15</v>
       </c>
-      <c r="O2" s="45"/>
-      <c r="P2" s="46" t="s">
+      <c r="O2" s="49"/>
+      <c r="P2" s="44" t="s">
         <v>24</v>
       </c>
-      <c r="Q2" s="45"/>
+      <c r="Q2" s="49"/>
       <c r="R2" s="1"/>
       <c r="S2" s="4" t="s">
         <v>25</v>
@@ -6172,31 +6211,31 @@
       </c>
     </row>
     <row r="3" spans="1:21" x14ac:dyDescent="0.45">
-      <c r="A3" s="47"/>
-      <c r="B3" s="47"/>
-      <c r="C3" s="47"/>
-      <c r="D3" s="47"/>
-      <c r="E3" s="47"/>
-      <c r="F3" s="51"/>
+      <c r="A3" s="45"/>
+      <c r="B3" s="45"/>
+      <c r="C3" s="45"/>
+      <c r="D3" s="45"/>
+      <c r="E3" s="45"/>
+      <c r="F3" s="54"/>
       <c r="G3" s="42"/>
       <c r="H3" s="42"/>
       <c r="I3" s="42"/>
       <c r="J3" s="42"/>
       <c r="K3" s="42"/>
-      <c r="L3" s="44">
+      <c r="L3" s="51">
         <v>17485</v>
       </c>
       <c r="M3" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="N3" s="44">
+      <c r="N3" s="51">
         <v>14760</v>
       </c>
-      <c r="O3" s="45"/>
-      <c r="P3" s="44">
+      <c r="O3" s="49"/>
+      <c r="P3" s="51">
         <v>8125</v>
       </c>
-      <c r="Q3" s="45"/>
+      <c r="Q3" s="49"/>
       <c r="R3" s="1"/>
       <c r="S3" s="4" t="s">
         <v>27</v>
@@ -6209,29 +6248,29 @@
       </c>
     </row>
     <row r="4" spans="1:21" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A4" s="48"/>
-      <c r="B4" s="48"/>
-      <c r="C4" s="48"/>
-      <c r="D4" s="48"/>
-      <c r="E4" s="48"/>
-      <c r="F4" s="51"/>
+      <c r="A4" s="46"/>
+      <c r="B4" s="46"/>
+      <c r="C4" s="46"/>
+      <c r="D4" s="46"/>
+      <c r="E4" s="46"/>
+      <c r="F4" s="54"/>
       <c r="G4" s="42"/>
       <c r="H4" s="42"/>
       <c r="I4" s="42"/>
       <c r="J4" s="42"/>
       <c r="K4" s="42"/>
-      <c r="L4" s="48"/>
+      <c r="L4" s="46"/>
       <c r="M4" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="N4" s="52">
+      <c r="N4" s="55">
         <v>34705</v>
       </c>
-      <c r="O4" s="53"/>
-      <c r="P4" s="44">
+      <c r="O4" s="56"/>
+      <c r="P4" s="51">
         <v>13230</v>
       </c>
-      <c r="Q4" s="45"/>
+      <c r="Q4" s="49"/>
       <c r="R4" s="1"/>
       <c r="S4" s="4" t="s">
         <v>29</v>
@@ -6669,16 +6708,6 @@
     </row>
   </sheetData>
   <mergeCells count="17">
-    <mergeCell ref="A1:A4"/>
-    <mergeCell ref="D1:D4"/>
-    <mergeCell ref="B1:B4"/>
-    <mergeCell ref="L1:L2"/>
-    <mergeCell ref="E1:E4"/>
-    <mergeCell ref="T1:U1"/>
-    <mergeCell ref="N2:O2"/>
-    <mergeCell ref="P2:Q2"/>
-    <mergeCell ref="M1:O1"/>
-    <mergeCell ref="P1:Q1"/>
     <mergeCell ref="P4:Q4"/>
     <mergeCell ref="P3:Q3"/>
     <mergeCell ref="N3:O3"/>
@@ -6686,6 +6715,16 @@
     <mergeCell ref="F1:K4"/>
     <mergeCell ref="L3:L4"/>
     <mergeCell ref="N4:O4"/>
+    <mergeCell ref="T1:U1"/>
+    <mergeCell ref="N2:O2"/>
+    <mergeCell ref="P2:Q2"/>
+    <mergeCell ref="M1:O1"/>
+    <mergeCell ref="P1:Q1"/>
+    <mergeCell ref="A1:A4"/>
+    <mergeCell ref="D1:D4"/>
+    <mergeCell ref="B1:B4"/>
+    <mergeCell ref="L1:L2"/>
+    <mergeCell ref="E1:E4"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="E5:E10">

--- a/input.xlsx
+++ b/input.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\backup01\Desktop\병아리\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{961306BA-A59C-4496-B20C-F29F85993D4B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{33FDDB2E-875B-4350-BD54-51E1EACD2D66}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="25490" yWindow="690" windowWidth="25820" windowHeight="13900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -730,22 +730,15 @@
     <xf numFmtId="0" fontId="10" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="41" fontId="4" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="9" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="41" fontId="4" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -755,6 +748,13 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="9" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="백분율" xfId="2" builtinId="5"/>
@@ -1037,7 +1037,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M183"/>
+  <dimension ref="A1:M184"/>
   <sheetFormatPr defaultRowHeight="16" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="12" style="31" customWidth="1"/>
@@ -6108,6 +6108,45 @@
       </c>
       <c r="M183" s="40">
         <v>5087940</v>
+      </c>
+    </row>
+    <row r="184" spans="1:13" ht="16.5" x14ac:dyDescent="0.45">
+      <c r="A184" s="35">
+        <v>46226</v>
+      </c>
+      <c r="B184" s="36">
+        <v>140069220</v>
+      </c>
+      <c r="C184" s="37"/>
+      <c r="D184" s="38">
+        <v>7096.89</v>
+      </c>
+      <c r="E184" s="37">
+        <v>0</v>
+      </c>
+      <c r="F184" s="40">
+        <v>6205120</v>
+      </c>
+      <c r="G184" s="40">
+        <v>10366870</v>
+      </c>
+      <c r="H184" s="40">
+        <v>14824170</v>
+      </c>
+      <c r="I184" s="40">
+        <v>18048050</v>
+      </c>
+      <c r="J184" s="40">
+        <v>37874050</v>
+      </c>
+      <c r="K184" s="40">
+        <v>26195360</v>
+      </c>
+      <c r="L184" s="40">
+        <v>20772680</v>
+      </c>
+      <c r="M184" s="40">
+        <v>5782920</v>
       </c>
     </row>
   </sheetData>
@@ -6133,72 +6172,72 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:21" x14ac:dyDescent="0.45">
-      <c r="A1" s="44" t="s">
+      <c r="A1" s="46" t="s">
         <v>17</v>
       </c>
-      <c r="B1" s="44" t="s">
+      <c r="B1" s="46" t="s">
         <v>16</v>
       </c>
-      <c r="C1" s="44" t="s">
+      <c r="C1" s="46" t="s">
         <v>18</v>
       </c>
-      <c r="D1" s="44" t="s">
+      <c r="D1" s="46" t="s">
         <v>19</v>
       </c>
-      <c r="E1" s="48" t="s">
+      <c r="E1" s="56" t="s">
         <v>20</v>
       </c>
-      <c r="F1" s="52" t="s">
+      <c r="F1" s="49" t="s">
         <v>21</v>
       </c>
-      <c r="G1" s="53"/>
-      <c r="H1" s="53"/>
-      <c r="I1" s="53"/>
-      <c r="J1" s="53"/>
-      <c r="K1" s="53"/>
-      <c r="L1" s="47">
+      <c r="G1" s="50"/>
+      <c r="H1" s="50"/>
+      <c r="I1" s="50"/>
+      <c r="J1" s="50"/>
+      <c r="K1" s="50"/>
+      <c r="L1" s="54">
         <v>0.7</v>
       </c>
-      <c r="M1" s="44" t="s">
+      <c r="M1" s="46" t="s">
         <v>22</v>
       </c>
-      <c r="N1" s="50"/>
-      <c r="O1" s="49"/>
-      <c r="P1" s="47">
+      <c r="N1" s="55"/>
+      <c r="O1" s="45"/>
+      <c r="P1" s="54">
         <v>0.25</v>
       </c>
-      <c r="Q1" s="49"/>
+      <c r="Q1" s="45"/>
       <c r="R1" s="1"/>
       <c r="S1" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="T1" s="44" t="s">
+      <c r="T1" s="46" t="s">
         <v>23</v>
       </c>
-      <c r="U1" s="49"/>
+      <c r="U1" s="45"/>
     </row>
     <row r="2" spans="1:21" x14ac:dyDescent="0.45">
-      <c r="A2" s="45"/>
-      <c r="B2" s="45"/>
-      <c r="C2" s="45"/>
-      <c r="D2" s="45"/>
-      <c r="E2" s="45"/>
-      <c r="F2" s="54"/>
+      <c r="A2" s="47"/>
+      <c r="B2" s="47"/>
+      <c r="C2" s="47"/>
+      <c r="D2" s="47"/>
+      <c r="E2" s="47"/>
+      <c r="F2" s="51"/>
       <c r="G2" s="42"/>
       <c r="H2" s="42"/>
       <c r="I2" s="42"/>
       <c r="J2" s="42"/>
       <c r="K2" s="42"/>
-      <c r="L2" s="46"/>
+      <c r="L2" s="48"/>
       <c r="M2" s="3"/>
-      <c r="N2" s="47" t="s">
+      <c r="N2" s="54" t="s">
         <v>15</v>
       </c>
-      <c r="O2" s="49"/>
-      <c r="P2" s="44" t="s">
+      <c r="O2" s="45"/>
+      <c r="P2" s="46" t="s">
         <v>24</v>
       </c>
-      <c r="Q2" s="49"/>
+      <c r="Q2" s="45"/>
       <c r="R2" s="1"/>
       <c r="S2" s="4" t="s">
         <v>25</v>
@@ -6211,31 +6250,31 @@
       </c>
     </row>
     <row r="3" spans="1:21" x14ac:dyDescent="0.45">
-      <c r="A3" s="45"/>
-      <c r="B3" s="45"/>
-      <c r="C3" s="45"/>
-      <c r="D3" s="45"/>
-      <c r="E3" s="45"/>
-      <c r="F3" s="54"/>
+      <c r="A3" s="47"/>
+      <c r="B3" s="47"/>
+      <c r="C3" s="47"/>
+      <c r="D3" s="47"/>
+      <c r="E3" s="47"/>
+      <c r="F3" s="51"/>
       <c r="G3" s="42"/>
       <c r="H3" s="42"/>
       <c r="I3" s="42"/>
       <c r="J3" s="42"/>
       <c r="K3" s="42"/>
-      <c r="L3" s="51">
+      <c r="L3" s="44">
         <v>17485</v>
       </c>
       <c r="M3" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="N3" s="51">
+      <c r="N3" s="44">
         <v>14760</v>
       </c>
-      <c r="O3" s="49"/>
-      <c r="P3" s="51">
+      <c r="O3" s="45"/>
+      <c r="P3" s="44">
         <v>8125</v>
       </c>
-      <c r="Q3" s="49"/>
+      <c r="Q3" s="45"/>
       <c r="R3" s="1"/>
       <c r="S3" s="4" t="s">
         <v>27</v>
@@ -6248,29 +6287,29 @@
       </c>
     </row>
     <row r="4" spans="1:21" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A4" s="46"/>
-      <c r="B4" s="46"/>
-      <c r="C4" s="46"/>
-      <c r="D4" s="46"/>
-      <c r="E4" s="46"/>
-      <c r="F4" s="54"/>
+      <c r="A4" s="48"/>
+      <c r="B4" s="48"/>
+      <c r="C4" s="48"/>
+      <c r="D4" s="48"/>
+      <c r="E4" s="48"/>
+      <c r="F4" s="51"/>
       <c r="G4" s="42"/>
       <c r="H4" s="42"/>
       <c r="I4" s="42"/>
       <c r="J4" s="42"/>
       <c r="K4" s="42"/>
-      <c r="L4" s="46"/>
+      <c r="L4" s="48"/>
       <c r="M4" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="N4" s="55">
+      <c r="N4" s="52">
         <v>34705</v>
       </c>
-      <c r="O4" s="56"/>
-      <c r="P4" s="51">
+      <c r="O4" s="53"/>
+      <c r="P4" s="44">
         <v>13230</v>
       </c>
-      <c r="Q4" s="49"/>
+      <c r="Q4" s="45"/>
       <c r="R4" s="1"/>
       <c r="S4" s="4" t="s">
         <v>29</v>
@@ -6708,6 +6747,16 @@
     </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="A1:A4"/>
+    <mergeCell ref="D1:D4"/>
+    <mergeCell ref="B1:B4"/>
+    <mergeCell ref="L1:L2"/>
+    <mergeCell ref="E1:E4"/>
+    <mergeCell ref="T1:U1"/>
+    <mergeCell ref="N2:O2"/>
+    <mergeCell ref="P2:Q2"/>
+    <mergeCell ref="M1:O1"/>
+    <mergeCell ref="P1:Q1"/>
     <mergeCell ref="P4:Q4"/>
     <mergeCell ref="P3:Q3"/>
     <mergeCell ref="N3:O3"/>
@@ -6715,16 +6764,6 @@
     <mergeCell ref="F1:K4"/>
     <mergeCell ref="L3:L4"/>
     <mergeCell ref="N4:O4"/>
-    <mergeCell ref="T1:U1"/>
-    <mergeCell ref="N2:O2"/>
-    <mergeCell ref="P2:Q2"/>
-    <mergeCell ref="M1:O1"/>
-    <mergeCell ref="P1:Q1"/>
-    <mergeCell ref="A1:A4"/>
-    <mergeCell ref="D1:D4"/>
-    <mergeCell ref="B1:B4"/>
-    <mergeCell ref="L1:L2"/>
-    <mergeCell ref="E1:E4"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="E5:E10">

--- a/input.xlsx
+++ b/input.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\backup01\Desktop\병아리\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{33FDDB2E-875B-4350-BD54-51E1EACD2D66}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{00B20799-F35E-4C4A-856F-612A475E5D44}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="25490" yWindow="690" windowWidth="25820" windowHeight="13900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -730,15 +730,22 @@
     <xf numFmtId="0" fontId="10" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="4" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="9" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="41" fontId="4" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -748,13 +755,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="9" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="백분율" xfId="2" builtinId="5"/>
@@ -6122,7 +6122,7 @@
         <v>7096.89</v>
       </c>
       <c r="E184" s="37">
-        <v>0</v>
+        <v>555570</v>
       </c>
       <c r="F184" s="40">
         <v>6205120</v>
@@ -6172,72 +6172,72 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:21" x14ac:dyDescent="0.45">
-      <c r="A1" s="46" t="s">
+      <c r="A1" s="44" t="s">
         <v>17</v>
       </c>
-      <c r="B1" s="46" t="s">
+      <c r="B1" s="44" t="s">
         <v>16</v>
       </c>
-      <c r="C1" s="46" t="s">
+      <c r="C1" s="44" t="s">
         <v>18</v>
       </c>
-      <c r="D1" s="46" t="s">
+      <c r="D1" s="44" t="s">
         <v>19</v>
       </c>
-      <c r="E1" s="56" t="s">
+      <c r="E1" s="48" t="s">
         <v>20</v>
       </c>
-      <c r="F1" s="49" t="s">
+      <c r="F1" s="52" t="s">
         <v>21</v>
       </c>
-      <c r="G1" s="50"/>
-      <c r="H1" s="50"/>
-      <c r="I1" s="50"/>
-      <c r="J1" s="50"/>
-      <c r="K1" s="50"/>
-      <c r="L1" s="54">
+      <c r="G1" s="53"/>
+      <c r="H1" s="53"/>
+      <c r="I1" s="53"/>
+      <c r="J1" s="53"/>
+      <c r="K1" s="53"/>
+      <c r="L1" s="47">
         <v>0.7</v>
       </c>
-      <c r="M1" s="46" t="s">
+      <c r="M1" s="44" t="s">
         <v>22</v>
       </c>
-      <c r="N1" s="55"/>
-      <c r="O1" s="45"/>
-      <c r="P1" s="54">
+      <c r="N1" s="50"/>
+      <c r="O1" s="49"/>
+      <c r="P1" s="47">
         <v>0.25</v>
       </c>
-      <c r="Q1" s="45"/>
+      <c r="Q1" s="49"/>
       <c r="R1" s="1"/>
       <c r="S1" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="T1" s="46" t="s">
+      <c r="T1" s="44" t="s">
         <v>23</v>
       </c>
-      <c r="U1" s="45"/>
+      <c r="U1" s="49"/>
     </row>
     <row r="2" spans="1:21" x14ac:dyDescent="0.45">
-      <c r="A2" s="47"/>
-      <c r="B2" s="47"/>
-      <c r="C2" s="47"/>
-      <c r="D2" s="47"/>
-      <c r="E2" s="47"/>
-      <c r="F2" s="51"/>
+      <c r="A2" s="45"/>
+      <c r="B2" s="45"/>
+      <c r="C2" s="45"/>
+      <c r="D2" s="45"/>
+      <c r="E2" s="45"/>
+      <c r="F2" s="54"/>
       <c r="G2" s="42"/>
       <c r="H2" s="42"/>
       <c r="I2" s="42"/>
       <c r="J2" s="42"/>
       <c r="K2" s="42"/>
-      <c r="L2" s="48"/>
+      <c r="L2" s="46"/>
       <c r="M2" s="3"/>
-      <c r="N2" s="54" t="s">
+      <c r="N2" s="47" t="s">
         <v>15</v>
       </c>
-      <c r="O2" s="45"/>
-      <c r="P2" s="46" t="s">
+      <c r="O2" s="49"/>
+      <c r="P2" s="44" t="s">
         <v>24</v>
       </c>
-      <c r="Q2" s="45"/>
+      <c r="Q2" s="49"/>
       <c r="R2" s="1"/>
       <c r="S2" s="4" t="s">
         <v>25</v>
@@ -6250,31 +6250,31 @@
       </c>
     </row>
     <row r="3" spans="1:21" x14ac:dyDescent="0.45">
-      <c r="A3" s="47"/>
-      <c r="B3" s="47"/>
-      <c r="C3" s="47"/>
-      <c r="D3" s="47"/>
-      <c r="E3" s="47"/>
-      <c r="F3" s="51"/>
+      <c r="A3" s="45"/>
+      <c r="B3" s="45"/>
+      <c r="C3" s="45"/>
+      <c r="D3" s="45"/>
+      <c r="E3" s="45"/>
+      <c r="F3" s="54"/>
       <c r="G3" s="42"/>
       <c r="H3" s="42"/>
       <c r="I3" s="42"/>
       <c r="J3" s="42"/>
       <c r="K3" s="42"/>
-      <c r="L3" s="44">
+      <c r="L3" s="51">
         <v>17485</v>
       </c>
       <c r="M3" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="N3" s="44">
+      <c r="N3" s="51">
         <v>14760</v>
       </c>
-      <c r="O3" s="45"/>
-      <c r="P3" s="44">
+      <c r="O3" s="49"/>
+      <c r="P3" s="51">
         <v>8125</v>
       </c>
-      <c r="Q3" s="45"/>
+      <c r="Q3" s="49"/>
       <c r="R3" s="1"/>
       <c r="S3" s="4" t="s">
         <v>27</v>
@@ -6287,29 +6287,29 @@
       </c>
     </row>
     <row r="4" spans="1:21" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A4" s="48"/>
-      <c r="B4" s="48"/>
-      <c r="C4" s="48"/>
-      <c r="D4" s="48"/>
-      <c r="E4" s="48"/>
-      <c r="F4" s="51"/>
+      <c r="A4" s="46"/>
+      <c r="B4" s="46"/>
+      <c r="C4" s="46"/>
+      <c r="D4" s="46"/>
+      <c r="E4" s="46"/>
+      <c r="F4" s="54"/>
       <c r="G4" s="42"/>
       <c r="H4" s="42"/>
       <c r="I4" s="42"/>
       <c r="J4" s="42"/>
       <c r="K4" s="42"/>
-      <c r="L4" s="48"/>
+      <c r="L4" s="46"/>
       <c r="M4" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="N4" s="52">
+      <c r="N4" s="55">
         <v>34705</v>
       </c>
-      <c r="O4" s="53"/>
-      <c r="P4" s="44">
+      <c r="O4" s="56"/>
+      <c r="P4" s="51">
         <v>13230</v>
       </c>
-      <c r="Q4" s="45"/>
+      <c r="Q4" s="49"/>
       <c r="R4" s="1"/>
       <c r="S4" s="4" t="s">
         <v>29</v>
@@ -6747,16 +6747,6 @@
     </row>
   </sheetData>
   <mergeCells count="17">
-    <mergeCell ref="A1:A4"/>
-    <mergeCell ref="D1:D4"/>
-    <mergeCell ref="B1:B4"/>
-    <mergeCell ref="L1:L2"/>
-    <mergeCell ref="E1:E4"/>
-    <mergeCell ref="T1:U1"/>
-    <mergeCell ref="N2:O2"/>
-    <mergeCell ref="P2:Q2"/>
-    <mergeCell ref="M1:O1"/>
-    <mergeCell ref="P1:Q1"/>
     <mergeCell ref="P4:Q4"/>
     <mergeCell ref="P3:Q3"/>
     <mergeCell ref="N3:O3"/>
@@ -6764,6 +6754,16 @@
     <mergeCell ref="F1:K4"/>
     <mergeCell ref="L3:L4"/>
     <mergeCell ref="N4:O4"/>
+    <mergeCell ref="T1:U1"/>
+    <mergeCell ref="N2:O2"/>
+    <mergeCell ref="P2:Q2"/>
+    <mergeCell ref="M1:O1"/>
+    <mergeCell ref="P1:Q1"/>
+    <mergeCell ref="A1:A4"/>
+    <mergeCell ref="D1:D4"/>
+    <mergeCell ref="B1:B4"/>
+    <mergeCell ref="L1:L2"/>
+    <mergeCell ref="E1:E4"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="E5:E10">
